--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -7030,7 +7030,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>see git log</t>
+          <t>1f82df6</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>4631de5074b3382f305f2fecda53775b70bb615f before the hard-rules commit (working tree has uncommitted DECISION_LOG.md edits and untracked DATA_LOCALITY_DECISION.md from another session; left untouched, see A14)</t>
+          <t>e9d3b46 before the Phase 0 runbook commits (working tree still has uncommitted DECISION_LOG.md edits and untracked DATA_LOCALITY_DECISION.md from another session; left untouched, see A14)</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ECS skin-scan-cluster/skin-scan-service, task definition skin-scan:1 (only revision), image skin-scan:sha-7f3695ef2bfbda37273411766531848774bd098e, digest sha256:668b1f56c440..., 2/2 tasks, /health ok cv2 4.11.0 (verified 2026-10-03).</t>
+          <t>ECS skin-scan-cluster/skin-scan-service, task definition skin-scan:1 (only revision), image skin-scan:sha-7f3695ef2bfbda37273411766531848774bd098e, running digest sha256:668b1f56c4405b4aacad3b77076ac12c7d8e59a09bacc95693952a2e09455005 (OCI index), 2/2 tasks HEALTHY, /health/ready scan-0.1.5-provisional cv2 4.11.0 (verified 2026-10-03).</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>4631de5 working tree, 2026-10-03: vitest 216 passed / 0 failed / 24 skipped (the 24 are the rules file); npm run test:rules 24/24 against the emulator. typecheck, lint and next build NOT re-run.</t>
+          <t>e9d3b46, 2026-10-03: typecheck pass (tsc 0 errors), lint pass (no ESLint warnings or errors), next build pass (compiled successfully), vitest 216 passed / 0 failed / 24 skipped (the 24 are the rules file), npm run test:rules 24/24 against the emulator.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>30% = DONE 13 / (total 51 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>29% = DONE 14 / (total 55 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 13, IN PROGRESS 0, NOT STARTED 4, BLOCKED 20, OWNER ACTION 7, LATER 7 (total 51)</t>
+          <t>DONE 14, IN PROGRESS 0, NOT STARTED 5, BLOCKED 20, OWNER ACTION 9, LATER 7 (total 55)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 0, CHECKED LOCAL 8, NOT NEEDED 5, NOT CHECKED 38</t>
+          <t>CHECKED PROD 0, CHECKED LOCAL 8, NOT NEEDED 6, NOT CHECKED 41</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,6 +889,23 @@
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>ls / grep of variable names, 2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Live replay vs plan §8</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ENGINE_0_1_6_DEPLOYMENT_PLAN §8 says Phase 0 evidence comes from the pinned digest run locally, never the live service. The owner asked for a live replay after job C (local run was emulated amd64). Runbook C5 keeps it to 30 matrix requests and labels it post-deploy verification, not protocol evidence.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>docs/PHASE_0_RUNBOOK.md C5</t>
         </is>
       </c>
     </row>
@@ -903,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1399,7 +1416,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Owner reviews FIRESTORE_RESET_RUNBOOK.md, authorizes, executes; record new location/settings here.</t>
+          <t>Owner reviews FIRESTORE_RESET_RUNBOOK.md, authorizes, executes; record new location/settings here. Runbook: docs/PHASE_0_RUNBOOK.md job A.</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1507,7 +1524,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>Merge ff08107 into the release path; ship in the same window as A04; verify with `vercel inspect`; consider setting project default region too.</t>
+          <t>Merge ff08107 into the release path; ship in the same window as A04; verify with `vercel inspect`; consider setting project default region too. Runbook: docs/PHASE_0_RUNBOOK.md job B.</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -2223,7 +2240,7 @@
       <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Owner go-ahead to resume: re-verify image identity + local smoke, push, confirm ECR digest == 9a8f96c0 (else replay on the ECR digest); then owner sign-off; register skin-scan:2 by digest; update service; verify health/version/engine_build; rollback = update-service skin-scan:1. record ECR manifest digest; register skin-scan:2 by digest; update service.</t>
+          <t>Owner go-ahead to resume: re-verify image identity + local smoke, push, confirm ECR digest == 9a8f96c0 (else replay on the ECR digest); then owner sign-off; register skin-scan:2 by digest; update service; verify health/version/engine_build; rollback = update-service skin-scan:1. record ECR manifest digest; register skin-scan:2 by digest; update service. Runbook: docs/PHASE_0_RUNBOOK.md job C.</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -2327,7 +2344,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>After A04: open PR longitudinal-platform -&gt; master, preview deploy, smoke test, promote.</t>
+          <t>After A04 and A05: follow docs/PHASE_0_RUNBOOK.md job D (A14 merge, push, PR, merge = production deploy; preview has no Firebase/S3 credentials so it cannot be used for a full smoke test).</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2442,44 +2459,44 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Added by tracker 2026-10-03.</t>
+          <t>Added by tracker 2026-10-03. A14 proposal step 4 duplicate-ID grep matches **D-03a as **D-03; use grep -oE '^\*\*D-[0-9]+[a-z]?' (runbook D0).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dev/prod separation</t>
+          <t>Phase 0 runbook</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
+          <t>Owner step-by-step runbook for jobs C (engine 0.1.6), A (Firestore asia-south1), B (Vercel bom1), D (website gates 01-04), with checks, undo and STOP lines.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2487,56 +2504,60 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>A12, A04, A05, A13</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>D-22 / ENGINE_0_1_6_DEPLOYMENT_PLAN</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
+          <t>docs/PHASE_0_RUNBOOK.md</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
+          <t>Committed runbook</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
+          <t>PHASE_0_RUNBOOK.md, verified against the repository by a read-only verifier agent</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>ff08107 (unmerged)</t>
+          <t>922a111</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
-        </is>
-      </c>
+          <t>Document task; no test needed (CLAUDE.md). Commands not executed.</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Owner: unset S3_SKIN_IMAGES_* locally today; approve dev-only emulator gate; rotate Admin key after removal.</t>
+          <t>Owner runs job C first.</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2544,42 +2565,46 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Job C includes a live 30-request replay that ENGINE_0_1_6_DEPLOYMENT_PLAN §8 advises against; labelled post-deploy verification, not protocol evidence.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Server-authoritative analysis writes</t>
+          <t>Back up unpushed branches</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Browser is not authoritative for analysis-derived scores.</t>
+          <t>longitudinal-platform exists on no remote; skin-scan remote has only prod-hardening 8df8418, so the live engine source 7f3695e and 0.1.6 source 8dc37dc are laptop-only.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2587,60 +2612,52 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>D-02 / D-26</t>
-        </is>
-      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan, lib/skin-state*</t>
+          <t>skin-check origin; skin-scan origin</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>git ls-remote shows the branches</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>6e9081d, 155cb69</t>
-        </is>
-      </c>
+          <t>git ls-remote --heads origin (2026-10-03): skin-check has master, firebase-phone-auth; skin-scan has prod-hardening only</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Pushing is the owner's action.</t>
+        </is>
+      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
+          <t>Owner: git -C ../skin-scan push origin engine-build-identity (runbook P1); push longitudinal-platform at runbook D1 or earlier (Preview env has no Firebase/S3 credentials).</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>TRUSTED MEASUREMENT</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2653,93 +2670,93 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Echo authentication and ownership</t>
+          <t>SkinState engine metadata for scan-0.1.6</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Echo derives identity/context server-side and verifies ownership.</t>
+          <t>lib/skin-state.ts ENGINE_TABLE lists only scan-0.1.5-provisional; after 0.1.6 is live, SkinState landmarkModel/opencvVersion are null (unknown) for new records.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Gate 02 / D-26</t>
+          <t>D-23</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-check/chat</t>
+          <t>lib/skin-state.ts</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + live E2E</t>
+          <t>Owner decision + commit + tests</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>skin-check-chat-auth tests (13); cross-user 409</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>155cb69, 955c1cc</t>
-        </is>
-      </c>
+          <t>lib/skin-state.ts:27</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr"/>
+          <t>Not started. Not breaking: null means unknown by design.</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Adding a version is a skinstate-1 mapping change; D-23 says mapping changes need a new version.</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; verify live in I01.</t>
+          <t>Owner decides: amend skinstate-1 ENGINE_TABLE for 0.1.6, or leave unknown until skinstate-2.</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2757,7 +2774,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2772,22 +2789,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Gemini browser-state isolation</t>
+          <t>Dev/prod separation</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Gemini never trusts browser-supplied scores/context.</t>
+          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2795,60 +2812,56 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Gate 02 / D-26</t>
-        </is>
-      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
+          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + live E2E</t>
+          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
+          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>ff08107 (unmerged)</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr"/>
+          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
+        </is>
+      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; verify live in I01.</t>
+          <t>Owner: unset S3_SKIN_IMAGES_* locally today; approve dev-only emulator gate; rotate Admin key after removal.</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2861,46 +2874,54 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Guided capture quality gate</t>
+          <t>Server-authoritative analysis writes</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
+          <t>Browser is not authoritative for analysis-derived scores.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>D-02 / D-26</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -2908,35 +2929,43 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check capture step</t>
+          <t>app/api/skin-scan, lib/skin-state*</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Design doc + approved gate + tests</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+          <t>Commit + tests</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6e9081d, 155cb69</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk).</t>
+          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2949,37 +2978,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Per-region / per-metric comparability</t>
+          <t>Echo authentication and ownership</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Decide whether two scans are comparable before computing change.</t>
+          <t>Echo derives identity/context server-side and verifies ownership.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2989,12 +3018,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>A07, A12, A13, C07</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>Gate 02 / D-26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3004,39 +3033,43 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-state*</t>
+          <t>app/api/skin-check/chat</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Comparability function + tests + noise inputs</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+          <t>Commit + tests + live E2E</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>skin-check-chat-auth tests (13); cross-user 409</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
-        </is>
-      </c>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07.</t>
+          <t>Deploy via A13; verify live in I01.</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -3049,27 +3082,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Human measurement validation protocol</t>
+          <t>Gemini browser-state isolation</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Protocol for human validation and repeatability.</t>
+          <t>Gemini never trusts browser-supplied scores/context.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3079,7 +3112,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3087,10 +3120,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>D-24 (uncommitted)</t>
+          <t>Gate 02 / D-26</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3100,43 +3137,43 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Committed protocol</t>
+          <t>Commit + tests + live E2E</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59d9923</t>
+          <t>155cb69, 955c1cc</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
+          <t>Deploy via A13; verify live in I01.</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3149,32 +3186,32 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Human validation pilot</t>
+          <t>Deny rules miss npx firebase form</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Run pilot of C03 protocol.</t>
+          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3184,14 +3221,10 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>C03, A12, A13, H01</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -3200,17 +3233,17 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Pre-registration + pilot dataset + report</t>
+          <t>Commit with added rules</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr"/>
@@ -3220,19 +3253,15 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
-        </is>
-      </c>
+      <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
+          <t>Add Bash(npx * firebase-tools* firestore:databases:delete *), Bash(npx * firebase-tools* firestore:delete *), Bash(npx * firebase-tools* deploy *).</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3240,12 +3269,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 while writing the Phase 0 runbook.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3260,17 +3293,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Full test-retest / calibration</t>
+          <t>Guided capture quality gate</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
+          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3280,14 +3313,10 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>C04</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -3296,13 +3325,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>components/skin-check capture step</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Pre-registered study report</t>
+          <t>Design doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
@@ -3312,14 +3345,10 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>Waits on C04 pilot.</t>
-        </is>
-      </c>
+      <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Size from pilot variance.</t>
+          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk).</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -3337,7 +3366,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -3352,12 +3381,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tone-stratified validation / model card</t>
+          <t>Per-region / per-metric comparability</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
+          <t>Decide whether two scans are comparable before computing change.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3377,10 +3406,14 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
+          <t>A07, A12, A13, C07</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3391,32 +3424,36 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>lib/skin-state*</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Per-band results + model card</t>
+          <t>Comparability function + tests + noise inputs</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05 data.</t>
+          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Define model card template alongside C05.</t>
+          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07.</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3429,7 +3466,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3444,22 +3481,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Validated measurement/noise tables</t>
+          <t>Human measurement validation protocol</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
+          <t>Protocol for human validation and repeatability.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3467,12 +3504,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>C05, C06</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>D-24 (uncommitted)</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3483,27 +3520,35 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Versioned noise table tied to engine build</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+          <t>Committed protocol</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>59d9923</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>Waits on C05/C06.</t>
-        </is>
-      </c>
+          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Fix table schema (field x region x band x engine build).</t>
+          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3516,36 +3561,32 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
-        </is>
-      </c>
+      <c r="V26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Baseline window definition</t>
+          <t>Human validation pilot</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>How a user's baseline is formed.</t>
+          <t>Run pilot of C03 protocol.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3560,12 +3601,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C03, A12, A13, H01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -3579,10 +3620,14 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Method doc + decision</t>
+          <t>Pre-registration + pilot dataset + report</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
@@ -3594,17 +3639,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Needs between-day noise (C07).</t>
+          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
+          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3617,27 +3662,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Change-vs-noise engine</t>
+          <t>Full test-retest / calibration</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
+          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3657,14 +3702,10 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>C02, C07, D01</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>D-13 / D-24</t>
-        </is>
-      </c>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3672,13 +3713,13 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Engine + tests + noise table version</t>
+          <t>Pre-registered study report</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
@@ -3690,17 +3731,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Needs comparability (C02) and validated noise (C07).</t>
+          <t>Waits on C04 pilot.</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Wait; design pairwise interface first (D-13).</t>
+          <t>Size from pilot variance.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3713,27 +3754,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Persistence/evidence tiers</t>
+          <t>Tone-stratified validation / model card</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Separate transient observations from persistent patterns.</t>
+          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3748,12 +3789,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -3770,7 +3811,7 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Tier definitions + tests</t>
+          <t>Per-band results + model card</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
@@ -3782,17 +3823,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Needs D02.</t>
+          <t>Waits on C05 data.</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Wait on D02.</t>
+          <t>Define model card template alongside C05.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3800,41 +3841,37 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
-        </is>
-      </c>
+      <c r="V29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Scheduled anchor scans / irregular sampling</t>
+          <t>Validated measurement/noise tables</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sampling strategy.</t>
+          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3844,12 +3881,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C05, C06</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -3858,21 +3895,37 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Versioned noise table tied to engine build</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Waits on C05/C06.</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Revisit after D02.</t>
+          <t>Fix table schema (field x region x band x engine build).</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3880,12 +3933,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3900,17 +3957,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Engine-version re-baselining</t>
+          <t>Baseline window definition</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Handle engine build changes across history.</t>
+          <t>How a user's baseline is formed.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3920,12 +3977,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -3934,16 +3991,32 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Method doc + decision</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Needs between-day noise (C07).</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Revisit at first engine change after D02.</t>
+          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -3961,32 +4034,32 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Product catalog normalization</t>
+          <t>Change-vs-noise engine</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
+          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3996,29 +4069,33 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>C02, C07, D01</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>D-08 / D-09</t>
+          <t>D-13 / D-24</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Owner-supplied master data + versioned schema</t>
+          <t>Engine + tests + noise table version</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
@@ -4030,17 +4107,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
+          <t>Needs comparability (C02) and validated noise (C07).</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>Owner supplies catalog data and decides OPEN-R1.</t>
+          <t>Wait; design pairwise interface first (D-13).</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4053,27 +4130,27 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Product eligibility / safety rules</t>
+          <t>Persistence/evidence tiers</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Deterministic, versioned eligibility + safety constraints.</t>
+          <t>Separate transient observations from persistent patterns.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4093,14 +4170,10 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>E01, E05</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>D-08</t>
-        </is>
-      </c>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4108,13 +4181,13 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Pure function + version constant + tests</t>
+          <t>Tier definitions + tests</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -4126,17 +4199,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+          <t>Needs D02.</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Wait on E01.</t>
+          <t>Wait on D02.</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4144,37 +4217,41 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Routine model + event history</t>
+          <t>Scheduled anchor scans / irregular sampling</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
+          <t>Sampling strategy.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4184,12 +4261,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -4198,33 +4275,21 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Backend/Data Engineer</t>
-        </is>
-      </c>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Data model doc + approved gate + tests</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Design data model on branch; no production writes before A04.</t>
+          <t>Revisit after D02.</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,41 +4297,37 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>A04 dependency applies to deployment only.</t>
-        </is>
-      </c>
+      <c r="V34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Adherence summary</t>
+          <t>Engine-version re-baselining</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
+          <t>Handle engine build changes across history.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4276,12 +4337,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4290,37 +4351,21 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
+      <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Function + tests</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>Needs E03.</t>
-        </is>
-      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Wait on E03.</t>
+          <t>Revisit at first engine change after D02.</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4333,7 +4378,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4348,12 +4393,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Red-flag triage interlock</t>
+          <t>Product catalog normalization</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Safety layer overrides cosmetic recommendations.</t>
+          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4368,13 +4413,13 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08 / D-09</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -4390,7 +4435,7 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+          <t>Owner-supplied master data + versioned schema</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -4402,17 +4447,17 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
+          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
+          <t>Owner supplies catalog data and decides OPEN-R1.</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4425,27 +4470,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Product eligibility / safety rules</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>Deterministic, versioned eligibility + safety constraints.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4465,12 +4510,12 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>A08, D02, E03, E04, E05</t>
+          <t>E01, E05</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -4480,20 +4525,16 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Pure builder + tests</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
-        </is>
-      </c>
+          <t>Pure function + version constant + tests</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
@@ -4502,17 +4543,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
+          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Wait; may define schema with null sections earlier if approved.</t>
+          <t>Wait on E01.</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4525,32 +4566,32 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Routine model + event history</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4560,19 +4601,15 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4580,43 +4617,31 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>lib/gemini.ts</t>
-        </is>
-      </c>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
-        </is>
-      </c>
+          <t>Data model doc + approved gate + tests</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>Schema renderer not built.</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>Needs F01.</t>
-        </is>
-      </c>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Wait on F01.</t>
+          <t>Design data model on branch; no production writes before A04.</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4626,34 +4651,34 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Seed status PARTIALLY READY.</t>
+          <t>A04 dependency applies to deployment only.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Adherence summary</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4668,19 +4693,15 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>D-14 / D-12</t>
-        </is>
-      </c>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4688,13 +4709,13 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
+          <t>Function + tests</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
@@ -4706,17 +4727,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Needs F02 output schema.</t>
+          <t>Needs E03.</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Wait on F02.</t>
+          <t>Wait on E03.</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4729,32 +4750,32 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Red-flag triage interlock</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>Safety layer overrides cosmetic recommendations.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4764,51 +4785,51 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>D-14 (store rejected for now)</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
-        </is>
-      </c>
+          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
+          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4821,27 +4842,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -4861,10 +4882,14 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
+          <t>A08, D02, E03, E04, E05</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4872,16 +4897,20 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr"/>
+          <t>Pure builder + tests</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
@@ -4890,17 +4919,17 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
+          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>Wait; may define schema with null sections earlier if approved.</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4913,27 +4942,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -4948,17 +4977,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>E03, G01</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>D-12 (LOCKED)</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -4968,35 +4997,43 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>Gemini/Context Engineer</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr"/>
+          <t>Schema + renderer + tests</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Schema renderer not built.</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Needs E03 and G01.</t>
+          <t>Needs F01.</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Wait on F01.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5004,32 +5041,36 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Seed status PARTIALLY READY.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5044,17 +5085,17 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-17</t>
+          <t>D-14 / D-12</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -5064,20 +5105,16 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
-        </is>
-      </c>
+          <t>Validator + adversarial tests</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
@@ -5086,17 +5123,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
+          <t>Needs F02 output schema.</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention.</t>
+          <t>Wait on F02.</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5109,27 +5146,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5144,13 +5181,13 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-14 (store rejected for now)</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -5160,31 +5197,35 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
+        </is>
+      </c>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Not started; 18+ check is client-only today.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr"/>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Write gate brief for D-19.</t>
+          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5197,32 +5238,32 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5232,29 +5273,29 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>PREFLIGHT G1 / D-14</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
+          <t>Approved design + tests + E2E</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
@@ -5266,17 +5307,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers).</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5289,27 +5330,27 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5324,15 +5365,19 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr"/>
+          <t>E03, G01</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>D-12 (LOCKED)</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5340,13 +5385,13 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Design reviewed against D-12</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr"/>
@@ -5358,17 +5403,17 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Nothing longitudinal is deployed yet.</t>
+          <t>Needs E03 and G01.</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5381,27 +5426,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5421,10 +5466,14 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr"/>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / D-17</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5432,16 +5481,20 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr"/>
+          <t>Ledger + erasure route + tests + live verification</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
+        </is>
+      </c>
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
@@ -5450,17 +5503,17 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention.</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5473,32 +5526,32 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5508,31 +5561,47 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>D-19</t>
+        </is>
+      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Gate + tests</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>Not started; 18+ check is client-only today.</t>
+        </is>
+      </c>
       <c r="R48" s="2" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Write gate brief for D-19.</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5545,32 +5614,32 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5580,31 +5649,51 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>PREFLIGHT G1 / D-14</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Field inventory + key ownership/tier + consent copy</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers).</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5617,32 +5706,32 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5652,26 +5741,46 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>A12, A13, B01, H01, H03</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>QA/Test Engineer</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Recorded E2E run against prod</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
-      <c r="Q50" s="2" t="inlineStr"/>
-      <c r="R50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Nothing longitudinal is deployed yet.</t>
+        </is>
+      </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -5689,32 +5798,32 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5724,31 +5833,51 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -5756,16 +5885,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -5780,7 +5905,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -5833,6 +5958,298 @@
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>ML recommendation ranking</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>J03</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Indian cross-user benchmark</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6795,7 +7212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7047,22 +7464,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>lead-session-2026-10-03 workers</t>
+          <t>phase0-runbook-session-2026-10-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>QA/Test, Measurement, Security</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>I01 draft, C01 brief (stopped: scope narrowed to Phase 0); A12 QA + security re-verification (stopped by owner)</t>
+          <t>Phase 0 runbook (A15), done-rule split, typecheck/lint/build, owner-action list</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>I01, C01, A12</t>
+          <t>A12, A04, A05, A13</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7077,7 +7494,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>STOPPED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -7087,17 +7504,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>none (no files left)</t>
+          <t>CLAUDE.md, .gitignore, docs/PHASE_0_RUNBOOK.md, docs/PROJECT_SKIN_EXECUTION_TRACKER.{md,xlsx}</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>typecheck, lint, next build (all pass at e9d3b46); comparison script dry-run 30/30 on local data</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>none recorded</t>
+          <t>Verifier (general-purpose agent with verifier.md instructions, read-only): FAIL with 4 blocking + 9 minor; all fixed</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7107,17 +7524,17 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (no decision changed)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>922a111</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Verifier findings fixed</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -7129,37 +7546,37 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>india-region session</t>
+          <t>lead-session-2026-10-03 workers</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>QA/Test, Measurement, Security</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Prepare India-region Firestore + Vercel</t>
+          <t>I01 draft, C01 brief (stopped: scope narrowed to Phase 0); A12 QA + security re-verification (stopped by owner)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>A04, A05</t>
+          <t>I01, C01, A12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>.claude/worktrees/india-region</t>
+          <t>main (skin-check)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>infra/india-region</t>
+          <t>longitudinal-platform</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>STOPPED</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -7169,122 +7586,204 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>vercel.json, DATA_LOCALITY_DECISION.md, DECISION_LOG.md, DEV_PROD_BOUNDARY.md, FIRESTORE_RESET_RUNBOOK.md</t>
+          <t>none (no files left)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>none recorded</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D-22 approved</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>ff08107</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Not merged</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Worktree still exists (clean)</t>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>india-region session</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Prepare India-region Firestore + Vercel</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>A04, A05</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>.claude/worktrees/india-region</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>infra/india-region</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>vercel.json, DATA_LOCALITY_DECISION.md, DECISION_LOG.md, DEV_PROD_BOUNDARY.md, FIRESTORE_RESET_RUNBOOK.md</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>D-22</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>D-22 approved</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>ff08107</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Not merged</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Worktree still exists (clean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>earlier sessions (gates 01-04, Phase 0)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>A01-A12, B02-B04</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>longitudinal-platform</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>see commits</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>see DECISION_LOG</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>61c149a..91d20bc</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>unknown - not reconstructable from repo</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ENGINE_0_1_6_DEPLOYMENT_PLAN.md; local release image built and replayed (91d20bc)</t>
+          <t>ENGINE_0_1_6_DEPLOYMENT_PLAN.md; local release image built and replayed (91d20bc); image re-verification 2026-10-03 PASS (read-only verifier: index has one linux/amd64 manifest + one attestation; /app identical to git archive 8dc37dc for all 30 copied files, 62 files excluded by .dockerignore, none extra; local /health/ready scan-0.1.6-provisional, cv2 4.11.0; ENGINE_BUILD sha-8dc37dc...)</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Owner go-ahead to resume: re-verify image identity + local smoke, push, confirm ECR digest == 9a8f96c0 (else replay on the ECR digest); then owner sign-off; register skin-scan:2 by digest; update service; verify health/version/engine_build; rollback = update-service skin-scan:1. record ECR manifest digest; register skin-scan:2 by digest; update service. Runbook: docs/PHASE_0_RUNBOOK.md job C.</t>
+          <t>Image re-verification done (PASS 2026-10-03). Owner: push, confirm ECR digest == 9a8f96c0 (else replay on the ECR digest); then owner sign-off; runbook job C (C2 now checks one container, C2b records the baseline).</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>922a111</t>
+          <t>922a111, 3e06858</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Job C includes a live 30-request replay that ENGINE_0_1_6_DEPLOYMENT_PLAN §8 advises against; labelled post-deploy verification, not protocol evidence.</t>
+          <t>Job C includes a live 30-request replay that ENGINE_0_1_6_DEPLOYMENT_PLAN §8 advises against; labelled post-deploy verification, not protocol evidence. Revised 2026-10-03 (3e06858): C2 one-container check, new C2b baseline step (ALB 5xx + /scan p95, 24 h), A0 flag check (firebase-tools 15.32.1 has all A2 flags), D0 note (checks need no production keys).</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2740,25 +2740,21 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-state.ts:27</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
+          <t>ENGINE_TABLE row scan-0.1.6-provisional (landmarkModel mediapipe-0.10.21-face_mesh, opencvVersion 4.11.0) from skin-scan 8dc37dc requirements.txt, face_mesh.py, main.py EXPECTED_CV2_VERSION; test 'skinstate-1: engine 0.1.6 (A17)'; vitest 217 passed / 24 skipped (emulator rules file), typecheck and lint pass</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>7af7df0</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Not started. Not breaking: null means unknown by design.</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>Adding a version is a skinstate-1 mapping change; D-23 says mapping changes need a new version.</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>Owner decides: amend skinstate-1 ENGINE_TABLE for 0.1.6, or leave unknown until skinstate-2.</t>
-        </is>
-      </c>
+          <t>Done. cv2 4.11.0 also confirmed at runtime by the local image's /health/ready.</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
           <t>TRUSTED MEASUREMENT</t>
@@ -2769,7 +2765,11 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision 2026-10-03: adding a version row is allowed and does not change skinstate-1 (note under D-23).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3246,19 +3246,23 @@
           <t>Commit with added rules</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands: 13 forms denied (npx -y firebase-tools@latest databases:delete, npx firebase-tools deploy, F deploy, npx firebase firestore:delete, bare and -chdir terraform apply, aws with --region or env before ecs, gcloud --project ... delete, vc --target=production, npx vercel --prod, bare vc promote), 2 controls allowed (terraform plan, a firebase-tools string).</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>ae457a0</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>Add Bash(npx * firebase-tools* firestore:databases:delete *), Bash(npx * firebase-tools* firestore:delete *), Bash(npx * firebase-tools* deploy *).</t>
-        </is>
-      </c>
+      <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
           <t>PRIVACY/SAFETY</t>
@@ -3271,34 +3275,34 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 while writing the Phase 0 runbook.</t>
+          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Guided capture quality gate</t>
+          <t>Deny rules miss other production-changing commands</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
+          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*. Only the CLAUDE.md hard rules stop agents.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3316,7 +3320,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -3325,17 +3333,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check capture step</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Design doc + approved gate + tests</t>
+          <t>Commit with added rules + echo probe</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
@@ -3348,12 +3356,12 @@
       <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk).</t>
+          <t>Owner decides which to deny (git push and gh pr merge are also normal development actions).</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3361,12 +3369,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 during B05.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -3381,17 +3393,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Per-region / per-metric comparability</t>
+          <t>Guided capture quality gate</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Decide whether two scans are comparable before computing change.</t>
+          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3401,19 +3413,11 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>A07, A12, A13, C07</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3421,39 +3425,35 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-state*</t>
+          <t>components/skin-check capture step</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Comparability function + tests + noise inputs</t>
+          <t>Design doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
-        </is>
-      </c>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07.</t>
+          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk).</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3481,22 +3481,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Human measurement validation protocol</t>
+          <t>Per-region / per-metric comparability</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Protocol for human validation and repeatability.</t>
+          <t>Decide whether two scans are comparable before computing change.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3504,10 +3504,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>A07, A12, A13, C07</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>D-24 (uncommitted)</t>
+          <t>D-13</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3522,38 +3526,34 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>lib/skin-state*</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Committed protocol</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>59d9923</t>
-        </is>
-      </c>
+          <t>Comparability function + tests + noise inputs</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr"/>
+          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
+          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07.</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -3581,22 +3581,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Human validation pilot</t>
+          <t>Human measurement validation protocol</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Run pilot of C03 protocol.</t>
+          <t>Protocol for human validation and repeatability.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>C03, A12, A13, H01</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>D-24 (uncommitted)</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3627,24 +3627,28 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Pre-registration + pilot dataset + report</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
+          <t>Committed protocol</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>59d9923</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
-        </is>
-      </c>
+          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
+          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
@@ -3662,7 +3666,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3677,12 +3681,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Full test-retest / calibration</t>
+          <t>Human validation pilot</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
+          <t>Run pilot of C03 protocol.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3702,7 +3706,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03, A12, A13, H01</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -3716,10 +3720,14 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Pre-registered study report</t>
+          <t>Pre-registration + pilot dataset + report</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
@@ -3731,12 +3739,12 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Waits on C04 pilot.</t>
+          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Size from pilot variance.</t>
+          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3754,7 +3762,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -3769,12 +3777,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Tone-stratified validation / model card</t>
+          <t>Full test-retest / calibration</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
+          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3794,7 +3802,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -3811,7 +3819,7 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Per-band results + model card</t>
+          <t>Pre-registered study report</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
@@ -3823,12 +3831,12 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05 data.</t>
+          <t>Waits on C04 pilot.</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Define model card template alongside C05.</t>
+          <t>Size from pilot variance.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3846,7 +3854,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3861,12 +3869,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Validated measurement/noise tables</t>
+          <t>Tone-stratified validation / model card</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
+          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3886,7 +3894,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>C05, C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -3903,7 +3911,7 @@
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Versioned noise table tied to engine build</t>
+          <t>Per-band results + model card</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
@@ -3915,12 +3923,12 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05/C06.</t>
+          <t>Waits on C05 data.</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Fix table schema (field x region x band x engine build).</t>
+          <t>Define model card template alongside C05.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -3933,36 +3941,32 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
-        </is>
-      </c>
+      <c r="V30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Baseline window definition</t>
+          <t>Validated measurement/noise tables</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>How a user's baseline is formed.</t>
+          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3977,12 +3981,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C05, C06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -3999,7 +4003,7 @@
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Method doc + decision</t>
+          <t>Versioned noise table tied to engine build</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr"/>
@@ -4011,17 +4015,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>Needs between-day noise (C07).</t>
+          <t>Waits on C05/C06.</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
+          <t>Fix table schema (field x region x band x engine build).</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4029,12 +4033,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4049,12 +4057,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Change-vs-noise engine</t>
+          <t>Baseline window definition</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
+          <t>How a user's baseline is formed.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4069,19 +4077,15 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>C02, C07, D01</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>D-13 / D-24</t>
-        </is>
-      </c>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4089,13 +4093,13 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Engine + tests + noise table version</t>
+          <t>Method doc + decision</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
@@ -4107,12 +4111,12 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Needs comparability (C02) and validated noise (C07).</t>
+          <t>Needs between-day noise (C07).</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>Wait; design pairwise interface first (D-13).</t>
+          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4130,7 +4134,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -4145,12 +4149,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Persistence/evidence tiers</t>
+          <t>Change-vs-noise engine</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Separate transient observations from persistent patterns.</t>
+          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4165,15 +4169,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
+          <t>C02, C07, D01</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>D-13 / D-24</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4181,13 +4189,13 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Tier definitions + tests</t>
+          <t>Engine + tests + noise table version</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -4199,12 +4207,12 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Needs D02.</t>
+          <t>Needs comparability (C02) and validated noise (C07).</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Wait on D02.</t>
+          <t>Wait; design pairwise interface first (D-13).</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
@@ -4217,16 +4225,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
-        </is>
-      </c>
+      <c r="V33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4241,17 +4245,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Scheduled anchor scans / irregular sampling</t>
+          <t>Persistence/evidence tiers</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Sampling strategy.</t>
+          <t>Separate transient observations from persistent patterns.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4261,7 +4265,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4275,16 +4279,32 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Tier definitions + tests</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Needs D02.</t>
+        </is>
+      </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Revisit after D02.</t>
+          <t>Wait on D02.</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -4297,12 +4317,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -4317,12 +4341,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Engine-version re-baselining</t>
+          <t>Scheduled anchor scans / irregular sampling</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Handle engine build changes across history.</t>
+          <t>Sampling strategy.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4360,7 +4384,7 @@
       <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Revisit at first engine change after D02.</t>
+          <t>Revisit after D02.</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4378,32 +4402,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Product catalog normalization</t>
+          <t>Engine-version re-baselining</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
+          <t>Handle engine build changes across history.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4413,51 +4437,35 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>D-08 / D-09</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>Owner-supplied master data + versioned schema</t>
-        </is>
-      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
-        </is>
-      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Owner supplies catalog data and decides OPEN-R1.</t>
+          <t>Revisit at first engine change after D02.</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4470,7 +4478,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -4485,17 +4493,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Product eligibility / safety rules</t>
+          <t>Product catalog normalization</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Deterministic, versioned eligibility + safety constraints.</t>
+          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,19 +4516,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>E01, E05</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-08 / D-09</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4531,7 +4535,7 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Pure function + version constant + tests</t>
+          <t>Owner-supplied master data + versioned schema</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
@@ -4543,12 +4547,12 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Wait on E01.</t>
+          <t>Owner supplies catalog data and decides OPEN-R1.</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4566,7 +4570,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4581,17 +4585,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Routine model + event history</t>
+          <t>Product eligibility / safety rules</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
+          <t>Deterministic, versioned eligibility + safety constraints.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4601,15 +4605,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
+          <t>E01, E05</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4617,13 +4625,13 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Data model doc + approved gate + tests</t>
+          <t>Pure function + version constant + tests</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
@@ -4633,10 +4641,14 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Design data model on branch; no production writes before A04.</t>
+          <t>Wait on E01.</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4649,16 +4661,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>A04 dependency applies to deployment only.</t>
-        </is>
-      </c>
+      <c r="V38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -4673,17 +4681,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Adherence summary</t>
+          <t>Routine model + event history</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
+          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4698,7 +4706,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -4709,13 +4717,13 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Function + tests</t>
+          <t>Data model doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
@@ -4725,14 +4733,10 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>Needs E03.</t>
-        </is>
-      </c>
+      <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Wait on E03.</t>
+          <t>Design data model on branch; no production writes before A04.</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -4745,12 +4749,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>A04 dependency applies to deployment only.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4765,17 +4773,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Red-flag triage interlock</t>
+          <t>Adherence summary</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Safety layer overrides cosmetic recommendations.</t>
+          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4785,18 +4793,18 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4807,7 +4815,7 @@
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+          <t>Function + tests</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
@@ -4819,17 +4827,17 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
+          <t>Needs E03.</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
+          <t>Wait on E03.</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4842,32 +4850,32 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Red-flag triage interlock</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>Safety layer overrides cosmetic recommendations.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4877,14 +4885,10 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>A08, D02, E03, E04, E05</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
           <t>D-14</t>
@@ -4892,25 +4896,21 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Pure builder + tests</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
-        </is>
-      </c>
+          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
@@ -4919,17 +4919,17 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
+          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Wait; may define schema with null sections earlier if approved.</t>
+          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>A08, D02, E03, E04, E05</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5000,35 +5000,31 @@
           <t>Gemini/Context Engineer</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>lib/gemini.ts</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
+          <t>Pure builder + tests</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Schema renderer not built.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Needs F01.</t>
+          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Wait on F01.</t>
+          <t>Wait; may define schema with null sections earlier if approved.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -5041,16 +5037,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Seed status PARTIALLY READY.</t>
-        </is>
-      </c>
+      <c r="V42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -5065,12 +5057,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5090,12 +5082,12 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>D-14 / D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -5108,27 +5100,35 @@
           <t>Gemini/Context Engineer</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr"/>
+          <t>Schema + renderer + tests</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+        </is>
+      </c>
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Schema renderer not built.</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Needs F02 output schema.</t>
+          <t>Needs F01.</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Wait on F02.</t>
+          <t>Wait on F01.</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -5141,12 +5141,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Seed status PARTIALLY READY.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -5161,17 +5165,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5181,13 +5185,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>D-14 (store rejected for now)</t>
+          <t>D-14 / D-12</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -5203,24 +5211,24 @@
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
-        </is>
-      </c>
+          <t>Validator + adversarial tests</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Needs F02 output schema.</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
+          <t>Wait on F02.</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -5238,32 +5246,32 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5273,15 +5281,15 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>D-14 (store rejected for now)</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5289,35 +5297,35 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
-        </is>
-      </c>
+      <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5330,7 +5338,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -5345,12 +5353,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5365,19 +5373,15 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>E03, G01</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>D-12 (LOCKED)</t>
-        </is>
-      </c>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5391,7 +5395,7 @@
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
+          <t>Approved design + tests + E2E</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr"/>
@@ -5403,12 +5407,12 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Needs E03 and G01.</t>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -5426,27 +5430,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5461,17 +5465,17 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>E03, G01</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-17</t>
+          <t>D-12 (LOCKED)</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -5481,20 +5485,16 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
-        </is>
-      </c>
+          <t>Design reviewed against D-12</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
@@ -5503,17 +5503,17 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
+          <t>Needs E03 and G01.</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -5541,17 +5541,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5561,13 +5561,17 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-16 / D-17</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -5577,26 +5581,34 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr"/>
+          <t>Ledger + erasure route + tests + live verification</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Not started; 18+ check is client-only today.</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
+        </is>
+      </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Write gate brief for D-19.</t>
+          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention.</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
@@ -5614,7 +5626,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -5629,17 +5641,17 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5649,46 +5661,42 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14</t>
+          <t>D-19</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
+          <t>Gate + tests</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
-        </is>
-      </c>
+          <t>Not started; 18+ check is client-only today.</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers).</t>
+          <t>Write gate brief for D-19.</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
@@ -5706,32 +5714,32 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5744,26 +5752,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>PREFLIGHT G1 / D-14</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Field inventory + key ownership/tier + consent copy</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr"/>
@@ -5775,17 +5783,17 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Nothing longitudinal is deployed yet.</t>
+          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers).</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5798,7 +5806,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -5813,12 +5821,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -5838,7 +5846,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
+          <t>A12, A13, B01, H01, H03</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -5849,13 +5857,13 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Recorded E2E run against prod</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr"/>
@@ -5867,17 +5875,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>Nothing longitudinal is deployed yet.</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>RELEASE</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -5890,32 +5898,32 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -5925,31 +5933,51 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -5962,7 +5990,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -5977,7 +6005,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6034,7 +6062,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6049,7 +6077,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>ML recommendation ranking</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6106,7 +6134,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6121,7 +6149,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Indian cross-user benchmark</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6173,16 +6201,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6197,7 +6221,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Forecasting</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6249,7 +6273,83 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7212,7 +7312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7546,22 +7646,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>lead-session-2026-10-03 workers</t>
+          <t>b05-a12-a17-session-2026-10-03</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>QA/Test, Measurement, Security</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>I01 draft, C01 brief (stopped: scope narrowed to Phase 0); A12 QA + security re-verification (stopped by owner)</t>
+          <t>B05 deny rules, A12 image re-verification, four runbook fixes, A17 ENGINE_TABLE row</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>I01, C01, A12</t>
+          <t>B05, A12, A15, A17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7576,7 +7676,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>STOPPED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -7586,17 +7686,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>none (no files left)</t>
+          <t>.claude/settings.json, lib/skin-state.ts, tests/skin-state.test.ts, docs/PHASE_0_RUNBOOK.md, docs/PROJECT_SKIN_EXECUTION_TRACKER.{md,xlsx}</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>vitest (217 pass, 24 skipped), typecheck, lint, next build with no env files (clean worktree), deny-rule echo probes</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>none recorded</t>
+          <t>Verifier (general-purpose agent with verifier.md, read-only + local docker): A12 PASS. New row B06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7606,17 +7706,17 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>D-23 note (owner decision, A17)</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ae457a0, 7af7df0, 3e06858</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Verifier PASS (A12)</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7628,37 +7728,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>india-region session</t>
+          <t>lead-session-2026-10-03 workers</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>QA/Test, Measurement, Security</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Prepare India-region Firestore + Vercel</t>
+          <t>I01 draft, C01 brief (stopped: scope narrowed to Phase 0); A12 QA + security re-verification (stopped by owner)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>A04, A05</t>
+          <t>I01, C01, A12</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>.claude/worktrees/india-region</t>
+          <t>main (skin-check)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>infra/india-region</t>
+          <t>longitudinal-platform</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>STOPPED</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -7668,122 +7768,204 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>vercel.json, DATA_LOCALITY_DECISION.md, DECISION_LOG.md, DEV_PROD_BOUNDARY.md, FIRESTORE_RESET_RUNBOOK.md</t>
+          <t>none (no files left)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>none recorded</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>D-22 approved</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>ff08107</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Not merged</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Worktree still exists (clean)</t>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>india-region session</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Prepare India-region Firestore + Vercel</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>A04, A05</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>.claude/worktrees/india-region</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>infra/india-region</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>vercel.json, DATA_LOCALITY_DECISION.md, DECISION_LOG.md, DEV_PROD_BOUNDARY.md, FIRESTORE_RESET_RUNBOOK.md</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>D-22</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>D-22 approved</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>ff08107</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Not merged</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Worktree still exists (clean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>earlier sessions (gates 01-04, Phase 0)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>A01-A12, B02-B04</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>longitudinal-platform</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>see commits</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>see DECISION_LOG</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>61c149a..91d20bc</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>unknown - not reconstructable from repo</t>
         </is>
@@ -7970,7 +8152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8286,69 +8468,69 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TD-01</t>
+          <t>D-23 (note: A17)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Malformed raw analysis is rejected</t>
+          <t>New engine-version rows in ENGINE_TABLE are allowed</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Raw records may be incomplete</t>
+          <t>0.1.6 changed no formula, mask or dependency (version.py at 8dc37dc)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Best-effort mapping</t>
+          <t>Leave 0.1.6 unknown until skinstate-2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>toSkinState returns invalid (11 malformed cases tested)</t>
+          <t>Owner decision: adding a pipelineVersion row to ENGINE_TABLE does not change the skinstate-1 contract; existing rows stay frozen</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>No fabricated values</t>
+          <t>A new row adds verified facts for a new engine; no existing mapping changes</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTATION_GATE_03.md (dd9a3fe)</t>
+          <t>7af7df0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Changing or removing an existing row still needs a new contract version</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>DONE (not in DECISION_LOG)</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TD-02</t>
+          <t>TD-01</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -8358,47 +8540,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Uncertainty unknown until calibrated</t>
+          <t>Malformed raw analysis is rejected</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>No calibration exists</t>
+          <t>Raw records may be incomplete</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Heuristic intervals</t>
+          <t>Best-effort mapping</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>uncertainty.policy = unknown always</t>
+          <t>toSkinState returns invalid (11 malformed cases tested)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>No unvalidated precision</t>
+          <t>No fabricated values</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>GATE_03 (dd9a3fe)</t>
+          <t>IMPLEMENTATION_GATE_03.md (dd9a3fe)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>A08, C07, D02</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>C07 delivers calibration</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -8410,7 +8592,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TD-03</t>
+          <t>TD-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -8420,47 +8602,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Empty regions = region absent</t>
+          <t>Uncertainty unknown until calibrated</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Engine writes 0.0 for empty masks</t>
+          <t>No calibration exists</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expose 0.0</t>
+          <t>Heuristic intervals</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>region_px 0 -&gt; absent_region, nulls</t>
+          <t>uncertainty.policy = unknown always</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0.0 indistinguishable from real zero</t>
+          <t>No unvalidated precision</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SKIN_STATE_CONTRACT_FINAL.md, GATE_03</t>
+          <t>GATE_03 (dd9a3fe)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A08, C07, D02</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>C07 delivers calibration</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -8472,131 +8654,131 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>TD-03</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Native L*/a* are provisional research candidates only</t>
+          <t>Empty regions = region absent</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 screening</t>
+          <t>Engine writes 0.0 for empty masks</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Keep b*, ITA, lbpEntropy</t>
+          <t>Expose 0.0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Primary endpoints for the human study only; not validated measurements</t>
+          <t>region_px 0 -&gt; absent_region, nulls</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Only survivors of screening</t>
+          <t>0.0 indistinguishable from real zero</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
+          <t>SKIN_STATE_CONTRACT_FINAL.md, GATE_03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>C03-C07</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Owner may reverse before Phase 1 pre-registration</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>ACCEPTED for study design</t>
+          <t>DONE (not in DECISION_LOG)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>D-13 / D-24</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal comparisons require comparability + noise/evidence</t>
+          <t>Native L*/a* are provisional research candidates only</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Naive % change misleads</t>
+          <t>Phase 0 screening</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Research-doc point ladder</t>
+          <t>Keep b*, ITA, lbpEntropy</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
+          <t>Primary endpoints for the human study only; not validated measurements</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Measurement noise unknown</t>
+          <t>Only survivors of screening</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-13; D-24 uncommitted</t>
+          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>C02, D02, G01</t>
+          <t>C03-C07</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Owner may reverse before Phase 1 pre-registration</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (D-24 uncommitted)</t>
+          <t>ACCEPTED for study design</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-13 / D-24</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -8606,59 +8788,59 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Recommender deterministic and versioned</t>
+          <t>Longitudinal comparisons require comparability + noise/evidence</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4 SKUs, ~6 rules</t>
+          <t>Naive % change misleads</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>DMN/rules engine; ML ranking</t>
+          <t>Research-doc point ladder</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Plain TS pure function + version constants</t>
+          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Auditable</t>
+          <t>Measurement noise unknown</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-08</t>
+          <t>DECISION_LOG D-13; D-24 uncommitted</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>E02, J02</t>
+          <t>C02, D02, G01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>&gt;20 SKUs or non-engineer rule authors</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>PROPOSED (D-24 uncommitted)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -8668,42 +8850,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Gemini is explanation layer, not authority</t>
+          <t>Recommender deterministic and versioned</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Gemini hallucination/claims risk</t>
+          <t>4 SKUs, ~6 rules</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Gemini owns context</t>
+          <t>DMN/rules engine; ML ranking</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+          <t>Plain TS pure function + version constants</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Auditable</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-14; GATE_02</t>
+          <t>DECISION_LOG D-08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>B04, F01-F04</t>
+          <t>E02, J02</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&gt;20 SKUs or non-engineer rule authors</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -8713,14 +8895,14 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (paid tier is release gate)</t>
+          <t>PROPOSED</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -8730,104 +8912,104 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>No attribution/efficacy/forecasting</t>
+          <t>Gemini is explanation layer, not authority</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Gemini hallucination/claims risk</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Gemini owns context</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Evidence tiers 3-4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Prohibited in UI, Gemini, analytics</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>CLAUDE.md</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-12</t>
+          <t>DECISION_LOG D-14; GATE_02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>G02, J04, R08</t>
+          <t>B04, F01-F04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Explicit owner approval</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>PROPOSED (paid tier is release gate)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Client input never authoritative for measured state</t>
+          <t>No attribution/efficacy/forecasting</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Gate 02</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Rules tightening; server chat storage</t>
+          <t>Evidence tiers 3-4</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Path-structural trust; authenticated Echo</t>
+          <t>Prohibited in UI, Gemini, analytics</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Forgeable browser state</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>DECISION_LOG D-12</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>A09, B02-B04, C02</t>
+          <t>G02, J04, R08</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Open: client-asserted captureMethod/persistAttempt</t>
+          <t>Explicit owner approval</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -8837,67 +9019,129 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED (branch); owner decision open</t>
+          <t>LOCKED</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>D-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Client input never authoritative for measured state</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Rules tightening; server chat storage</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Path-structural trust; authenticated Echo</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Forgeable browser state</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>A09, B02-B04, C02</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Open: client-asserted captureMethod/persistAttempt</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (branch); owner decision open</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>D-21</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Gate 01 stores raw analysis in scanAnalyses</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Raw preservation</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>skinStates collection</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>users/{uid}/scanAnalyses/{scanId}_{sha16}</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Immutable raw substrate</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6e9081d</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Systems Architect</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>IMPLEMENTED (not deployed); ID duplicated in HEAD</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -2567,7 +2567,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Job C includes a live 30-request replay that ENGINE_0_1_6_DEPLOYMENT_PLAN §8 advises against; labelled post-deploy verification, not protocol evidence. Revised 2026-10-03 (3e06858): C2 one-container check, new C2b baseline step (ALB 5xx + /scan p95, 24 h), A0 flag check (firebase-tools 15.32.1 has all A2 flags), D0 note (checks need no production keys).</t>
+          <t>Job C includes a live 30-request replay that ENGINE_0_1_6_DEPLOYMENT_PLAN §8 advises against; labelled post-deploy verification, not protocol evidence. Revised 2026-10-03 (3e06858): C2 one-container check, new C2b baseline step (ALB 5xx + /scan p95, 24 h), A0 flag check (firebase-tools 15.32.1 has all A2 flags), D0 note (test/typecheck/lint/build pass with no env files), C0 PASS note, Known gaps points to B06. C2's jq also refuses more than one container, so registration cannot run past it (tested on fake input).</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands: 13 forms denied (npx -y firebase-tools@latest databases:delete, npx firebase-tools deploy, F deploy, npx firebase firestore:delete, bare and -chdir terraform apply, aws with --region or env before ecs, gcloud --project ... delete, vc --target=production, npx vercel --prod, bare vc promote), 2 controls allowed (terraform plan, a firebase-tools string).</t>
+          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>ae457a0</t>
+          <t>ae457a0, 44e0352</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*. Only the CLAUDE.md hard rules stop agents.</t>
+          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>vitest (217 pass, 24 skipped), typecheck, lint, next build with no env files (clean worktree), deny-rule echo probes</t>
+          <t>vitest (217 pass, 24 skipped), typecheck, lint, test/typecheck/lint/build with no env files (clean worktree), 39 deny-rule echo probes</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>ae457a0, 7af7df0, 3e06858</t>
+          <t>ae457a0, 7af7df0, 3e06858, b0a7424, 44e0352</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Verifier PASS (A12)</t>
+          <t>Verifier PASS (A12); hashes re-checked by lead (30 shared, 0 differ)</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -3307,12 +3307,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3346,19 +3346,23 @@
           <t>Commit with added rules + echo probe</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2371f78</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>Owner decides which to deny (git push and gh pr merge are also normal development actions).</t>
-        </is>
-      </c>
+      <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
           <t>PRIVACY/SAFETY</t>
@@ -3371,7 +3375,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 during B05.</t>
+          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7728,22 +7732,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>lead-session-2026-10-03 workers</t>
+          <t>b06-session-2026-10-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>QA/Test, Measurement, Security</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>I01 draft, C01 brief (stopped: scope narrowed to Phase 0); A12 QA + security re-verification (stopped by owner)</t>
+          <t>B06 deny rules (owner decision)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>I01, C01, A12</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7758,7 +7762,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>STOPPED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -7768,17 +7772,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>none (no files left)</t>
+          <t>.claude/settings.json, docs/PHASE_0_RUNBOOK.md, docs/PROJECT_SKIN_EXECUTION_TRACKER.{md,xlsx}</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>44 echo probes (32 denied, 12 allowed)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>none recorded</t>
+          <t>Branch- and variable-dependent git push forms cannot be matched by deny patterns</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7793,12 +7797,12 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2371f78</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>n/a (config)</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7810,37 +7814,37 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>india-region session</t>
+          <t>lead-session-2026-10-03 workers</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>QA/Test, Measurement, Security</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Prepare India-region Firestore + Vercel</t>
+          <t>I01 draft, C01 brief (stopped: scope narrowed to Phase 0); A12 QA + security re-verification (stopped by owner)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>A04, A05</t>
+          <t>I01, C01, A12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>.claude/worktrees/india-region</t>
+          <t>main (skin-check)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>infra/india-region</t>
+          <t>longitudinal-platform</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>STOPPED</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7850,122 +7854,204 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>vercel.json, DATA_LOCALITY_DECISION.md, DECISION_LOG.md, DEV_PROD_BOUNDARY.md, FIRESTORE_RESET_RUNBOOK.md</t>
+          <t>none (no files left)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>none recorded</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>D-22 approved</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>ff08107</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Not merged</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Worktree still exists (clean)</t>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>india-region session</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Prepare India-region Firestore + Vercel</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>A04, A05</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>.claude/worktrees/india-region</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>infra/india-region</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>vercel.json, DATA_LOCALITY_DECISION.md, DECISION_LOG.md, DEV_PROD_BOUNDARY.md, FIRESTORE_RESET_RUNBOOK.md</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>D-22</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>D-22 approved</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>ff08107</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Not merged</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Worktree still exists (clean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>earlier sessions (gates 01-04, Phase 0)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>A01-A12, B02-B04</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>longitudinal-platform</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>see commits</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>see DECISION_LOG</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>61c149a..91d20bc</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>unknown - not reconstructable from repo</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>29% = DONE 14 / (total 55 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>36% = DONE 18 / (total 57 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 14, IN PROGRESS 0, NOT STARTED 5, BLOCKED 20, OWNER ACTION 9, LATER 7 (total 55)</t>
+          <t>DONE 18, IN PROGRESS 0, NOT STARTED 5, BLOCKED 20, OWNER ACTION 7, LATER 7 (total 57)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 0, CHECKED LOCAL 8, NOT NEEDED 6, NOT CHECKED 41</t>
+          <t>CHECKED PROD 0, CHECKED LOCAL 11, NOT NEEDED 7, NOT CHECKED 39</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>This is the LOCAL image ID (built 2026-10-03, tag sha-8dc37dc...). ECR has only the 7f3695e image. The ECR manifest digest is unknown until push and may differ from the local ID.</t>
+          <t>This is the LOCAL image ID (built 2026-10-03, tag sha-8dc37dc...). ECR has only the 7f3695e image. Resolved 2026-10-03: after push, ECR digest for the tag is sha256:9a8f96c0a54025c4137b89dee181ba7fb140db1431fa95156cc20d8880e1fc2c, equal to the local ID.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Destructive production action: requires explicit owner authorization and execution. Recommended after B01 items 1-3 so laptops do not write into the new database.</t>
+          <t>Destructive production action: requires explicit owner authorization and execution. Recommended after B01 items 1-3 so laptops do not write into the new database. Paused by TD-04 (owner, 2026-10-03): features are built on lane branches first; this deploy step runs at the end via docs/PHASE_0_RUNBOOK.md.</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Waits on A04 Firestore reset and A14 merge of ff08107.</t>
+          <t>Waits on A04 Firestore reset and A14 merge of ff08107. Paused by TD-04 (owner, 2026-10-03): features are built on lane branches first; this deploy step runs at the end via docs/PHASE_0_RUNBOOK.md.</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -2234,13 +2234,17 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Live 2026-10-03 (re-verified): service on skin-scan:1 (only revision), 2/2 RUNNING HEALTHY on digest 668b1f56..., /health/ready scan-0.1.5-provisional, runtimePlatform null (Fargate X86_64). ECR holds only the 0.1.5 index. Local release image sha256:9a8f96c0a54025c4137b89dee181ba7fb140db1431fa95156cc20d8880e1fc2c (linux/amd64, ENGINE_BUILD=sha-8dc37dc..., already tagged with the ECR tag) NOT pushed.</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr"/>
+          <t>Live 2026-10-03 (re-verified): service on skin-scan:1 (only revision), 2/2 RUNNING HEALTHY on digest 668b1f56..., /health/ready scan-0.1.5-provisional, runtimePlatform null (Fargate X86_64). 2026-10-03 runbook C0 PASS (local image sha256:9a8f96c0a54025c4137b89dee181ba7fb140db1431fa95156cc20d8880e1fc2c linux/amd64); C1 PASS: owner pushed tag sha-8dc37dc501ea974825427c665acd7019120c20ec, push digest and aws ecr describe-images both sha256:9a8f96c0a54025c4137b89dee181ba7fb140db1431fa95156cc20d8880e1fc2c (equal to the replayed image, so no replay on a new digest). Image stored only; service still on skin-scan:1. C2b baseline 2026-10-03 (24 h to 14:15Z, read-only, agent): RequestCount 1450, ELB 5xx 0, Target 5xx 0 (5xx rate 0, so any 5xx after C3 counts), scan_request 200 n 0 (p95 n/a; 7-day n 4, p95_ms 384). p95 rollback rule does not apply; C4 and a real website scan are the main proof. Pre-C3 config: skin-scan:1 has 1 container (skin-scan); circuit breaker enable true, rollback true (BOUNDED_PERCENT 50), min healthy 100%, max 200%, desired 2 running 2.</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Paused by TD-04 (owner, 2026-10-03): features are built on lane branches first; this deploy step runs at the end via docs/PHASE_0_RUNBOOK.md.</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Image re-verification done (PASS 2026-10-03). Owner: push, confirm ECR digest == 9a8f96c0 (else replay on the ECR digest); then owner sign-off; runbook job C (C2 now checks one container, C2b records the baseline).</t>
+          <t>Resume at runbook C2 when the owner ends the TD-04 pause. C0 and C1 PASS 2026-10-03: ECR tag sha-8dc37dc501ea974825427c665acd7019120c20ec = sha256:9a8f96c0a54025c4137b89dee181ba7fb140db1431fa95156cc20d8880e1fc2c; service still on skin-scan:1. Watch the untagged children (A18).</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -2339,7 +2343,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>A04 Firestore reset not executed; gate 02 cannot deploy without gate 01 (Echo 409s).</t>
+          <t>A04 Firestore reset not executed; gate 02 cannot deploy without gate 01 (Echo 409s). Paused by TD-04 (owner, 2026-10-03): features are built on lane branches first; this deploy step runs at the end via docs/PHASE_0_RUNBOOK.md.</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -2599,12 +2603,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2636,23 +2640,23 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>git ls-remote --heads origin (2026-10-03): skin-check has master, firebase-phone-auth; skin-scan has prod-hardening only</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
+          <t>git ls-remote --heads origin 2026-10-03 after push: skin-check longitudinal-platform 519f5aa; skin-scan engine-build-identity 8dc37dc</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>pushed refs: skin-check 519f5aa (now 3733e99 on origin); skin-scan 8dc37dc</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>Pushing is the owner's action.</t>
-        </is>
-      </c>
+          <t>Done 2026-10-03 (runbook P1 + longitudinal-platform push, owner-authorized). skin-scan 7f3695e (live 0.1.5 source, rollback source) is an ancestor of origin/engine-build-identity, so it is on GitHub (checked 2026-10-03).</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>Owner: git -C ../skin-scan push origin engine-build-identity (runbook P1); push longitudinal-platform at runbook D1 or earlier (Preview env has no Firebase/S3 credentials).</t>
+          <t>Later commits on longitudinal-platform need pushing again.</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2774,32 +2778,32 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Dev/prod separation</t>
+          <t>Watch 0.1.6 index children in ECR during the pause</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
+          <t>ECR lifecycle expires untagged images after 1 day. The 0.1.6 index's two untagged children (sha256:6bf0f2bc9d8c39b4fb4cd88324912b4d0be2ead8f9342578d0a9d2b4ff29cb45, sha256:74ad34fcaf5c21d8effe0b8943d90748a0e55f78b15f687107849674c1602950, pushed 2026-10-03 19:40 IST) survive only by observed behaviour; a long TD-04 pause makes that a longer bet.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2809,59 +2813,59 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>TD-04</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>CV/ML Engineer</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
+          <t>ECR skin-scan</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
+          <t>Dated read-only describe-images results</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>ff08107 (unmerged)</t>
-        </is>
-      </c>
+          <t>2026-10-03: both children present</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
-        </is>
-      </c>
+          <t>Not started. Read-only check, no policy change.</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Owner: unset S3_SKIN_IMAGES_* locally today; approve dev-only emulator gate; rotate Admin key after removal.</t>
+          <t>Every few days: aws ecr describe-images --region ap-south-1 --repository-name skin-scan --image-ids imageDigest=&lt;each child&gt; ; if one is gone, stop and tell the owner before any C2.</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2869,12 +2873,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Do not change the lifecycle policy without the owner.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2889,22 +2897,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Server-authoritative analysis writes</t>
+          <t>Dev/prod separation</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Browser is not authoritative for analysis-derived scores.</t>
+          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2912,60 +2920,56 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>D-02 / D-26</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan, lib/skin-state*</t>
+          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
+          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6e9081d, 155cb69</t>
+          <t>ff08107 (unmerged)</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr"/>
+          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
+          <t>Owner: unset S3_SKIN_IMAGES_* locally today; approve dev-only emulator gate; rotate Admin key after removal.</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>TRUSTED MEASUREMENT</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2978,7 +2982,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2993,12 +2997,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Echo authentication and ownership</t>
+          <t>Server-authoritative analysis writes</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Echo derives identity/context server-side and verifies ownership.</t>
+          <t>Browser is not authoritative for analysis-derived scores.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3023,7 +3027,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Gate 02 / D-26</t>
+          <t>D-02 / D-26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3033,38 +3037,38 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-check/chat</t>
+          <t>app/api/skin-scan, lib/skin-state*</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + live E2E</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>skin-check-chat-auth tests (13); cross-user 409</t>
+          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>6e9081d, 155cb69</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; verify live in I01.</t>
+          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -3082,7 +3086,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3097,12 +3101,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Gemini browser-state isolation</t>
+          <t>Echo authentication and ownership</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Gemini never trusts browser-supplied scores/context.</t>
+          <t>Echo derives identity/context server-side and verifies ownership.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3137,12 +3141,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
+          <t>app/api/skin-check/chat</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
+          <t>skin-check-chat-auth tests (13); cross-user 409</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3162,7 +3166,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr"/>
@@ -3173,7 +3177,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3186,7 +3190,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3201,12 +3205,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss npx firebase form</t>
+          <t>Gemini browser-state isolation</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
+          <t>Gemini never trusts browser-supplied scores/context.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3221,11 +3225,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02 / D-26</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3233,39 +3245,43 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json</t>
+          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules</t>
+          <t>Commit + tests + live E2E</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
+          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>ae457a0, 44e0352</t>
+          <t>155cb69, 955c1cc</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>Deploy via A13; verify live in I01.</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3273,16 +3289,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
-        </is>
-      </c>
+      <c r="V23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3297,12 +3309,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss other production-changing commands</t>
+          <t>Deny rules miss npx firebase form</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
+          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3320,11 +3332,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>B05</t>
-        </is>
-      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -3343,22 +3351,22 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules + echo probe</t>
+          <t>Commit with added rules</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2371f78</t>
+          <t>ae457a0, 44e0352</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
+          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
@@ -3375,44 +3383,44 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Guided capture quality gate</t>
+          <t>Deny rules miss other production-changing commands</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
+          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3420,7 +3428,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -3429,35 +3441,39 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check capture step</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Design doc + approved gate + tests</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
+          <t>Commit with added rules + echo probe</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2371f78</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk).</t>
-        </is>
-      </c>
+      <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3465,12 +3481,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3485,17 +3505,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Per-region / per-metric comparability</t>
+          <t>Guided capture quality gate</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Decide whether two scans are comparable before computing change.</t>
+          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3505,19 +3525,11 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>A07, A12, A13, C07</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3525,39 +3537,35 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-state*</t>
+          <t>components/skin-check capture step</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Comparability function + tests + noise inputs</t>
+          <t>Design doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
-        </is>
-      </c>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07.</t>
+          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk).</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3570,7 +3578,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -3585,22 +3593,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Human measurement validation protocol</t>
+          <t>Per-region / per-metric comparability</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Protocol for human validation and repeatability.</t>
+          <t>Decide whether two scans are comparable before computing change.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3608,10 +3616,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>A07, A12, A13, C07</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>D-24 (uncommitted)</t>
+          <t>D-13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3626,38 +3638,34 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>lib/skin-state*</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Committed protocol</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>59d9923</t>
-        </is>
-      </c>
+          <t>Comparability function + tests + noise inputs</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr"/>
+          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
+          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07.</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3670,7 +3678,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3685,22 +3693,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Human validation pilot</t>
+          <t>Human measurement validation protocol</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Run pilot of C03 protocol.</t>
+          <t>Protocol for human validation and repeatability.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3708,12 +3716,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>C03, A12, A13, H01</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>D-24 (uncommitted)</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3731,24 +3739,28 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Pre-registration + pilot dataset + report</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
+          <t>Committed protocol</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>59d9923</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
-        </is>
-      </c>
+          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
+          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3766,7 +3778,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -3781,12 +3793,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Full test-retest / calibration</t>
+          <t>Human validation pilot</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
+          <t>Run pilot of C03 protocol.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3806,7 +3818,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03, A12, A13, H01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -3820,10 +3832,14 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Pre-registered study report</t>
+          <t>Pre-registration + pilot dataset + report</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
@@ -3835,12 +3851,12 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Waits on C04 pilot.</t>
+          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Size from pilot variance.</t>
+          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3858,7 +3874,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3873,12 +3889,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Tone-stratified validation / model card</t>
+          <t>Full test-retest / calibration</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
+          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3898,7 +3914,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -3915,7 +3931,7 @@
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Per-band results + model card</t>
+          <t>Pre-registered study report</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
@@ -3927,12 +3943,12 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05 data.</t>
+          <t>Waits on C04 pilot.</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Define model card template alongside C05.</t>
+          <t>Size from pilot variance.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -3950,7 +3966,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3965,12 +3981,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Validated measurement/noise tables</t>
+          <t>Tone-stratified validation / model card</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
+          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3990,7 +4006,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>C05, C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -4007,7 +4023,7 @@
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Versioned noise table tied to engine build</t>
+          <t>Per-band results + model card</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr"/>
@@ -4019,12 +4035,12 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05/C06.</t>
+          <t>Waits on C05 data.</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Fix table schema (field x region x band x engine build).</t>
+          <t>Define model card template alongside C05.</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4037,36 +4053,32 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
-        </is>
-      </c>
+      <c r="V31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Baseline window definition</t>
+          <t>Validated measurement/noise tables</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>How a user's baseline is formed.</t>
+          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4081,12 +4093,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C05, C06</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -4103,7 +4115,7 @@
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Method doc + decision</t>
+          <t>Versioned noise table tied to engine build</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
@@ -4115,17 +4127,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Needs between-day noise (C07).</t>
+          <t>Waits on C05/C06.</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
+          <t>Fix table schema (field x region x band x engine build).</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4133,12 +4145,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -4153,12 +4169,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Change-vs-noise engine</t>
+          <t>Baseline window definition</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
+          <t>How a user's baseline is formed.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4173,19 +4189,15 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>C02, C07, D01</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>D-13 / D-24</t>
-        </is>
-      </c>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4193,13 +4205,13 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Engine + tests + noise table version</t>
+          <t>Method doc + decision</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -4211,12 +4223,12 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Needs comparability (C02) and validated noise (C07).</t>
+          <t>Needs between-day noise (C07).</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Wait; design pairwise interface first (D-13).</t>
+          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
@@ -4234,7 +4246,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4249,12 +4261,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Persistence/evidence tiers</t>
+          <t>Change-vs-noise engine</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Separate transient observations from persistent patterns.</t>
+          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4269,15 +4281,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+          <t>C02, C07, D01</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>D-13 / D-24</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4285,13 +4301,13 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Tier definitions + tests</t>
+          <t>Engine + tests + noise table version</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
@@ -4303,12 +4319,12 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Needs D02.</t>
+          <t>Needs comparability (C02) and validated noise (C07).</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Wait on D02.</t>
+          <t>Wait; design pairwise interface first (D-13).</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -4321,16 +4337,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
-        </is>
-      </c>
+      <c r="V34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -4345,17 +4357,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Scheduled anchor scans / irregular sampling</t>
+          <t>Persistence/evidence tiers</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Sampling strategy.</t>
+          <t>Separate transient observations from persistent patterns.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4365,7 +4377,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4379,16 +4391,32 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Tier definitions + tests</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Needs D02.</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Revisit after D02.</t>
+          <t>Wait on D02.</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4401,12 +4429,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4421,12 +4453,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Engine-version re-baselining</t>
+          <t>Scheduled anchor scans / irregular sampling</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Handle engine build changes across history.</t>
+          <t>Sampling strategy.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4464,7 +4496,7 @@
       <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Revisit at first engine change after D02.</t>
+          <t>Revisit after D02.</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -4482,32 +4514,32 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Product catalog normalization</t>
+          <t>Engine-version re-baselining</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
+          <t>Handle engine build changes across history.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4517,51 +4549,35 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>D-08 / D-09</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>Owner-supplied master data + versioned schema</t>
-        </is>
-      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
-        </is>
-      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Owner supplies catalog data and decides OPEN-R1.</t>
+          <t>Revisit at first engine change after D02.</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4574,7 +4590,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4589,17 +4605,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Product eligibility / safety rules</t>
+          <t>Product catalog normalization</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Deterministic, versioned eligibility + safety constraints.</t>
+          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4612,19 +4628,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>E01, E05</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-08 / D-09</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4635,7 +4647,7 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Pure function + version constant + tests</t>
+          <t>Owner-supplied master data + versioned schema</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
@@ -4647,12 +4659,12 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Wait on E01.</t>
+          <t>Owner supplies catalog data and decides OPEN-R1.</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4670,7 +4682,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -4685,17 +4697,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Routine model + event history</t>
+          <t>Product eligibility / safety rules</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
+          <t>Deterministic, versioned eligibility + safety constraints.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4705,15 +4717,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
+          <t>E01, E05</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4721,13 +4737,13 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Data model doc + approved gate + tests</t>
+          <t>Pure function + version constant + tests</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
@@ -4737,10 +4753,14 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Design data model on branch; no production writes before A04.</t>
+          <t>Wait on E01.</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -4753,16 +4773,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>A04 dependency applies to deployment only.</t>
-        </is>
-      </c>
+      <c r="V39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4777,17 +4793,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Adherence summary</t>
+          <t>Routine model + event history</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
+          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4802,7 +4818,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -4813,13 +4829,13 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Function + tests</t>
+          <t>Data model doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
@@ -4829,14 +4845,10 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>Needs E03.</t>
-        </is>
-      </c>
+      <c r="R40" s="2" t="inlineStr"/>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Wait on E03.</t>
+          <t>Design data model on branch; no production writes before A04.</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -4849,12 +4861,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>A04 dependency applies to deployment only.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -4869,17 +4885,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Red-flag triage interlock</t>
+          <t>Adherence summary</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Safety layer overrides cosmetic recommendations.</t>
+          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4889,18 +4905,18 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4911,7 +4927,7 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+          <t>Function + tests</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
@@ -4923,17 +4939,17 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
+          <t>Needs E03.</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
+          <t>Wait on E03.</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4946,32 +4962,32 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Red-flag triage interlock</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>Safety layer overrides cosmetic recommendations.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4981,14 +4997,10 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>A08, D02, E03, E04, E05</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
           <t>D-14</t>
@@ -4996,25 +5008,21 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Pure builder + tests</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
-        </is>
-      </c>
+          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
@@ -5023,17 +5031,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
+          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Wait; may define schema with null sections earlier if approved.</t>
+          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5046,7 +5054,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -5061,12 +5069,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5086,7 +5094,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>A08, D02, E03, E04, E05</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5104,35 +5112,31 @@
           <t>Gemini/Context Engineer</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>lib/gemini.ts</t>
-        </is>
-      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
+          <t>Pure builder + tests</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>Schema renderer not built.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Needs F01.</t>
+          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Wait on F01.</t>
+          <t>Wait; may define schema with null sections earlier if approved.</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -5145,16 +5149,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>Seed status PARTIALLY READY.</t>
-        </is>
-      </c>
+      <c r="V43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>D-14 / D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -5212,27 +5212,35 @@
           <t>Gemini/Context Engineer</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr"/>
+          <t>Schema + renderer + tests</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+        </is>
+      </c>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Schema renderer not built.</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Needs F02 output schema.</t>
+          <t>Needs F01.</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Wait on F02.</t>
+          <t>Wait on F01.</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -5245,12 +5253,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Seed status PARTIALLY READY.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -5265,17 +5277,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5285,13 +5297,17 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>D-14 (store rejected for now)</t>
+          <t>D-14 / D-12</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -5307,24 +5323,24 @@
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
-        </is>
-      </c>
+          <t>Validator + adversarial tests</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Needs F02 output schema.</t>
+        </is>
+      </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
+          <t>Wait on F02.</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -5342,32 +5358,32 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5377,15 +5393,15 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>D-14 (store rejected for now)</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5393,35 +5409,35 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
-        </is>
-      </c>
+      <c r="R46" s="2" t="inlineStr"/>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5434,7 +5450,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -5449,12 +5465,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5469,19 +5485,15 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>E03, G01</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>D-12 (LOCKED)</t>
-        </is>
-      </c>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5495,7 +5507,7 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
+          <t>Approved design + tests + E2E</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr"/>
@@ -5507,12 +5519,12 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Needs E03 and G01.</t>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
@@ -5530,27 +5542,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -5565,17 +5577,17 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>E03, G01</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-17</t>
+          <t>D-12 (LOCKED)</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -5585,20 +5597,16 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
-        </is>
-      </c>
+          <t>Design reviewed against D-12</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
@@ -5607,17 +5615,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
+          <t>Needs E03 and G01.</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5630,7 +5638,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -5645,17 +5653,17 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5665,13 +5673,17 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-16 / D-17</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -5681,26 +5693,34 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr"/>
+          <t>Ledger + erasure route + tests + live verification</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Not started; 18+ check is client-only today.</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Write gate brief for D-19.</t>
+          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention.</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
@@ -5718,7 +5738,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -5733,17 +5753,17 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5753,46 +5773,42 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14</t>
+          <t>D-19</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
+          <t>Gate + tests</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
-        </is>
-      </c>
+          <t>Not started; 18+ check is client-only today.</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers).</t>
+          <t>Write gate brief for D-19.</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -5810,32 +5826,32 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5848,26 +5864,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>PREFLIGHT G1 / D-14</t>
+        </is>
+      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Field inventory + key ownership/tier + consent copy</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr"/>
@@ -5879,17 +5895,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Nothing longitudinal is deployed yet.</t>
+          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers).</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -5902,7 +5918,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -5917,12 +5933,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -5942,7 +5958,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
+          <t>A12, A13, B01, H01, H03</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -5953,13 +5969,13 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Recorded E2E run against prod</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr"/>
@@ -5971,17 +5987,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>Nothing longitudinal is deployed yet.</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>RELEASE</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -5994,32 +6010,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6029,31 +6045,51 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6066,7 +6102,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6081,7 +6117,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6138,7 +6174,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6153,7 +6189,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>ML recommendation ranking</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6210,7 +6246,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6225,7 +6261,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Indian cross-user benchmark</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6277,16 +6313,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6301,7 +6333,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Forecasting</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6353,7 +6385,83 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8238,7 +8346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8802,7 +8910,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>TD-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -8812,42 +8920,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Native L*/a* are provisional research candidates only</t>
+          <t>Phase 0 deploy paused after C1; features first; full deploy at the end</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 screening</t>
+          <t>Owner decision 2026-10-03. Runbook job C stopped after C1: the 0.1.6 image is stored in ECR (sha256:9a8f96c0a54025c4137b89dee181ba7fb140db1431fa95156cc20d8880e1fc2c) and nothing else is switched (service on skin-scan:1, Firestore nam5, Vercel iad1, master 1b39f88).</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Keep b*, ITA, lbpEntropy</t>
+          <t>Continue runbook C2-D now</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Primary endpoints for the human study only; not validated measurements</t>
+          <t>Build features on lane branches (capture, routine, privacy), tested on the local stack with no production keys; run the full runbook (C2 onward, then A, B, D) at the end</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Only survivors of screening</t>
+          <t>Owner decision</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
+          <t>ECR describe-images; ecs describe-services (skin-scan:1)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>C03-C07</t>
+          <t>A12, A04, A05, A13, A18, I01; lanes C01, C02, E01, E03, E04, H01, H02, H03</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Owner may reverse before Phase 1 pre-registration</t>
+          <t>Owner ends the pause</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -8857,76 +8965,76 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>ACCEPTED for study design</t>
+          <t>DECIDED (owner). Tracker-local until A14 lets DECISION_LOG.md take new entries; then copy it in as a D-number.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>D-13 / D-24</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal comparisons require comparability + noise/evidence</t>
+          <t>Native L*/a* are provisional research candidates only</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Naive % change misleads</t>
+          <t>Phase 0 screening</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Research-doc point ladder</t>
+          <t>Keep b*, ITA, lbpEntropy</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
+          <t>Primary endpoints for the human study only; not validated measurements</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Measurement noise unknown</t>
+          <t>Only survivors of screening</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-13; D-24 uncommitted</t>
+          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>C02, D02, G01</t>
+          <t>C03-C07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Owner may reverse before Phase 1 pre-registration</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (D-24 uncommitted)</t>
+          <t>ACCEPTED for study design</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-13 / D-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -8936,59 +9044,59 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Recommender deterministic and versioned</t>
+          <t>Longitudinal comparisons require comparability + noise/evidence</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4 SKUs, ~6 rules</t>
+          <t>Naive % change misleads</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>DMN/rules engine; ML ranking</t>
+          <t>Research-doc point ladder</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Plain TS pure function + version constants</t>
+          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Auditable</t>
+          <t>Measurement noise unknown</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-08</t>
+          <t>DECISION_LOG D-13; D-24 uncommitted</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>E02, J02</t>
+          <t>C02, D02, G01</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>&gt;20 SKUs or non-engineer rule authors</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>PROPOSED (D-24 uncommitted)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -8998,42 +9106,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Gemini is explanation layer, not authority</t>
+          <t>Recommender deterministic and versioned</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Gemini hallucination/claims risk</t>
+          <t>4 SKUs, ~6 rules</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Gemini owns context</t>
+          <t>DMN/rules engine; ML ranking</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+          <t>Plain TS pure function + version constants</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Auditable</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-14; GATE_02</t>
+          <t>DECISION_LOG D-08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>B04, F01-F04</t>
+          <t>E02, J02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&gt;20 SKUs or non-engineer rule authors</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -9043,14 +9151,14 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (paid tier is release gate)</t>
+          <t>PROPOSED</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -9060,104 +9168,104 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>No attribution/efficacy/forecasting</t>
+          <t>Gemini is explanation layer, not authority</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Gemini hallucination/claims risk</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Gemini owns context</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Evidence tiers 3-4</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Prohibited in UI, Gemini, analytics</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>CLAUDE.md</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-12</t>
+          <t>DECISION_LOG D-14; GATE_02</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>G02, J04, R08</t>
+          <t>B04, F01-F04</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Explicit owner approval</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>PROPOSED (paid tier is release gate)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Client input never authoritative for measured state</t>
+          <t>No attribution/efficacy/forecasting</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Gate 02</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Rules tightening; server chat storage</t>
+          <t>Evidence tiers 3-4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Path-structural trust; authenticated Echo</t>
+          <t>Prohibited in UI, Gemini, analytics</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Forgeable browser state</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>DECISION_LOG D-12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>A09, B02-B04, C02</t>
+          <t>G02, J04, R08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Open: client-asserted captureMethod/persistAttempt</t>
+          <t>Explicit owner approval</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -9167,67 +9275,129 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED (branch); owner decision open</t>
+          <t>LOCKED</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>D-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Client input never authoritative for measured state</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Rules tightening; server chat storage</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Path-structural trust; authenticated Echo</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Forgeable browser state</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>A09, B02-B04, C02</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Open: client-asserted captureMethod/persistAttempt</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (branch); owner decision open</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>D-21</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Gate 01 stores raw analysis in scanAnalyses</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Raw preservation</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>skinStates collection</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>users/{uid}/scanAnalyses/{scanId}_{sha16}</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Immutable raw substrate</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>6e9081d</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Systems Architect</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>IMPLEMENTED (not deployed); ID duplicated in HEAD</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>e9d3b46, 2026-10-03: typecheck pass (tsc 0 errors), lint pass (no ESLint warnings or errors), next build pass (compiled successfully), vitest 216 passed / 0 failed / 24 skipped (the 24 are the rules file), npm run test:rules 24/24 against the emulator.</t>
+          <t>6758fe6, 2026-10-03: typecheck 0 errors, lint clean, vitest 242 passed / 25 skipped, npm run test:local green (rules 24/24, end-to-end 1/1). next build pass.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>36% = DONE 18 / (total 57 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>38% = DONE 20 / (total 59 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 18, IN PROGRESS 0, NOT STARTED 5, BLOCKED 20, OWNER ACTION 7, LATER 7 (total 57)</t>
+          <t>DONE 20, IN PROGRESS 0, NOT STARTED 5, BLOCKED 20, OWNER ACTION 7, LATER 7 (total 59)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 0, CHECKED LOCAL 11, NOT NEEDED 7, NOT CHECKED 39</t>
+          <t>CHECKED PROD 0, CHECKED LOCAL 12, NOT NEEDED 8, NOT CHECKED 39</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V58"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2882,94 +2882,98 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dev/prod separation</t>
+          <t>Prepare three lanes</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
+          <t>Worktrees and branches for capture (C01, C02), routine (E01, E03, E04) and privacy (H01-H03); file ownership, shared-file plan, ports, briefs.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>TD-04</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
+          <t>docs/lanes/</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
+          <t>Committed briefs + worktrees</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
+          <t>docs/lanes/README.md, capture.md, routine.md, privacy.md; worktrees ../skin-check-{capture,routine,privacy} on lane/* at 6758fe6, .env.lane PORT_BASE 3200/3300/3400</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>ff08107 (unmerged)</t>
+          <t>6758fe6</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
-        </is>
-      </c>
+          <t>Document task. No lane work started.</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Owner: unset S3_SKIN_IMAGES_* locally today; approve dev-only emulator gate; rotate Admin key after removal.</t>
+          <t>Owner approves each lane's design brief; lanes run npm ci then npm run test:local.</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2977,12 +2981,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Lanes never edit the tracker; it is updated from docs/lanes/&lt;lane&gt;-report.md at merge.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2997,22 +3005,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Server-authoritative analysis writes</t>
+          <t>Dev/prod separation</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Browser is not authoritative for analysis-derived scores.</t>
+          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3020,60 +3028,56 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>D-02 / D-26</t>
-        </is>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan, lib/skin-state*</t>
+          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
+          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6e9081d, 155cb69</t>
+          <t>ff08107 (unmerged)</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr"/>
+          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
+          <t>Agent part done in B07 (local stack, no production keys; next dev refuses production values). Owner: remove FIREBASE_PRIVATE_KEY, FIREBASE_CLIENT_EMAIL and S3_SKIN_IMAGES_* from .env.local and the Desktop adminsdk JSON, then rotate the Admin key.</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>TRUSTED MEASUREMENT</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -3086,7 +3090,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3101,12 +3105,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Echo authentication and ownership</t>
+          <t>Server-authoritative analysis writes</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Echo derives identity/context server-side and verifies ownership.</t>
+          <t>Browser is not authoritative for analysis-derived scores.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3131,7 +3135,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Gate 02 / D-26</t>
+          <t>D-02 / D-26</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3141,38 +3145,38 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-check/chat</t>
+          <t>app/api/skin-scan, lib/skin-state*</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + live E2E</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>skin-check-chat-auth tests (13); cross-user 409</t>
+          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>6e9081d, 155cb69</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; verify live in I01.</t>
+          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -3190,7 +3194,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3205,12 +3209,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Gemini browser-state isolation</t>
+          <t>Echo authentication and ownership</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Gemini never trusts browser-supplied scores/context.</t>
+          <t>Echo derives identity/context server-side and verifies ownership.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3245,12 +3249,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
+          <t>app/api/skin-check/chat</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3260,7 +3264,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
+          <t>skin-check-chat-auth tests (13); cross-user 409</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3270,7 +3274,7 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
@@ -3281,7 +3285,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3294,7 +3298,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3309,12 +3313,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss npx firebase form</t>
+          <t>Gemini browser-state isolation</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
+          <t>Gemini never trusts browser-supplied scores/context.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3329,11 +3333,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02 / D-26</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3341,39 +3353,43 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json</t>
+          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules</t>
+          <t>Commit + tests + live E2E</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
+          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>ae457a0, 44e0352</t>
+          <t>155cb69, 955c1cc</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>Deploy via A13; verify live in I01.</t>
+        </is>
+      </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3381,16 +3397,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
-        </is>
-      </c>
+      <c r="V24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -3405,12 +3417,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss other production-changing commands</t>
+          <t>Local stack with no production keys</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
+          <t>Firebase Auth + Firestore emulators with the real rules, local engine 0.1.6, S3Mock, Gemini dev key or test fake, seed data, dev guard, one start and one test command.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3425,14 +3437,10 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>B05</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -3441,36 +3449,40 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json</t>
+          <t>scripts/local-stack*.sh, scripts/seed-local.ts, .env.development.example, lib/dev-env-guard.cjs, lib/gemini-key.ts, lib/firebase/{client,admin}.ts, lib/s3.ts, next.config.js</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules + echo probe</t>
+          <t>Commit + tests + end-to-end run</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+          <t>npm run test:local: unit 242 passed / 25 skipped, rules 24/24, end-to-end 1/1 (seeded phone user signs in via Auth emulator, upload to S3Mock, scan via local 0.1.6 engine, scanAnalyses + skinChecks saved in emulator); also green at PORT_BASE=3200. next dev with only .env.local refuses to start (7 variables named). typecheck 0, lint clean.</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2371f78</t>
+          <t>9ea6ad5, 6758fe6</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
+          <t>Local only. No UI click-through: the end-to-end test drives the real dev server through its HTTP API and the client SDK.</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>Owner: fill GEMINI_DEV_API_KEY in .env.development.local when a separate dev key exists.</t>
+        </is>
+      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
           <t>PRIVACY/SAFETY</t>
@@ -3483,44 +3495,44 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+          <t>Plain npm run dev with today's .env.local now refuses to start; use npm run dev:local.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Guided capture quality gate</t>
+          <t>Deny rules miss npx firebase form</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
+          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3537,35 +3549,39 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check capture step</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Design doc + approved gate + tests</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+          <t>Commit with added rules</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>ae457a0, 44e0352</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk).</t>
-        </is>
-      </c>
+      <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3573,59 +3589,59 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Per-region / per-metric comparability</t>
+          <t>Deny rules miss other production-changing commands</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Decide whether two scans are comparable before computing change.</t>
+          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>A07, A12, A13, C07</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
+          <t>B05</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3633,39 +3649,39 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-state*</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Comparability function + tests + noise inputs</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
+          <t>Commit with added rules + echo probe</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2371f78</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07.</t>
-        </is>
-      </c>
+          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3673,12 +3689,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3693,35 +3713,31 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Human measurement validation protocol</t>
+          <t>Guided capture quality gate</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Protocol for human validation and repeatability.</t>
+          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>D-24 (uncommitted)</t>
-        </is>
-      </c>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3729,38 +3745,30 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>components/skin-check capture step</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Committed protocol</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>59d9923</t>
-        </is>
-      </c>
+          <t>Design doc + approved gate + tests</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
+          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk). Lane: capture (branch lane/capture, brief docs/lanes/capture.md); results come via docs/lanes/capture-report.md at merge.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3778,7 +3786,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -3793,12 +3801,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Human validation pilot</t>
+          <t>Per-region / per-metric comparability</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Run pilot of C03 protocol.</t>
+          <t>Decide whether two scans are comparable before computing change.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3818,10 +3826,14 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>C03, A12, A13, H01</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr"/>
+          <t>A07, A12, A13, C07</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3834,34 +3846,34 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>lib/skin-state*</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Pre-registration + pilot dataset + report</t>
+          <t>Comparability function + tests + noise inputs</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
+          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
+          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07. Lane: capture (branch lane/capture, brief docs/lanes/capture.md); results come via docs/lanes/capture-report.md at merge.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3874,7 +3886,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3889,22 +3901,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Full test-retest / calibration</t>
+          <t>Human measurement validation protocol</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
+          <t>Protocol for human validation and repeatability.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3912,12 +3924,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>C04</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>D-24 (uncommitted)</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3928,27 +3940,35 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Pre-registered study report</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
+          <t>Committed protocol</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>59d9923</t>
+        </is>
+      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>Waits on C04 pilot.</t>
-        </is>
-      </c>
+          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Size from pilot variance.</t>
+          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -3966,7 +3986,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3981,12 +4001,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Tone-stratified validation / model card</t>
+          <t>Human validation pilot</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
+          <t>Run pilot of C03 protocol.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4006,7 +4026,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C03, A12, A13, H01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -4020,10 +4040,14 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Per-band results + model card</t>
+          <t>Pre-registration + pilot dataset + report</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr"/>
@@ -4035,12 +4059,12 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05 data.</t>
+          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Define model card template alongside C05.</t>
+          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4058,7 +4082,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4073,12 +4097,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Validated measurement/noise tables</t>
+          <t>Full test-retest / calibration</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
+          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4098,7 +4122,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>C05, C06</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -4115,7 +4139,7 @@
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Versioned noise table tied to engine build</t>
+          <t>Pre-registered study report</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
@@ -4127,12 +4151,12 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05/C06.</t>
+          <t>Waits on C04 pilot.</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>Fix table schema (field x region x band x engine build).</t>
+          <t>Size from pilot variance.</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4145,36 +4169,32 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
-        </is>
-      </c>
+      <c r="V32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Baseline window definition</t>
+          <t>Tone-stratified validation / model card</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>How a user's baseline is formed.</t>
+          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4189,12 +4209,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -4211,7 +4231,7 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Method doc + decision</t>
+          <t>Per-band results + model card</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -4223,17 +4243,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Needs between-day noise (C07).</t>
+          <t>Waits on C05 data.</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
+          <t>Define model card template alongside C05.</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4246,27 +4266,27 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Change-vs-noise engine</t>
+          <t>Validated measurement/noise tables</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
+          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4286,14 +4306,10 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>C02, C07, D01</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>D-13 / D-24</t>
-        </is>
-      </c>
+          <t>C05, C06</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4301,13 +4317,13 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Engine + tests + noise table version</t>
+          <t>Versioned noise table tied to engine build</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
@@ -4319,17 +4335,17 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Needs comparability (C02) and validated noise (C07).</t>
+          <t>Waits on C05/C06.</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Wait; design pairwise interface first (D-13).</t>
+          <t>Fix table schema (field x region x band x engine build).</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4337,12 +4353,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -4357,12 +4377,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Persistence/evidence tiers</t>
+          <t>Baseline window definition</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Separate transient observations from persistent patterns.</t>
+          <t>How a user's baseline is formed.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4382,7 +4402,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4399,7 +4419,7 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Tier definitions + tests</t>
+          <t>Method doc + decision</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr"/>
@@ -4411,12 +4431,12 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Needs D02.</t>
+          <t>Needs between-day noise (C07).</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Wait on D02.</t>
+          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4429,16 +4449,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
-        </is>
-      </c>
+      <c r="V35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4453,17 +4469,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Scheduled anchor scans / irregular sampling</t>
+          <t>Change-vs-noise engine</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sampling strategy.</t>
+          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4473,30 +4489,50 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
+          <t>C02, C07, D01</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>D-13 / D-24</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Engine + tests + noise table version</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Needs comparability (C02) and validated noise (C07).</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Revisit after D02.</t>
+          <t>Wait; design pairwise interface first (D-13).</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -4514,7 +4550,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -4529,17 +4565,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Engine-version re-baselining</t>
+          <t>Persistence/evidence tiers</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Handle engine build changes across history.</t>
+          <t>Separate transient observations from persistent patterns.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4549,7 +4585,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4563,16 +4599,32 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Tier definitions + tests</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Needs D02.</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Revisit at first engine change after D02.</t>
+          <t>Wait on D02.</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4585,37 +4637,41 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Product catalog normalization</t>
+          <t>Scheduled anchor scans / irregular sampling</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
+          <t>Sampling strategy.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4625,51 +4681,35 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>D-08 / D-09</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>Owner-supplied master data + versioned schema</t>
-        </is>
-      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
-        </is>
-      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Owner supplies catalog data and decides OPEN-R1.</t>
+          <t>Revisit after D02.</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4682,32 +4722,32 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Product eligibility / safety rules</t>
+          <t>Engine-version re-baselining</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Deterministic, versioned eligibility + safety constraints.</t>
+          <t>Handle engine build changes across history.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4717,55 +4757,35 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>E01, E05</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>D-08</t>
-        </is>
-      </c>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
+      <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>Pure function + version constant + tests</t>
-        </is>
-      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
-        </is>
-      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Wait on E01.</t>
+          <t>Revisit at first engine change after D02.</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4778,7 +4798,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4793,17 +4813,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Routine model + event history</t>
+          <t>Product catalog normalization</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
+          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4813,29 +4833,29 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>D-08 / D-09</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Data model doc + approved gate + tests</t>
+          <t>Owner-supplied master data + versioned schema</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
@@ -4845,10 +4865,14 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Design data model on branch; no production writes before A04.</t>
+          <t>Owner supplies catalog data and decides OPEN-R1. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -4861,16 +4885,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>A04 dependency applies to deployment only.</t>
-        </is>
-      </c>
+      <c r="V40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -4885,12 +4905,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Adherence summary</t>
+          <t>Product eligibility / safety rules</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
+          <t>Deterministic, versioned eligibility + safety constraints.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -4905,15 +4925,19 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
+          <t>E01, E05</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4927,7 +4951,7 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Function + tests</t>
+          <t>Pure function + version constant + tests</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
@@ -4939,12 +4963,12 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Needs E03.</t>
+          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Wait on E03.</t>
+          <t>Wait on E01.</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -4962,7 +4986,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4977,17 +5001,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Red-flag triage interlock</t>
+          <t>Routine model + event history</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Safety layer overrides cosmetic recommendations.</t>
+          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4997,29 +5021,29 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+          <t>Data model doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
@@ -5029,19 +5053,15 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
-        </is>
-      </c>
+      <c r="R42" s="2" t="inlineStr"/>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
+          <t>Design data model on branch; no production writes before A04. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5049,32 +5069,36 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>A04 dependency applies to deployment only.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Adherence summary</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5089,19 +5113,15 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>A08, D02, E03, E04, E05</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5109,20 +5129,16 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Pure builder + tests</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
-        </is>
-      </c>
+          <t>Function + tests</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
@@ -5131,17 +5147,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
+          <t>Needs E03.</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Wait; may define schema with null sections earlier if approved.</t>
+          <t>Wait on E03. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5154,32 +5170,32 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Red-flag triage interlock</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Safety layer overrides cosmetic recommendations.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5189,14 +5205,10 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t>D-14</t>
@@ -5204,48 +5216,40 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>lib/gemini.ts</t>
-        </is>
-      </c>
+          <t>Product/Routine Rules Engineer</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
-        </is>
-      </c>
+          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Schema renderer not built.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Needs F01.</t>
+          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Wait on F01.</t>
+          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5253,16 +5257,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>Seed status PARTIALLY READY.</t>
-        </is>
-      </c>
+      <c r="V44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>A08, D02, E03, E04, E05</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>D-14 / D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -5323,10 +5323,14 @@
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr"/>
+          <t>Pure builder + tests</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
@@ -5335,12 +5339,12 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Needs F02 output schema.</t>
+          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Wait on F02.</t>
+          <t>Wait; may define schema with null sections earlier if approved.</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -5358,7 +5362,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -5373,17 +5377,17 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5393,13 +5397,17 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>D-14 (store rejected for now)</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -5412,27 +5420,35 @@
           <t>Gemini/Context Engineer</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
+          <t>Schema + renderer + tests</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
+          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr"/>
+          <t>Schema renderer not built.</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Needs F01.</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
+          <t>Wait on F01.</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -5445,32 +5461,36 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Seed status PARTIALLY READY.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5490,10 +5510,14 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr"/>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>D-14 / D-12</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5501,13 +5525,13 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
+          <t>Validator + adversarial tests</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr"/>
@@ -5519,17 +5543,17 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
+          <t>Needs F02 output schema.</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>Wait on F02.</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5542,32 +5566,32 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5580,14 +5604,10 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>E03, G01</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>D-12 (LOCKED)</t>
+          <t>D-14 (store rejected for now)</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -5597,35 +5617,35 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>Needs E03 and G01.</t>
-        </is>
-      </c>
+      <c r="R48" s="2" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5638,27 +5658,27 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -5673,19 +5693,15 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>D-16 / D-17</t>
-        </is>
-      </c>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5693,20 +5709,16 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
-        </is>
-      </c>
+          <t>Approved design + tests + E2E</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
@@ -5715,17 +5727,17 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention.</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5738,32 +5750,32 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5773,13 +5785,17 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>E03, G01</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-12 (LOCKED)</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -5795,25 +5811,29 @@
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
+          <t>Design reviewed against D-12</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Not started; 18+ check is client-only today.</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Needs E03 and G01.</t>
+        </is>
+      </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Write gate brief for D-19.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5826,7 +5846,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -5841,17 +5861,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5864,15 +5884,19 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14</t>
+          <t>D-16 / D-17</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -5883,10 +5907,14 @@
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr"/>
+          <t>Ledger + erasure route + tests + live verification</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
+        </is>
+      </c>
       <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
@@ -5895,12 +5923,12 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
+          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers).</t>
+          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention. Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
@@ -5918,32 +5946,32 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -5953,15 +5981,15 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>D-19</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5969,35 +5997,31 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Gate + tests</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>Nothing longitudinal is deployed yet.</t>
-        </is>
-      </c>
+          <t>Not started; 18+ check is client-only today.</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Write gate brief for D-19. Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6010,32 +6034,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6048,26 +6072,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>I01, F03, E05</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>PREFLIGHT G1 / D-14</t>
+        </is>
+      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Field inventory + key ownership/tier + consent copy</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr"/>
@@ -6079,17 +6103,17 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers). Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6102,32 +6126,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6137,26 +6161,46 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>A12, A13, B01, H01, H03</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>QA/Test Engineer</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Recorded E2E run against prod</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Nothing longitudinal is deployed yet.</t>
+        </is>
+      </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
@@ -6174,32 +6218,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6209,31 +6253,51 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr"/>
       <c r="P55" s="2" t="inlineStr"/>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6246,7 +6310,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6261,7 +6325,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6318,7 +6382,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6333,7 +6397,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>ML recommendation ranking</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6385,16 +6449,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6409,7 +6469,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Indian cross-user benchmark</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6462,6 +6522,154 @@
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7424,7 +7632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7758,7 +7966,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>b05-a12-a17-session-2026-10-03</t>
+          <t>local-stack-lanes-session-2026-10-03</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -7768,12 +7976,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>B05 deny rules, A12 image re-verification, four runbook fixes, A17 ENGINE_TABLE row</t>
+          <t>TD-04 record; B07 local stack; A19 lanes</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>B05, A12, A15, A17</t>
+          <t>B01, C01-H03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7798,17 +8006,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json, lib/skin-state.ts, tests/skin-state.test.ts, docs/PHASE_0_RUNBOOK.md, docs/PROJECT_SKIN_EXECUTION_TRACKER.{md,xlsx}</t>
+          <t>CLAUDE.md, tracker, scripts/build_execution_tracker.py, .gitignore, package.json, next.config.js, lib/{dev-env-guard.cjs,gemini-key.ts,gemini.ts,s3.ts}, lib/firebase/{client,admin}.ts, app/api/skin-check/chat/route.ts, .env.development.example, scripts/{local-stack.sh,local-stack-e2e.sh,seed-local.ts}, tests/{dev-env-guard,local-dev-switches,local-stack.e2e}.test.ts, docs/lanes/*</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>vitest (217 pass, 24 skipped), typecheck, lint, test/typecheck/lint/build with no env files (clean worktree), 39 deny-rule echo probes</t>
+          <t>typecheck, lint, vitest, test:local (3100 and 3200)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Verifier (general-purpose agent with verifier.md, read-only + local docker): A12 PASS. New row B06</t>
+          <t>Overview counts were stale (fixed; script now checks)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7818,17 +8026,17 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D-23 note (owner decision, A17)</t>
+          <t>TD-04 recorded (owner)</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>ae457a0, 7af7df0, 3e06858, b0a7424, 44e0352</t>
+          <t>5fd789c, 9ea6ad5, 6758fe6</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Verifier PASS (A12); hashes re-checked by lead (30 shared, 0 differ)</t>
+          <t>Awaiting owner review</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7840,7 +8048,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>b06-session-2026-10-03</t>
+          <t>b05-a12-a17-session-2026-10-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7850,12 +8058,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>B06 deny rules (owner decision)</t>
+          <t>B05 deny rules, A12 image re-verification, four runbook fixes, A17 ENGINE_TABLE row</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B05, A12, A15, A17</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7880,17 +8088,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json, docs/PHASE_0_RUNBOOK.md, docs/PROJECT_SKIN_EXECUTION_TRACKER.{md,xlsx}</t>
+          <t>.claude/settings.json, lib/skin-state.ts, tests/skin-state.test.ts, docs/PHASE_0_RUNBOOK.md, docs/PROJECT_SKIN_EXECUTION_TRACKER.{md,xlsx}</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44 echo probes (32 denied, 12 allowed)</t>
+          <t>vitest (217 pass, 24 skipped), typecheck, lint, test/typecheck/lint/build with no env files (clean worktree), 39 deny-rule echo probes</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Branch- and variable-dependent git push forms cannot be matched by deny patterns</t>
+          <t>Verifier (general-purpose agent with verifier.md, read-only + local docker): A12 PASS. New row B06</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7900,17 +8108,17 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>D-23 note (owner decision, A17)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2371f78</t>
+          <t>ae457a0, 7af7df0, 3e06858, b0a7424, 44e0352</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>n/a (config)</t>
+          <t>Verifier PASS (A12); hashes re-checked by lead (30 shared, 0 differ)</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7922,22 +8130,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>lead-session-2026-10-03 workers</t>
+          <t>b06-session-2026-10-03</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>QA/Test, Measurement, Security</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>I01 draft, C01 brief (stopped: scope narrowed to Phase 0); A12 QA + security re-verification (stopped by owner)</t>
+          <t>B06 deny rules (owner decision)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>I01, C01, A12</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7952,7 +8160,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>STOPPED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7962,17 +8170,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>none (no files left)</t>
+          <t>.claude/settings.json, docs/PHASE_0_RUNBOOK.md, docs/PROJECT_SKIN_EXECUTION_TRACKER.{md,xlsx}</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>44 echo probes (32 denied, 12 allowed)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>none recorded</t>
+          <t>Branch- and variable-dependent git push forms cannot be matched by deny patterns</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7987,12 +8195,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2371f78</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>n/a (config)</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -8004,37 +8212,37 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>india-region session</t>
+          <t>lead-session-2026-10-03 workers</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>QA/Test, Measurement, Security</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Prepare India-region Firestore + Vercel</t>
+          <t>I01 draft, C01 brief (stopped: scope narrowed to Phase 0); A12 QA + security re-verification (stopped by owner)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>A04, A05</t>
+          <t>I01, C01, A12</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>.claude/worktrees/india-region</t>
+          <t>main (skin-check)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>infra/india-region</t>
+          <t>longitudinal-platform</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>STOPPED</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -8044,122 +8252,204 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>vercel.json, DATA_LOCALITY_DECISION.md, DECISION_LOG.md, DEV_PROD_BOUNDARY.md, FIRESTORE_RESET_RUNBOOK.md</t>
+          <t>none (no files left)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>none recorded</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>D-22 approved</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>ff08107</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Not merged</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Worktree still exists (clean)</t>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>india-region session</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Prepare India-region Firestore + Vercel</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>A04, A05</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>.claude/worktrees/india-region</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>infra/india-region</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>vercel.json, DATA_LOCALITY_DECISION.md, DECISION_LOG.md, DEV_PROD_BOUNDARY.md, FIRESTORE_RESET_RUNBOOK.md</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>D-22</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>D-22 approved</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>ff08107</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Not merged</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Worktree still exists (clean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>earlier sessions (gates 01-04, Phase 0)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>A01-A12, B02-B04</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>longitudinal-platform</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>see commits</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>see DECISION_LOG</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>61c149a..91d20bc</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>unknown - not reconstructable from repo</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>38% = DONE 20 / (total 59 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>38% = DONE 20 / (total 60 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 20, IN PROGRESS 0, NOT STARTED 5, BLOCKED 20, OWNER ACTION 7, LATER 7 (total 59)</t>
+          <t>DONE 20, IN PROGRESS 0, NOT STARTED 5, BLOCKED 20, OWNER ACTION 8, LATER 7 (total 60)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 0, CHECKED LOCAL 12, NOT NEEDED 8, NOT CHECKED 39</t>
+          <t>CHECKED PROD 0, CHECKED LOCAL 12, NOT NEEDED 8, NOT CHECKED 40</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>docs/lanes/README.md, capture.md, routine.md, privacy.md; worktrees ../skin-check-{capture,routine,privacy} on lane/* at 6758fe6, .env.lane PORT_BASE 3200/3300/3400</t>
+          <t>docs/lanes/README.md, capture.md, routine.md, privacy.md; worktrees ../skin-check-{capture,routine,privacy} on lane/* at 0fc1e57, .env.lane PORT_BASE 3200/3300/3400</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6758fe6</t>
+          <t>6758fe6, 0fc1e57</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9ea6ad5, 6758fe6</t>
+          <t>9ea6ad5, 6758fe6, 0fc1e57</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3517,22 +3517,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss npx firebase form</t>
+          <t>Vercel Preview holds production secrets</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
+          <t>Vercel env Preview scope has production SKIN_SCAN_API_URL, SCAN_API_SECRET, GEMINI_API_KEY (names from vercel env ls, 2026-10-03). Any pushed branch (lane/*, longitudinal-platform) gets a preview that calls the production engine and Gemini.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3541,10 +3541,14 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>D-26</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3554,31 +3558,35 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json</t>
+          <t>Vercel project skin-check env (Preview)</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules</t>
+          <t>vercel env ls showing Preview without production secrets, or a decision to keep them</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>ae457a0, 44e0352</t>
-        </is>
-      </c>
+          <t>vercel env ls (names and targets only)</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Changing Vercel env is the owner's action.</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>Owner: remove the Preview copies of SCAN_API_SECRET, SKIN_SCAN_API_URL and GEMINI_API_KEY (or use separate preview values); until then do not push lane/* branches.</t>
+        </is>
+      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
           <t>PRIVACY/SAFETY</t>
@@ -3591,14 +3599,14 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
+          <t>Found while preparing lanes.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -3613,12 +3621,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss other production-changing commands</t>
+          <t>Deny rules miss npx firebase form</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
+          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3636,11 +3644,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>B05</t>
-        </is>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3659,22 +3663,22 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules + echo probe</t>
+          <t>Commit with added rules</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2371f78</t>
+          <t>ae457a0, 44e0352</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
+          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr"/>
@@ -3691,44 +3695,44 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Guided capture quality gate</t>
+          <t>Deny rules miss other production-changing commands</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
+          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3736,7 +3740,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3745,35 +3753,39 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check capture step</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Design doc + approved gate + tests</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
+          <t>Commit with added rules + echo probe</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2371f78</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk). Lane: capture (branch lane/capture, brief docs/lanes/capture.md); results come via docs/lanes/capture-report.md at merge.</t>
-        </is>
-      </c>
+      <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3781,12 +3793,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -3801,17 +3817,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Per-region / per-metric comparability</t>
+          <t>Guided capture quality gate</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Decide whether two scans are comparable before computing change.</t>
+          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3821,19 +3837,11 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>A07, A12, A13, C07</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3841,39 +3849,35 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-state*</t>
+          <t>components/skin-check capture step</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Comparability function + tests + noise inputs</t>
+          <t>Design doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
-        </is>
-      </c>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07. Lane: capture (branch lane/capture, brief docs/lanes/capture.md); results come via docs/lanes/capture-report.md at merge.</t>
+          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk). Lane: capture (branch lane/capture, brief docs/lanes/capture.md); results come via docs/lanes/capture-report.md at merge.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3886,7 +3890,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3901,22 +3905,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Human measurement validation protocol</t>
+          <t>Per-region / per-metric comparability</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Protocol for human validation and repeatability.</t>
+          <t>Decide whether two scans are comparable before computing change.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3924,10 +3928,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>A07, A12, A13, C07</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>D-24 (uncommitted)</t>
+          <t>D-13</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3942,38 +3950,34 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>lib/skin-state*</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Committed protocol</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>59d9923</t>
-        </is>
-      </c>
+          <t>Comparability function + tests + noise inputs</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr"/>
+          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
+          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07. Lane: capture (branch lane/capture, brief docs/lanes/capture.md); results come via docs/lanes/capture-report.md at merge.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3986,7 +3990,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -4001,22 +4005,22 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Human validation pilot</t>
+          <t>Human measurement validation protocol</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Run pilot of C03 protocol.</t>
+          <t>Protocol for human validation and repeatability.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4024,12 +4028,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>C03, A12, A13, H01</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>D-24 (uncommitted)</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4047,24 +4051,28 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Pre-registration + pilot dataset + report</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
+          <t>Committed protocol</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>59d9923</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
-        </is>
-      </c>
+          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
+          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4082,7 +4090,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4097,12 +4105,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Full test-retest / calibration</t>
+          <t>Human validation pilot</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
+          <t>Run pilot of C03 protocol.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4122,7 +4130,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03, A12, A13, H01</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -4136,10 +4144,14 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Pre-registered study report</t>
+          <t>Pre-registration + pilot dataset + report</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
@@ -4151,12 +4163,12 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Waits on C04 pilot.</t>
+          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>Size from pilot variance.</t>
+          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4174,7 +4186,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -4189,12 +4201,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tone-stratified validation / model card</t>
+          <t>Full test-retest / calibration</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
+          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4214,7 +4226,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -4231,7 +4243,7 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Per-band results + model card</t>
+          <t>Pre-registered study report</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -4243,12 +4255,12 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05 data.</t>
+          <t>Waits on C04 pilot.</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Define model card template alongside C05.</t>
+          <t>Size from pilot variance.</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
@@ -4266,7 +4278,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4281,12 +4293,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Validated measurement/noise tables</t>
+          <t>Tone-stratified validation / model card</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
+          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4306,7 +4318,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>C05, C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -4323,7 +4335,7 @@
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Versioned noise table tied to engine build</t>
+          <t>Per-band results + model card</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
@@ -4335,12 +4347,12 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05/C06.</t>
+          <t>Waits on C05 data.</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Fix table schema (field x region x band x engine build).</t>
+          <t>Define model card template alongside C05.</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -4353,36 +4365,32 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
-        </is>
-      </c>
+      <c r="V34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Baseline window definition</t>
+          <t>Validated measurement/noise tables</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>How a user's baseline is formed.</t>
+          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4397,12 +4405,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C05, C06</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4419,7 +4427,7 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Method doc + decision</t>
+          <t>Versioned noise table tied to engine build</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr"/>
@@ -4431,17 +4439,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Needs between-day noise (C07).</t>
+          <t>Waits on C05/C06.</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
+          <t>Fix table schema (field x region x band x engine build).</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4449,12 +4457,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4469,12 +4481,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Change-vs-noise engine</t>
+          <t>Baseline window definition</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
+          <t>How a user's baseline is formed.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4489,19 +4501,15 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>C02, C07, D01</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>D-13 / D-24</t>
-        </is>
-      </c>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4509,13 +4517,13 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Engine + tests + noise table version</t>
+          <t>Method doc + decision</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -4527,12 +4535,12 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>Needs comparability (C02) and validated noise (C07).</t>
+          <t>Needs between-day noise (C07).</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Wait; design pairwise interface first (D-13).</t>
+          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -4550,7 +4558,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -4565,12 +4573,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Persistence/evidence tiers</t>
+          <t>Change-vs-noise engine</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Separate transient observations from persistent patterns.</t>
+          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4585,15 +4593,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
+          <t>C02, C07, D01</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>D-13 / D-24</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4601,13 +4613,13 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Tier definitions + tests</t>
+          <t>Engine + tests + noise table version</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
@@ -4619,12 +4631,12 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Needs D02.</t>
+          <t>Needs comparability (C02) and validated noise (C07).</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Wait on D02.</t>
+          <t>Wait; design pairwise interface first (D-13).</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4637,16 +4649,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
-        </is>
-      </c>
+      <c r="V37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4661,17 +4669,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Scheduled anchor scans / irregular sampling</t>
+          <t>Persistence/evidence tiers</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sampling strategy.</t>
+          <t>Separate transient observations from persistent patterns.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4681,7 +4689,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4695,16 +4703,32 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Tier definitions + tests</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Needs D02.</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Revisit after D02.</t>
+          <t>Wait on D02.</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4717,12 +4741,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -4737,12 +4765,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Engine-version re-baselining</t>
+          <t>Scheduled anchor scans / irregular sampling</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Handle engine build changes across history.</t>
+          <t>Sampling strategy.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4780,7 +4808,7 @@
       <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Revisit at first engine change after D02.</t>
+          <t>Revisit after D02.</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -4798,32 +4826,32 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Product catalog normalization</t>
+          <t>Engine-version re-baselining</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
+          <t>Handle engine build changes across history.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,51 +4861,35 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>D-08 / D-09</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>Owner-supplied master data + versioned schema</t>
-        </is>
-      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
-        </is>
-      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Owner supplies catalog data and decides OPEN-R1. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
+          <t>Revisit at first engine change after D02.</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4890,7 +4902,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -4905,17 +4917,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Product eligibility / safety rules</t>
+          <t>Product catalog normalization</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Deterministic, versioned eligibility + safety constraints.</t>
+          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4928,19 +4940,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>E01, E05</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-08 / D-09</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4951,7 +4959,7 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Pure function + version constant + tests</t>
+          <t>Owner-supplied master data + versioned schema</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
@@ -4963,12 +4971,12 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Wait on E01.</t>
+          <t>Owner supplies catalog data and decides OPEN-R1. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -4986,7 +4994,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -5001,17 +5009,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Routine model + event history</t>
+          <t>Product eligibility / safety rules</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
+          <t>Deterministic, versioned eligibility + safety constraints.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5021,15 +5029,19 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
+          <t>E01, E05</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5037,13 +5049,13 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Data model doc + approved gate + tests</t>
+          <t>Pure function + version constant + tests</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
@@ -5053,10 +5065,14 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+        </is>
+      </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Design data model on branch; no production writes before A04. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
+          <t>Wait on E01.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -5069,16 +5085,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>A04 dependency applies to deployment only.</t>
-        </is>
-      </c>
+      <c r="V42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -5093,17 +5105,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Adherence summary</t>
+          <t>Routine model + event history</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
+          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5118,7 +5130,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5129,13 +5141,13 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Function + tests</t>
+          <t>Data model doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
@@ -5145,14 +5157,10 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>Needs E03.</t>
-        </is>
-      </c>
+      <c r="R43" s="2" t="inlineStr"/>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Wait on E03. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
+          <t>Design data model on branch; no production writes before A04. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -5165,12 +5173,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>A04 dependency applies to deployment only.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -5185,17 +5197,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Red-flag triage interlock</t>
+          <t>Adherence summary</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Safety layer overrides cosmetic recommendations.</t>
+          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5205,18 +5217,18 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5227,7 +5239,7 @@
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+          <t>Function + tests</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
@@ -5239,17 +5251,17 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
+          <t>Needs E03.</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
+          <t>Wait on E03. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5262,32 +5274,32 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Red-flag triage interlock</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>Safety layer overrides cosmetic recommendations.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5297,14 +5309,10 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>A08, D02, E03, E04, E05</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
           <t>D-14</t>
@@ -5312,25 +5320,21 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Pure builder + tests</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
-        </is>
-      </c>
+          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
@@ -5339,17 +5343,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
+          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Wait; may define schema with null sections earlier if approved.</t>
+          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5362,7 +5366,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -5377,12 +5381,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5402,7 +5406,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>A08, D02, E03, E04, E05</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5420,35 +5424,31 @@
           <t>Gemini/Context Engineer</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>lib/gemini.ts</t>
-        </is>
-      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
+          <t>Pure builder + tests</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Schema renderer not built.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Needs F01.</t>
+          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Wait on F01.</t>
+          <t>Wait; may define schema with null sections earlier if approved.</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -5461,16 +5461,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Seed status PARTIALLY READY.</t>
-        </is>
-      </c>
+      <c r="V46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -5485,12 +5481,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5510,12 +5506,12 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>D-14 / D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -5528,27 +5524,35 @@
           <t>Gemini/Context Engineer</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr"/>
+          <t>Schema + renderer + tests</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+        </is>
+      </c>
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Schema renderer not built.</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Needs F02 output schema.</t>
+          <t>Needs F01.</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Wait on F02.</t>
+          <t>Wait on F01.</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
@@ -5561,12 +5565,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Seed status PARTIALLY READY.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -5581,17 +5589,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5601,13 +5609,17 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>D-14 (store rejected for now)</t>
+          <t>D-14 / D-12</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -5623,24 +5635,24 @@
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
-        </is>
-      </c>
+          <t>Validator + adversarial tests</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Needs F02 output schema.</t>
+        </is>
+      </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
+          <t>Wait on F02.</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
@@ -5658,32 +5670,32 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5693,15 +5705,15 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>D-14 (store rejected for now)</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5709,35 +5721,35 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
-        </is>
-      </c>
+      <c r="R49" s="2" t="inlineStr"/>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5750,7 +5762,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -5765,12 +5777,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -5785,19 +5797,15 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>E03, G01</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>D-12 (LOCKED)</t>
-        </is>
-      </c>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5811,7 +5819,7 @@
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
+          <t>Approved design + tests + E2E</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr"/>
@@ -5823,12 +5831,12 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Needs E03 and G01.</t>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -5846,27 +5854,27 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -5881,17 +5889,17 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>E03, G01</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-17</t>
+          <t>D-12 (LOCKED)</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -5901,20 +5909,16 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
-        </is>
-      </c>
+          <t>Design reviewed against D-12</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
@@ -5923,17 +5927,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
+          <t>Needs E03 and G01.</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention. Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -5946,7 +5950,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -5961,17 +5965,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -5981,13 +5985,17 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-16 / D-17</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -5997,26 +6005,34 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr"/>
+          <t>Ledger + erasure route + tests + live verification</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
+        </is>
+      </c>
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Not started; 18+ check is client-only today.</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
+        </is>
+      </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Write gate brief for D-19. Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
+          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention. Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
@@ -6034,7 +6050,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -6049,17 +6065,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6069,46 +6085,42 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14</t>
+          <t>D-19</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
+          <t>Gate + tests</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
-        </is>
-      </c>
+          <t>Not started; 18+ check is client-only today.</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers). Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
+          <t>Write gate brief for D-19. Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
@@ -6126,32 +6138,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6164,26 +6176,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>PREFLIGHT G1 / D-14</t>
+        </is>
+      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Field inventory + key ownership/tier + consent copy</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr"/>
@@ -6195,17 +6207,17 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Nothing longitudinal is deployed yet.</t>
+          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers). Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6218,7 +6230,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6233,12 +6245,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6258,7 +6270,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
+          <t>A12, A13, B01, H01, H03</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -6269,13 +6281,13 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Recorded E2E run against prod</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr"/>
@@ -6287,17 +6299,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>Nothing longitudinal is deployed yet.</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>RELEASE</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6310,32 +6322,32 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6345,31 +6357,51 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6382,7 +6414,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6397,7 +6429,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6454,7 +6486,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6469,7 +6501,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>ML recommendation ranking</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6526,7 +6558,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -6541,7 +6573,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Indian cross-user benchmark</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6593,16 +6625,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6617,7 +6645,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Forecasting</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -6669,7 +6697,83 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8031,7 +8135,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5fd789c, 9ea6ad5, 6758fe6</t>
+          <t>5fd789c, 9ea6ad5, 6758fe6, 080247d, 0fc1e57</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>38% = DONE 20 / (total 60 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>40% = DONE 21 / (total 60 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 20, IN PROGRESS 0, NOT STARTED 5, BLOCKED 20, OWNER ACTION 8, LATER 7 (total 60)</t>
+          <t>DONE 21, IN PROGRESS 0, NOT STARTED 4, BLOCKED 20, OWNER ACTION 8, LATER 7 (total 60)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 0, CHECKED LOCAL 12, NOT NEEDED 8, NOT CHECKED 40</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 12, NOT NEEDED 8, NOT CHECKED 39</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Resume at runbook C2 when the owner ends the TD-04 pause. C0 and C1 PASS 2026-10-03: ECR tag sha-8dc37dc501ea974825427c665acd7019120c20ec = sha256:9a8f96c0a54025c4137b89dee181ba7fb140db1431fa95156cc20d8880e1fc2c; service still on skin-scan:1. Watch the untagged children (A18).</t>
+          <t>Resume at runbook C2 when the owner ends the TD-04 pause. C0 and C1 PASS 2026-10-03: ECR tag sha-8dc37dc501ea974825427c665acd7019120c20ec = sha256:9a8f96c0a54025c4137b89dee181ba7fb140db1431fa95156cc20d8880e1fc2c; service still on skin-scan:1. Untagged children are protected by their tagged index (A18).</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED PROD</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2848,19 +2848,23 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03: both children present</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
+          <t>Read-only, 2026-10-03: the 0.1.5 index sha256:668b1f56... (tag sha-7f3695e...) still has both untagged children, amd64 image sha256:e0ecd1c90f87306b0fe7827198bb696544873306a75f08bd6a810c579bc5e58d and attestation sha256:1b4e4f5daa2ec0ad72538d9e56fa4e35e0269c8eb4e9c60edee3b4b7310dc34a, ACTIVE 29 days after push under the 1-day untagged rule. The 0.1.6 index 9a8f96c0 lists its two children (6bf0f2bc amd64, 74ad34fc attestation), both ACTIVE. AWS ECR lifecycle docs (LifecyclePolicies.html, evaluation rules): 'If an image is referenced by a manifest list, it cannot be expired or archived without the manifest list being deleted or archived first.' So the untagged rule cannot delete the children of a tagged index; earlier 'observed, not documented' is now documented.</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>n/a: read-only AWS check, no code (aws ecr describe-images, batch-get-image, get-lifecycle-policy)</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Not started. Read-only check, no policy change.</t>
+          <t>Children are protected while their tagged index exists. Remaining exposure is the index itself: rule 2 keeps the newest 20 sha- tags (2 today), so sha-7f3695e (rollback) and sha-8dc37dc are safe until 19+ newer sha- tags exist.</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Every few days: aws ecr describe-images --region ap-south-1 --repository-name skin-scan --image-ids imageDigest=&lt;each child&gt; ; if one is gone, stop and tell the owner before any C2.</t>
+          <t>No periodic check needed. Before pushing many new sha- tags, re-check that the rollback tag stays within the newest 20.</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>e9d3b46 before the Phase 0 runbook commits (working tree still has uncommitted DECISION_LOG.md edits and untracked DATA_LOCALITY_DECISION.md from another session; left untouched, see A14)</t>
+          <t>bff6e25 (lanes capture, routine, privacy merged 2026-10-03/04, plus follow-ups); working tree still has uncommitted DECISION_LOG.md edits and untracked DATA_LOCALITY_DECISION.md from another session, left untouched (A14)</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6758fe6, 2026-10-03: typecheck 0 errors, lint clean, vitest 242 passed / 25 skipped, npm run test:local green (rules 24/24, end-to-end 1/1). next build pass.</t>
+          <t>bff6e25, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 597 passed / 41 skipped; stack 41/41).</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>40% = DONE 21 / (total 60 - LATER 7). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>32% = DONE 23 / (total 79 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 21, IN PROGRESS 0, NOT STARTED 4, BLOCKED 20, OWNER ACTION 8, LATER 7 (total 60)</t>
+          <t>DONE 23, IN PROGRESS 1, NOT STARTED 15, BLOCKED 19, OWNER ACTION 13, LATER 8 (total 79)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 12, NOT NEEDED 8, NOT CHECKED 39</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 20, NOT NEEDED 9, NOT CHECKED 49</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>A04, A05, B01</t>
+          <t>A04, A05, B01, E01, H05, H06</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2361,7 +2361,11 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04: E01 (no synthetic catalogue), H05 (under-18 support tool) and H06 (final consent copy) are deploy blockers.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2994,32 +2998,32 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Dev/prod separation</t>
+          <t>SkinState contract version: engine_build and client-asserted fields</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
+          <t>New contract version (skinstate-2) that maps engine_build, and names captureMethod, persistAttempt and captureQuality as client-asserted, with the bound (a forged captureMethod can only merge two capture paths). Also: provenance.processingConsentVersion is still null in skinstate-1.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3029,11 +3033,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>A07, A12, A13</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>D-23 / D-26 (O-1 A)</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -3041,107 +3053,95 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
+          <t>docs/architecture/SKIN_STATE_CONTRACT_FINAL.md, lib/skin-state.ts</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>ff08107 (unmerged)</t>
-        </is>
-      </c>
+          <t>Owner-approved contract text + commit + tests</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
+          <t>Not started (owner: do not do now).</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
+          <t>A new contract version needs owner approval (D-23).</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Agent part done in B07 (local stack, no production keys; next dev refuses production values). Owner: remove FIREBASE_PRIVATE_KEY, FIREBASE_CLIENT_EMAIL and S3_SKIN_IMAGES_* from .env.local and the Desktop adminsdk JSON, then rotate the Admin key.</t>
+          <t>Draft skinstate-2 for owner approval; C02 stays blocked until it lands.</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 4 (main 1, 2) and section 5 (D-26 amendment).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Server-authoritative analysis writes</t>
+          <t>Architecture docs alignment after the lane merges</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Browser is not authoritative for analysis-derived scores.</t>
+          <t>LONGITUDINAL_METHOD section 3 and the capture brief (quality-gate steps 2 and 5 unmet until a server producer exists); RECOMMENDATION_MODEL sections 3 and 8, DATA_MODEL Events row, SYSTEM_MODEL C16, B14, IMPLEMENTATION_MAP C8 (lib/catalog/ folder, R-1 A, R-6 A); docs/lanes/routine.md (owned files, line 23 "allow create" -&gt; R-6 A); SKIN_STATE_CONTRACT_FINAL.md:269 (processing consent now versioned).</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>D-02 / D-26</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3149,103 +3149,91 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan, lib/skin-state*</t>
+          <t>docs/architecture/, docs/lanes/</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>6e9081d, 155cb69</t>
-        </is>
-      </c>
+          <t>Committed doc edits</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
+          <t>Edit the named sections; document task.</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>TRUSTED MEASUREMENT</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 4 (main 3); routine report rows T2, T4, T5; verifier 2026-10-04.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Echo authentication and ownership</t>
+          <t>Lint coverage of tests/</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Echo derives identity/context server-side and verifies ownership.</t>
+          <t>npm run lint does not lint tests/. npx next lint --dir tests still reports one error: tests/privacy-erase.test.ts:18 unused "_".</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Gate 02 / D-26</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3253,48 +3241,40 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-check/chat</t>
+          <t>tests/, package.json lint script</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + live E2E</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>skin-check-chat-auth tests (13); cross-user 409</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>155cb69, 955c1cc</t>
-        </is>
-      </c>
+          <t>Commit + lint output</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
+          <t>Not started. Found 2026-10-04 while fixing tests/api-chat-auth.test.ts (73d85cf).</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; verify live in I01.</t>
+          <t>Fix the one error; decide whether npm run lint should cover tests/.</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>TRUSTED MEASUREMENT</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr"/>
@@ -3302,7 +3282,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3317,22 +3297,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Gemini browser-state isolation</t>
+          <t>Dev/prod separation</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Gemini never trusts browser-supplied scores/context.</t>
+          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3340,60 +3320,56 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Gate 02 / D-26</t>
-        </is>
-      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
+          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + live E2E</t>
+          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
+          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>ff08107 (unmerged)</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr"/>
+          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
+        </is>
+      </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; verify live in I01.</t>
+          <t>Agent part done in B07 (local stack, no production keys; next dev refuses production values). Owner: remove FIREBASE_PRIVATE_KEY, FIREBASE_CLIENT_EMAIL and S3_SKIN_IMAGES_* from .env.local and the Desktop adminsdk JSON, then rotate the Admin key.</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3406,7 +3382,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>B07</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -3421,12 +3397,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Local stack with no production keys</t>
+          <t>Server-authoritative analysis writes</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Firebase Auth + Firestore emulators with the real rules, local engine 0.1.6, S3Mock, Gemini dev key or test fake, seed data, dev guard, one start and one test command.</t>
+          <t>Browser is not authoritative for analysis-derived scores.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3444,8 +3420,16 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>D-02 / D-26</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3458,38 +3442,38 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>scripts/local-stack*.sh, scripts/seed-local.ts, .env.development.example, lib/dev-env-guard.cjs, lib/gemini-key.ts, lib/firebase/{client,admin}.ts, lib/s3.ts, next.config.js</t>
+          <t>app/api/skin-scan, lib/skin-state*</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + end-to-end run</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>npm run test:local: unit 242 passed / 25 skipped, rules 24/24, end-to-end 1/1 (seeded phone user signs in via Auth emulator, upload to S3Mock, scan via local 0.1.6 engine, scanAnalyses + skinChecks saved in emulator); also green at PORT_BASE=3200. next dev with only .env.local refuses to start (7 variables named). typecheck 0, lint clean.</t>
+          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9ea6ad5, 6758fe6, 0fc1e57</t>
+          <t>6e9081d, 155cb69</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Local only. No UI click-through: the end-to-end test drives the real dev server through its HTTP API and the client SDK.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Owner: fill GEMINI_DEV_API_KEY in .env.development.local when a separate dev key exists.</t>
+          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3497,16 +3481,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Plain npm run dev with today's .env.local now refuses to start; use npm run dev:local.</t>
-        </is>
-      </c>
+      <c r="V25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3521,38 +3501,42 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Vercel Preview holds production secrets</t>
+          <t>Echo authentication and ownership</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Vercel env Preview scope has production SKIN_SCAN_API_URL, SCAN_API_SECRET, GEMINI_API_KEY (names from vercel env ls, 2026-10-03). Any pushed branch (lane/*, longitudinal-platform) gets a preview that calls the production engine and Gemini.</t>
+          <t>Echo derives identity/context server-side and verifies ownership.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>Gate 02 / D-26</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3562,38 +3546,38 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Vercel project skin-check env (Preview)</t>
+          <t>app/api/skin-check/chat</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>vercel env ls showing Preview without production secrets, or a decision to keep them</t>
+          <t>Commit + tests + live E2E</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>vercel env ls (names and targets only)</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr"/>
+          <t>skin-check-chat-auth tests (13); cross-user 409</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>Changing Vercel env is the owner's action.</t>
-        </is>
-      </c>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Owner: remove the Preview copies of SCAN_API_SECRET, SKIN_SCAN_API_URL and GEMINI_API_KEY (or use separate preview values); until then do not push lane/* branches.</t>
+          <t>Deploy via A13; verify live in I01.</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3601,16 +3585,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Found while preparing lanes.</t>
-        </is>
-      </c>
+      <c r="V26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -3625,12 +3605,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss npx firebase form</t>
+          <t>Gemini browser-state isolation</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
+          <t>Gemini never trusts browser-supplied scores/context.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3645,11 +3625,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02 / D-26</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3657,39 +3645,43 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json</t>
+          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules</t>
+          <t>Commit + tests + live E2E</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
+          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>ae457a0, 44e0352</t>
+          <t>155cb69, 955c1cc</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>Deploy via A13; verify live in I01.</t>
+        </is>
+      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3697,16 +3689,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
-        </is>
-      </c>
+      <c r="V27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3721,12 +3709,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss other production-changing commands</t>
+          <t>Local stack with no production keys</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
+          <t>Firebase Auth + Firestore emulators with the real rules, local engine 0.1.6, S3Mock, Gemini dev key or test fake, seed data, dev guard, one start and one test command.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3741,14 +3729,10 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>B05</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3757,36 +3741,40 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json</t>
+          <t>scripts/local-stack*.sh, scripts/seed-local.ts, .env.development.example, lib/dev-env-guard.cjs, lib/gemini-key.ts, lib/firebase/{client,admin}.ts, lib/s3.ts, next.config.js</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules + echo probe</t>
+          <t>Commit + tests + end-to-end run</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+          <t>npm run test:local: unit 242 passed / 25 skipped, rules 24/24, end-to-end 1/1 (seeded phone user signs in via Auth emulator, upload to S3Mock, scan via local 0.1.6 engine, scanAnalyses + skinChecks saved in emulator); also green at PORT_BASE=3200. next dev with only .env.local refuses to start (7 variables named). typecheck 0, lint clean.</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2371f78</t>
+          <t>9ea6ad5, 6758fe6, 0fc1e57</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
+          <t>Local only. No UI click-through: the end-to-end test drives the real dev server through its HTTP API and the client SDK.</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>Owner: fill GEMINI_DEV_API_KEY in .env.development.local when a separate dev key exists.</t>
+        </is>
+      </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
           <t>PRIVACY/SAFETY</t>
@@ -3799,39 +3787,39 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+          <t>Plain npm run dev with today's .env.local now refuses to start; use npm run dev:local.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Guided capture quality gate</t>
+          <t>Vercel Preview holds production secrets</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
+          <t>Vercel env Preview scope has production SKIN_SCAN_API_URL, SCAN_API_SECRET, GEMINI_API_KEY (names from vercel env ls, 2026-10-03). Any pushed branch (lane/*, longitudinal-platform) gets a preview that calls the production engine and Gemini.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3845,43 +3833,55 @@
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>D-26</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check capture step</t>
+          <t>Vercel project skin-check env (Preview)</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Design doc + approved gate + tests</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr"/>
+          <t>vercel env ls showing Preview without production secrets, or a decision to keep them</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>vercel env ls (names and targets only)</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Changing Vercel env is the owner's action.</t>
+        </is>
+      </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Write design gate: checks, thresholds, retake UX; exposure first (dominant Phase 0 risk). Lane: capture (branch lane/capture, brief docs/lanes/capture.md); results come via docs/lanes/capture-report.md at merge.</t>
+          <t>Owner: remove the Preview copies of SCAN_API_SECRET, SKIN_SCAN_API_URL and GEMINI_API_KEY (or use separate preview values); until then do not push lane/* branches.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3889,37 +3889,41 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Found while preparing lanes.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Per-region / per-metric comparability</t>
+          <t>Rate-limit store and per-route buckets</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Decide whether two scans are comparable before computing change.</t>
+          <t>Routine writes are capped in memory per instance (200/uid/day); account routes share the scan bucket (5/min/IP); ledger appends per purpose are not capped (latestGrant reads all ai_share entries; fails closed).</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3929,19 +3933,11 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>A07, A12, A13, C07</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3949,72 +3945,72 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-state*</t>
+          <t>lib/rate-limit.ts, app/api/routine/events, app/api/account/*</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Comparability function + tests + noise inputs</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Not started. engine.build is null in all records until 0.1.6 + gate 04 are deployed.</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>engine.build not populated (A12, A13); D-26 owner decision on client-asserted captureMethod; per-metric thresholds need C07.</t>
-        </is>
-      </c>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Owner decides D-26; implement key-based comparability after A12/A13; noise thresholds after C07. Lane: capture (branch lane/capture, brief docs/lanes/capture.md); results come via docs/lanes/capture-report.md at merge.</t>
+          <t>Move limits to a shared store if a hard global cap is needed; give account routes their own bucket; cap ledger appends per purpose.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by routine report T3; privacy report T11.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Human measurement validation protocol</t>
+          <t>Deny rules miss npx firebase form</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Protocol for human validation and repeatability.</t>
+          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4024,20 +4020,16 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>D-24 (uncommitted)</t>
-        </is>
-      </c>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4045,43 +4037,39 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Committed protocol</t>
+          <t>Commit with added rules</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>59d9923</t>
+          <t>ae457a0, 44e0352</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
-        </is>
-      </c>
+      <c r="S31" s="2" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4089,52 +4077,56 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Human validation pilot</t>
+          <t>Deny rules miss other production-changing commands</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Run pilot of C03 protocol.</t>
+          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>C03, A12, A13, H01</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -4145,39 +4137,39 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Pre-registration + pilot dataset + report</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
+          <t>Commit with added rules + echo probe</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2371f78</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
-        </is>
-      </c>
+          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4185,12 +4177,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -4205,35 +4201,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Full test-retest / calibration</t>
+          <t>Guided capture quality gate</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
+          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>C04</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Capture design (O-1..O-5, Q-1, Q-2; TD-05, TD-06)</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4241,30 +4237,38 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>lib/capture-quality/, components/skin-check/inputs/PhotoCapture.tsx, app/api/skin-scan/route.ts, lib/scan-retry.ts, SkinCheckDashboard.tsx</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Pre-registered study report</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
+          <t>Design doc + approved gate + tests</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane capture, merged 2970c86): exposure, blur (per capture path), resolution checks on the exact blob sent to the engine; gate verdict pass/retake/unchecked/override; soft block with override after 2 retakes (O-4 B); engine refusal codes become named retake reasons (O-5 A); captureQuality saved on scanAnalyses as client-asserted, schemaVersion 1 (O-2 A), never used for comparability (Q-2). Dashboard (capture requests 1 and 2, 102aeaa): a refused photo shows "Retake photo" (new scan) and no retry of the same photo; the retry carries captureQuality and keeps quality. Tests: capture-* (settings, exposure, blur, resolution, gate, retake, api-code, persist), scan-retry, capture.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier (fresh, 2026-10-04): capture PASS.</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>88a7505, da6ebfb, e45dcab, 3acb41d, 1f053cf, d29253a, 747df17, 9ec59f3; merge 2970c86; 102aeaa</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Waits on C04 pilot.</t>
-        </is>
-      </c>
+          <t>Local only; not deployed (TD-04). Thresholds provisional (cq-settings-0-provisional). Gate result is client-asserted.</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Size from pilot variance.</t>
+          <t>Open: pose, expression, distance and framing are not measured (O-3 C, no landmark library; they report not_measured) -&gt; C08. Thresholds from the R05 real-device sweep -&gt; C09. Deploy with A13.</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
@@ -4274,15 +4278,19 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Report: docs/lanes/capture-report.md.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4297,12 +4305,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tone-stratified validation / model card</t>
+          <t>Per-region / per-metric comparability</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
+          <t>Decide whether two scans are comparable before computing change.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4312,7 +4320,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4322,10 +4330,14 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+          <t>A07, A12, A13, A20, C07</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>D-13 / D-26 (O-1 A, TD-05)</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4336,45 +4348,61 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>lib/comparability.ts</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Per-band results + model card</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
+          <t>Comparability function + tests + noise inputs</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane capture, merged 2970c86): comparabilityKey, compareKeys, compareStates. Output comparable / not_comparable with named reasons in a fixed order; no numbers, percentages or direction. Fails closed: COMPARABLE_QUANTITIES is empty, and skinstate-1 maps engine.build to null, so every real pair is not_comparable (quantity_not_validated, engine_build_unknown). captureMethod stays in the key, marked client-asserted (O-1 A). Tests: comparability, comparability-wording, capture.e2e (seed is never comparable). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>afb7fe2, 94512b7; merge 2970c86</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Local only. Cannot say comparable on real data yet.</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05 data.</t>
+          <t>A new SkinState contract version that maps engine_build (A20); per-quantity validation needs C05-C07.</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Define model card template alongside C05.</t>
+          <t>A20 (contract version), then fill COMPARABLE_QUANTITIES from C07.</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Q-2: the browser quality result never feeds comparability; quality enters only via a server producer (C08).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -4389,22 +4417,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Validated measurement/noise tables</t>
+          <t>Human measurement validation protocol</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
+          <t>Protocol for human validation and repeatability.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4412,12 +4440,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>C05, C06</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>D-24 (uncommitted)</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4428,27 +4456,35 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Versioned noise table tied to engine build</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
+          <t>Committed protocol</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>59d9923</t>
+        </is>
+      </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>Waits on C05/C06.</t>
-        </is>
-      </c>
+          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Fix table schema (field x region x band x engine build).</t>
+          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4461,36 +4497,32 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
-        </is>
-      </c>
+      <c r="V35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Baseline window definition</t>
+          <t>Human validation pilot</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>How a user's baseline is formed.</t>
+          <t>Run pilot of C03 protocol.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4505,12 +4537,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C03, A12, A13, H01</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -4524,10 +4556,14 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Method doc + decision</t>
+          <t>Pre-registration + pilot dataset + report</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -4539,17 +4575,17 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>Needs between-day noise (C07).</t>
+          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
+          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4562,27 +4598,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Change-vs-noise engine</t>
+          <t>Full test-retest / calibration</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
+          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4602,14 +4638,10 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>C02, C07, D01</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>D-13 / D-24</t>
-        </is>
-      </c>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4617,13 +4649,13 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Engine + tests + noise table version</t>
+          <t>Pre-registered study report</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
@@ -4635,17 +4667,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Needs comparability (C02) and validated noise (C07).</t>
+          <t>Waits on C04 pilot.</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Wait; design pairwise interface first (D-13).</t>
+          <t>Size from pilot variance.</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4658,27 +4690,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Persistence/evidence tiers</t>
+          <t>Tone-stratified validation / model card</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Separate transient observations from persistent patterns.</t>
+          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4693,12 +4725,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -4715,7 +4747,7 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Tier definitions + tests</t>
+          <t>Per-band results + model card</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
@@ -4727,17 +4759,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Needs D02.</t>
+          <t>Waits on C05 data.</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Wait on D02.</t>
+          <t>Define model card template alongside C05.</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4745,41 +4777,37 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
-        </is>
-      </c>
+      <c r="V38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Scheduled anchor scans / irregular sampling</t>
+          <t>Validated measurement/noise tables</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Sampling strategy.</t>
+          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4789,12 +4817,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C05, C06</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -4803,21 +4831,37 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Versioned noise table tied to engine build</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Waits on C05/C06.</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Revisit after D02.</t>
+          <t>Fix table schema (field x region x band x engine build).</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4825,37 +4869,41 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Engine-version re-baselining</t>
+          <t>Server-side capture quality from engine landmarks</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Handle engine build changes across history.</t>
+          <t>Derive pose, distance (face scale) and framing on the server from the engine's mediapipe face landmarks, as a separately versioned quality producer. The only route by which quality can enter comparability (Q-2).</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4865,73 +4913,101 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>D-18 (engine work)</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>CV/ML Engineer</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>skin-scan engine; app/api/skin-scan</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Owner approval under D-18 + design + tests</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>Not started (owner: do not do now).</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Engine work needs owner approval (D-18).</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Revisit at first engine change after D02.</t>
+          <t>Write a design for owner approval.</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 5 (O-3 C follow-up).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Product catalog normalization</t>
+          <t>Capture thresholds from the R05 sweep</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
+          <t>Replace the provisional capture-quality settings (lib/capture-quality/settings.ts) with values from the R05 real-device sweep; bump settingsVersion.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4941,29 +5017,33 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>D-08 / D-09</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>lib/capture-quality/settings.ts</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Owner-supplied master data + versioned schema</t>
+          <t>Sweep results + commit + tests</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
@@ -4975,50 +5055,54 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Product master data and claims must come from the owner; D-09 OPEN-R1 (do product cards return).</t>
+          <t>Needs the R05 real-device data.</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Owner supplies catalog data and decides OPEN-R1. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
+          <t>After R05: set values, bump settingsVersion.</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 5.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Product eligibility / safety rules</t>
+          <t>Baseline window definition</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Deterministic, versioned eligibility + safety constraints.</t>
+          <t>How a user's baseline is formed.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5038,14 +5122,10 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>E01, E05</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>D-08</t>
-        </is>
-      </c>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5053,13 +5133,13 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Pure function + version constant + tests</t>
+          <t>Method doc + decision</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
@@ -5071,17 +5151,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+          <t>Needs between-day noise (C07).</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Wait on E01.</t>
+          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5094,32 +5174,32 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Routine model + event history</t>
+          <t>Change-vs-noise engine</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
+          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5129,15 +5209,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr"/>
+          <t>C02, C07, D01</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>D-13 / D-24</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5151,7 +5235,7 @@
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Data model doc + approved gate + tests</t>
+          <t>Engine + tests + noise table version</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
@@ -5161,15 +5245,19 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Needs comparability (C02) and validated noise (C07).</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Design data model on branch; no production writes before A04. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
+          <t>Wait; design pairwise interface first (D-13).</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5177,36 +5265,32 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>A04 dependency applies to deployment only.</t>
-        </is>
-      </c>
+      <c r="V43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Adherence summary</t>
+          <t>Persistence/evidence tiers</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
+          <t>Separate transient observations from persistent patterns.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5221,12 +5305,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5237,13 +5321,13 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Function + tests</t>
+          <t>Tier definitions + tests</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
@@ -5255,17 +5339,17 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Needs E03.</t>
+          <t>Needs D02.</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Wait on E03. Lane: routine (branch lane/routine, brief docs/lanes/routine.md); results come via docs/lanes/routine-report.md at merge.</t>
+          <t>Wait on D02.</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5273,37 +5357,41 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Red-flag triage interlock</t>
+          <t>Scheduled anchor scans / irregular sampling</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Safety layer overrides cosmetic recommendations.</t>
+          <t>Sampling strategy.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5313,51 +5401,35 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
-        </is>
-      </c>
+      <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
-        </is>
-      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
+          <t>Revisit after D02.</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5370,32 +5442,32 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Engine-version re-baselining</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>Handle engine build changes across history.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5405,59 +5477,35 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>A08, D02, E03, E04, E05</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Gemini/Context Engineer</t>
-        </is>
-      </c>
+      <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>Pure builder + tests</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
-        </is>
-      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
-        </is>
-      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Wait; may define schema with null sections earlier if approved.</t>
+          <t>Revisit at first engine change after D02.</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5470,37 +5518,37 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Product catalog normalization</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5508,97 +5556,97 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
+      <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08 / D-09 / D-12 (TD-07)</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>lib/gemini.ts</t>
+          <t>lib/catalog/</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
+          <t>Owner-supplied master data + versioned schema</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr"/>
+          <t>Built (lane routine, merged daa0b4a): versioned catalogue schema, synthetic sample, owner template lib/catalog/catalogue-template.csv with a drift check, D-12 word check with the exact-name exception (PRODUCT_NAME_EXCEPTIONS). Tests: catalog-schema (20). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>e45da38; merge daa0b4a</t>
+        </is>
+      </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>Schema renderer not built.</t>
+          <t>Schema only; data is synthetic (R-3 A).</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Needs F01.</t>
+          <t>Owner catalogue data. Deploy blocker (routine T1): the deploy is blocked while any product has dataSource "synthetic".</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Wait on F01.</t>
+          <t>Owner fills lib/catalog/catalogue-template.csv (fields: routine-report.md section 6), including "Clear Seal" as an owner row; then replace the synthetic CATALOGUE. OPEN-R1 answered by R-2 B (no product cards for now).</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Seed status PARTIALLY READY.</t>
+          <t>Proposed D-12 clarification (registered own-brand name is not by itself a claim) recorded in TD-07.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Product eligibility / safety rules</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>Deterministic, versioned eligibility + safety constraints.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -5618,12 +5666,12 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>E01, E05</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>D-14 / D-12</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -5633,13 +5681,13 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
+          <t>Pure function + version constant + tests</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr"/>
@@ -5651,17 +5699,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Needs F02 output schema.</t>
+          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Wait on F02.</t>
+          <t>Wait on E01.</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5674,37 +5722,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Routine model + event history</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5712,10 +5760,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>D-14 (store rejected for now)</t>
+          <t>R-1..R-6 (TD-07)</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -5725,88 +5777,100 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>lib/routine/, app/api/routine/events, components/routine, app/(marketing)/routine, firestore.rules lane:routine</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
+          <t>Data model doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr"/>
+          <t>Built (lane routine, merged daa0b4a): event schemas and currentRoutine(); GET/POST /api/routine/events (uid from the verified token only, strict schemas, idempotent eventIds, 4 KB body cap, 200 writes/uid/day); server-written events, owner read-only rules, collection-group denied; /routine page (own record only, no skin data, no claims). Follow-ups: purpose text moved to lib/consent.ts (7662ed7); root site description neutral (90c30a1, routine T6); erasure covers routineEvents (2f00819). Tests: routine-events, routine-copy, routine-route, firestore-rules-routine, routine.e2e, layout-description. Security review: no cross-user path. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier: routine PASS.</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>e9331f3, 6f8c22c, 0f56ea6, ac275fa, 0e37830, e08aa89, 779e967; merge daa0b4a; 7662ed7, 90c30a1, 2f00819</t>
+        </is>
+      </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Local only; not deployed (A04, A13). Signed-in /routine page not clicked through in a browser.</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr"/>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
+          <t>Browser click-through (E06). Doc alignment (A21). Rate-limit store (B09). Deploy with A13 after A04.</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>A04 dependency applies to deployment only.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>Adherence summary</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>A13, C02, D02</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -5817,40 +5881,48 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>Product/Routine Rules Engineer</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>lib/routine/adherence.ts</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="inlineStr"/>
+          <t>Function + tests</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>adherence(): used / skipped / unknown, counts only; a day with no log is unknown, never skipped. GET /api/routine/events?tz= returns the 7-day summary. Tests: routine-adherence (13), routine.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>0e4bf16; merge daa0b4a</t>
+        </is>
+      </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
-        </is>
-      </c>
+          <t>Local only.</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>None for the function. Deploy with E03.</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
@@ -5858,32 +5930,32 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Red-flag triage interlock</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>Safety layer overrides cosmetic recommendations.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5893,33 +5965,29 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>E03, G01</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>D-12 (LOCKED)</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
+          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr"/>
@@ -5931,17 +5999,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Needs E03 and G01.</t>
+          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -5949,37 +6017,41 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 (privacy T12): also review EXTRA_CAUTION_TRIGGERS and the caution sentence; decide whether the residual pregnancy inference is acceptable or drop the flag or trigger.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Routine page browser click-through</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Signed-in click-through of /routine on the local stack (read, add, stop, swap, log).</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -5989,19 +6061,15 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>D-16 / D-17</t>
-        </is>
-      </c>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6009,77 +6077,77 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>components/routine, app/(marketing)/routine</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle, no bucket policy; uploader is PutObject-only</t>
-        </is>
-      </c>
+          <t>Recorded local click-through</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>D-17 still blocked on IAM: no principal can list/delete originals. Versioning/Object Lock question answered (neither enabled). Retention (no lifecycle) undecided.</t>
-        </is>
-      </c>
+          <t>Not started. The API flow is covered by routine.e2e.</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Owner approves a separate erasure principal (ListBucket prefix + DeleteObject on users/*); decide retention. Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
+          <t>Run npm run dev:local and click through as a seeded user.</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by routine report T7.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6092,10 +6160,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>A08, D02, E03, E04, E05</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -6105,31 +6177,39 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr"/>
+          <t>Pure builder + tests</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
+        </is>
+      </c>
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>Not started; 18+ check is client-only today.</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
+        </is>
+      </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>Write gate brief for D-19. Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
+          <t>Wait; may define schema with null sections earlier if approved.</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6142,32 +6222,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6177,51 +6257,63 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>Gemini/Context Engineer</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr"/>
+          <t>Schema + renderer + tests</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+        </is>
+      </c>
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Schema renderer not built.</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Owner must state which Google project and tier own the production Gemini key (paid tier is a D-14 release gate).</t>
+          <t>Needs F01.</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1; reviewer inventories prompt fields (name, onboarding answers). Lane: privacy (branch lane/privacy, brief docs/lanes/privacy.md); results come via docs/lanes/privacy-report.md at merge.</t>
+          <t>Wait on F01.</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6229,32 +6321,36 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Seed status PARTIALLY READY.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6269,15 +6365,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr"/>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>D-14 / D-12</t>
+        </is>
+      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6285,13 +6385,13 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Validator + adversarial tests</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr"/>
@@ -6303,17 +6403,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Nothing longitudinal is deployed yet.</t>
+          <t>Needs F02 output schema.</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Wait on F02.</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6326,32 +6426,32 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6361,15 +6461,15 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>I01, F03, E05</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>D-14 (store rejected for now)</t>
+        </is>
+      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6377,35 +6477,35 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
+        </is>
+      </c>
       <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
-        </is>
-      </c>
+      <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6418,32 +6518,32 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6453,31 +6553,51 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Approved design + tests + E2E</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr"/>
       <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6490,32 +6610,32 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6525,31 +6645,55 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>E03, G01</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>D-12 (LOCKED)</t>
+        </is>
+      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Design reviewed against D-12</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr"/>
       <c r="P58" s="2" t="inlineStr"/>
-      <c r="Q58" s="2" t="inlineStr"/>
-      <c r="R58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Needs E03 and G01.</t>
+        </is>
+      </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6562,222 +6706,2074 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / D-17 (TD-08, TD-10)</t>
+        </is>
+      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr"/>
-      <c r="P59" s="2" t="inlineStr"/>
-      <c r="Q59" s="2" t="inlineStr"/>
-      <c r="R59" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Ledger + erasure route + tests + live verification</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
+        </is>
+      </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>D-19 (TD-08, TD-11, TD-12)</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Gate + tests</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky.</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Owner confirms the under-18 device marker effects A and B (TD-11, PENDING). Support tool to clear a wrong under-18 record (H05) must exist before the final deploy.</t>
+        </is>
+      </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Owner answers TD-11. Build H05. Cross-route test H07. Later: REQUIRE_AGE_ATTESTATION true (H10).</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>In-region prompt/data audit</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>OWNER ACTION</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>CHECKED LOCAL</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Field inventory + key ownership/tier + consent copy</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>H04</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Block writes after an account is erased</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>D-17</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Design + commit + tests</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>Not started (owner: do not do now).</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Needs a rules change outside the privacy lane.</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T3; widened to the routine route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>H05</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Support tool to clear a mistaken under-18 record</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>D-19 (decision 4)</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Design + commit + tests + audit trail</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>Not started (owner: do not do now).</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>Must exist before the final deploy (A13 depends on it).</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T17. Deploy blocker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>H06</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Final consent copy (AI share and processing)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>OWNER ACTION</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / decision 6, 7a</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>lib/consent.ts</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Owner/legal copy + version bump + tests updated on purpose</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Owner or legal supplies both sentences; G1 answered.</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Cross-route under-18 test</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>tests/</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Commit + test result</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>Write the test against the merged routes.</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>H08</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Gemini field scope: self-reported dryness and gender inference</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>OWNER ACTION</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Decision 8</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>lib/skin-check-format.ts</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision (+ commit if changed)</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision.</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T8, T9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>H09</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Required Gemini allowlist parameter</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Gemini/Context Engineer</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Commit + tests</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>Make the parameter required.</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>GEMINI CONTEXT LAYER</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Require age attestation on upload and scan</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Decision 3a</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Commit + tests</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>Later.</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>After old bundles are gone.</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Engine stores no image</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>CV/ML Engineer</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>skin-scan engine</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Code read + runtime check</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>Read-only check of the engine source and the container.</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>H12</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>DOM test renderer</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>OWNER ACTION</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>README rule 6</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>package.json, tests/</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Owner approval + commit</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>New dependency needs approval.</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>Owner approves or declines.</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>H13</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Processing consent after a draft restore</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / D-03a</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Decision + commit + tests</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>Owner decides whether restored drafts may carry the consent version.</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Withdraw AI-share consent in the UI</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Design check + commit + tests</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>Check the design, then add a withdraw control.</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>Security review 2026-10-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>H15</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Low-severity hardening from the security review</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Commit + tests</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>Add isPlainUid to the upload key path; log name and code only.</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>Security review 2026-10-04 (pre-existing logging).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Release Validation</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end production evaluation</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>A12, A13, B01, H01, H03</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>QA/Test Engineer</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Recorded E2E run against prod</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>Nothing longitudinal is deployed yet.</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>Write E2E script while A13 is pending.</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Release Validation</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Full red-team sweep</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>Wait.</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>RED TEAM</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>J01</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Population priors / mixed effects</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>ML recommendation ranking</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>J03</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Indian cross-user benchmark</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
           <t>J05</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Later / Research-dependent</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>True digital twin</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Not in core release.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>NOT CHECKED</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr"/>
-      <c r="S61" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr">
         <is>
           <t>Do not start without evidence and explicit approval.</t>
         </is>
       </c>
-      <c r="T61" s="2" t="inlineStr">
+      <c r="T80" s="2" t="inlineStr">
         <is>
           <t>RELEASE</t>
         </is>
       </c>
-      <c r="U61" s="2" t="inlineStr">
+      <c r="U80" s="2" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V61" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8744,7 +10740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9370,7 +11366,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>TD-05</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -9380,42 +11376,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Native L*/a* are provisional research candidates only</t>
+          <t>Capture O-1 A: captureMethod stays in the comparability key, marked client-asserted</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 screening</t>
+          <t>D-26 open item; capture design part 0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Keep b*, ITA, lbpEntropy</t>
+          <t>Remove it from the key</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Primary endpoints for the human study only; not validated measurements</t>
+          <t>Keep it, marked client-asserted; contract amendment names the client-asserted fields</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Only survivors of screening</t>
+          <t>Owner decision (changes D-26)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
+          <t>8ee4372, 94512b7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>C03-C07</t>
+          <t>C02, A20</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Owner may reverse before Phase 1 pre-registration</t>
+          <t>New contract version (A20)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -9425,247 +11421,247 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>ACCEPTED for study design</t>
+          <t>DECIDED (owner). Tracker-local until A14.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>D-13 / D-24</t>
+          <t>TD-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Capture O-2 A, O-3 C, O-4 B, O-5 A, Q-1, Q-2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Capture design part 0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>See capture-design.md part 0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>O-2: save the gate result on scanAnalyses, client-asserted, schemaVersion 1. O-3: no landmark library (C08 follow-up). O-4: soft block. O-5: lib/api.ts passes the server error code through. Q-1: follow the frozen contract, no caveats tier. Q-2: the browser quality result never feeds comparability</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8ee4372</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>C01, C02, C08</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Longitudinal comparisons require comparability + noise/evidence</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Naive % change misleads</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Research-doc point ladder</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Measurement noise unknown</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>DECISION_LOG D-13; D-24 uncommitted</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>C02, D02, G01</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (D-24 uncommitted)</t>
+          <t>DECIDED (owner).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>TD-07</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Recommender deterministic and versioned</t>
+          <t>Routine R-1 A, R-2 B, R-3 A, R-4 A, R-5 B, R-6 A, product-name exception</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4 SKUs, ~6 rules</t>
+          <t>Routine design section 0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>DMN/rules engine; ML ranking</t>
+          <t>See routine-design.md section 0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Plain TS pure function + version constants</t>
+          <t>R-1: own-record purpose only (supersedes B14 for this record). R-2: no product cards now. R-3: synthetic sample until owner data. R-4: no skin data, no claims on /routine. R-5: catalogue plus one "other product". R-6: server writes events (replaces client-written events). Exact-name exception recorded as a proposed D-12 clarification, not a change</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Auditable</t>
+          <t>Owner decision</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-08</t>
+          <t>5b058e0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>E02, J02</t>
+          <t>E01, E03, E04, A21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>&gt;20 SKUs or non-engineer rule authors</t>
+          <t>D-12 is LOCKED: the clarification needs the owner to record it in DECISION_LOG</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DECIDED (owner); D-12 clarification PROPOSED.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>TD-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Gemini is explanation layer, not authority</t>
+          <t>Privacy decisions 2-12</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Gemini hallucination/claims risk</t>
+          <t>Privacy design section 0</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Gemini owns context</t>
+          <t>See privacy-design.md section 0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+          <t>2a D-19 all parts; 3a degrade now, refuse later, under-18 refused from day one; 4a sticky; 5 not decided (retention); 6 owner checking G1 (step 13 local only); 7b DRAFT copy for building; 8a remove female_skin_context, gender, Dryness band, plus extraCaution; 9b receipt with no uid; 10a blank re-confirm with last-time hint; 11a separate erase principal, production only; 12 R1 and R6 approved, R2 one-time admin.ts add-only edit</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Owner decision</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-14; GATE_02</t>
+          <t>ab7eed7</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>B04, F01-F04</t>
+          <t>H01, H02, H03, H06, H08, H10</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 and 6 still open</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (paid tier is release gate)</t>
+          <t>DECIDED (owner) except 5 and 6.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>TD-09</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>R-A: merge lane/privacy-held with add-only test blocks</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Held gates break three unowned tests</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Ship without the held gates (Echo ungated)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Merge both branches; one add-only vi.mock block in each of three tests; no check removed or weakened</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Owner instruction for the merge task</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>bdc462f; block 2 completed for step 14 in bff6e25 (add-only)</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>H02, H03</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>No attribution/efficacy/forecasting</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>CLAUDE.md</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Evidence tiers 3-4</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Prohibited in UI, Gemini, analytics</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>CLAUDE.md</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>DECISION_LOG D-12</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>G02, J04, R08</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Explicit owner approval</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -9673,14 +11669,14 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>DECIDED (owner).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>TD-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9690,42 +11686,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Client input never authoritative for measured state</t>
+          <t>Account deletion also removes the under-18 record</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Gate 02</t>
+          <t>Privacy T7: erasure resets the sticky under-18 state (D-17 vs decision 4)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Rules tightening; server chat storage</t>
+          <t>Keep a uid-free marker after erase</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Path-structural trust; authenticated Echo</t>
+          <t>Remove it with the account, and clear the tab marker</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Forgeable browser state</t>
+          <t>Owner instruction for the merge task (follow-up 2)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>bc45a01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>A09, B02-B04, C02</t>
+          <t>H01, H02</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Open: client-asserted captureMethod/persistAttempt</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -9735,67 +11731,563 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED (branch); owner decision open</t>
+          <t>DECIDED (owner). Effect: a recorded minor can erase and start a new account.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>TD-11</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Under-18 device marker effects A and B</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Privacy report section 1: lane addition after review</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>(A) in one tab the marker applies to the next account that signs in; a signed-in shared browser records "&lt;18" against that account (privacy T18). (B) an adult who confirms a mis-tap stays blocked until support clears it (H05)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Lane proposal</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>d46d6a5, f15c24a</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>H02, H05</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Owner rejects</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>PENDING owner confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TD-12</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Confirm an under-18 answer before it is recorded</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Sticky under-18 (decision 4) makes a mis-tap costly</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Record on first choice</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>"You chose under 18. Is that right?"; Yes records, No clears the answer</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Owner instruction for the merge task (follow-up 4)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>edc4451</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>DECIDED (owner).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>D-25</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Native L*/a* are provisional research candidates only</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Phase 0 screening</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Keep b*, ITA, lbpEntropy</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Primary endpoints for the human study only; not validated measurements</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Only survivors of screening</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>C03-C07</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Owner may reverse before Phase 1 pre-registration</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPTED for study design</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>D-13 / D-24</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Longitudinal comparisons require comparability + noise/evidence</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Naive % change misleads</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Research-doc point ladder</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Measurement noise unknown</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>DECISION_LOG D-13; D-24 uncommitted</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>C02, D02, G01</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>PROPOSED (D-24 uncommitted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Recommender deterministic and versioned</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>4 SKUs, ~6 rules</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>DMN/rules engine; ML ranking</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Plain TS pure function + version constants</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Auditable</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>DECISION_LOG D-08</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>E02, J02</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>&gt;20 SKUs or non-engineer rule authors</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Systems Architect</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Gemini is explanation layer, not authority</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Gemini hallucination/claims risk</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Gemini owns context</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>DECISION_LOG D-14; GATE_02</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>B04, F01-F04</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Systems Architect</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>PROPOSED (paid tier is release gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>No attribution/efficacy/forecasting</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Evidence tiers 3-4</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Prohibited in UI, Gemini, analytics</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>DECISION_LOG D-12</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>G02, J04, R08</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Explicit owner approval</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>D-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Client input never authoritative for measured state</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Rules tightening; server chat storage</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Path-structural trust; authenticated Echo</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Forgeable browser state</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>A09, B02-B04, C02</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Open: client-asserted captureMethod/persistAttempt</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (branch); owner decision open</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>D-21</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Gate 01 stores raw analysis in scanAnalyses</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Raw preservation</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>skinStates collection</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>users/{uid}/scanAnalyses/{scanId}_{sha16}</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Immutable raw substrate</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>6e9081d</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Systems Architect</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>IMPLEMENTED (not deployed); ID duplicated in HEAD</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>32% = DONE 23 / (total 79 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>33% = DONE 24 / (total 80 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 23, IN PROGRESS 1, NOT STARTED 15, BLOCKED 19, OWNER ACTION 13, LATER 8 (total 79)</t>
+          <t>DONE 24, IN PROGRESS 1, NOT STARTED 16, BLOCKED 19, OWNER ACTION 12, LATER 8 (total 80)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 20, NOT NEEDED 9, NOT CHECKED 49</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 20, NOT NEEDED 9, NOT CHECKED 50</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V80"/>
+  <dimension ref="A1:V81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6894,17 +6894,13 @@
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky.</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>Owner confirms the under-18 device marker effects A and B (TD-11, PENDING). Support tool to clear a wrong under-18 record (H05) must exist before the final deploy.</t>
-        </is>
-      </c>
+          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Owner answers TD-11. Build H05. Cross-route test H07. Later: REQUIRE_AGE_ATTESTATION true (H10).</t>
+          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
@@ -8230,32 +8226,32 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H16</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Consent ledger write slows the scan response</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8265,15 +8261,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8281,13 +8281,17 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>app/api/skin-scan/route.ts</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Commit + test + timing</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
@@ -8297,32 +8301,32 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R74" s="2" t="inlineStr">
-        <is>
-          <t>Nothing longitudinal is deployed yet.</t>
-        </is>
-      </c>
+      <c r="R74" s="2" t="inlineStr"/>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V74" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>Verifier observation 2026-10-04 (a52f36d).</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -8337,12 +8341,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -8362,7 +8366,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
+          <t>A12, A13, B01, H01, H03</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -8373,13 +8377,13 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Recorded E2E run against prod</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr"/>
@@ -8391,17 +8395,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>Nothing longitudinal is deployed yet.</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>RELEASE</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8414,32 +8418,32 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8449,31 +8453,51 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="2" t="inlineStr"/>
-      <c r="Q76" s="2" t="inlineStr"/>
-      <c r="R76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8486,7 +8510,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -8501,7 +8525,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -8558,7 +8582,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -8573,7 +8597,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>ML recommendation ranking</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -8630,7 +8654,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -8645,7 +8669,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Indian cross-user benchmark</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -8697,16 +8721,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V79" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -8721,7 +8741,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Forecasting</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -8773,7 +8793,83 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11763,7 +11859,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>(A) in one tab the marker applies to the next account that signs in; a signed-in shared browser records "&lt;18" against that account (privacy T18). (B) an adult who confirms a mis-tap stays blocked until support clears it (H05)</t>
+          <t>Owner confirmed 2026-10-04: both effects accepted</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11793,7 +11889,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>PENDING owner confirmation.</t>
+          <t>DECIDED (owner, 2026-10-04).</t>
         </is>
       </c>
     </row>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>bff6e25 (lanes capture, routine, privacy merged 2026-10-03/04, plus follow-ups); working tree still has uncommitted DECISION_LOG.md edits and untracked DATA_LOCALITY_DECISION.md from another session, left untouched (A14)</t>
+          <t>bbe02da (wave 1 merged; wave-2 shapes and lanes prepared 2026-10-04); working tree still has uncommitted DECISION_LOG.md edits and untracked DATA_LOCALITY_DECISION.md from another session, left untouched (A14)</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>33% = DONE 24 / (total 80 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>34% = DONE 25 / (total 82 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 24, IN PROGRESS 1, NOT STARTED 16, BLOCKED 19, OWNER ACTION 12, LATER 8 (total 80)</t>
+          <t>DONE 25, IN PROGRESS 1, NOT STARTED 16, BLOCKED 19, OWNER ACTION 13, LATER 8 (total 82)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 20, NOT NEEDED 9, NOT CHECKED 50</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 21, NOT NEEDED 9, NOT CHECKED 51</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2998,7 +2998,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -3013,22 +3013,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>SkinState contract version: engine_build and client-asserted fields</t>
+          <t>Prepare wave-2 lanes and shared shapes</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>New contract version (skinstate-2) that maps engine_build, and names captureMethod, persistAttempt and captureQuality as client-asserted, with the bound (a forged captureMethod can only merge two capture paths). Also: provenance.processingConsentVersion is still null in skinstate-1.</t>
+          <t>Shared type-only shapes in lib/contracts/ (TD-13); worktrees and branches for longitudinal (A20, D01-D03), rules (E02, E05) and context (F01-F04); file ownership, shared-file plan, ports, briefs, merge order.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3038,54 +3038,58 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>A07, A12, A13</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>D-23 / D-26 (O-1 A)</t>
+          <t>TD-13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>docs/architecture/SKIN_STATE_CONTRACT_FINAL.md, lib/skin-state.ts</t>
+          <t>lib/contracts/, tests/contracts.test.ts, docs/lanes/</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Owner-approved contract text + commit + tests</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+          <t>Committed shapes + test + briefs + worktrees</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>lib/contracts/{longitudinal-result,recommendation-result,safety-state,context-package}.ts; tests/contracts.test.ts (types pinned by npm run typecheck, runtime checks by vitest); docs/lanes/README.md, longitudinal.md, rules.md, context.md; worktrees ../skin-check-{longitudinal,rules,context} on lane/* with .env.lane PORT_BASE 3500/3600/3700. Verifier: three passes (FAIL 4 high + 10 medium; FAIL 1 high + new mediums; FAIL 3 medium + lows), every finding fixed; 19 forbidden states proven as type errors. typecheck, lint clean; npm run test:local exit 0 (unit 615 passed / 41 skipped, stack 41/41).</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>a8eb0c0, bbe02da</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>A new contract version needs owner approval (D-23).</t>
-        </is>
-      </c>
+          <t>No lane work started.</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Draft skinstate-2 for owner approval; C02 stays blocked until it lands.</t>
+          <t>Owner answers the per-lane items in docs/lanes/README.md and approves each design brief.</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>TRUSTED MEASUREMENT</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -3095,14 +3099,14 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Proposed by capture report section 4 (main 1, 2) and section 5 (D-26 amendment).</t>
+          <t>Lanes never edit the tracker or lib/contracts/.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3117,12 +3121,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Architecture docs alignment after the lane merges</t>
+          <t>SkinState contract version: engine_build and client-asserted fields</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL_METHOD section 3 and the capture brief (quality-gate steps 2 and 5 unmet until a server producer exists); RECOMMENDATION_MODEL sections 3 and 8, DATA_MODEL Events row, SYSTEM_MODEL C16, B14, IMPLEMENTATION_MAP C8 (lib/catalog/ folder, R-1 A, R-6 A); docs/lanes/routine.md (owned files, line 23 "allow create" -&gt; R-6 A); SKIN_STATE_CONTRACT_FINAL.md:269 (processing consent now versioned).</t>
+          <t>New contract version (skinstate-2) that maps engine_build, and names captureMethod, persistAttempt and captureQuality as client-asserted, with the bound (a forged captureMethod can only merge two capture paths). Also: provenance.processingConsentVersion is still null in skinstate-1.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3132,19 +3136,27 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>A07, A12, A13</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>D-23 / D-26 (O-1 A)</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3154,30 +3166,34 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>docs/architecture/, docs/lanes/</t>
+          <t>docs/architecture/SKIN_STATE_CONTRACT_FINAL.md, lib/skin-state.ts</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Committed doc edits</t>
+          <t>Owner-approved contract text + commit + tests</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr"/>
+          <t>Not started (owner: do not do now).</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>A new contract version needs owner approval (D-23); the owner asked for it to be built in the longitudinal lane (2026-10-04), design gate first.</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Edit the named sections; document task.</t>
+          <t>Draft skinstate-2 for owner approval; C02 stays blocked until it lands. Lane: longitudinal (branch lane/longitudinal, brief docs/lanes/longitudinal.md); results come via docs/lanes/longitudinal-report.md at merge.</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>FOUNDATION</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3187,14 +3203,14 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Proposed by capture report section 4 (main 3); routine report rows T2, T4, T5; verifier 2026-10-04.</t>
+          <t>Proposed by capture report section 4 (main 1, 2) and section 5 (D-26 amendment).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3209,12 +3225,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Lint coverage of tests/</t>
+          <t>Architecture docs alignment after the lane merges</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>npm run lint does not lint tests/. npx next lint --dir tests still reports one error: tests/privacy-erase.test.ts:18 unused "_".</t>
+          <t>LONGITUDINAL_METHOD section 3 and the capture brief (quality-gate steps 2 and 5 unmet until a server producer exists); RECOMMENDATION_MODEL sections 3 and 8, DATA_MODEL Events row, SYSTEM_MODEL C16, B14, IMPLEMENTATION_MAP C8 (lib/catalog/ folder, R-1 A, R-6 A); docs/lanes/routine.md (owned files, line 23 "allow create" -&gt; R-6 A); SKIN_STATE_CONTRACT_FINAL.md:269 (processing consent now versioned).</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3224,12 +3240,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -3241,30 +3257,30 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>tests/, package.json lint script</t>
+          <t>docs/architecture/, docs/lanes/</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Commit + lint output</t>
+          <t>Committed doc edits</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Not started. Found 2026-10-04 while fixing tests/api-chat-auth.test.ts (73d85cf).</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Fix the one error; decide whether npm run lint should cover tests/.</t>
+          <t>Edit the named sections; document task.</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3277,37 +3293,41 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 4 (main 3); routine report rows T2, T4, T5; verifier 2026-10-04.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Dev/prod separation</t>
+          <t>Lint coverage of tests/</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
+          <t>npm run lint does not lint tests/. npx next lint --dir tests still reports one error: tests/privacy-erase.test.ts:18 unused "_".</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3317,64 +3337,52 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
+          <t>tests/, package.json lint script</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>ff08107 (unmerged)</t>
-        </is>
-      </c>
+          <t>Commit + lint output</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
-        </is>
-      </c>
+          <t>Not started. Found 2026-10-04 while fixing tests/api-chat-auth.test.ts (73d85cf).</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Agent part done in B07 (local stack, no production keys; next dev refuses production values). Owner: remove FIREBASE_PRIVATE_KEY, FIREBASE_CLIENT_EMAIL and S3_SKIN_IMAGES_* from .env.local and the Desktop adminsdk JSON, then rotate the Admin key.</t>
+          <t>Fix the one error; decide whether npm run lint should cover tests/.</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr"/>
@@ -3382,7 +3390,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -3397,22 +3405,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Server-authoritative analysis writes</t>
+          <t>Dev/prod separation</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Browser is not authoritative for analysis-derived scores.</t>
+          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3420,60 +3428,56 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>D-02 / D-26</t>
-        </is>
-      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan, lib/skin-state*</t>
+          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
+          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6e9081d, 155cb69</t>
+          <t>ff08107 (unmerged)</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr"/>
+          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
+          <t>Agent part done in B07 (local stack, no production keys; next dev refuses production values). Owner: remove FIREBASE_PRIVATE_KEY, FIREBASE_CLIENT_EMAIL and S3_SKIN_IMAGES_* from .env.local and the Desktop adminsdk JSON, then rotate the Admin key.</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>TRUSTED MEASUREMENT</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3486,7 +3490,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3501,12 +3505,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Echo authentication and ownership</t>
+          <t>Server-authoritative analysis writes</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Echo derives identity/context server-side and verifies ownership.</t>
+          <t>Browser is not authoritative for analysis-derived scores.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3531,7 +3535,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Gate 02 / D-26</t>
+          <t>D-02 / D-26</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3541,38 +3545,38 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-check/chat</t>
+          <t>app/api/skin-scan, lib/skin-state*</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + live E2E</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>skin-check-chat-auth tests (13); cross-user 409</t>
+          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>6e9081d, 155cb69</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; verify live in I01.</t>
+          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3590,7 +3594,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -3605,12 +3609,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Gemini browser-state isolation</t>
+          <t>Echo authentication and ownership</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Gemini never trusts browser-supplied scores/context.</t>
+          <t>Echo derives identity/context server-side and verifies ownership.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3645,12 +3649,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
+          <t>app/api/skin-check/chat</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3660,7 +3664,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
+          <t>skin-check-chat-auth tests (13); cross-user 409</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3674,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr"/>
@@ -3681,7 +3685,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3694,7 +3698,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>B07</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3709,12 +3713,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Local stack with no production keys</t>
+          <t>Gemini browser-state isolation</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Firebase Auth + Firestore emulators with the real rules, local engine 0.1.6, S3Mock, Gemini dev key or test fake, seed data, dev guard, one start and one test command.</t>
+          <t>Gemini never trusts browser-supplied scores/context.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3732,8 +3736,16 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02 / D-26</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3741,43 +3753,43 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>scripts/local-stack*.sh, scripts/seed-local.ts, .env.development.example, lib/dev-env-guard.cjs, lib/gemini-key.ts, lib/firebase/{client,admin}.ts, lib/s3.ts, next.config.js</t>
+          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + end-to-end run</t>
+          <t>Commit + tests + live E2E</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>npm run test:local: unit 242 passed / 25 skipped, rules 24/24, end-to-end 1/1 (seeded phone user signs in via Auth emulator, upload to S3Mock, scan via local 0.1.6 engine, scanAnalyses + skinChecks saved in emulator); also green at PORT_BASE=3200. next dev with only .env.local refuses to start (7 variables named). typecheck 0, lint clean.</t>
+          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9ea6ad5, 6758fe6, 0fc1e57</t>
+          <t>155cb69, 955c1cc</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Local only. No UI click-through: the end-to-end test drives the real dev server through its HTTP API and the client SDK.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Owner: fill GEMINI_DEV_API_KEY in .env.development.local when a separate dev key exists.</t>
+          <t>Deploy via A13; verify live in I01.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3785,16 +3797,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Plain npm run dev with today's .env.local now refuses to start; use npm run dev:local.</t>
-        </is>
-      </c>
+      <c r="V28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -3809,74 +3817,70 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Vercel Preview holds production secrets</t>
+          <t>Local stack with no production keys</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Vercel env Preview scope has production SKIN_SCAN_API_URL, SCAN_API_SECRET, GEMINI_API_KEY (names from vercel env ls, 2026-10-03). Any pushed branch (lane/*, longitudinal-platform) gets a preview that calls the production engine and Gemini.</t>
+          <t>Firebase Auth + Firestore emulators with the real rules, local engine 0.1.6, S3Mock, Gemini dev key or test fake, seed data, dev guard, one start and one test command.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>D-26</t>
-        </is>
-      </c>
+      <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Vercel project skin-check env (Preview)</t>
+          <t>scripts/local-stack*.sh, scripts/seed-local.ts, .env.development.example, lib/dev-env-guard.cjs, lib/gemini-key.ts, lib/firebase/{client,admin}.ts, lib/s3.ts, next.config.js</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>vercel env ls showing Preview without production secrets, or a decision to keep them</t>
+          <t>Commit + tests + end-to-end run</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>vercel env ls (names and targets only)</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr"/>
+          <t>npm run test:local: unit 242 passed / 25 skipped, rules 24/24, end-to-end 1/1 (seeded phone user signs in via Auth emulator, upload to S3Mock, scan via local 0.1.6 engine, scanAnalyses + skinChecks saved in emulator); also green at PORT_BASE=3200. next dev with only .env.local refuses to start (7 variables named). typecheck 0, lint clean.</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>9ea6ad5, 6758fe6, 0fc1e57</t>
+        </is>
+      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>Changing Vercel env is the owner's action.</t>
-        </is>
-      </c>
+          <t>Local only. No UI click-through: the end-to-end test drives the real dev server through its HTTP API and the client SDK.</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Owner: remove the Preview copies of SCAN_API_SECRET, SKIN_SCAN_API_URL and GEMINI_API_KEY (or use separate preview values); until then do not push lane/* branches.</t>
+          <t>Owner: fill GEMINI_DEV_API_KEY in .env.development.local when a separate dev key exists.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3891,14 +3895,14 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Found while preparing lanes.</t>
+          <t>Plain npm run dev with today's .env.local now refuses to start; use npm run dev:local.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>B09</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3913,17 +3917,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Rate-limit store and per-route buckets</t>
+          <t>Vercel Preview holds production secrets</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Routine writes are capped in memory per instance (200/uid/day); account routes share the scan bucket (5/min/IP); ledger appends per purpose are not capped (latestGrant reads all ai_share entries; fails closed).</t>
+          <t>Vercel env Preview scope has production SKIN_SCAN_API_URL, SCAN_API_SECRET, GEMINI_API_KEY (names from vercel env ls, 2026-10-03). Any pushed branch (lane/*, longitudinal-platform) gets a preview that calls the production engine and Gemini.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3933,42 +3937,54 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>D-26</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>lib/rate-limit.ts, app/api/routine/events, app/api/account/*</t>
+          <t>Vercel project skin-check env (Preview)</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr"/>
+          <t>vercel env ls showing Preview without production secrets, or a decision to keep them</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>vercel env ls (names and targets only)</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Changing Vercel env is the owner's action.</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Move limits to a shared store if a hard global cap is needed; give account routes their own bucket; cap ledger appends per purpose.</t>
+          <t>Owner: remove the Preview copies of SCAN_API_SECRET, SKIN_SCAN_API_URL and GEMINI_API_KEY (or use separate preview values); until then do not push lane/* branches.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -3978,19 +3994,19 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Proposed by routine report T3; privacy report T11.</t>
+          <t>Found while preparing lanes.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -4005,27 +4021,27 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss npx firebase form</t>
+          <t>Rate-limit store and per-route buckets</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
+          <t>Routine writes are capped in memory per instance (200/uid/day); account routes share the scan bucket (5/min/IP); ledger appends per purpose are not capped (latestGrant reads all ai_share entries; fails closed).</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -4037,36 +4053,32 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json</t>
+          <t>lib/rate-limit.ts, app/api/routine/events, app/api/account/*</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>ae457a0, 44e0352</t>
-        </is>
-      </c>
+          <t>Commit + tests</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>Move limits to a shared store if a hard global cap is needed; give account routes their own bucket; cap ledger appends per purpose.</t>
+        </is>
+      </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
           <t>PRIVACY/SAFETY</t>
@@ -4074,19 +4086,19 @@
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
+          <t>Proposed by routine report T3; privacy report T11.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4101,12 +4113,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss other production-changing commands</t>
+          <t>Deny rules miss npx firebase form</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
+          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4124,11 +4136,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>B05</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -4147,22 +4155,22 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules + echo probe</t>
+          <t>Commit with added rules</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2371f78</t>
+          <t>ae457a0, 44e0352</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
+          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
@@ -4179,39 +4187,39 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Guided capture quality gate</t>
+          <t>Deny rules miss other production-changing commands</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
+          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4224,12 +4232,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Capture design (O-1..O-5, Q-1, Q-2; TD-05, TD-06)</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4237,60 +4245,56 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>lib/capture-quality/, components/skin-check/inputs/PhotoCapture.tsx, app/api/skin-scan/route.ts, lib/scan-retry.ts, SkinCheckDashboard.tsx</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Design doc + approved gate + tests</t>
+          <t>Commit with added rules + echo probe</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Built (lane capture, merged 2970c86): exposure, blur (per capture path), resolution checks on the exact blob sent to the engine; gate verdict pass/retake/unchecked/override; soft block with override after 2 retakes (O-4 B); engine refusal codes become named retake reasons (O-5 A); captureQuality saved on scanAnalyses as client-asserted, schemaVersion 1 (O-2 A), never used for comparability (Q-2). Dashboard (capture requests 1 and 2, 102aeaa): a refused photo shows "Retake photo" (new scan) and no retry of the same photo; the retry carries captureQuality and keeps quality. Tests: capture-* (settings, exposure, blur, resolution, gate, retake, api-code, persist), scan-retry, capture.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier (fresh, 2026-10-04): capture PASS.</t>
+          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>88a7505, da6ebfb, e45dcab, 3acb41d, 1f053cf, d29253a, 747df17, 9ec59f3; merge 2970c86; 102aeaa</t>
+          <t>2371f78</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>Local only; not deployed (TD-04). Thresholds provisional (cq-settings-0-provisional). Gate result is client-asserted.</t>
+          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>Open: pose, expression, distance and framing are not measured (O-3 C, no landmark library; they report not_measured) -&gt; C08. Thresholds from the R05 real-device sweep -&gt; C09. Deploy with A13.</t>
-        </is>
-      </c>
+      <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Report: docs/lanes/capture-report.md.</t>
+          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -4305,17 +4309,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Per-region / per-metric comparability</t>
+          <t>Guided capture quality gate</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Decide whether two scans are comparable before computing change.</t>
+          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4325,17 +4329,13 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>A07, A12, A13, A20, C07</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>D-13 / D-26 (O-1 A, TD-05)</t>
+          <t>Capture design (O-1..O-5, Q-1, Q-2; TD-05, TD-06)</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -4345,47 +4345,43 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>lib/comparability.ts</t>
+          <t>lib/capture-quality/, components/skin-check/inputs/PhotoCapture.tsx, app/api/skin-scan/route.ts, lib/scan-retry.ts, SkinCheckDashboard.tsx</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Comparability function + tests + noise inputs</t>
+          <t>Design doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Built (lane capture, merged 2970c86): comparabilityKey, compareKeys, compareStates. Output comparable / not_comparable with named reasons in a fixed order; no numbers, percentages or direction. Fails closed: COMPARABLE_QUANTITIES is empty, and skinstate-1 maps engine.build to null, so every real pair is not_comparable (quantity_not_validated, engine_build_unknown). captureMethod stays in the key, marked client-asserted (O-1 A). Tests: comparability, comparability-wording, capture.e2e (seed is never comparable). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+          <t>Built (lane capture, merged 2970c86): exposure, blur (per capture path), resolution checks on the exact blob sent to the engine; gate verdict pass/retake/unchecked/override; soft block with override after 2 retakes (O-4 B); engine refusal codes become named retake reasons (O-5 A); captureQuality saved on scanAnalyses as client-asserted, schemaVersion 1 (O-2 A), never used for comparability (Q-2). Dashboard (capture requests 1 and 2, 102aeaa): a refused photo shows "Retake photo" (new scan) and no retry of the same photo; the retry carries captureQuality and keeps quality. Tests: capture-* (settings, exposure, blur, resolution, gate, retake, api-code, persist), scan-retry, capture.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier (fresh, 2026-10-04): capture PASS.</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>afb7fe2, 94512b7; merge 2970c86</t>
+          <t>88a7505, da6ebfb, e45dcab, 3acb41d, 1f053cf, d29253a, 747df17, 9ec59f3; merge 2970c86; 102aeaa</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Local only. Cannot say comparable on real data yet.</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>A new SkinState contract version that maps engine_build (A20); per-quantity validation needs C05-C07.</t>
-        </is>
-      </c>
+          <t>Local only; not deployed (TD-04). Thresholds provisional (cq-settings-0-provisional). Gate result is client-asserted.</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>A20 (contract version), then fill COMPARABLE_QUANTITIES from C07.</t>
+          <t>Open: pose, expression, distance and framing are not measured (O-3 C, no landmark library; they report not_measured) -&gt; C08. Thresholds from the R05 real-device sweep -&gt; C09. Deploy with A13.</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4395,14 +4391,14 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Q-2: the browser quality result never feeds comparability; quality enters only via a server producer (C08).</t>
+          <t>Report: docs/lanes/capture-report.md.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -4417,22 +4413,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Human measurement validation protocol</t>
+          <t>Per-region / per-metric comparability</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Protocol for human validation and repeatability.</t>
+          <t>Decide whether two scans are comparable before computing change.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4440,10 +4436,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>A07, A12, A13, A20, C07</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>D-24 (uncommitted)</t>
+          <t>D-13 / D-26 (O-1 A, TD-05)</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -4458,51 +4458,59 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>lib/comparability.ts</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Committed protocol</t>
+          <t>Comparability function + tests + noise inputs</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+          <t>Built (lane capture, merged 2970c86): comparabilityKey, compareKeys, compareStates. Output comparable / not_comparable with named reasons in a fixed order; no numbers, percentages or direction. Fails closed: COMPARABLE_QUANTITIES is empty, and skinstate-1 maps engine.build to null, so every real pair is not_comparable (quantity_not_validated, engine_build_unknown). captureMethod stays in the key, marked client-asserted (O-1 A). Tests: comparability, comparability-wording, capture.e2e (seed is never comparable). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>59d9923</t>
+          <t>afb7fe2, 94512b7; merge 2970c86</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr"/>
+          <t>Local only. Cannot say comparable on real data yet.</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>A new SkinState contract version that maps engine_build (A20); per-quantity validation needs C05-C07.</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
+          <t>A20 (contract version), then fill COMPARABLE_QUANTITIES from C07.</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Q-2: the browser quality result never feeds comparability; quality enters only via a server producer (C08).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -4517,22 +4525,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Human validation pilot</t>
+          <t>Human measurement validation protocol</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Run pilot of C03 protocol.</t>
+          <t>Protocol for human validation and repeatability.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4540,12 +4548,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>C03, A12, A13, H01</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>D-24 (uncommitted)</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4563,24 +4571,28 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Pre-registration + pilot dataset + report</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
+          <t>Committed protocol</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>59d9923</t>
+        </is>
+      </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
-        </is>
-      </c>
+          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
+          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -4598,7 +4610,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -4613,12 +4625,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Full test-retest / calibration</t>
+          <t>Human validation pilot</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
+          <t>Run pilot of C03 protocol.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4638,7 +4650,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03, A12, A13, H01</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -4652,10 +4664,14 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>docs/research/measurement-validation/</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Pre-registered study report</t>
+          <t>Pre-registration + pilot dataset + report</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
@@ -4667,12 +4683,12 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Waits on C04 pilot.</t>
+          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Size from pilot variance.</t>
+          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4690,7 +4706,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4705,12 +4721,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Tone-stratified validation / model card</t>
+          <t>Full test-retest / calibration</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
+          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4730,7 +4746,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -4747,7 +4763,7 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Per-band results + model card</t>
+          <t>Pre-registered study report</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
@@ -4759,12 +4775,12 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05 data.</t>
+          <t>Waits on C04 pilot.</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Define model card template alongside C05.</t>
+          <t>Size from pilot variance.</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4782,7 +4798,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -4797,12 +4813,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Validated measurement/noise tables</t>
+          <t>Tone-stratified validation / model card</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
+          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4822,7 +4838,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>C05, C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -4839,7 +4855,7 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Versioned noise table tied to engine build</t>
+          <t>Per-band results + model card</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
@@ -4851,12 +4867,12 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05/C06.</t>
+          <t>Waits on C05 data.</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Fix table schema (field x region x band x engine build).</t>
+          <t>Define model card template alongside C05.</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -4869,16 +4885,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
-        </is>
-      </c>
+      <c r="V39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4893,17 +4905,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Server-side capture quality from engine landmarks</t>
+          <t>Validated measurement/noise tables</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Derive pose, distance (face scale) and framing on the server from the engine's mediapipe face landmarks, as a separately versioned quality producer. The only route by which quality can enter comparability (Q-2).</t>
+          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4913,54 +4925,46 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>D-18 (engine work)</t>
-        </is>
-      </c>
+          <t>C05, C06</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>CV/ML Engineer</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>skin-scan engine; app/api/skin-scan</t>
-        </is>
-      </c>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Owner approval under D-18 + design + tests</t>
+          <t>Versioned noise table tied to engine build</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Engine work needs owner approval (D-18).</t>
+          <t>Waits on C05/C06.</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Write a design for owner approval.</t>
+          <t>Fix table schema (field x region x band x engine build).</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -4970,19 +4974,19 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Proposed by capture report section 5 (O-3 C follow-up).</t>
+          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -4997,17 +5001,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Capture thresholds from the R05 sweep</t>
+          <t>Server-side capture quality from engine landmarks</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Replace the provisional capture-quality settings (lib/capture-quality/settings.ts) with values from the R05 real-device sweep; bump settingsVersion.</t>
+          <t>Derive pose, distance (face scale) and framing on the server from the engine's mediapipe face landmarks, as a separately versioned quality producer. The only route by which quality can enter comparability (Q-2).</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5025,42 +5029,46 @@
           <t>C01</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>D-18 (engine work)</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>CV/ML Engineer</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>lib/capture-quality/settings.ts</t>
+          <t>skin-scan engine; app/api/skin-scan</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Sweep results + commit + tests</t>
+          <t>Owner approval under D-18 + design + tests</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Not started (owner: do not do now).</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Needs the R05 real-device data.</t>
+          <t>Engine work needs owner approval (D-18).</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>After R05: set values, bump settingsVersion.</t>
+          <t>Write a design for owner approval.</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -5075,34 +5083,34 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Proposed by capture report section 5.</t>
+          <t>Proposed by capture report section 5 (O-3 C follow-up).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Baseline window definition</t>
+          <t>Capture thresholds from the R05 sweep</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>How a user's baseline is formed.</t>
+          <t>Replace the provisional capture-quality settings (lib/capture-quality/settings.ts) with values from the R05 real-device sweep; bump settingsVersion.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5117,12 +5125,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -5136,10 +5144,14 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>lib/capture-quality/settings.ts</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Method doc + decision</t>
+          <t>Sweep results + commit + tests</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
@@ -5151,30 +5163,34 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Needs between-day noise (C07).</t>
+          <t>Needs the R05 real-device data.</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md.</t>
+          <t>After R05: set values, bump settingsVersion.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 5.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -5189,12 +5205,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Change-vs-noise engine</t>
+          <t>Baseline window definition</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
+          <t>How a user's baseline is formed.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5209,19 +5225,15 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>C02, C07, D01</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>D-13 / D-24</t>
-        </is>
-      </c>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5229,13 +5241,13 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Engine + tests + noise table version</t>
+          <t>Method doc + decision</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
@@ -5247,12 +5259,12 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Needs comparability (C02) and validated noise (C07).</t>
+          <t>Needs between-day noise (C07).</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Wait; design pairwise interface first (D-13).</t>
+          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md. Lane: longitudinal (branch lane/longitudinal, brief docs/lanes/longitudinal.md); results come via docs/lanes/longitudinal-report.md at merge.</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -5262,7 +5274,7 @@
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr"/>
@@ -5270,7 +5282,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -5285,12 +5297,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Persistence/evidence tiers</t>
+          <t>Change-vs-noise engine</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Separate transient observations from persistent patterns.</t>
+          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5305,15 +5317,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr"/>
+          <t>C02, C07, D01</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>D-13 / D-24</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5321,13 +5337,13 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Tier definitions + tests</t>
+          <t>Engine + tests + noise table version</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
@@ -5339,12 +5355,12 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Needs D02.</t>
+          <t>Needs comparability (C02) and validated noise (C07).</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Wait on D02.</t>
+          <t>Wait; design pairwise interface first (D-13). Lane: longitudinal (branch lane/longitudinal, brief docs/lanes/longitudinal.md); results come via docs/lanes/longitudinal-report.md at merge.</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -5354,19 +5370,15 @@
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
-        </is>
-      </c>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -5381,17 +5393,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Scheduled anchor scans / irregular sampling</t>
+          <t>Persistence/evidence tiers</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Sampling strategy.</t>
+          <t>Separate transient observations from persistent patterns.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5401,7 +5413,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5415,16 +5427,32 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Tier definitions + tests</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Needs D02.</t>
+        </is>
+      </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Revisit after D02.</t>
+          <t>Wait on D02. Lane: longitudinal (branch lane/longitudinal, brief docs/lanes/longitudinal.md); results come via docs/lanes/longitudinal-report.md at merge.</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -5434,15 +5462,19 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -5457,12 +5489,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Engine-version re-baselining</t>
+          <t>Scheduled anchor scans / irregular sampling</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Handle engine build changes across history.</t>
+          <t>Sampling strategy.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5500,7 +5532,7 @@
       <c r="R46" s="2" t="inlineStr"/>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Revisit at first engine change after D02.</t>
+          <t>Revisit after D02.</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -5518,115 +5550,83 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Product catalog normalization</t>
+          <t>Engine-version re-baselining</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
+          <t>Handle engine build changes across history.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>D-08 / D-09 / D-12 (TD-07)</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>lib/catalog/</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>Owner-supplied master data + versioned schema</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane routine, merged daa0b4a): versioned catalogue schema, synthetic sample, owner template lib/catalog/catalogue-template.csv with a drift check, D-12 word check with the exact-name exception (PRODUCT_NAME_EXCEPTIONS). Tests: catalog-schema (20). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>e45da38; merge daa0b4a</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>Schema only; data is synthetic (R-3 A).</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>Owner catalogue data. Deploy blocker (routine T1): the deploy is blocked while any product has dataSource "synthetic".</t>
-        </is>
-      </c>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Owner fills lib/catalog/catalogue-template.csv (fields: routine-report.md section 6), including "Clear Seal" as an owner row; then replace the synthetic CATALOGUE. OPEN-R1 answered by R-2 B (no product cards for now).</t>
+          <t>Revisit at first engine change after D02.</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Proposed D-12 clarification (registered own-brand name is not by itself a claim) recorded in TD-07.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -5641,22 +5641,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Product eligibility / safety rules</t>
+          <t>Product catalog normalization</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Deterministic, versioned eligibility + safety constraints.</t>
+          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5664,19 +5664,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>E01, E05</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-08 / D-09 / D-12 (TD-07)</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5684,27 +5680,39 @@
           <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>lib/catalog/</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Pure function + version constant + tests</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="inlineStr"/>
+          <t>Owner-supplied master data + versioned schema</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane routine, merged daa0b4a): versioned catalogue schema, synthetic sample, owner template lib/catalog/catalogue-template.csv with a drift check, D-12 word check with the exact-name exception (PRODUCT_NAME_EXCEPTIONS). Tests: catalog-schema (20). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>e45da38; merge daa0b4a</t>
+        </is>
+      </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Schema only; data is synthetic (R-3 A).</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+          <t>Owner catalogue data. Deploy blocker (routine T1): the deploy is blocked while any product has dataSource "synthetic".</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Wait on E01.</t>
+          <t>Owner fills lib/catalog/catalogue-template.csv (fields: routine-report.md section 6), including "Clear Seal" as an owner row; then replace the synthetic CATALOGUE. OPEN-R1 answered by R-2 B (no product cards for now).</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
@@ -5714,15 +5722,19 @@
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Proposed D-12 clarification (registered own-brand name is not by itself a claim) recorded in TD-07.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -5737,37 +5749,37 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Routine model + event history</t>
+          <t>Product eligibility / safety rules</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
+          <t>Deterministic, versioned eligibility + safety constraints.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>E01, E05</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>R-1..R-6 (TD-07)</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -5777,38 +5789,30 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>lib/routine/, app/api/routine/events, components/routine, app/(marketing)/routine, firestore.rules lane:routine</t>
-        </is>
-      </c>
+          <t>Product/Routine Rules Engineer</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Data model doc + approved gate + tests</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane routine, merged daa0b4a): event schemas and currentRoutine(); GET/POST /api/routine/events (uid from the verified token only, strict schemas, idempotent eventIds, 4 KB body cap, 200 writes/uid/day); server-written events, owner read-only rules, collection-group denied; /routine page (own record only, no skin data, no claims). Follow-ups: purpose text moved to lib/consent.ts (7662ed7); root site description neutral (90c30a1, routine T6); erasure covers routineEvents (2f00819). Tests: routine-events, routine-copy, routine-route, firestore-rules-routine, routine.e2e, layout-description. Security review: no cross-user path. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier: routine PASS.</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>e9331f3, 6f8c22c, 0f56ea6, ac275fa, 0e37830, e08aa89, 779e967; merge daa0b4a; 7662ed7, 90c30a1, 2f00819</t>
-        </is>
-      </c>
+          <t>Pure function + version constant + tests</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Local only; not deployed (A04, A13). Signed-in /routine page not clicked through in a browser.</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Browser click-through (E06). Doc alignment (A21). Rate-limit store (B09). Deploy with A13 after A04.</t>
+          <t>Wait on E01. Lane: rules (branch lane/rules, brief docs/lanes/rules.md); results come via docs/lanes/rules-report.md at merge.</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
@@ -5821,16 +5825,12 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>A04 dependency applies to deployment only.</t>
-        </is>
-      </c>
+      <c r="V49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Adherence summary</t>
+          <t>Routine model + event history</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
+          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -5870,10 +5870,14 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr"/>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>R-1..R-6 (TD-07)</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5881,38 +5885,38 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>lib/routine/adherence.ts</t>
+          <t>lib/routine/, app/api/routine/events, components/routine, app/(marketing)/routine, firestore.rules lane:routine</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Function + tests</t>
+          <t>Data model doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>adherence(): used / skipped / unknown, counts only; a day with no log is unknown, never skipped. GET /api/routine/events?tz= returns the 7-day summary. Tests: routine-adherence (13), routine.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+          <t>Built (lane routine, merged daa0b4a): event schemas and currentRoutine(); GET/POST /api/routine/events (uid from the verified token only, strict schemas, idempotent eventIds, 4 KB body cap, 200 writes/uid/day); server-written events, owner read-only rules, collection-group denied; /routine page (own record only, no skin data, no claims). Follow-ups: purpose text moved to lib/consent.ts (7662ed7); root site description neutral (90c30a1, routine T6); erasure covers routineEvents (2f00819). Tests: routine-events, routine-copy, routine-route, firestore-rules-routine, routine.e2e, layout-description. Security review: no cross-user path. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier: routine PASS.</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0e4bf16; merge daa0b4a</t>
+          <t>e9331f3, 6f8c22c, 0f56ea6, ac275fa, 0e37830, e08aa89, 779e967; merge daa0b4a; 7662ed7, 90c30a1, 2f00819</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Local only.</t>
+          <t>Local only; not deployed (A04, A13). Signed-in /routine page not clicked through in a browser.</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>None for the function. Deploy with E03.</t>
+          <t>Browser click-through (E06). Doc alignment (A21). Rate-limit store (B09). Deploy with A13 after A04.</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -5925,12 +5929,16 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>A04 dependency applies to deployment only.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -5945,38 +5953,38 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Red-flag triage interlock</t>
+          <t>Adherence summary</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Safety layer overrides cosmetic recommendations.</t>
+          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -5984,49 +5992,53 @@
           <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>lib/routine/adherence.ts</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
+          <t>Function + tests</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>adherence(): used / skipped / unknown, counts only; a day with no log is unknown, never skipped. GET /api/routine/events?tz= returns the 7-day summary. Tests: routine-adherence (13), routine.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>0e4bf16; merge daa0b4a</t>
+        </is>
+      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
-        </is>
-      </c>
+          <t>Local only.</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review.</t>
+          <t>None for the function. Deploy with E03.</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-04 (privacy T12): also review EXTRA_CAUTION_TRIGGERS and the caution sentence; decide whether the residual pregnancy inference is acceptable or drop the flag or trigger.</t>
-        </is>
-      </c>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -6041,17 +6053,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Routine page browser click-through</t>
+          <t>Red-flag triage interlock</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Signed-in click-through of /routine on the local stack (read, add, stop, swap, log).</t>
+          <t>Safety layer overrides cosmetic recommendations.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6061,51 +6073,51 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>components/routine, app/(marketing)/routine</t>
-        </is>
-      </c>
+          <t>Product/Routine Rules Engineer</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Recorded local click-through</t>
+          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Not started. The API flow is covered by routine.e2e.</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
+        </is>
+      </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Run npm run dev:local and click through as a seeded user.</t>
+          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review. Lane: rules (branch lane/rules, brief docs/lanes/rules.md); results come via docs/lanes/rules-report.md at merge.</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6115,39 +6127,39 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Proposed by routine report T7.</t>
+          <t>2026-10-04 (privacy T12): also review EXTRA_CAUTION_TRIGGERS and the caution sentence; decide whether the residual pregnancy inference is acceptable or drop the flag or trigger.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Routine page browser click-through</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>Signed-in click-through of /routine on the local stack (read, add, stop, swap, log).</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6157,19 +6169,15 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>A08, D02, E03, E04, E05</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6177,52 +6185,52 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>components/routine, app/(marketing)/routine</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Pure builder + tests</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
-        </is>
-      </c>
+          <t>Recorded local click-through</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
-        </is>
-      </c>
+          <t>Not started. The API flow is covered by routine.e2e.</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>Wait; may define schema with null sections earlier if approved.</t>
+          <t>Run npm run dev:local and click through as a seeded user.</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by routine report T7.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -6237,12 +6245,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6262,7 +6270,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>A08, D02, E03, E04, E05</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6280,35 +6288,31 @@
           <t>Gemini/Context Engineer</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>lib/gemini.ts</t>
-        </is>
-      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
+          <t>Pure builder + tests</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Schema renderer not built.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Needs F01.</t>
+          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>Wait on F01.</t>
+          <t>Wait; may define schema with null sections earlier if approved. Lane: context (branch lane/context, brief docs/lanes/context.md); results come via docs/lanes/context-report.md at merge.</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
@@ -6318,19 +6322,15 @@
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>Seed status PARTIALLY READY.</t>
-        </is>
-      </c>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>D-14 / D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -6388,27 +6388,35 @@
           <t>Gemini/Context Engineer</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr"/>
+          <t>Schema + renderer + tests</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
+        </is>
+      </c>
       <c r="P55" s="2" t="inlineStr"/>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Schema renderer not built.</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Needs F02 output schema.</t>
+          <t>Needs F01.</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>Wait on F02.</t>
+          <t>Wait on F01. Lane: context (branch lane/context, brief docs/lanes/context.md); results come via docs/lanes/context-report.md at merge.</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
@@ -6418,15 +6426,19 @@
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V55" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Seed status PARTIALLY READY.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6441,17 +6453,17 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6461,13 +6473,17 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>D-14 (store rejected for now)</t>
+          <t>D-14 / D-12</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -6483,24 +6499,24 @@
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
-        </is>
-      </c>
+          <t>Validator + adversarial tests</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Needs F02 output schema.</t>
+        </is>
+      </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only.</t>
+          <t>Wait on F02. Lane: context (branch lane/context, brief docs/lanes/context.md); results come via docs/lanes/context-report.md at merge.</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -6510,7 +6526,7 @@
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr"/>
@@ -6518,32 +6534,32 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6553,15 +6569,15 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>D-14 (store rejected for now)</t>
+        </is>
+      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6569,40 +6585,40 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
+        </is>
+      </c>
       <c r="P57" s="2" t="inlineStr"/>
       <c r="Q57" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
-        </is>
-      </c>
+      <c r="R57" s="2" t="inlineStr"/>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only. Lane: context (branch lane/context, brief docs/lanes/context.md); results come via docs/lanes/context-report.md at merge.</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr"/>
@@ -6610,32 +6626,32 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Routine and adherence in the context package</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>The owner asked for a routine and adherence summary in the context package. R-1 A (TD-07) says routine data is not sent to Gemini, and users are told so (ROUTINE_PURPOSE_COPY). The shape allows only { status: "not_shared" }. Routine data next to a "beyond noise" result also invites an attribution claim (D-12).</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6650,221 +6666,213 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>E03, G01</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>D-12 (LOCKED)</t>
+          <t>TD-07 (R-1 A) / D-12</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>Gemini/Context Engineer</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>lib/contracts/context-package.ts, lib/consent.ts</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
+          <t>Owner decision; if reopened: new purpose copy, new package version, attribution guard</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr"/>
       <c r="P58" s="2" t="inlineStr"/>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Concern recorded 2026-10-04; the frozen decision is not changed.</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>Needs E03 and G01.</t>
+          <t>Owner decision: keep R-1 A (drop the routine item) or reopen it and change the purpose copy.</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Owner decides.</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V58" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>Found while writing the shared shapes.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>D-16 / D-17 (TD-08, TD-10)</t>
-        </is>
-      </c>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
-        </is>
-      </c>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
-        </is>
-      </c>
+          <t>Approved design + tests + E2E</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>E03, G01</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>D-19 (TD-08, TD-11, TD-12)</t>
+          <t>D-12 (LOCKED)</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -6872,57 +6880,45 @@
           <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
-        </is>
-      </c>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
-        </is>
-      </c>
+          <t>Design reviewed against D-12</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Needs E03 and G01.</t>
+        </is>
+      </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -6937,12 +6933,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -6960,10 +6956,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
+          <t>D-16 / D-17 (TD-08, TD-10)</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -6978,37 +6978,37 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
+          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
+          <t>Ledger + erasure route + tests + live verification</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
+          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
+          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
+          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
@@ -7023,14 +7023,14 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7045,22 +7045,22 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Block writes after an account is erased</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7068,51 +7068,51 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-19 (TD-08, TD-11, TD-12)</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
+          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="inlineStr"/>
+          <t>Gate + tests</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
+        </is>
+      </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>Needs a rules change outside the privacy lane.</t>
-        </is>
-      </c>
+          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
+          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
@@ -7127,14 +7127,14 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T3; widened to the routine route.</t>
+          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -7149,22 +7149,22 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Support tool to clear a mistaken under-18 record</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -7172,51 +7172,55 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>D-19 (decision 4)</t>
+          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
+          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests + audit trail</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="inlineStr"/>
+          <t>Field inventory + key ownership/tier + consent copy</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+        </is>
+      </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
+          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>Must exist before the final deploy (A13 depends on it).</t>
+          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
+          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
@@ -7231,14 +7235,14 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T17. Deploy blocker.</t>
+          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7253,17 +7257,17 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Final consent copy (AI share and processing)</t>
+          <t>Block writes after an account is erased</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
+          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7273,22 +7277,22 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>D-16 / decision 6, 7a</t>
+          <t>D-17</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -7298,29 +7302,29 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>lib/consent.ts</t>
+          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Owner/legal copy + version bump + tests updated on purpose</t>
+          <t>Design + commit + tests</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr"/>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
+          <t>Not started (owner: do not do now).</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>Owner or legal supplies both sentences; G1 answered.</t>
+          <t>Needs a rules change outside the privacy lane.</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
+          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
@@ -7335,14 +7339,14 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
+          <t>Proposed by privacy report T3; widened to the routine route.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -7357,12 +7361,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Cross-route under-18 test</t>
+          <t>Support tool to clear a mistaken under-18 record</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
+          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -7377,7 +7381,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -7385,7 +7389,11 @@
           <t>H02</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>D-19 (decision 4)</t>
+        </is>
+      </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -7393,30 +7401,34 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>tests/</t>
+          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Commit + test result</t>
+          <t>Design + commit + tests + audit trail</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr"/>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="inlineStr"/>
+          <t>Not started (owner: do not do now).</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>Must exist before the final deploy (A13 depends on it).</t>
+        </is>
+      </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>Write the test against the merged routes.</t>
+          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
@@ -7431,14 +7443,14 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T6.</t>
+          <t>Proposed by privacy report T17. Deploy blocker.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7453,12 +7465,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Gemini field scope: self-reported dryness and gender inference</t>
+          <t>Final consent copy (AI share and processing)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
+          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -7473,7 +7485,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -7483,7 +7495,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Decision 8</t>
+          <t>D-16 / decision 6, 7a</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -7498,12 +7510,12 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts</t>
+          <t>lib/consent.ts</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Owner decision (+ commit if changed)</t>
+          <t>Owner/legal copy + version bump + tests updated on purpose</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr"/>
@@ -7515,12 +7527,12 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Owner decision.</t>
+          <t>Owner or legal supplies both sentences; G1 answered.</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
+          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
@@ -7535,14 +7547,14 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T8, T9.</t>
+          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -7557,12 +7569,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Required Gemini allowlist parameter</t>
+          <t>Cross-route under-18 test</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
+          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -7577,12 +7589,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -7593,17 +7605,17 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
+          <t>tests/</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Commit + test result</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr"/>
@@ -7616,12 +7628,12 @@
       <c r="R67" s="2" t="inlineStr"/>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>Make the parameter required.</t>
+          <t>Write the test against the merged routes.</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7631,14 +7643,14 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T10.</t>
+          <t>Proposed by privacy report T6.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>H10</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -7653,17 +7665,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Require age attestation on upload and scan</t>
+          <t>Gemini field scope: self-reported dryness and gender inference</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
+          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7673,50 +7685,54 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Decision 3a</t>
+          <t>Decision 8</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
+          <t>lib/skin-check-format.ts</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Owner decision (+ commit if changed)</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Later.</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr"/>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision.</t>
+        </is>
+      </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>After old bundles are gone.</t>
+          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
@@ -7731,14 +7747,14 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T13.</t>
+          <t>Proposed by privacy report T8, T9.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -7753,12 +7769,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Engine stores no image</t>
+          <t>Required Gemini allowlist parameter</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
+          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -7773,10 +7789,14 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7785,17 +7805,17 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>CV/ML Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>skin-scan engine</t>
+          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Code read + runtime check</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr"/>
@@ -7808,12 +7828,12 @@
       <c r="R69" s="2" t="inlineStr"/>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>Read-only check of the engine source and the container.</t>
+          <t>Make the parameter required.</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -7823,14 +7843,14 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T15.</t>
+          <t>Proposed by privacy report T10.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>H10</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -7845,17 +7865,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>DOM test renderer</t>
+          <t>Require age attestation on upload and scan</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
+          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -7868,47 +7888,47 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>README rule 6</t>
+          <t>Decision 3a</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>package.json, tests/</t>
+          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Owner approval + commit</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr"/>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>New dependency needs approval.</t>
-        </is>
-      </c>
+          <t>Later.</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>Owner approves or declines.</t>
+          <t>After old bundles are gone.</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
@@ -7923,14 +7943,14 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T16.</t>
+          <t>Proposed by privacy report T13.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>H13</t>
+          <t>H11</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -7945,12 +7965,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Processing consent after a draft restore</t>
+          <t>Engine stores no image</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
+          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -7965,37 +7985,29 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>D-16 / D-03a</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>CV/ML Engineer</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
+          <t>skin-scan engine</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Decision + commit + tests</t>
+          <t>Code read + runtime check</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr"/>
@@ -8005,14 +8017,10 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R71" s="2" t="inlineStr">
-        <is>
-          <t>Owner decides whether restored drafts may carry the consent version.</t>
-        </is>
-      </c>
+      <c r="R71" s="2" t="inlineStr"/>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
+          <t>Read-only check of the engine source and the container.</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
@@ -8027,14 +8035,14 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
+          <t>Proposed by privacy report T15.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>H14</t>
+          <t>H12</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -8049,17 +8057,17 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Withdraw AI-share consent in the UI</t>
+          <t>DOM test renderer</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
+          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8069,50 +8077,50 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>README rule 6</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
+          <t>package.json, tests/</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Design check + commit + tests</t>
+          <t>Owner approval + commit</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr"/>
       <c r="P72" s="2" t="inlineStr"/>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr"/>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>New dependency needs approval.</t>
+        </is>
+      </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Check the design, then add a withdraw control.</t>
+          <t>Owner approves or declines.</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
@@ -8127,14 +8135,14 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04.</t>
+          <t>Proposed by privacy report T16.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>H15</t>
+          <t>H13</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -8149,12 +8157,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Low-severity hardening from the security review</t>
+          <t>Processing consent after a draft restore</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
+          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -8172,26 +8180,34 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / D-03a</t>
+        </is>
+      </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
+          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Decision + commit + tests</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr"/>
@@ -8201,10 +8217,14 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Owner decides whether restored drafts may carry the consent version.</t>
+        </is>
+      </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>Add isPlainUid to the upload key path; log name and code only.</t>
+          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
@@ -8219,14 +8239,14 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04 (pre-existing logging).</t>
+          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>H16</t>
+          <t>H14</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -8241,12 +8261,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Consent ledger write slows the scan response</t>
+          <t>Withdraw AI-share consent in the UI</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
+          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -8261,17 +8281,17 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -8281,17 +8301,17 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/route.ts</t>
+          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Commit + test + timing</t>
+          <t>Design check + commit + tests</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
@@ -8304,7 +8324,7 @@
       <c r="R74" s="2" t="inlineStr"/>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
+          <t>Check the design, then add a withdraw control.</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
@@ -8319,39 +8339,39 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Verifier observation 2026-10-04 (a52f36d).</t>
+          <t>Security review 2026-10-04.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H15</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Low-severity hardening from the security review</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8361,14 +8381,10 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -8377,13 +8393,17 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr"/>
@@ -8393,57 +8413,57 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R75" s="2" t="inlineStr">
-        <is>
-          <t>Nothing longitudinal is deployed yet.</t>
-        </is>
-      </c>
+      <c r="R75" s="2" t="inlineStr"/>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Add isPlainUid to the upload key path; log name and code only.</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V75" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>Security review 2026-10-04 (pre-existing logging).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>H16</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>Consent ledger write slows the scan response</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8453,15 +8473,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr"/>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8469,13 +8493,17 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>app/api/skin-scan/route.ts</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Commit + test + timing</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr"/>
@@ -8485,57 +8513,57 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R76" s="2" t="inlineStr">
-        <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
-        </is>
-      </c>
+      <c r="R76" s="2" t="inlineStr"/>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V76" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>Verifier observation 2026-10-04 (a52f36d).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -8545,26 +8573,46 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>A12, A13, B01, H01, H03</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>QA/Test Engineer</t>
+        </is>
+      </c>
       <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Recorded E2E run against prod</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr"/>
       <c r="P77" s="2" t="inlineStr"/>
-      <c r="Q77" s="2" t="inlineStr"/>
-      <c r="R77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>Nothing longitudinal is deployed yet.</t>
+        </is>
+      </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
@@ -8582,32 +8630,32 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -8617,31 +8665,51 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr"/>
-      <c r="Q78" s="2" t="inlineStr"/>
-      <c r="R78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -8654,7 +8722,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -8669,7 +8737,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -8726,7 +8794,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -8741,7 +8809,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>ML recommendation ranking</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -8793,16 +8861,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V80" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -8817,7 +8881,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Indian cross-user benchmark</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -8870,6 +8934,154 @@
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10836,7 +11048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11958,52 +12170,52 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>TD-13</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Native L*/a* are provisional research candidates only</t>
+          <t>Wave-2 shared shapes in lib/contracts/, frozen for lanes</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 screening</t>
+          <t>Three parallel lanes (longitudinal, rules, context) need one shape for each hand-off</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Keep b*, ITA, lbpEntropy</t>
+          <t>Each lane defines its own types; GEMINI_BOUNDARY §4 ctx-1 facts-list sketch as is</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Primary endpoints for the human study only; not validated measurements</t>
+          <t>Four type-only files: LongitudinalResult, RecommendationResult, SafetyState, ContextPackage. Context types are standalone (not Omit&lt;&gt; views) and carry facts with id and pre-rendered text; routine is only "not shared" (R-1 A). Supersedes the ctx-1 sketch in GEMINI_BOUNDARY §4. No lane edits the folder; changes go through the main session with tests/contracts.test.ts</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Only survivors of screening</t>
+          <t>Owner instruction 2026-10-04 (Part 2); verifier-checked</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
+          <t>a8eb0c0, bbe02da</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>C03-C07</t>
+          <t>A23, A20, D01-D03, E02, E05, F01-F05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Owner may reverse before Phase 1 pre-registration</t>
+          <t>A shape a lane cannot build on: main session changes it with a test between waves</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -12013,76 +12225,76 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>ACCEPTED for study design</t>
+          <t>DECIDED (owner instruction). Tracker-local until A14.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>D-13 / D-24</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal comparisons require comparability + noise/evidence</t>
+          <t>Native L*/a* are provisional research candidates only</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Naive % change misleads</t>
+          <t>Phase 0 screening</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Research-doc point ladder</t>
+          <t>Keep b*, ITA, lbpEntropy</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
+          <t>Primary endpoints for the human study only; not validated measurements</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Measurement noise unknown</t>
+          <t>Only survivors of screening</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-13; D-24 uncommitted</t>
+          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>C02, D02, G01</t>
+          <t>C03-C07</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Owner may reverse before Phase 1 pre-registration</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (D-24 uncommitted)</t>
+          <t>ACCEPTED for study design</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-13 / D-24</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -12092,59 +12304,59 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Recommender deterministic and versioned</t>
+          <t>Longitudinal comparisons require comparability + noise/evidence</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4 SKUs, ~6 rules</t>
+          <t>Naive % change misleads</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>DMN/rules engine; ML ranking</t>
+          <t>Research-doc point ladder</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Plain TS pure function + version constants</t>
+          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Auditable</t>
+          <t>Measurement noise unknown</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-08</t>
+          <t>DECISION_LOG D-13; D-24 uncommitted</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>E02, J02</t>
+          <t>C02, D02, G01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>&gt;20 SKUs or non-engineer rule authors</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>PROPOSED (D-24 uncommitted)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -12154,42 +12366,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Gemini is explanation layer, not authority</t>
+          <t>Recommender deterministic and versioned</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Gemini hallucination/claims risk</t>
+          <t>4 SKUs, ~6 rules</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Gemini owns context</t>
+          <t>DMN/rules engine; ML ranking</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+          <t>Plain TS pure function + version constants</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Auditable</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-14; GATE_02</t>
+          <t>DECISION_LOG D-08</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>B04, F01-F04</t>
+          <t>E02, J02</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&gt;20 SKUs or non-engineer rule authors</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -12199,14 +12411,14 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (paid tier is release gate)</t>
+          <t>PROPOSED</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -12216,104 +12428,104 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>No attribution/efficacy/forecasting</t>
+          <t>Gemini is explanation layer, not authority</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Gemini hallucination/claims risk</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Gemini owns context</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Evidence tiers 3-4</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Prohibited in UI, Gemini, analytics</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>CLAUDE.md</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-12</t>
+          <t>DECISION_LOG D-14; GATE_02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>G02, J04, R08</t>
+          <t>B04, F01-F04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Explicit owner approval</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>PROPOSED (paid tier is release gate)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Client input never authoritative for measured state</t>
+          <t>No attribution/efficacy/forecasting</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Gate 02</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Rules tightening; server chat storage</t>
+          <t>Evidence tiers 3-4</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Path-structural trust; authenticated Echo</t>
+          <t>Prohibited in UI, Gemini, analytics</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Forgeable browser state</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>DECISION_LOG D-12</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>A09, B02-B04, C02</t>
+          <t>G02, J04, R08</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Open: client-asserted captureMethod/persistAttempt</t>
+          <t>Explicit owner approval</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -12323,67 +12535,129 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED (branch); owner decision open</t>
+          <t>LOCKED</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>D-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Client input never authoritative for measured state</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Rules tightening; server chat storage</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Path-structural trust; authenticated Echo</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Forgeable browser state</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>A09, B02-B04, C02</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Open: client-asserted captureMethod/persistAttempt</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (branch); owner decision open</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>D-21</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Gate 01 stores raw analysis in scanAnalyses</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Raw preservation</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>skinStates collection</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>users/{uid}/scanAnalyses/{scanId}_{sha16}</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Immutable raw substrate</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>6e9081d</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Systems Architect</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>IMPLEMENTED (not deployed); ID duplicated in HEAD</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 25, IN PROGRESS 1, NOT STARTED 16, BLOCKED 19, OWNER ACTION 13, LATER 8 (total 82)</t>
+          <t>DONE 25, IN PROGRESS 1, NOT STARTED 16, BLOCKED 19, OWNER ACTION 14, LATER 8 (total 83)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 21, NOT NEEDED 9, NOT CHECKED 51</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 21, NOT NEEDED 9, NOT CHECKED 52</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V83"/>
+  <dimension ref="A1:V84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6730,32 +6730,32 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>Verified helpline number in the referral copy</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>The red-flag and self-harm referral message ships with no phone number (TD-16). A number may be added only after the owner supplies one and verifies it and its hours.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6765,64 +6765,72 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>TD-16 / GEMINI_BOUNDARY §6</t>
+        </is>
+      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>Gemini/Context Engineer</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>lib/context/prefilter.ts (REFERRAL_COPY)</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
+          <t>Owner-verified number and hours + commit + test</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr"/>
       <c r="P59" s="2" t="inlineStr"/>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>No number in the copy.</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
+          <t>Owner has not supplied a verified India helpline.</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>Owner supplies and verifies the number; engineer adds it with a test. DEPLOY BLOCKER for switching the context path on in production.</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision 2026-10-04.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6837,12 +6845,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -6857,19 +6865,15 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>E03, G01</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>D-12 (LOCKED)</t>
-        </is>
-      </c>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6883,7 +6887,7 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
+          <t>Approved design + tests + E2E</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr"/>
@@ -6895,12 +6899,12 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>Needs E03 and G01.</t>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
@@ -6918,119 +6922,103 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>E03, G01</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-17 (TD-08, TD-10)</t>
+          <t>D-12 (LOCKED)</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
-        </is>
-      </c>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
-        </is>
-      </c>
+          <t>Design reviewed against D-12</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
+          <t>Needs E03 and G01.</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7045,17 +7033,17 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7065,13 +7053,17 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>D-19 (TD-08, TD-11, TD-12)</t>
+          <t>D-16 / D-17 (TD-08, TD-10)</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -7081,38 +7073,42 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
+          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
+          <t>Ledger + erasure route + tests + live verification</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
+          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
+          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr"/>
+          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
+        </is>
+      </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
+          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
@@ -7127,14 +7123,14 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -7149,17 +7145,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7169,13 +7165,13 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
+          <t>D-19 (TD-08, TD-11, TD-12)</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -7185,42 +7181,38 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
+          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
+          <t>Gate + tests</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
-        </is>
-      </c>
+          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
+          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
@@ -7235,14 +7227,14 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
+          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7257,42 +7249,38 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Block writes after an account is erased</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -7302,29 +7290,37 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
+          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" s="2" t="inlineStr"/>
+          <t>Field inventory + key ownership/tier + consent copy</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+        </is>
+      </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
+          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>Needs a rules change outside the privacy lane.</t>
+          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
+          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
@@ -7339,14 +7335,14 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T3; widened to the routine route.</t>
+          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -7361,12 +7357,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Support tool to clear a mistaken under-18 record</t>
+          <t>Block writes after an account is erased</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
+          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -7381,17 +7377,17 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>D-19 (decision 4)</t>
+          <t>D-17</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -7401,17 +7397,17 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
+          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests + audit trail</t>
+          <t>Design + commit + tests</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
@@ -7423,12 +7419,12 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>Must exist before the final deploy (A13 depends on it).</t>
+          <t>Needs a rules change outside the privacy lane.</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
+          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
@@ -7443,14 +7439,14 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T17. Deploy blocker.</t>
+          <t>Proposed by privacy report T3; widened to the routine route.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7465,17 +7461,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Final consent copy (AI share and processing)</t>
+          <t>Support tool to clear a mistaken under-18 record</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
+          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7490,49 +7486,49 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>D-16 / decision 6, 7a</t>
+          <t>D-19 (decision 4)</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>lib/consent.ts</t>
+          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Owner/legal copy + version bump + tests updated on purpose</t>
+          <t>Design + commit + tests + audit trail</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="inlineStr"/>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
+          <t>Not started (owner: do not do now).</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Owner or legal supplies both sentences; G1 answered.</t>
+          <t>Must exist before the final deploy (A13 depends on it).</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
+          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
@@ -7547,14 +7543,14 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
+          <t>Proposed by privacy report T17. Deploy blocker.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -7569,17 +7565,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Cross-route under-18 test</t>
+          <t>Final consent copy (AI share and processing)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
+          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7589,46 +7585,54 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr"/>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / decision 6, 7a</t>
+        </is>
+      </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>tests/</t>
+          <t>lib/consent.ts</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Commit + test result</t>
+          <t>Owner/legal copy + version bump + tests updated on purpose</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr"/>
       <c r="P67" s="2" t="inlineStr"/>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R67" s="2" t="inlineStr"/>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>Owner or legal supplies both sentences; G1 answered.</t>
+        </is>
+      </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>Write the test against the merged routes.</t>
+          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
@@ -7643,14 +7647,14 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T6.</t>
+          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -7665,17 +7669,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Gemini field scope: self-reported dryness and gender inference</t>
+          <t>Cross-route under-18 test</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
+          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7690,49 +7694,41 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>Decision 8</t>
-        </is>
-      </c>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts</t>
+          <t>tests/</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Owner decision (+ commit if changed)</t>
+          <t>Commit + test result</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>Owner decision.</t>
-        </is>
-      </c>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
+          <t>Write the test against the merged routes.</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
@@ -7747,14 +7743,14 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T8, T9.</t>
+          <t>Proposed by privacy report T6.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -7769,17 +7765,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Required Gemini allowlist parameter</t>
+          <t>Gemini field scope: self-reported dryness and gender inference</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
+          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -7789,7 +7785,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -7797,43 +7793,51 @@
           <t>H03</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Decision 8</t>
+        </is>
+      </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
+          <t>lib/skin-check-format.ts</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Owner decision (+ commit if changed)</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr"/>
       <c r="P69" s="2" t="inlineStr"/>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr"/>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision.</t>
+        </is>
+      </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>Make the parameter required.</t>
+          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -7843,14 +7847,14 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T10.</t>
+          <t>Proposed by privacy report T8, T9.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>H10</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -7865,17 +7869,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Require age attestation on upload and scan</t>
+          <t>Required Gemini allowlist parameter</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
+          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -7890,14 +7894,10 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Decision 3a</t>
-        </is>
-      </c>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -7905,12 +7905,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
+          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -7922,18 +7922,18 @@
       <c r="P70" s="2" t="inlineStr"/>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>Later.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr"/>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>After old bundles are gone.</t>
+          <t>Make the parameter required.</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -7943,14 +7943,14 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T13.</t>
+          <t>Proposed by privacy report T10.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>H10</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Engine stores no image</t>
+          <t>Require age attestation on upload and scan</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
+          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -7985,11 +7985,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Decision 3a</t>
+        </is>
+      </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -7997,30 +8005,30 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>CV/ML Engineer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>skin-scan engine</t>
+          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Code read + runtime check</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr"/>
       <c r="P71" s="2" t="inlineStr"/>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Later.</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr"/>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>Read-only check of the engine source and the container.</t>
+          <t>After old bundles are gone.</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
@@ -8035,14 +8043,14 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T15.</t>
+          <t>Proposed by privacy report T13.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>H11</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -8057,17 +8065,17 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>DOM test renderer</t>
+          <t>Engine stores no image</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
+          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8077,50 +8085,42 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>README rule 6</t>
-        </is>
-      </c>
+      <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>CV/ML Engineer</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>package.json, tests/</t>
+          <t>skin-scan engine</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Owner approval + commit</t>
+          <t>Code read + runtime check</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr"/>
       <c r="P72" s="2" t="inlineStr"/>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>New dependency needs approval.</t>
-        </is>
-      </c>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Owner approves or declines.</t>
+          <t>Read-only check of the engine source and the container.</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
@@ -8135,14 +8135,14 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T16.</t>
+          <t>Proposed by privacy report T15.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>H13</t>
+          <t>H12</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -8157,17 +8157,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Processing consent after a draft restore</t>
+          <t>DOM test renderer</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
+          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8180,14 +8180,10 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-03a</t>
+          <t>README rule 6</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -8197,34 +8193,34 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
+          <t>package.json, tests/</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Decision + commit + tests</t>
+          <t>Owner approval + commit</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr"/>
       <c r="P73" s="2" t="inlineStr"/>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Owner action.</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>Owner decides whether restored drafts may carry the consent version.</t>
+          <t>New dependency needs approval.</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
+          <t>Owner approves or declines.</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
@@ -8239,14 +8235,14 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
+          <t>Proposed by privacy report T16.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>H14</t>
+          <t>H13</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -8261,12 +8257,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Withdraw AI-share consent in the UI</t>
+          <t>Processing consent after a draft restore</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
+          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -8281,22 +8277,22 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-16 / D-03a</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -8306,12 +8302,12 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
+          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Design check + commit + tests</t>
+          <t>Decision + commit + tests</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
@@ -8321,10 +8317,14 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>Owner decides whether restored drafts may carry the consent version.</t>
+        </is>
+      </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Check the design, then add a withdraw control.</t>
+          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
@@ -8339,14 +8339,14 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04.</t>
+          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>H15</t>
+          <t>H14</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Low-severity hardening from the security review</t>
+          <t>Withdraw AI-share consent in the UI</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
+          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -8381,11 +8381,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8393,17 +8401,17 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
+          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Design check + commit + tests</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr"/>
@@ -8416,7 +8424,7 @@
       <c r="R75" s="2" t="inlineStr"/>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Add isPlainUid to the upload key path; log name and code only.</t>
+          <t>Check the design, then add a withdraw control.</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
@@ -8431,14 +8439,14 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04 (pre-existing logging).</t>
+          <t>Security review 2026-10-04.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>H16</t>
+          <t>H15</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -8453,12 +8461,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Consent ledger write slows the scan response</t>
+          <t>Low-severity hardening from the security review</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
+          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -8476,16 +8484,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8493,17 +8493,17 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/route.ts</t>
+          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Commit + test + timing</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr"/>
@@ -8516,7 +8516,7 @@
       <c r="R76" s="2" t="inlineStr"/>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
+          <t>Add isPlainUid to the upload key path; log name and code only.</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
@@ -8531,39 +8531,39 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Verifier observation 2026-10-04 (a52f36d).</t>
+          <t>Security review 2026-10-04 (pre-existing logging).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H16</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Consent ledger write slows the scan response</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -8573,15 +8573,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr"/>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8589,13 +8593,17 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>app/api/skin-scan/route.ts</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Commit + test + timing</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr"/>
@@ -8605,32 +8613,32 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R77" s="2" t="inlineStr">
-        <is>
-          <t>Nothing longitudinal is deployed yet.</t>
-        </is>
-      </c>
+      <c r="R77" s="2" t="inlineStr"/>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V77" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>Verifier observation 2026-10-04 (a52f36d).</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -8645,12 +8653,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -8670,7 +8678,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
+          <t>A12, A13, B01, H01, H03</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -8681,13 +8689,13 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Recorded E2E run against prod</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr"/>
@@ -8699,17 +8707,17 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>Nothing longitudinal is deployed yet.</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>RELEASE</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -8722,32 +8730,32 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -8757,31 +8765,51 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr"/>
       <c r="P79" s="2" t="inlineStr"/>
-      <c r="Q79" s="2" t="inlineStr"/>
-      <c r="R79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -8794,7 +8822,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -8809,7 +8837,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -8866,7 +8894,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -8881,7 +8909,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>ML recommendation ranking</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -8938,7 +8966,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -8953,7 +8981,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Indian cross-user benchmark</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -9005,16 +9033,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V82" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -9029,7 +9053,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Forecasting</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -9081,7 +9105,83 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11048,7 +11148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12232,52 +12332,52 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>TD-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Native L*/a* are provisional research candidates only</t>
+          <t>Longitudinal lane owner decisions</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 screening</t>
+          <t>Longitudinal report section 4</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Keep b*, ITA, lbpEntropy</t>
+          <t>See longitudinal-report.md section 4</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Primary endpoints for the human study only; not validated measurements</t>
+          <t>(1) SKIN_STATE_CONTRACT_2.md text approved as written. (2) After an engine change the user stays at "not enough evidence" (engine_boundary) until D05 decides re-baselining (option a). (3) A baseline scan whose capture method differs from the latest is skipped (option b). (4) At most one scan per calendar day (server analyzedAt) counts toward the baseline (option c). All settings stay marked provisional</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Only survivors of screening</t>
+          <t>Owner instruction 2026-10-04 (wave-2 merge task)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
+          <t>longitudinal-report.md section 4</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>C03-C07</t>
+          <t>A20, D01, D02, D05, D06</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Owner may reverse before Phase 1 pre-registration</t>
+          <t>D05 design; validated noise (C07)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -12287,200 +12387,200 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>ACCEPTED for study design</t>
+          <t>DECIDED (owner, 2026-10-04). Decisions 3 and 4 are not built yet (D06). Tracker-local until A14.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>D-13 / D-24</t>
+          <t>TD-15</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal comparisons require comparability + noise/evidence</t>
+          <t>Rules lane owner decisions</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Naive % change misleads</t>
+          <t>Rules report section 5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Research-doc point ladder</t>
+          <t>See rules-report.md section 5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
+          <t>All four recommendations accepted: (1a) extra caution withholds the active; (2a) under a red flag the prescriber line is recorded but not shown; (3a) the questionnaire save records the step ids confirmed on this check, server-side; (4) inputSha256 hashes the ruleset version, catalogue version, catalogue content digest and the normalised six rule fields only</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Measurement noise unknown</t>
+          <t>Owner instruction 2026-10-04 (wave-2 merge task)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-13; D-24 uncommitted</t>
+          <t>rules-report.md section 5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>C02, D02, G01</t>
+          <t>E02, E05, E07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Clinical reviewer (E05) says otherwise</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (D-24 uncommitted)</t>
+          <t>DECIDED (owner, 2026-10-04). Tracker-local until A14.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>TD-16</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Recommender deterministic and versioned</t>
+          <t>Context lane owner decisions</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4 SKUs, ~6 rules</t>
+          <t>Context report section 5</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>DMN/rules engine; ML ranking</t>
+          <t>See context-report.md section 5</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Plain TS pure function + version constants</t>
+          <t>(1) CTX-1 quantity-to-metric mapping approved as provisional. (2) The strict (recall-first) comparison pre-filter stays until the offline check measures misfires. (3) The routine_as_directed claim type is removed (never in allowedClaims at runtime; the type in lib/contracts/ is not edited by this task). (4) The referral message carries no phone number until the owner supplies a verified one: deploy blocker F06</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Auditable</t>
+          <t>Owner instruction 2026-10-04 (wave-2 merge task)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-08</t>
+          <t>context-report.md section 5</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>E02, J02</t>
+          <t>F01-F04, F06, F08</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>&gt;20 SKUs or non-engineer rule authors</t>
+          <t>Offline evaluation result; owner supplies a verified helpline</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DECIDED (owner, 2026-10-04). Tracker-local until A14.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Gemini is explanation layer, not authority</t>
+          <t>Native L*/a* are provisional research candidates only</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Gemini hallucination/claims risk</t>
+          <t>Phase 0 screening</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Gemini owns context</t>
+          <t>Keep b*, ITA, lbpEntropy</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+          <t>Primary endpoints for the human study only; not validated measurements</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Only survivors of screening</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-14; GATE_02</t>
+          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>B04, F01-F04</t>
+          <t>C03-C07</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Owner may reverse before Phase 1 pre-registration</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (paid tier is release gate)</t>
+          <t>ACCEPTED for study design</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-13 / D-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -12490,174 +12590,360 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>No attribution/efficacy/forecasting</t>
+          <t>Longitudinal comparisons require comparability + noise/evidence</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Naive % change misleads</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Evidence tiers 3-4</t>
+          <t>Research-doc point ladder</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Prohibited in UI, Gemini, analytics</t>
+          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Measurement noise unknown</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-12</t>
+          <t>DECISION_LOG D-13; D-24 uncommitted</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>G02, J04, R08</t>
+          <t>C02, D02, G01</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Explicit owner approval</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>PROPOSED (D-24 uncommitted)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Client input never authoritative for measured state</t>
+          <t>Recommender deterministic and versioned</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Gate 02</t>
+          <t>4 SKUs, ~6 rules</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Rules tightening; server chat storage</t>
+          <t>DMN/rules engine; ML ranking</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Path-structural trust; authenticated Echo</t>
+          <t>Plain TS pure function + version constants</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Forgeable browser state</t>
+          <t>Auditable</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>DECISION_LOG D-08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>A09, B02-B04, C02</t>
+          <t>E02, J02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Open: client-asserted captureMethod/persistAttempt</t>
+          <t>&gt;20 SKUs or non-engineer rule authors</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED (branch); owner decision open</t>
+          <t>PROPOSED</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Gemini is explanation layer, not authority</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Gemini hallucination/claims risk</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Gemini owns context</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>DECISION_LOG D-14; GATE_02</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>B04, F01-F04</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Systems Architect</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>PROPOSED (paid tier is release gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>No attribution/efficacy/forecasting</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Evidence tiers 3-4</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Prohibited in UI, Gemini, analytics</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>DECISION_LOG D-12</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>G02, J04, R08</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Explicit owner approval</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>D-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Client input never authoritative for measured state</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Rules tightening; server chat storage</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Path-structural trust; authenticated Echo</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Forgeable browser state</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>A09, B02-B04, C02</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Open: client-asserted captureMethod/persistAttempt</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (branch); owner decision open</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>D-21</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Gate 01 stores raw analysis in scanAnalyses</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Raw preservation</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>skinStates collection</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>users/{uid}/scanAnalyses/{scanId}_{sha16}</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Immutable raw substrate</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>6e9081d</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Systems Architect</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>IMPLEMENTED (not deployed); ID duplicated in HEAD</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>bbe02da (wave 1 merged; wave-2 shapes and lanes prepared 2026-10-04); working tree still has uncommitted DECISION_LOG.md edits and untracked DATA_LOCALITY_DECISION.md from another session, left untouched (A14)</t>
+          <t>(see Last validated commit) wave-2 lanes longitudinal, rules and context merged and wired 2026-10-04; working tree still has uncommitted DECISION_LOG.md edits and untracked DATA_LOCALITY_DECISION.md from another session, left untouched (A14)</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>34% = DONE 25 / (total 82 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>38% = DONE 34 / (total 98 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 25, IN PROGRESS 1, NOT STARTED 16, BLOCKED 19, OWNER ACTION 14, LATER 8 (total 83)</t>
+          <t>DONE 34, IN PROGRESS 1, NOT STARTED 21, BLOCKED 15, OWNER ACTION 19, LATER 8 (total 98)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 21, NOT NEEDED 9, NOT CHECKED 52</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 33, NOT NEEDED 11, NOT CHECKED 53</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V84"/>
+  <dimension ref="A1:V99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3106,7 +3106,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3121,17 +3121,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SkinState contract version: engine_build and client-asserted fields</t>
+          <t>D-24 missing from DECISION_LOG</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>New contract version (skinstate-2) that maps engine_build, and names captureMethod, persistAttempt and captureQuality as client-asserted, with the bound (a forged captureMethod can only merge two capture paths). Also: provenance.processingConsentVersion is still null in skinstate-1.</t>
+          <t>D-24 is cited by the longitudinal brief, the shared shape and D02, but DECISION_LOG.md in HEAD has no D-24 entry.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>A07, A12, A13</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>D-23 / D-26 (O-1 A)</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3166,34 +3166,26 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>docs/architecture/SKIN_STATE_CONTRACT_FINAL.md, lib/skin-state.ts</t>
+          <t>docs/architecture/DECISION_LOG.md</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Owner-approved contract text + commit + tests</t>
+          <t>Committed D-24 entry</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>Not started (owner: do not do now).</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>A new contract version needs owner approval (D-23); the owner asked for it to be built in the longitudinal lane (2026-10-04), design gate first.</t>
-        </is>
-      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Draft skinstate-2 for owner approval; C02 stays blocked until it lands. Lane: longitudinal (branch lane/longitudinal, brief docs/lanes/longitudinal.md); results come via docs/lanes/longitudinal-report.md at merge.</t>
+          <t>Resolve with A14 (DECISION_LOG.md has uncommitted edits from another session; this task left it untouched).</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>TRUSTED MEASUREMENT</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3203,14 +3195,14 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Proposed by capture report section 4 (main 1, 2) and section 5 (D-26 amendment).</t>
+          <t>Longitudinal report 5.5; Owner instruction 2026-10-04 (wave-2 merge task).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3225,31 +3217,39 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Architecture docs alignment after the lane merges</t>
+          <t>Wave-2 merge, shared-shape edits and integration wiring</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL_METHOD section 3 and the capture brief (quality-gate steps 2 and 5 unmet until a server producer exists); RECOMMENDATION_MODEL sections 3 and 8, DATA_MODEL Events row, SYSTEM_MODEL C16, B14, IMPLEMENTATION_MAP C8 (lib/catalog/ folder, R-1 A, R-6 A); docs/lanes/routine.md (owned files, line 23 "allow create" -&gt; R-6 A); SKIN_STATE_CONTRACT_FINAL.md:269 (processing consent now versioned).</t>
+          <t>Merge lane/longitudinal, lane/rules, lane/context; three owner-approved lib/contracts edits; wiring items 1-8 (item 9 is E07).</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>TD-13, TD-14, TD-15, TD-16</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3257,30 +3257,38 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>docs/architecture/, docs/lanes/</t>
+          <t>lib/contracts/, lib/context/chat.ts, lib/skin-state-2-loader.ts, lib/gemini.ts, lib/rules/safety.ts, lib/scan-analysis-record.ts</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Committed doc edits</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
+          <t>Merges + commits + tests + verifier</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Merges clean (no conflicts). Shapes: not_evaluated comparability, histogram_quantity reason, internal SafetyState.extraCautionRaisedBy (banned from the package), position and inputSha256 comments; verifier PASS. Wiring: 1 loader, 2 real inputs, 3 one caution list, 4 fail-closed fallback, 5 guard forwarding, 6 processingConsentVersion stored, 7 erase removes chatTurns, 8 catalogue screen test. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>merges 53d0894, 7da1a54, dda2a91; eee588c, 077330a, 64b4b8c, 7fe39da, ad98ac5, 3f61b3e, 4ae015e, 73380c8, bd6bb86</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Local only. Final verifier and security review recorded in section 4.</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Edit the named sections; document task.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3295,14 +3303,14 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Proposed by capture report section 4 (main 3); routine report rows T2, T4, T5; verifier 2026-10-04.</t>
+          <t>Owner instruction 2026-10-04 (wave-2 merge task).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3317,12 +3325,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Lint coverage of tests/</t>
+          <t>Map processingConsentVersion in a new SkinState contract version</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>npm run lint does not lint tests/. npx next lint --dir tests still reports one error: tests/privacy-erase.test.ts:18 unused "_".</t>
+          <t>scanAnalyses now stores processingConsentVersion (4ae015e), but skinstate-1 (frozen) and skinstate-2 (approved text) map provenance.processingConsentVersion to null.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3340,44 +3348,48 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>D-23</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>tests/, package.json lint script</t>
+          <t>lib/skin-state-2.ts</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Commit + lint output</t>
+          <t>Owner-approved contract text + commit + tests</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>Not started. Found 2026-10-04 while fixing tests/api-chat-auth.test.ts (73d85cf).</t>
-        </is>
-      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Fix the one error; decide whether npm run lint should cover tests/.</t>
+          <t>Fold into the next contract version; records written before 4ae015e stay null.</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>FOUNDATION</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3385,132 +3397,124 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Longitudinal report 5.4.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Dev/prod separation</t>
+          <t>Lane ownership table names lane design documents</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
+          <t>docs/lanes/README.md ownership table should list docs/lanes/&lt;lane&gt;-design.md (capture-design.md is the precedent).</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Program Lead</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
+          <t>docs/lanes/README.md</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>ff08107 (unmerged)</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
-        </is>
-      </c>
+          <t>Committed doc</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Agent part done in B07 (local stack, no production keys; next dev refuses production values). Owner: remove FIREBASE_PRIVATE_KEY, FIREBASE_CLIENT_EMAIL and S3_SKIN_IMAGES_* from .env.local and the Desktop adminsdk JSON, then rotate the Admin key.</t>
+          <t>Edit the README before the next wave.</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Longitudinal report 5.6.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Server-authoritative analysis writes</t>
+          <t>SkinState contract version: engine_build and client-asserted fields</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Browser is not authoritative for analysis-derived scores.</t>
+          <t>New contract version (skinstate-2) that maps engine_build, and names captureMethod, persistAttempt and captureQuality as client-asserted, with the bound (a forged captureMethod can only merge two capture paths). Also: provenance.processingConsentVersion is still null in skinstate-1.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3525,58 +3529,58 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A07, A12, A13</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>D-02 / D-26</t>
+          <t>D-23 / D-26 (O-1 A)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan, lib/skin-state*</t>
+          <t>lib/skin-state-2.ts, lib/skin-state-2-loader.ts, docs/architecture/SKIN_STATE_CONTRACT_2.md</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Owner-approved contract text + commit + tests</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
+          <t>skinstate-2 next to skinstate-1 (frozen, unchanged): maps engine_build, names captureMethod, persistAttempt, captureQuality client-asserted (CLIENT_ASSERTED). Contract text approved by the owner 2026-10-04 (TD-14). Server-only series loader loadTrustedSkinState2Series (077330a). Tests: skin-state-2 (11), comparability-2 (7), skin-state-2-loader (7), longitudinal-series.e2e. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6e9081d, 155cb69</t>
+          <t>1b0dd32, 1d69f61; merge 53d0894; loader 077330a</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
+          <t>Local only. provenance.processingConsentVersion stays null in both contracts; the field is now stored on scanAnalyses (4ae015e), mapping it needs a new contract version (A26).</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
+          <t>A26 when a contract version is next opened.</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3586,62 +3590,58 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 4 (main 1, 2) and section 5 (D-26 amendment).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Echo authentication and ownership</t>
+          <t>Architecture docs alignment after the lane merges</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Echo derives identity/context server-side and verifies ownership.</t>
+          <t>docs/lanes/longitudinal-design.md §2 still describes the all-unknown-key convention replaced by not_evaluated (eee588c). LONGITUDINAL_METHOD section 3 and the capture brief (quality-gate steps 2 and 5 unmet until a server producer exists); RECOMMENDATION_MODEL sections 3 and 8, DATA_MODEL Events row, SYSTEM_MODEL C16, B14, IMPLEMENTATION_MAP C8 (lib/catalog/ folder, R-1 A, R-6 A); docs/lanes/routine.md (owned files, line 23 "allow create" -&gt; R-6 A); SKIN_STATE_CONTRACT_FINAL.md:269 (processing consent now versioned).</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Gate 02 / D-26</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3649,103 +3649,91 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-check/chat</t>
+          <t>docs/architecture/, docs/lanes/</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + live E2E</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>skin-check-chat-auth tests (13); cross-user 409</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>155cb69, 955c1cc</t>
-        </is>
-      </c>
+          <t>Committed doc edits</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr"/>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; verify live in I01.</t>
+          <t>Edit the named sections; document task.</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>TRUSTED MEASUREMENT</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 4 (main 3); routine report rows T2, T4, T5; verifier 2026-10-04.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Trust / Security</t>
+          <t>Foundation / Architecture</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Gemini browser-state isolation</t>
+          <t>Lint coverage of tests/</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Gemini never trusts browser-supplied scores/context.</t>
+          <t>npm run lint does not lint tests/. npx next lint --dir tests still reports one error: tests/privacy-erase.test.ts:18 unused "_".</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Gate 02 / D-26</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -3753,48 +3741,40 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
+          <t>tests/, package.json lint script</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + live E2E</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>155cb69, 955c1cc</t>
-        </is>
-      </c>
+          <t>Commit + lint output</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
+          <t>Not started. Found 2026-10-04 while fixing tests/api-chat-auth.test.ts (73d85cf).</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Deploy via A13; verify live in I01.</t>
+          <t>Fix the one error; decide whether npm run lint should cover tests/.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>FOUNDATION</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
@@ -3802,7 +3782,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>B07</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -3817,22 +3797,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Local stack with no production keys</t>
+          <t>Dev/prod separation</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Firebase Auth + Firestore emulators with the real rules, local engine 0.1.6, S3Mock, Gemini dev key or test fake, seed data, dev guard, one start and one test command.</t>
+          <t>Stop local dev writing production resources; emulators / isolated dev resources.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3844,43 +3824,47 @@
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>scripts/local-stack*.sh, scripts/seed-local.ts, .env.development.example, lib/dev-env-guard.cjs, lib/gemini-key.ts, lib/firebase/{client,admin}.ts, lib/s3.ts, next.config.js</t>
+          <t>.env.local, lib/firebase/client.ts, lib/firebase/admin.ts</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests + end-to-end run</t>
+          <t>Admin key removed from laptops + rotated; S3 vars unset or dev bucket; emulator switch committed</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>npm run test:local: unit 242 passed / 25 skipped, rules 24/24, end-to-end 1/1 (seeded phone user signs in via Auth emulator, upload to S3Mock, scan via local 0.1.6 engine, scanAnalyses + skinChecks saved in emulator); also green at PORT_BASE=3200. next dev with only .env.local refuses to start (7 variables named). typecheck 0, lint clean.</t>
+          <t>DEV_PROD_BOUNDARY.md (on ff08107)</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9ea6ad5, 6758fe6, 0fc1e57</t>
+          <t>ff08107 (unmerged)</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Local only. No UI click-through: the end-to-end test drives the real dev server through its HTTP API and the client SDK.</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr"/>
+          <t>Not started. Verified 2026-10-03 (variable names only, no values read): .env.local defines FIREBASE_PRIVATE_KEY/FIREBASE_CLIENT_EMAIL, S3_SKIN_IMAGES_ACCESS_KEY_ID/SECRET, SCAN_API_SECRET with SKIN_SCAN_API_URL=https://api.theprojectskin.com, GEMINI_API_KEY; no emulator variables.</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Credential removal/rotation and dev resources need the owner; emulator code switch needs an approved gate.</t>
+        </is>
+      </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Owner: fill GEMINI_DEV_API_KEY in .env.development.local when a separate dev key exists.</t>
+          <t>Agent part done in B07 (local stack, no production keys; next dev refuses production values). Owner: remove FIREBASE_PRIVATE_KEY, FIREBASE_CLIENT_EMAIL and S3_SKIN_IMAGES_* from .env.local and the Desktop adminsdk JSON, then rotate the Admin key.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3893,16 +3877,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Plain npm run dev with today's .env.local now refuses to start; use npm run dev:local.</t>
-        </is>
-      </c>
+      <c r="V29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3917,79 +3897,83 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Vercel Preview holds production secrets</t>
+          <t>Server-authoritative analysis writes</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Vercel env Preview scope has production SKIN_SCAN_API_URL, SCAN_API_SECRET, GEMINI_API_KEY (names from vercel env ls, 2026-10-03). Any pushed branch (lane/*, longitudinal-platform) gets a preview that calls the production engine and Gemini.</t>
+          <t>Browser is not authoritative for analysis-derived scores.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-02 / D-26</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Vercel project skin-check env (Preview)</t>
+          <t>app/api/skin-scan, lib/skin-state*</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>vercel env ls showing Preview without production secrets, or a decision to keep them</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>vercel env ls (names and targets only)</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr"/>
+          <t>scanAnalyses written server-side; SkinState trust is path-structural</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>6e9081d, 155cb69</t>
+        </is>
+      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>Changing Vercel env is the owner's action.</t>
-        </is>
-      </c>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: dashboard still renders browser-held result (GATE_02 7.3); skinChecks.result remains owner-writable but no consumer reads it.</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Owner: remove the Preview copies of SCAN_API_SECRET, SKIN_SCAN_API_URL and GEMINI_API_KEY (or use separate preview values); until then do not push lane/* branches.</t>
+          <t>Deploy via A13; dashboard read path moves to server state in G01.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3997,16 +3981,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Found while preparing lanes.</t>
-        </is>
-      </c>
+      <c r="V30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>B09</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -4021,31 +4001,39 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Rate-limit store and per-route buckets</t>
+          <t>Echo authentication and ownership</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Routine writes are capped in memory per instance (200/uid/day); account routes share the scan bucket (5/min/IP); ledger appends per purpose are not capped (latestGrant reads all ai_share entries; fails closed).</t>
+          <t>Echo derives identity/context server-side and verifies ownership.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02 / D-26</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4053,52 +4041,56 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>lib/rate-limit.ts, app/api/routine/events, app/api/account/*</t>
+          <t>app/api/skin-check/chat</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
+          <t>Commit + tests + live E2E</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>skin-check-chat-auth tests (13); cross-user 409</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Production Echo is unauthenticated today.</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr"/>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Move limits to a shared store if a hard global cap is needed; give account routes their own bucket; cap ledger appends per purpose.</t>
+          <t>Deploy via A13; verify live in I01.</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>TRUSTED MEASUREMENT</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by routine report T3; privacy report T11.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4113,12 +4105,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss npx firebase form</t>
+          <t>Gemini browser-state isolation</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
+          <t>Gemini never trusts browser-supplied scores/context.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4133,11 +4125,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02 / D-26</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4145,39 +4145,43 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json</t>
+          <t>lib/echo-trusted-context.ts, lib/gemini.ts</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules</t>
+          <t>Commit + tests + live E2E</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
+          <t>Strict body schema rejects scores/uid; HMAC-signed history</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>ae457a0, 44e0352</t>
+          <t>155cb69, 955c1cc</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
+          <t>Implemented on branch longitudinal-platform only. NOT deployed: production frontend is 1b39f88 (master), which contains none of gates 01-04. Residual: user's own name still in system instruction (GATE_02 7.12).</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Deploy via A13; verify live in I01.</t>
+        </is>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4185,16 +4189,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
-        </is>
-      </c>
+      <c r="V32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Deny rules miss other production-changing commands</t>
+          <t>Local stack with no production keys</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
+          <t>Firebase Auth + Firestore emulators with the real rules, local engine 0.1.6, S3Mock, Gemini dev key or test fake, seed data, dev guard, one start and one test command.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4229,14 +4229,10 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>B05</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -4245,36 +4241,40 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>.claude/settings.json</t>
+          <t>scripts/local-stack*.sh, scripts/seed-local.ts, .env.development.example, lib/dev-env-guard.cjs, lib/gemini-key.ts, lib/firebase/{client,admin}.ts, lib/s3.ts, next.config.js</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Commit with added rules + echo probe</t>
+          <t>Commit + tests + end-to-end run</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+          <t>npm run test:local: unit 242 passed / 25 skipped, rules 24/24, end-to-end 1/1 (seeded phone user signs in via Auth emulator, upload to S3Mock, scan via local 0.1.6 engine, scanAnalyses + skinChecks saved in emulator); also green at PORT_BASE=3200. next dev with only .env.local refuses to start (7 variables named). typecheck 0, lint clean.</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2371f78</t>
+          <t>9ea6ad5, 6758fe6, 0fc1e57</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
+          <t>Local only. No UI click-through: the end-to-end test drives the real dev server through its HTTP API and the client SDK.</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>Owner: fill GEMINI_DEV_API_KEY in .env.development.local when a separate dev key exists.</t>
+        </is>
+      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
           <t>PRIVACY/SAFETY</t>
@@ -4287,44 +4287,44 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+          <t>Plain npm run dev with today's .env.local now refuses to start; use npm run dev:local.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Guided capture quality gate</t>
+          <t>Vercel Preview holds production secrets</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
+          <t>Vercel env Preview scope has production SKIN_SCAN_API_URL, SCAN_API_SECRET, GEMINI_API_KEY (names from vercel env ls, 2026-10-03). Any pushed branch (lane/*, longitudinal-platform) gets a preview that calls the production engine and Gemini.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4335,117 +4335,109 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Capture design (O-1..O-5, Q-1, Q-2; TD-05, TD-06)</t>
+          <t>D-26</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>lib/capture-quality/, components/skin-check/inputs/PhotoCapture.tsx, app/api/skin-scan/route.ts, lib/scan-retry.ts, SkinCheckDashboard.tsx</t>
+          <t>Vercel project skin-check env (Preview)</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Design doc + approved gate + tests</t>
+          <t>vercel env ls showing Preview without production secrets, or a decision to keep them</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Built (lane capture, merged 2970c86): exposure, blur (per capture path), resolution checks on the exact blob sent to the engine; gate verdict pass/retake/unchecked/override; soft block with override after 2 retakes (O-4 B); engine refusal codes become named retake reasons (O-5 A); captureQuality saved on scanAnalyses as client-asserted, schemaVersion 1 (O-2 A), never used for comparability (Q-2). Dashboard (capture requests 1 and 2, 102aeaa): a refused photo shows "Retake photo" (new scan) and no retry of the same photo; the retry carries captureQuality and keeps quality. Tests: capture-* (settings, exposure, blur, resolution, gate, retake, api-code, persist), scan-retry, capture.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier (fresh, 2026-10-04): capture PASS.</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>88a7505, da6ebfb, e45dcab, 3acb41d, 1f053cf, d29253a, 747df17, 9ec59f3; merge 2970c86; 102aeaa</t>
-        </is>
-      </c>
+          <t>vercel env ls (names and targets only)</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Local only; not deployed (TD-04). Thresholds provisional (cq-settings-0-provisional). Gate result is client-asserted.</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Changing Vercel env is the owner's action.</t>
+        </is>
+      </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Open: pose, expression, distance and framing are not measured (O-3 C, no landmark library; they report not_measured) -&gt; C08. Thresholds from the R05 real-device sweep -&gt; C09. Deploy with A13.</t>
+          <t>Owner: remove the Preview copies of SCAN_API_SECRET, SKIN_SCAN_API_URL and GEMINI_API_KEY (or use separate preview values); until then do not push lane/* branches.</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Report: docs/lanes/capture-report.md.</t>
+          <t>Found while preparing lanes.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Per-region / per-metric comparability</t>
+          <t>Rate-limit store and per-route buckets</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Decide whether two scans are comparable before computing change.</t>
+          <t>Routine writes are capped in memory per instance (200/uid/day); account routes share the scan bucket (5/min/IP); ledger appends per purpose are not capped (latestGrant reads all ai_share entries; fails closed).</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>A07, A12, A13, A20, C07</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>D-13 / D-26 (O-1 A, TD-05)</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4453,47 +4445,35 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>lib/comparability.ts</t>
+          <t>lib/rate-limit.ts, app/api/routine/events, app/api/account/*</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Comparability function + tests + noise inputs</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane capture, merged 2970c86): comparabilityKey, compareKeys, compareStates. Output comparable / not_comparable with named reasons in a fixed order; no numbers, percentages or direction. Fails closed: COMPARABLE_QUANTITIES is empty, and skinstate-1 maps engine.build to null, so every real pair is not_comparable (quantity_not_validated, engine_build_unknown). captureMethod stays in the key, marked client-asserted (O-1 A). Tests: comparability, comparability-wording, capture.e2e (seed is never comparable). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>afb7fe2, 94512b7; merge 2970c86</t>
-        </is>
-      </c>
+          <t>Commit + tests</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Local only. Cannot say comparable on real data yet.</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>A new SkinState contract version that maps engine_build (A20); per-quantity validation needs C05-C07.</t>
-        </is>
-      </c>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>A20 (contract version), then fill COMPARABLE_QUANTITIES from C07.</t>
+          <t>Move limits to a shared store if a hard global cap is needed; give account routes their own bucket; cap ledger appends per purpose.</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4503,55 +4483,59 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Q-2: the browser quality result never feeds comparability; quality enters only via a server producer (C08).</t>
+          <t>Proposed by routine report T3; privacy report T11.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>B10</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Human measurement validation protocol</t>
+          <t>Per-user Gemini quota</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Protocol for human validation and repeatability.</t>
+          <t>GEMINI_BOUNDARY §3 step 2: a uid-keyed Firestore quota for chat. Only the existing IP quota exists.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>B09</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>D-24 (uncommitted)</t>
+          <t>GEMINI_BOUNDARY §3</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -4561,98 +4545,86 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>app/api/skin-check/chat/route.ts, lib/rate-limit.ts</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Committed protocol</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>59d9923</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
-        </is>
-      </c>
+          <t>Quota + tests (emulator)</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
+          <t>Design with B09.</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Context report §6; Owner instruction 2026-10-04 (wave-2 merge task).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Human validation pilot</t>
+          <t>Deny rules miss npx firebase form</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Run pilot of C03 protocol.</t>
+          <t>Deny rules match `firebase …` and `* firebase …` but not `npx -y firebase-tools@latest firestore:databases:delete` or `… deploy`, the form the runbooks use.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>C03, A12, A13, H01</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4661,39 +4633,39 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>docs/research/measurement-validation/</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Pre-registration + pilot dataset + report</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
+          <t>Commit with added rules</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Rules rewritten with leading/trailing wildcards. Probe 2026-10-03 with harmless echo commands, one per call: 36 forms denied, 3 controls allowed (terraform plan, F firestore:indexes, a firebase-tools string). Firebase matrix: 6 prefixes (firebase, npx firebase, npx firebase-tools, with and without -y, with and without @latest) x 3 commands (firestore:databases:delete, firestore:delete, deploy), plus the runbook F function x 3, all denied. Also denied: bare and -chdir terraform apply/destroy, aws ecs update-service/register-task-definition bare and with --region or env first, gcloud --project ... firestore databases delete, bare vc --prod, vc --target=production, vercel --target production, npx vercel --prod, vercel/vc promote. Bare 'F deploy' passed the first rule set; fixed by Bash(*F deploy*). MCP firestore_delete_document denied (tool disappeared from the session).</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>ae457a0, 44e0352</t>
+        </is>
+      </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
-        </is>
-      </c>
+          <t>Done. Side effect: any Bash command whose text contains a blocked string is denied, including git commit -m messages; use git commit -F.</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4701,52 +4673,56 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 while writing the Phase 0 runbook. Other production-changing commands are still not denied: B06.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Measurement Quality</t>
+          <t>Trust / Security</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Full test-retest / calibration</t>
+          <t>Deny rules miss other production-changing commands</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
+          <t>Not denied: vercel rollback, gh pr merge (merging to master is the production deploy), git push, docker push, aws ecs deregister-task-definition, aws ecr batch-delete-image, firestore:databases:update (can disable delete protection), firestore:backups:schedules:*, MCP firestore_update_database. The kept MCP deny entries firestore_delete_database and firebase_deploy match no tool in the current Firebase MCP server (kept in case a later version adds them). Only the CLAUDE.md hard rules stop agents.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -4757,35 +4733,39 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>.claude/settings.json</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Pre-registered study report</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr"/>
+          <t>Commit with added rules + echo probe</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Probe 2026-10-03 with harmless echo commands, one per call: 32 forms denied, 12 controls allowed. Denied: gh pr merge (also gh -R ... pr merge); vercel/npx vercel/vc rollback; aws ecs deregister-task-definition and aws ecr batch-delete-image (bare, --region first, env first); firestore:databases:update with firebase, npx firebase, npx firebase-tools, -y, @latest, -y @latest and F; gcloud firestore databases update; git push origin master, -u origin master, master --force, HEAD:master, x:master, +master, x:refs/heads/master, git -C dir push origin master, --all, --mirror; docker push / docker image push / buildx --push (either order) to 550428926515.dkr.ecr.ap-south-1.amazonaws.com, and docker push with a $ variable target. MCP firestore_update_database denied (tool disappeared from the session). Allowed: git push origin longitudinal-platform, feature/master-notes, master-fix, bare git push, git push --delete; docker push to ghcr.io and to another ECR account; gh pr create --base master; gh pr view; git fetch origin master; read-only aws and F commands.</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2371f78</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>Waits on C04 pilot.</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>Size from pilot variance.</t>
-        </is>
-      </c>
+          <t>Done. Still allowed (patterns cannot see branch or variable values): bare git push or git push origin HEAD while on master; git push origin "$B" with B=master. Side effect: any command whose text contains a blocked string is denied (e.g. a commit message mentioning 'push origin master'); use git commit -F.</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4793,12 +4773,16 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-03 during B05. Owner decision 2026-10-03: deny these; other git push and docker push forms stay allowed.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -4813,35 +4797,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Tone-stratified validation / model card</t>
+          <t>Guided capture quality gate</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
+          <t>On-device checks: pose, expression, exposure, distance, blur, framing; retake loop.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>C05</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Capture design (O-1..O-5, Q-1, Q-2; TD-05, TD-06)</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4849,30 +4833,38 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>lib/capture-quality/, components/skin-check/inputs/PhotoCapture.tsx, app/api/skin-scan/route.ts, lib/scan-retry.ts, SkinCheckDashboard.tsx</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Per-band results + model card</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
+          <t>Design doc + approved gate + tests</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane capture, merged 2970c86): exposure, blur (per capture path), resolution checks on the exact blob sent to the engine; gate verdict pass/retake/unchecked/override; soft block with override after 2 retakes (O-4 B); engine refusal codes become named retake reasons (O-5 A); captureQuality saved on scanAnalyses as client-asserted, schemaVersion 1 (O-2 A), never used for comparability (Q-2). Dashboard (capture requests 1 and 2, 102aeaa): a refused photo shows "Retake photo" (new scan) and no retry of the same photo; the retry carries captureQuality and keeps quality. Tests: capture-* (settings, exposure, blur, resolution, gate, retake, api-code, persist), scan-retry, capture.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier (fresh, 2026-10-04): capture PASS.</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>88a7505, da6ebfb, e45dcab, 3acb41d, 1f053cf, d29253a, 747df17, 9ec59f3; merge 2970c86; 102aeaa</t>
+        </is>
+      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>Waits on C05 data.</t>
-        </is>
-      </c>
+          <t>Local only; not deployed (TD-04). Thresholds provisional (cq-settings-0-provisional). Gate result is client-asserted.</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Define model card template alongside C05.</t>
+          <t>Open: pose, expression, distance and framing are not measured (O-3 C, no landmark library; they report not_measured) -&gt; C08. Thresholds from the R05 real-device sweep -&gt; C09. Deploy with A13.</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -4882,15 +4874,19 @@
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Report: docs/lanes/capture-report.md.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -4905,12 +4901,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Validated measurement/noise tables</t>
+          <t>Per-region / per-metric comparability</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
+          <t>Decide whether two scans are comparable before computing change.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -4920,7 +4916,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4930,10 +4926,14 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>C05, C06</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>A07, A12, A13, A20, C07</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>D-13 / D-26 (O-1 A, TD-05)</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -4944,49 +4944,61 @@
           <t>Measurement Scientist</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>lib/comparability.ts</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Versioned noise table tied to engine build</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="2" t="inlineStr"/>
+          <t>Comparability function + tests + noise inputs</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane capture, merged 2970c86): comparabilityKey, compareKeys, compareStates; fails closed (COMPARABLE_QUANTITIES empty). Wave 2: accepts skinstate-2, which maps engine_build, so real pairs can match on the build and are still quantity_not_validated (1d69f61). The longitudinal engine forwards its test-only table through the guard under one allowed name, with positive controls (64b4b8c). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>afb7fe2, 94512b7; merge 2970c86; 1d69f61; 64b4b8c</t>
+        </is>
+      </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Local only. Cannot say comparable on real data yet.</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Waits on C05/C06.</t>
+          <t>Per-quantity validation needs C05-C07.</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Fix table schema (field x region x band x engine build).</t>
+          <t>Fill COMPARABLE_QUANTITIES from C07. A20 is done.</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
+          <t>Q-2: the browser quality result never feeds comparability; quality enters only via a server producer (C08).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -5001,74 +5013,74 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Server-side capture quality from engine landmarks</t>
+          <t>Human measurement validation protocol</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Derive pose, distance (face scale) and framing on the server from the engine's mediapipe face landmarks, as a separately versioned quality producer. The only route by which quality can enter comparability (Q-2).</t>
+          <t>Protocol for human validation and repeatability.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>D-18 (engine work)</t>
+          <t>D-24 (uncommitted)</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>CV/ML Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>skin-scan engine; app/api/skin-scan</t>
+          <t>docs/research/measurement-validation/</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Owner approval under D-18 + design + tests</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
+          <t>Committed protocol</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>PROTOCOL.md, ANALYSIS_PLAN.md, ACCEPTANCE_CRITERIA.md, DATA_SPEC.md</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>59d9923</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>Engine work needs owner approval (D-18).</t>
-        </is>
-      </c>
+          <t>Design only; not executed. D-24 adopting it exists only as uncommitted working-tree text.</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Write a design for owner approval.</t>
+          <t>Commit D-24 (A14); owner may revise MD-1 endpoint cut before Phase 1 pre-registration (D-25).</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -5078,19 +5090,15 @@
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by capture report section 5 (O-3 C follow-up).</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -5105,12 +5113,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Capture thresholds from the R05 sweep</t>
+          <t>Human validation pilot</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Replace the provisional capture-quality settings (lib/capture-quality/settings.ts) with values from the R05 real-device sweep; bump settingsVersion.</t>
+          <t>Run pilot of C03 protocol.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5125,12 +5133,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>C03, A12, A13, H01</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -5146,12 +5154,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>lib/capture-quality/settings.ts</t>
+          <t>docs/research/measurement-validation/</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sweep results + commit + tests</t>
+          <t>Pre-registration + pilot dataset + report</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
@@ -5163,12 +5171,12 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Needs the R05 real-device data.</t>
+          <t>Protocol scores via the production HTTP path (D-24), which needs 0.1.6 + gate 04 deployed (A12, A13); consent (H01); owner approval of recruitment, devices, budget, ColorChecker/colorimeter.</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>After R05: set values, bump settingsVersion.</t>
+          <t>Owner approves pilot logistics; pre-register Phase 1.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -5178,39 +5186,35 @@
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by capture report section 5.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Baseline window definition</t>
+          <t>Full test-retest / calibration</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>How a user's baseline is formed.</t>
+          <t>D0/D7/D28 test-retest per field x region x tone band.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5225,12 +5229,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5247,7 +5251,7 @@
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Method doc + decision</t>
+          <t>Pre-registered study report</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
@@ -5259,22 +5263,22 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Needs between-day noise (C07).</t>
+          <t>Waits on C04 pilot.</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Draft candidate baseline rules against LONGITUDINAL_METHOD.md. Lane: longitudinal (branch lane/longitudinal, brief docs/lanes/longitudinal.md); results come via docs/lanes/longitudinal-report.md at merge.</t>
+          <t>Size from pilot variance.</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr"/>
@@ -5282,27 +5286,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Change-vs-noise engine</t>
+          <t>Tone-stratified validation / model card</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
+          <t>Performance/noise across MST bands 1-4/5-6/7-10; documented limitations.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5322,14 +5326,10 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>C02, C07, D01</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>D-13 / D-24</t>
-        </is>
-      </c>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5337,13 +5337,13 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Engine + tests + noise table version</t>
+          <t>Per-band results + model card</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
@@ -5355,22 +5355,22 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Needs comparability (C02) and validated noise (C07).</t>
+          <t>Waits on C05 data.</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Wait; design pairwise interface first (D-13). Lane: longitudinal (branch lane/longitudinal, brief docs/lanes/longitudinal.md); results come via docs/lanes/longitudinal-report.md at merge.</t>
+          <t>Define model card template alongside C05.</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr"/>
@@ -5378,27 +5378,27 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Persistence/evidence tiers</t>
+          <t>Validated measurement/noise tables</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Separate transient observations from persistent patterns.</t>
+          <t>Empirical reliability, SEM/MDC95, metric/region conditions.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C05, C06</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -5435,7 +5435,7 @@
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Tier definitions + tests</t>
+          <t>Versioned noise table tied to engine build</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
@@ -5447,59 +5447,59 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Needs D02.</t>
+          <t>Waits on C05/C06.</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Wait on D02. Lane: longitudinal (branch lane/longitudinal, brief docs/lanes/longitudinal.md); results come via docs/lanes/longitudinal-report.md at merge.</t>
+          <t>Fix table schema (field x region x band x engine build).</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
+          <t>Provisional candidates only: native L* (cheeks, forehead), native a* (cheeks, nose). Not validated.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Scheduled anchor scans / irregular sampling</t>
+          <t>Server-side capture quality from engine landmarks</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sampling strategy.</t>
+          <t>Derive pose, distance (face scale) and framing on the server from the engine's mediapipe face landmarks, as a separately versioned quality producer. The only route by which quality can enter comparability (Q-2).</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5509,73 +5509,101 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr"/>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>D-18 (engine work)</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>CV/ML Engineer</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>skin-scan engine; app/api/skin-scan</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Owner approval under D-18 + design + tests</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>Not started (owner: do not do now).</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Engine work needs owner approval (D-18).</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Revisit after D02.</t>
+          <t>Write a design for owner approval.</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 5 (O-3 C follow-up).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Intelligence</t>
+          <t>Measurement Quality</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Engine-version re-baselining</t>
+          <t>Capture thresholds from the R05 sweep</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Handle engine build changes across history.</t>
+          <t>Replace the provisional capture-quality settings (lib/capture-quality/settings.ts) with values from the R05 real-device sweep; bump settingsVersion.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5585,12 +5613,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -5599,59 +5627,83 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>lib/capture-quality/settings.ts</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Sweep results + commit + tests</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Needs the R05 real-device data.</t>
+        </is>
+      </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Revisit at first engine change after D02.</t>
+          <t>After R05: set values, bump settingsVersion.</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>LONGITUDINAL INTELLIGENCE</t>
+          <t>CALIBRATION</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by capture report section 5.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Product catalog normalization</t>
+          <t>Baseline window definition</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
+          <t>How a user's baseline is formed.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5664,60 +5716,56 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>D-08 / D-09 / D-12 (TD-07)</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>lib/catalog/</t>
+          <t>lib/longitudinal/settings.ts, lib/longitudinal/baseline.ts</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Owner-supplied master data + versioned schema</t>
+          <t>Method doc + decision</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Built (lane routine, merged daa0b4a): versioned catalogue schema, synthetic sample, owner template lib/catalog/catalogue-template.csv with a drift check, D-12 word check with the exact-name exception (PRODUCT_NAME_EXCEPTIONS). Tests: catalog-schema (20). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+          <t>BASELINE_RULE = first 3 comparable scans, named and PROVISIONAL. A scan unusable on its own (missing region, low pixels, no native stats, unknown capture method) is skipped; engine identity never skips one, so a window never crosses an engine change. Tests: longitudinal-baseline (7), engine skip cases. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>e45da38; merge daa0b4a</t>
+          <t>lane/longitudinal 1b0dd32, 1d69f61, 0bd5c08, 087fb2c, 8095b72, 330991f; merge 53d0894</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Schema only; data is synthetic (R-3 A).</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>Owner catalogue data. Deploy blocker (routine T1): the deploy is blocked while any product has dataSource "synthetic".</t>
-        </is>
-      </c>
+          <t>Local only. The shipped rule predates owner decisions TD-14 (3) and (4): a different capture method still blocks rather than being skipped, and retakes on one day can fill the baseline. Both are D06.</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Owner fills lib/catalog/catalogue-template.csv (fields: routine-report.md section 6), including "Clear Seal" as an owner row; then replace the synthetic CATALOGUE. OPEN-R1 answered by R-2 B (no product cards for now).</t>
+          <t>D06 (capture-method skip, one scan per day).</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5727,59 +5775,59 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Proposed D-12 clarification (registered own-brand name is not by itself a claim) recorded in TD-07.</t>
+          <t>Owner decisions TD-14 (2026-10-04). All settings provisional.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Product eligibility / safety rules</t>
+          <t>Change-vs-noise engine</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Deterministic, versioned eligibility + safety constraints.</t>
+          <t>Report change only beyond comparability + MDC rules. Never naive % change.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>E01, E05</t>
+          <t>C02, C07, D01</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-13 / D-24</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -5789,35 +5837,43 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>lib/longitudinal/engine.ts, lib/context/chat.ts</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Pure function + version constant + tests</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr"/>
+          <t>Engine + tests + noise table version</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>longitudinalResult: latest comparable scan vs the 3-scan window, one quantity in one region; two levels only. Two gates stop a change answer in production (empty COMPARABLE_QUANTITIES; empty frozen NOISE_TABLE), and the shared type refuses pairwise without a known floor. No pair gives comparability not_evaluated; histogram readings name histogram_quantity (eee588c). Wired into the context chat path for every quantity in every region over the trusted series, cut at the discussed scan (ad98ac5); the guard allows only that importer, with three arguments. Tests: longitudinal-engine (55), longitudinal-guard (6), context-route. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>lane/longitudinal 1b0dd32, 1d69f61, 0bd5c08, 087fb2c, 8095b72, 330991f; merge 53d0894; eee588c, 64b4b8c, ad98ac5</t>
+        </is>
+      </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>Needs catalog (E01) and red-flag criteria (E05).</t>
-        </is>
-      </c>
+          <t>Local only. Output is always 'not enough evidence' until C07 (owner accepted).</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Wait on E01. Lane: rules (branch lane/rules, brief docs/lanes/rules.md); results come via docs/lanes/rules-report.md at merge.</t>
+          <t>Nothing until C07; D05 decides re-baselining (TD-14: stay at not enough evidence after an engine change).</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5830,27 +5886,27 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Routine model + event history</t>
+          <t>Persistence/evidence tiers</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
+          <t>Separate transient observations from persistent patterns.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -5865,19 +5921,15 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>R-1..R-6 (TD-07)</t>
-        </is>
-      </c>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -5885,43 +5937,39 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>lib/routine/, app/api/routine/events, components/routine, app/(marketing)/routine, firestore.rules lane:routine</t>
-        </is>
-      </c>
+          <t>Measurement Scientist</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Data model doc + approved gate + tests</t>
+          <t>Tier definitions + tests</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Built (lane routine, merged daa0b4a): event schemas and currentRoutine(); GET/POST /api/routine/events (uid from the verified token only, strict schemas, idempotent eventIds, 4 KB body cap, 200 writes/uid/day); server-written events, owner read-only rules, collection-group denied; /routine page (own record only, no skin data, no claims). Follow-ups: purpose text moved to lib/consent.ts (7662ed7); root site description neutral (90c30a1, routine T6); erasure covers routineEvents (2f00819). Tests: routine-events, routine-copy, routine-route, firestore-rules-routine, routine.e2e, layout-description. Security review: no cross-user path. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier: routine PASS.</t>
+          <t>Two evidence levels only (not_enough_evidence, pairwise). persistence_not_available on every pairwise answer; every pairwise answer names all ten confounders in a fixed order. Reason texts carry no digits, percentages or change words (tested). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>e9331f3, 6f8c22c, 0f56ea6, ac275fa, 0e37830, e08aa89, 779e967; merge daa0b4a; 7662ed7, 90c30a1, 2f00819</t>
+          <t>lane/longitudinal 1b0dd32, 1d69f61, 0bd5c08, 087fb2c, 8095b72, 330991f; merge 53d0894</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Local only; not deployed (A04, A13). Signed-in /routine page not clicked through in a browser.</t>
+          <t>Local only.</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Browser click-through (E06). Doc alignment (A21). Rate-limit store (B09). Deploy with A13 after A04.</t>
+          <t>None; persistence tiers stay research-dependent (LONGITUDINAL_METHOD §3.6).</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5931,54 +5979,54 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>A04 dependency applies to deployment only.</t>
+          <t>D-12/D-13 reject research-doc tiers 3-4 and the 4/10-point ladder as primary output.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Adherence summary</t>
+          <t>Scheduled anchor scans / irregular sampling</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
+          <t>Sampling strategy.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -5987,50 +6035,26 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>lib/routine/adherence.ts</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>Function + tests</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>adherence(): used / skipped / unknown, counts only; a day with no log is unknown, never skipped. GET /api/routine/events?tz= returns the 7-day summary. Tests: routine-adherence (13), routine.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>0e4bf16; merge daa0b4a</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>Local only.</t>
-        </is>
-      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr"/>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>None for the function. Deploy with E03.</t>
+          <t>Revisit after D02.</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr"/>
@@ -6038,32 +6062,32 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Red-flag triage interlock</t>
+          <t>Engine-version re-baselining</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Safety layer overrides cosmetic recommendations.</t>
+          <t>Handle engine build changes across history.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6073,88 +6097,68 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>Product/Routine Rules Engineer</t>
-        </is>
-      </c>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
-        </is>
-      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>Red-flag criteria need qualified clinical sign-off sourced by the owner.</t>
-        </is>
-      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Owner nominates clinical reviewer; engineer drafts criteria list for review. Lane: rules (branch lane/rules, brief docs/lanes/rules.md); results come via docs/lanes/rules-report.md at merge.</t>
+          <t>Revisit at first engine change after D02.</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-04 (privacy T12): also review EXTRA_CAUTION_TRIGGERS and the caution sentence; decide whether the residual pregnancy inference is acceptable or drop the flag or trigger.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Routine page browser click-through</t>
+          <t>Baseline: skip a different capture method; one scan per day</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Signed-in click-through of /routine on the local stack (read, add, stop, swap, log).</t>
+          <t>TD-14 (3): a baseline scan whose capture method differs from the latest is skipped. TD-14 (4): at most one scan per calendar day (server analyzedAt) counts toward the baseline. Both provisional.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6174,10 +6178,14 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr"/>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>TD-14</t>
+        </is>
+      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6185,35 +6193,31 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>components/routine, app/(marketing)/routine</t>
+          <t>lib/longitudinal/baseline.ts, lib/longitudinal/engine.ts</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Recorded local click-through</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>Not started. The API flow is covered by routine.e2e.</t>
-        </is>
-      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr"/>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>Run npm run dev:local and click through as a seeded user.</t>
+          <t>Build in the next longitudinal task; the guard tests stay.</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6223,44 +6227,44 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Proposed by routine report T7.</t>
+          <t>Longitudinal report 4.3, 4.4. Not built in the merge task (owner: add rows, do not build).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Product catalog normalization</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6268,56 +6272,60 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>A08, D02, E03, E04, E05</t>
-        </is>
-      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08 / D-09 / D-12 (TD-07)</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>Product/Routine Rules Engineer</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>lib/catalog/</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Pure builder + tests</t>
+          <t>Owner-supplied master data + versioned schema</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Precursor: lib/echo-trusted-context.ts (155cb69)</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr"/>
+          <t>Built (lane routine, merged daa0b4a): versioned catalogue schema, synthetic sample, owner template lib/catalog/catalogue-template.csv with a drift check, D-12 word check with the exact-name exception (PRODUCT_NAME_EXCEPTIONS). Tests: catalog-schema (20). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>e45da38; merge daa0b4a</t>
+        </is>
+      </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Schema only; data is synthetic (R-3 A).</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Needs longitudinal (D02), routine (E03/E04) and safety (E05) inputs.</t>
+          <t>Owner catalogue data. Deploy blocker (routine T1): the deploy is blocked while any product has dataSource "synthetic".</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>Wait; may define schema with null sections earlier if approved. Lane: context (branch lane/context, brief docs/lanes/context.md); results come via docs/lanes/context-report.md at merge.</t>
+          <t>Owner fills lib/catalog/catalogue-template.csv (fields: routine-report.md section 6), including "Clear Seal" as an owner row; then replace the synthetic CATALOGUE. OPEN-R1 answered by R-2 B (no product cards for now).</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6325,32 +6333,36 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Proposed D-12 clarification (registered own-brand name is not by itself a claim) recorded in TD-07.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Product eligibility / safety rules</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Deterministic, versioned eligibility + safety constraints.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6360,7 +6372,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6370,12 +6382,12 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E01, E05</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -6385,43 +6397,47 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>lib/gemini.ts</t>
+          <t>lib/rules/</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
+          <t>Pure function + version constant + tests</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Precursor: GEMINI_BOUNDARY.md; server-grounded Echo prompt (155cb69)</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr"/>
+          <t>Library built: recommend(input, catalogue) with RULESET_VERSION rules-0-provisional, inputSha256 (scope per TD-15), base/active by ingredient class. Off in production builds (on only for NODE_ENV test/development; fails closed), tested for production, unset, empty and staging. Not called anywhere: the context package's recommendation section stays empty. Tests: 143 rules tests in 5 files (+2 in wave-2 wiring). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>lane/rules 8cd98f9, 619dd7c, d0a7409, 45b6231, 1b0741f; merge 7da1a54</t>
+        </is>
+      </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>Schema renderer not built.</t>
+          <t>Local only. Owner decisions TD-15 applied (extra caution withholds the active; prescriber line hidden under a red flag).</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Needs F01.</t>
+          <t>Real catalogue (E01; the synthetic one has no niacinamide serum, so the active never has an item) and clinical sign-off (E05).</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>Wait on F01. Lane: context (branch lane/context, brief docs/lanes/context.md); results come via docs/lanes/context-report.md at merge.</t>
+          <t>E01 data, then E05 sign-off (E09), then a caller that treats any throw as 'show nothing' (rules report 6.4).</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6429,61 +6445,57 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>Seed status PARTIALLY READY.</t>
-        </is>
-      </c>
+      <c r="V55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Routine model + event history</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>D-14 / D-12</t>
+          <t>R-1..R-6 (TD-07)</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -6493,35 +6505,43 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>lib/routine/, app/api/routine/events, components/routine, app/(marketing)/routine, firestore.rules lane:routine</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr"/>
+          <t>Data model doc + approved gate + tests</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane routine, merged daa0b4a): event schemas and currentRoutine(); GET/POST /api/routine/events (uid from the verified token only, strict schemas, idempotent eventIds, 4 KB body cap, 200 writes/uid/day); server-written events, owner read-only rules, collection-group denied; /routine page (own record only, no skin data, no claims). Follow-ups: purpose text moved to lib/consent.ts (7662ed7); root site description neutral (90c30a1, routine T6); erasure covers routineEvents (2f00819). Tests: routine-events, routine-copy, routine-route, firestore-rules-routine, routine.e2e, layout-description. Security review: no cross-user path. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier: routine PASS.</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>e9331f3, 6f8c22c, 0f56ea6, ac275fa, 0e37830, e08aa89, 779e967; merge daa0b4a; 7662ed7, 90c30a1, 2f00819</t>
+        </is>
+      </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>Needs F02 output schema.</t>
-        </is>
-      </c>
+          <t>Local only; not deployed (A04, A13). Signed-in /routine page not clicked through in a browser.</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>Wait on F02. Lane: context (branch lane/context, brief docs/lanes/context.md); results come via docs/lanes/context-report.md at merge.</t>
+          <t>Browser click-through (E06). Doc alignment (A21). Rate-limit store (B09). Deploy with A13 after A04.</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6529,42 +6549,46 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>A04 dependency applies to deployment only.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Adherence summary</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6572,12 +6596,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>D-14 (store rejected for now)</t>
-        </is>
-      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6585,35 +6609,43 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>Product/Routine Rules Engineer</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>lib/routine/adherence.ts</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
+          <t>Function + tests</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Answers already labelled SELF_REPORTED (GATE_02 7.1)</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr"/>
+          <t>adherence(): used / skipped / unknown, counts only; a day with no log is unknown, never skipped. GET /api/routine/events?tz= returns the 7-day summary. Tests: routine-adherence (13), routine.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>0e4bf16; merge daa0b4a</t>
+        </is>
+      </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Local only.</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr"/>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>Design quarantine labelling; D-14 lists the UserAssertion store as LATER, so scope to labelling only. Lane: context (branch lane/context, brief docs/lanes/context.md); results come via docs/lanes/context-report.md at merge.</t>
+          <t>None for the function. Deploy with E03.</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6626,27 +6658,27 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Routine and adherence in the context package</t>
+          <t>Red-flag triage interlock</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>The owner asked for a routine and adherence summary in the context package. R-1 A (TD-07) says routine data is not sent to Gemini, and users are told so (ROUTINE_PURPOSE_COPY). The shape allows only { status: "not_shared" }. Routine data next to a "beyond noise" result also invites an attribution claim (D-12).</t>
+          <t>Safety layer overrides cosmetic recommendations.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -6656,22 +6688,18 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>TD-07 (R-1 A) / D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -6681,39 +6709,47 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>lib/contracts/context-package.ts, lib/consent.ts</t>
+          <t>lib/rules/safety.ts, lib/rules/settings.ts, lib/context/prefilter.ts</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Owner decision; if reopened: new purpose copy, new package version, attribution guard</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="inlineStr"/>
+          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>lane/rules 8cd98f9, 619dd7c, d0a7409, 45b6231, 1b0741f; merge 7da1a54; eee588c, 7fe39da, 3f61b3e</t>
+        </is>
+      </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Concern recorded 2026-10-04; the frozen decision is not changed.</t>
+          <t>Local only. Lists PROVISIONAL (REVIEW_STATUS provisional).</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>Owner decision: keep R-1 A (drop the routine item) or reopen it and change the purpose copy.</t>
+          <t>Red-flag and caution lists need qualified clinical sign-off sourced by the owner.</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>Owner decides.</t>
+          <t>Owner nominates the clinical reviewer, who signs rules report §4, the caution sentence and the pregnancy-inference question; then E09.</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6723,39 +6759,39 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Found while writing the shared shapes.</t>
+          <t>2026-10-04 (privacy T12): also review EXTRA_CAUTION_TRIGGERS and the caution sentence; decide whether the residual pregnancy inference is acceptable or drop the flag or trigger.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Verified helpline number in the referral copy</t>
+          <t>Routine page browser click-through</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>The red-flag and self-harm referral message ships with no phone number (TD-16). A number may be added only after the owner supplies one and verifies it and its hours.</t>
+          <t>Signed-in click-through of /routine on the local stack (read, add, stop, swap, log).</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6765,55 +6801,51 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>TD-16 / GEMINI_BOUNDARY §6</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>lib/context/prefilter.ts (REFERRAL_COPY)</t>
+          <t>components/routine, app/(marketing)/routine</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Owner-verified number and hours + commit + test</t>
+          <t>Recorded local click-through</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr"/>
       <c r="P59" s="2" t="inlineStr"/>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>No number in the copy.</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>Owner has not supplied a verified India helpline.</t>
-        </is>
-      </c>
+          <t>Not started. The API flow is covered by routine.e2e.</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>Owner supplies and verifies the number; engineer adds it with a test. DEPLOY BLOCKER for switching the context path on in production.</t>
+          <t>Run npm run dev:local and click through as a seeded user.</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -6823,39 +6855,39 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Owner decision 2026-10-04.</t>
+          <t>Proposed by routine report T7.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>Record which answers were confirmed on this check, server-side</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>TD-15 (3a). Rules and the context package need the step ids answered or re-confirmed on this check (confirmedThisScan; SelfReportedStatement.fresh). Today every answer counts as reused.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6865,15 +6897,19 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr"/>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>TD-15 / D-19 / D-26</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6881,78 +6917,78 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>lib/firebase/skin-checks.ts, firestore.rules, a new server save route</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
+          <t>Route + rules + tests</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
-        </is>
-      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>Design with the D-10 record task.</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V60" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Not a small change: skinChecks are written by the browser (setDoc under firestore.rules); there is no server save route to hook into. Wiring item 9 of the wave-2 merge task.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Catalogue texts that fail the context screen</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>tests/context-catalogue-screen.test.ts pins two texts the context builder would drop from chat: the synthetic name 'Sample Sunscreen SPF 50' (digits) and the owner-approved name exception 'Clear Seal' ('clear' is a change word).</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -6962,158 +6998,154 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>E03, G01</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>D-12 (LOCKED)</t>
+          <t>TD-16</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>Product/Routine Rules Engineer</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>lib/catalog/catalogue.ts, lib/context/builder.ts</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>Needs E03 and G01.</t>
-        </is>
-      </c>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>bd6bb86</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>bd6bb86</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Owner decides: a chat display name without digits or change words per product, or accept that the product is left out of chat. The screen is not loosened.</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V61" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>Wiring item 8.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Clinical sign-off commit for the rules</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>After sign-off, flip REVIEW_STATUS to clinically_reviewed in a reviewed commit with a RULESET_VERSION bump; there is no environment override.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-17 (TD-08, TD-10)</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
+          <t>lib/rules/settings.ts, tests/rules-settings.test.ts</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
-        </is>
-      </c>
+          <t>Reviewer record + commit + tests</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr"/>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
+          <t>Clinical reviewer sign-off (E05).</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
+          <t>Wait on E05.</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7123,34 +7155,34 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
+          <t>Rules report §7.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7168,56 +7200,60 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>A08, D02, E03, E04, E05</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>D-19 (TD-08, TD-11, TD-12)</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
+          <t>lib/context/builder.ts, lib/context/chat.ts</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
+          <t>Pure builder + tests</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
+          <t>buildContextPackage: allowlist serialiser, our own text for every fact and reason, catalogue screen. Real inputs wired: longitudinal results and the evaluateSafety state (ad98ac5); the builder hides exactly the answers SafetyState.extraCautionRaisedBy names (7fe39da); recommendation section empty by design (rules off in production). Tests: context-builder, context-route (+9 in wave 2), context-catalogue-screen. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; ad98ac5, 7fe39da, 3f61b3e, bd6bb86</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
+          <t>Local only, behind the local-only switch (off in production builds). Context path in production is F08.</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr"/>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
+          <t>F08 (production switch) after its blockers.</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7227,39 +7263,39 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
+          <t>Owner decisions TD-16. Formal owner approval of the context brief (lanes README rule 3) was recorded via TD-16.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7269,63 +7305,63 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
+          <t>lib/context/renderer.ts, lib/gemini.ts</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
+          <t>Schema + renderer + tests</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+          <t>Renderer ctx-prompt-1; generateContextAnswer with structured output, per-request fact-id enum, explicit safety settings, no tools. Proven with a fake at the @google/genai boundary (no dev key locally). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
-        </is>
-      </c>
+          <t>Local only (fake Gemini). Production needs G1 and H06 (F08).</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
+          <t>F08.</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7335,44 +7371,44 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
+          <t>Seed status PARTIALLY READY.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Block writes after an account is erased</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -7382,12 +7418,12 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14 / D-12</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -7397,39 +7433,43 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
+          <t>lib/context/validator.ts, lib/context/answer.ts</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr"/>
-      <c r="P65" s="2" t="inlineStr"/>
+          <t>Validator + adversarial tests</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
+        </is>
+      </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>Needs a rules change outside the privacy lane.</t>
-        </is>
-      </c>
+          <t>Local only. The second security-fix round (6daa5c7) is re-checked in the wave-2 final review.</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
+          <t>F07 offline false-positive check.</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7437,61 +7477,53 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by privacy report T3; widened to the routine route.</t>
-        </is>
-      </c>
+      <c r="V65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Support tool to clear a mistaken under-18 record</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>D-19 (decision 4)</t>
+          <t>D-14 (store rejected for now)</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -7501,39 +7533,43 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
+          <t>lib/context/builder.ts, lib/context/validator.ts</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests + audit trail</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>Self-reported statements are a separate section (source self_reported), citable only by self_reported_echo; a self fact under any other claim type fails self_report_as_measurement. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
+        </is>
+      </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
-        </is>
-      </c>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>Must exist before the final deploy (A13 depends on it).</t>
-        </is>
-      </c>
+          <t>Local only. SelfReportedStatement.fresh is always true until E07 records confirmations.</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
+          <t>E07.</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7541,36 +7577,32 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V66" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by privacy report T17. Deploy blocker.</t>
-        </is>
-      </c>
+      <c r="V66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Final consent copy (AI share and processing)</t>
+          <t>Routine and adherence in the context package</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
+          <t>The owner asked for a routine and adherence summary in the context package. R-1 A (TD-07) says routine data is not sent to Gemini, and users are told so (ROUTINE_PURPOSE_COPY). The shape allows only { status: "not_shared" }. Routine data next to a "beyond noise" result also invites an attribution claim (D-12).</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -7585,17 +7617,17 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>D-16 / decision 6, 7a</t>
+          <t>TD-07 (R-1 A) / D-12</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -7605,39 +7637,39 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>lib/consent.ts</t>
+          <t>lib/contracts/context-package.ts, lib/consent.ts</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Owner/legal copy + version bump + tests updated on purpose</t>
+          <t>Owner decision; if reopened: new purpose copy, new package version, attribution guard</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr"/>
       <c r="P67" s="2" t="inlineStr"/>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
+          <t>Concern recorded 2026-10-04; the frozen decision is not changed.</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>Owner or legal supplies both sentences; G1 answered.</t>
+          <t>Owner decision: keep R-1 A (drop the routine item) or reopen it and change the purpose copy.</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
+          <t>Owner decides.</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7647,39 +7679,39 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
+          <t>Found while writing the shared shapes.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Cross-route under-18 test</t>
+          <t>Verified helpline number in the referral copy</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
+          <t>The red-flag and self-harm referral message ships with no phone number (TD-16). A number may be added only after the owner supplies one and verifies it and its hours.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7689,51 +7721,55 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>TD-16 / GEMINI_BOUNDARY §6</t>
+        </is>
+      </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>tests/</t>
+          <t>lib/context/prefilter.ts (REFERRAL_COPY)</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Commit + test result</t>
+          <t>Owner-verified number and hours + commit + test</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr"/>
+          <t>No number in the copy.</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Owner has not supplied a verified India helpline.</t>
+        </is>
+      </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>Write the test against the merged routes.</t>
+          <t>Owner supplies and verifies the number; engineer adds it with a test. DEPLOY BLOCKER for switching the context path on in production.</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -7743,39 +7779,39 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T6.</t>
+          <t>Owner decision 2026-10-04.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Gemini field scope: self-reported dryness and gender inference</t>
+          <t>Offline check of pre-filter and validator misfires</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
+          <t>EVALUATION_PLAN §4: measure how often the strict comparison pre-filter (kept by TD-16) and the validator misfire on ordinary questions (e.g. 'should I apply this before bed?').</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -7790,54 +7826,46 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Decision 8</t>
+          <t>TD-16</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts</t>
+          <t>lib/context/prefilter.ts, lib/context/validator.ts</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Owner decision (+ commit if changed)</t>
+          <t>Labelled question set + report</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr"/>
       <c r="P69" s="2" t="inlineStr"/>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>Owner action.</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>Owner decision.</t>
-        </is>
-      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
+          <t>Build a labelled EN and Hinglish question set; report rates; owner revisits TD-16 (2).</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -7847,39 +7875,39 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T8, T9.</t>
+          <t>Context report §5.3; Owner instruction 2026-10-04 (wave-2 merge task).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Required Gemini allowlist parameter</t>
+          <t>Switch the context path on in production</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
+          <t>The context-package chat path is on for local development only (switch ignores production builds).</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -7889,18 +7917,22 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr"/>
+          <t>F06, H06, E05, H17, B10</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>G1 / D-14 / O-4</t>
+        </is>
+      </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -7910,25 +7942,25 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
+          <t>lib/context/switch.ts</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Owner decision + production test</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>G1 (Gemini data handling), H06 consent copy, F06 helpline, H17 TTL. Also: evaluateSafety throws in production builds until E05/E09, so every context answer would be the fixed fallback.</t>
+        </is>
+      </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>Make the parameter required.</t>
+          <t>Owner decides after the blockers.</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
@@ -7943,39 +7975,39 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T10.</t>
+          <t>Context report §7.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>H10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Require age attestation on upload and scan</t>
+          <t>ContextSkinState.contractVersion label</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
+          <t>Bands come from scanAnalyses, so the context lane writes scan-analysis-1. Decide the label now that skinstate-2 exists.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -7988,52 +8020,40 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>Decision 3a</t>
-        </is>
-      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
+          <t>lib/context/builder.ts</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Decision + commit</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr"/>
       <c r="P71" s="2" t="inlineStr"/>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>Later.</t>
-        </is>
-      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
       <c r="R71" s="2" t="inlineStr"/>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>After old bundles are gone.</t>
+          <t>Owner decides.</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8043,39 +8063,39 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T13.</t>
+          <t>Context report §6.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Engine stores no image</t>
+          <t>Remove routine_as_directed from the AllowedClaim type</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
+          <t>TD-16 (3) removes the claim type. It was never in allowedClaims at runtime; the type in lib/contracts/context-package.ts still lists it, and that edit was not among the approved contract edits.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8085,47 +8105,51 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>TD-13 / TD-16</t>
+        </is>
+      </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>CV/ML Engineer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>skin-scan engine</t>
+          <t>lib/contracts/context-package.ts</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Code read + runtime check</t>
+          <t>Owner approval of the contract edit + commit + test</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr"/>
       <c r="P72" s="2" t="inlineStr"/>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr"/>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Read-only check of the engine source and the container.</t>
+          <t>Owner approves the one-line contract edit, or keeps it until F05 is decided.</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8133,41 +8157,37 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V72" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by privacy report T15.</t>
-        </is>
-      </c>
+      <c r="V72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>DOM test renderer</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8177,97 +8197,89 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>README rule 6</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>package.json, tests/</t>
-        </is>
-      </c>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Owner approval + commit</t>
+          <t>Approved design + tests + E2E</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr"/>
       <c r="P73" s="2" t="inlineStr"/>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>New dependency needs approval.</t>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>Owner approves or declines.</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V73" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by privacy report T16.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>H13</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Processing consent after a draft restore</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8277,22 +8289,22 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>E03, G01</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-03a</t>
+          <t>D-12 (LOCKED)</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -8300,14 +8312,10 @@
           <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
-        </is>
-      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Decision + commit + tests</t>
+          <t>Design reviewed against D-12</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
@@ -8319,34 +8327,30 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>Owner decides whether restored drafts may carry the consent version.</t>
+          <t>Needs E03 and G01.</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V74" s="2" t="inlineStr">
-        <is>
-          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>H14</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -8361,70 +8365,82 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Withdraw AI-share consent in the UI</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-16 / D-17 (TD-08, TD-10)</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
+          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Design check + commit + tests</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="2" t="inlineStr"/>
+          <t>Ledger + erasure route + tests + live verification</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
+        </is>
+      </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R75" s="2" t="inlineStr"/>
+          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
+        </is>
+      </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Check the design, then add a withdraw control.</t>
+          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
@@ -8439,14 +8455,14 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04.</t>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>H15</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -8461,62 +8477,74 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Low-severity hardening from the security review</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>D-19 (TD-08, TD-11, TD-12)</t>
+        </is>
+      </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
+          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="inlineStr"/>
+          <t>Gate + tests</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
+        </is>
+      </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr"/>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Add isPlainUid to the upload key path; log name and code only.</t>
+          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
@@ -8531,14 +8559,14 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04 (pre-existing logging).</t>
+          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>H16</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -8553,70 +8581,78 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Consent ledger write slows the scan response</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/route.ts</t>
+          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Commit + test + timing</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr"/>
-      <c r="P77" s="2" t="inlineStr"/>
+          <t>Field inventory + key ownership/tier + consent copy</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+        </is>
+      </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R77" s="2" t="inlineStr"/>
+          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
+        </is>
+      </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
+          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
@@ -8631,39 +8667,39 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Verifier observation 2026-10-04 (a52f36d).</t>
+          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Block writes after an account is erased</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -8673,15 +8709,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr"/>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>D-17</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8689,73 +8729,81 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Design + commit + tests</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr"/>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Not started (owner: do not do now).</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>Nothing longitudinal is deployed yet.</t>
+          <t>Needs a rules change outside the privacy lane.</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V78" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T3; widened to the routine route.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>Support tool to clear a mistaken under-18 record</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -8770,10 +8818,14 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr"/>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>D-19 (decision 4)</t>
+        </is>
+      </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8781,73 +8833,81 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Design + commit + tests + audit trail</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr"/>
       <c r="P79" s="2" t="inlineStr"/>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Not started (owner: do not do now).</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>Must exist before the final deploy (A13 depends on it).</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V79" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T17. Deploy blocker.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Final consent copy (AI share and processing)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -8857,69 +8917,101 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / decision 6, 7a</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>lib/consent.ts</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Owner/legal copy + version bump + tests updated on purpose</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr"/>
-      <c r="R80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>Owner or legal supplies both sentences; G1 answered.</t>
+        </is>
+      </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V80" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Cross-route under-18 test</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -8929,69 +9021,93 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>tests/</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Commit + test result</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr"/>
-      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
       <c r="R81" s="2" t="inlineStr"/>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Write the test against the merged routes.</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V81" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T6.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>Gemini field scope: self-reported dryness and gender inference</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9001,69 +9117,101 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Decision 8</t>
+        </is>
+      </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>lib/skin-check-format.ts</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision (+ commit if changed)</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr"/>
-      <c r="Q82" s="2" t="inlineStr"/>
-      <c r="R82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision.</t>
+        </is>
+      </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V82" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T8, T9.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Required Gemini allowlist parameter</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9073,68 +9221,88 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Gemini/Context Engineer</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Commit + tests</t>
+        </is>
+      </c>
       <c r="O83" s="2" t="inlineStr"/>
       <c r="P83" s="2" t="inlineStr"/>
-      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
       <c r="R83" s="2" t="inlineStr"/>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Make the parameter required.</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+          <t>Proposed by privacy report T10.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>H10</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Require age attestation on upload and scan</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -9149,39 +9317,1395 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Decision 3a</t>
+        </is>
+      </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Commit + tests</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr"/>
-      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>Later.</t>
+        </is>
+      </c>
       <c r="R84" s="2" t="inlineStr"/>
       <c r="S84" s="2" t="inlineStr">
         <is>
+          <t>After old bundles are gone.</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Engine stores no image</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>CV/ML Engineer</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>skin-scan engine</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Code read + runtime check</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>Read-only check of the engine source and the container.</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>H12</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>DOM test renderer</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>OWNER ACTION</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>README rule 6</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>package.json, tests/</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Owner approval + commit</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>New dependency needs approval.</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>Owner approves or declines.</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>Proposed by privacy report T16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>H13</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Processing consent after a draft restore</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / D-03a</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Decision + commit + tests</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>Owner decides whether restored drafts may carry the consent version.</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Withdraw AI-share consent in the UI</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Design check + commit + tests</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>Check the design, then add a withdraw control.</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>Security review 2026-10-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>H15</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Low-severity hardening from the security review</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Commit + tests</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>Add isPlainUid to the upload key path; log name and code only.</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>Security review 2026-10-04 (pre-existing logging).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>H16</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Consent ledger write slows the scan response</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>app/api/skin-scan/route.ts</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Commit + test + timing</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>Verifier observation 2026-10-04 (a52f36d).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>H17</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Firestore expiry (TTL) policy for chat turns</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>users/*/chatTurns carry expireAt (90 days, D-15) but no TTL policy exists. Turns include red-flag and self-harm message text.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>OWNER ACTION</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>Firestore (infrastructure)</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Policy configured on the India-region database + check</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>Owner creates the TTL policy on chatTurns.expireAt when the Firestore reset (A04) lands. Deploy blocker for F08.</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>Context report §6; Owner instruction 2026-10-04 (wave-2 merge task).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>H18</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Document the context path's sent data</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>privacy-report.md §5 should list what the new path sends: version labels, lowConfidence, uncertainty and missing facts, not-enough-evidence longitudinal facts, rec.* facts. Pin tests already cover it (add-only).</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>NOT NEEDED</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>docs/lanes/privacy-report.md</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Committed doc</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>Write the section.</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>Context report §6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Release Validation</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end production evaluation</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>A12, A13, B01, H01, H03</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>QA/Test Engineer</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Recorded E2E run against prod</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>Nothing longitudinal is deployed yet.</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>Write E2E script while A13 is pending.</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Release Validation</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Full red-team sweep</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>Wait.</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>RED TEAM</t>
+        </is>
+      </c>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>J01</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Population priors / mixed effects</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
           <t>Do not start without evidence and explicit approval.</t>
         </is>
       </c>
-      <c r="T84" s="2" t="inlineStr">
+      <c r="T95" s="2" t="inlineStr">
         <is>
           <t>RELEASE</t>
         </is>
       </c>
-      <c r="U84" s="2" t="inlineStr">
+      <c r="U95" s="2" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V84" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>ML recommendation ranking</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>J03</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Indian cross-user benchmark</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>bff6e25, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 597 passed / 41 skipped; stack 41/41).</t>
+          <t>2bb45e1, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47).</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>38% = DONE 34 / (total 98 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>37% = DONE 34 / (total 99 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 34, IN PROGRESS 1, NOT STARTED 21, BLOCKED 15, OWNER ACTION 19, LATER 8 (total 98)</t>
+          <t>DONE 34, IN PROGRESS 1, NOT STARTED 21, BLOCKED 15, OWNER ACTION 20, LATER 8 (total 99)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 33, NOT NEEDED 11, NOT CHECKED 53</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 33, NOT NEEDED 11, NOT CHECKED 54</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V99"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Merges clean (no conflicts). Shapes: not_evaluated comparability, histogram_quantity reason, internal SafetyState.extraCautionRaisedBy (banned from the package), position and inputSha256 comments; verifier PASS. Wiring: 1 loader, 2 real inputs, 3 one caution list, 4 fail-closed fallback, 5 guard forwarding, 6 processingConsentVersion stored, 7 erase removes chatTurns, 8 catalogue screen test. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>Merges clean (no conflicts). Shapes: not_evaluated comparability, histogram_quantity reason, internal SafetyState.extraCautionRaisedBy (banned from the package), position and inputSha256 comments; verifier PASS. Wiring: 1 loader, 2 real inputs, 3 one caution list, 4 fail-closed fallback, 5 guard forwarding, 6 processingConsentVersion stored, 7 erase removes chatTurns, 8 catalogue screen test. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Local only. Final verifier and security review recorded in section 4.</t>
+          <t>Local only. Final verifier PASS (all three designs); security review: 6 findings, 5 fixed with tests (e508028, 2bb45e1), 1 is an owner question (H19). See section 4.</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>skinstate-2 next to skinstate-1 (frozen, unchanged): maps engine_build, names captureMethod, persistAttempt, captureQuality client-asserted (CLIENT_ASSERTED). Contract text approved by the owner 2026-10-04 (TD-14). Server-only series loader loadTrustedSkinState2Series (077330a). Tests: skin-state-2 (11), comparability-2 (7), skin-state-2-loader (7), longitudinal-series.e2e. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>skinstate-2 next to skinstate-1 (frozen, unchanged): maps engine_build, names captureMethod, persistAttempt, captureQuality client-asserted (CLIENT_ASSERTED). Contract text approved by the owner 2026-10-04 (TD-14). Server-only series loader loadTrustedSkinState2Series (077330a). Tests: skin-state-2 (11), comparability-2 (7), skin-state-2-loader (7), longitudinal-series.e2e. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Built (lane capture, merged 2970c86): comparabilityKey, compareKeys, compareStates; fails closed (COMPARABLE_QUANTITIES empty). Wave 2: accepts skinstate-2, which maps engine_build, so real pairs can match on the build and are still quantity_not_validated (1d69f61). The longitudinal engine forwards its test-only table through the guard under one allowed name, with positive controls (64b4b8c). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>Built (lane capture, merged 2970c86): comparabilityKey, compareKeys, compareStates; fails closed (COMPARABLE_QUANTITIES empty). Wave 2: accepts skinstate-2, which maps engine_build, so real pairs can match on the build and are still quantity_not_validated (1d69f61). The longitudinal engine forwards its test-only table through the guard under one allowed name, with positive controls (64b4b8c). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>BASELINE_RULE = first 3 comparable scans, named and PROVISIONAL. A scan unusable on its own (missing region, low pixels, no native stats, unknown capture method) is skipped; engine identity never skips one, so a window never crosses an engine change. Tests: longitudinal-baseline (7), engine skip cases. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>BASELINE_RULE = first 3 comparable scans, named and PROVISIONAL. A scan unusable on its own (missing region, low pixels, no native stats, unknown capture method) is skipped; engine identity never skips one, so a window never crosses an engine change. Tests: longitudinal-baseline (7), engine skip cases. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>longitudinalResult: latest comparable scan vs the 3-scan window, one quantity in one region; two levels only. Two gates stop a change answer in production (empty COMPARABLE_QUANTITIES; empty frozen NOISE_TABLE), and the shared type refuses pairwise without a known floor. No pair gives comparability not_evaluated; histogram readings name histogram_quantity (eee588c). Wired into the context chat path for every quantity in every region over the trusted series, cut at the discussed scan (ad98ac5); the guard allows only that importer, with three arguments. Tests: longitudinal-engine (55), longitudinal-guard (6), context-route. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>longitudinalResult: latest comparable scan vs the 3-scan window, one quantity in one region; two levels only. Two gates stop a change answer in production (empty COMPARABLE_QUANTITIES; empty frozen NOISE_TABLE), and the shared type refuses pairwise without a known floor. No pair gives comparability not_evaluated; histogram readings name histogram_quantity (eee588c). Wired into the context chat path for every quantity in every region over the trusted series, cut at the discussed scan (ad98ac5); the guard allows only that importer, with three arguments. Tests: longitudinal-engine (55), longitudinal-guard (6), context-route. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Two evidence levels only (not_enough_evidence, pairwise). persistence_not_available on every pairwise answer; every pairwise answer names all ten confounders in a fixed order. Reason texts carry no digits, percentages or change words (tested). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>Two evidence levels only (not_enough_evidence, pairwise). persistence_not_available on every pairwise answer; every pairwise answer names all ten confounders in a fixed order. Reason texts carry no digits, percentages or change words (tested). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Library built: recommend(input, catalogue) with RULESET_VERSION rules-0-provisional, inputSha256 (scope per TD-15), base/active by ingredient class. Off in production builds (on only for NODE_ENV test/development; fails closed), tested for production, unset, empty and staging. Not called anywhere: the context package's recommendation section stays empty. Tests: 143 rules tests in 5 files (+2 in wave-2 wiring). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>Library built: recommend(input, catalogue) with RULESET_VERSION rules-0-provisional, inputSha256 (scope per TD-15), base/active by ingredient class. Off in production builds (on only for NODE_ENV test/development; fails closed), tested for production, unset, empty and staging. Not called anywhere: the context package's recommendation section stays empty. Tests: 143 rules tests in 5 files (+2 in wave-2 wiring). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6724,17 +6724,17 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>lane/rules 8cd98f9, 619dd7c, d0a7409, 45b6231, 1b0741f; merge 7da1a54; eee588c, 7fe39da, 3f61b3e</t>
+          <t>lane/rules 8cd98f9, 619dd7c, d0a7409, 45b6231, 1b0741f; merge 7da1a54; eee588c, 7fe39da, 3f61b3e, e508028, 2bb45e1</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Local only. Lists PROVISIONAL (REVIEW_STATUS provisional).</t>
+          <t>Local only. Security review (wave 2) fixes: pre-filter disguises, splits and Hinglish on both chat paths (e508028); validator descriptions, echoes, uncited claims, joined reply (2bb45e1). Lists PROVISIONAL (REVIEW_STATUS provisional).</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>bd6bb86</t>
+          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>buildContextPackage: allowlist serialiser, our own text for every fact and reason, catalogue screen. Real inputs wired: longitudinal results and the evaluateSafety state (ad98ac5); the builder hides exactly the answers SafetyState.extraCautionRaisedBy names (7fe39da); recommendation section empty by design (rules off in production). Tests: context-builder, context-route (+9 in wave 2), context-catalogue-screen. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>buildContextPackage: allowlist serialiser, our own text for every fact and reason, catalogue screen. Real inputs wired: longitudinal results and the evaluateSafety state (ad98ac5); the builder hides exactly the answers SafetyState.extraCautionRaisedBy names (7fe39da); recommendation section empty by design (rules off in production). Tests: context-builder, context-route (+9 in wave 2), context-catalogue-screen. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Renderer ctx-prompt-1; generateContextAnswer with structured output, per-request fact-id enum, explicit safety settings, no tools. Proven with a fake at the @google/genai boundary (no dev key locally). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>Renderer ctx-prompt-1; generateContextAnswer with structured output, per-request fact-id enum, explicit safety settings, no tools. Proven with a fake at the @google/genai boundary (no dev key locally). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; e508028, 2bb45e1</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Local only. The second security-fix round (6daa5c7) is re-checked in the wave-2 final review.</t>
+          <t>Local only. The second security-fix round (6daa5c7) was re-checked in the wave-2 final review; its findings are fixed. Security review (wave 2) fixes: pre-filter disguises, splits and Hinglish on both chat paths (e508028); validator descriptions, echoes, uncited claims, joined reply (2bb45e1).</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr"/>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Self-reported statements are a separate section (source self_reported), citable only by self_reported_echo; a self fact under any other claim type fails self_report_as_measurement. npm run test:local exit 0 after the merges and wiring (unit 1120 passed / 47 skipped; stack 10 files 47/47, logs in the wave-2 session); typecheck 0; lint clean</t>
+          <t>Self-reported statements are a separate section (source self_reported), citable only by self_reported_echo; a self fact under any other claim type fails self_report_as_measurement. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -10162,32 +10162,32 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H19</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Hidden caution answer can be inferred from what is still sent</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>With extra caution on, withoutCautionAnswers hides only the matching value. 'Current products: Nothing right now' plus caution can only mean pregnant or breastfeeding; any male_skin_context answer plus caution means a prescription. Affects today's Echo and the context path.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10197,56 +10197,68 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr"/>
+          <t>E05, H08</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>TD-08 decision 8</t>
+        </is>
+      </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts (withoutCautionAnswers), lib/context/builder.ts</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
-        </is>
-      </c>
-      <c r="O93" s="2" t="inlineStr"/>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Security review (wave 2) finding 5. The current behaviour (other current products still sent) is pinned by tests/privacy-gemini-inventory.test.ts per owner decision 8, so it was not changed (frozen decision).</t>
+        </is>
+      </c>
       <c r="P93" s="2" t="inlineStr"/>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Not changed.</t>
         </is>
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>Nothing longitudinal is deployed yet.</t>
+          <t>Owner decision: extends the open pregnancy-inference question in E05.</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Owner decides: drop the whole current_products and male_skin_context fields while caution is on, drop the flag from the prompt, or accept the inference.</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr"/>
@@ -10254,7 +10266,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -10269,12 +10281,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -10294,7 +10306,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
+          <t>A12, A13, B01, H01, H03</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -10305,13 +10317,13 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Recorded E2E run against prod</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
@@ -10323,17 +10335,17 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>Nothing longitudinal is deployed yet.</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>RELEASE</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -10346,32 +10358,32 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -10381,31 +10393,51 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr"/>
-      <c r="Q95" s="2" t="inlineStr"/>
-      <c r="R95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -10418,7 +10450,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -10433,7 +10465,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -10490,7 +10522,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -10505,7 +10537,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>ML recommendation ranking</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -10562,7 +10594,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -10577,7 +10609,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Indian cross-user benchmark</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -10629,16 +10661,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -10653,7 +10681,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Forecasting</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -10705,7 +10733,83 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11668,7 +11772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12412,80 +12516,162 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>wave2-merge-session-2026-10-04</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Program Lead</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Record owner decisions; merge lanes longitudinal, rules, context; shape edits; wiring 1-8; final review</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A20, C02, D01-D03, E02, E05, F01-F04, A25</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>main (skin-check)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>longitudinal-platform</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>lib/contracts/*, lib/context/{chat,builder,prefilter,validator,lexicon}.ts, lib/gemini.ts, lib/rules/{safety,input,settings}.ts, lib/longitudinal/engine.ts, lib/skin-state-2-loader.ts, lib/scan-analysis-record.ts, app/api/skin-scan/route.ts, app/api/skin-check/chat/route.ts, scripts/seed-lane-privacy.ts, tests, tracker</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>typecheck, lint, next build, npm run test:local after each merge and at the end (2bb45e1: unit 1189 passed / 47 skipped; stack 47/47)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Merges: no conflicts. Verifier on shapes: PASS. Final verifier: PASS on all three designs, 4 tracker-text fixes + 2 stale texts (fixed in 1474c34 and this row). Security reviewer: 6 findings (pre-filter misses incl. disguises/Hinglish/splits; today's Echo had no pre-filter or safety settings; validator free text in descriptions; uncited claims and joined reply; caution answer inference; catalogue screen lookalikes) - 5 fixed with tests (e508028, 2bb45e1), 1 owner row H19</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>TD-14, TD-15, TD-16 recorded</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6a36a91, 53d0894, 7da1a54, dda2a91, eee588c, 077330a, 64b4b8c, 7fe39da, ad98ac5, 3f61b3e, 4ae015e, 73380c8, bd6bb86, 49c01bd, 1474c34, e508028, 2bb45e1</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Verifier PASS; security findings fixed or tracked</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>earlier sessions (gates 01-04, Phase 0)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>A01-A12, B02-B04</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>longitudinal-platform</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>see commits</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>see DECISION_LOG</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>61c149a..91d20bc</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>unknown - not reconstructable from repo</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2bb45e1, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47).</t>
+          <t>3fa1229, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47).</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Merges clean (no conflicts). Shapes: not_evaluated comparability, histogram_quantity reason, internal SafetyState.extraCautionRaisedBy (banned from the package), position and inputSha256 comments; verifier PASS. Wiring: 1 loader, 2 real inputs, 3 one caution list, 4 fail-closed fallback, 5 guard forwarding, 6 processingConsentVersion stored, 7 erase removes chatTurns, 8 catalogue screen test. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>Merges clean (no conflicts). Shapes: not_evaluated comparability, histogram_quantity reason, internal SafetyState.extraCautionRaisedBy (banned from the package), position and inputSha256 comments; verifier PASS. Wiring: 1 loader, 2 real inputs, 3 one caution list, 4 fail-closed fallback, 5 guard forwarding, 6 processingConsentVersion stored, 7 erase removes chatTurns, 8 catalogue screen test. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Local only. Final verifier PASS (all three designs); security review: 6 findings, 5 fixed with tests (e508028, 2bb45e1), 1 is an owner question (H19). See section 4.</t>
+          <t>Local only. Final verifier PASS (all three designs); security review: 6 findings, 5 fixed with tests (e508028, 2bb45e1, narrowed in 3fa1229), 1 is an owner question (H19). See section 4.</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>skinstate-2 next to skinstate-1 (frozen, unchanged): maps engine_build, names captureMethod, persistAttempt, captureQuality client-asserted (CLIENT_ASSERTED). Contract text approved by the owner 2026-10-04 (TD-14). Server-only series loader loadTrustedSkinState2Series (077330a). Tests: skin-state-2 (11), comparability-2 (7), skin-state-2-loader (7), longitudinal-series.e2e. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>skinstate-2 next to skinstate-1 (frozen, unchanged): maps engine_build, names captureMethod, persistAttempt, captureQuality client-asserted (CLIENT_ASSERTED). Contract text approved by the owner 2026-10-04 (TD-14). Server-only series loader loadTrustedSkinState2Series (077330a). Tests: skin-state-2 (11), comparability-2 (7), skin-state-2-loader (7), longitudinal-series.e2e. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Built (lane capture, merged 2970c86): comparabilityKey, compareKeys, compareStates; fails closed (COMPARABLE_QUANTITIES empty). Wave 2: accepts skinstate-2, which maps engine_build, so real pairs can match on the build and are still quantity_not_validated (1d69f61). The longitudinal engine forwards its test-only table through the guard under one allowed name, with positive controls (64b4b8c). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>Built (lane capture, merged 2970c86): comparabilityKey, compareKeys, compareStates; fails closed (COMPARABLE_QUANTITIES empty). Wave 2: accepts skinstate-2, which maps engine_build, so real pairs can match on the build and are still quantity_not_validated (1d69f61). The longitudinal engine forwards its test-only table through the guard under one allowed name, with positive controls (64b4b8c). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>BASELINE_RULE = first 3 comparable scans, named and PROVISIONAL. A scan unusable on its own (missing region, low pixels, no native stats, unknown capture method) is skipped; engine identity never skips one, so a window never crosses an engine change. Tests: longitudinal-baseline (7), engine skip cases. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>BASELINE_RULE = first 3 comparable scans, named and PROVISIONAL. A scan unusable on its own (missing region, low pixels, no native stats, unknown capture method) is skipped; engine identity never skips one, so a window never crosses an engine change. Tests: longitudinal-baseline (7), engine skip cases. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>longitudinalResult: latest comparable scan vs the 3-scan window, one quantity in one region; two levels only. Two gates stop a change answer in production (empty COMPARABLE_QUANTITIES; empty frozen NOISE_TABLE), and the shared type refuses pairwise without a known floor. No pair gives comparability not_evaluated; histogram readings name histogram_quantity (eee588c). Wired into the context chat path for every quantity in every region over the trusted series, cut at the discussed scan (ad98ac5); the guard allows only that importer, with three arguments. Tests: longitudinal-engine (55), longitudinal-guard (6), context-route. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>longitudinalResult: latest comparable scan vs the 3-scan window, one quantity in one region; two levels only. Two gates stop a change answer in production (empty COMPARABLE_QUANTITIES; empty frozen NOISE_TABLE), and the shared type refuses pairwise without a known floor. No pair gives comparability not_evaluated; histogram readings name histogram_quantity (eee588c). Wired into the context chat path for every quantity in every region over the trusted series, cut at the discussed scan (ad98ac5); the guard allows only that importer, with three arguments. Tests: longitudinal-engine (55), longitudinal-guard (6), context-route. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Two evidence levels only (not_enough_evidence, pairwise). persistence_not_available on every pairwise answer; every pairwise answer names all ten confounders in a fixed order. Reason texts carry no digits, percentages or change words (tested). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>Two evidence levels only (not_enough_evidence, pairwise). persistence_not_available on every pairwise answer; every pairwise answer names all ten confounders in a fixed order. Reason texts carry no digits, percentages or change words (tested). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Library built: recommend(input, catalogue) with RULESET_VERSION rules-0-provisional, inputSha256 (scope per TD-15), base/active by ingredient class. Off in production builds (on only for NODE_ENV test/development; fails closed), tested for production, unset, empty and staging. Not called anywhere: the context package's recommendation section stays empty. Tests: 143 rules tests in 5 files (+2 in wave-2 wiring). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>Library built: recommend(input, catalogue) with RULESET_VERSION rules-0-provisional, inputSha256 (scope per TD-15), base/active by ingredient class. Off in production builds (on only for NODE_ENV test/development; fails closed), tested for production, unset, empty and staging. Not called anywhere: the context package's recommendation section stays empty. Tests: 143 rules tests in 5 files (+2 in wave-2 wiring). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>buildContextPackage: allowlist serialiser, our own text for every fact and reason, catalogue screen. Real inputs wired: longitudinal results and the evaluateSafety state (ad98ac5); the builder hides exactly the answers SafetyState.extraCautionRaisedBy names (7fe39da); recommendation section empty by design (rules off in production). Tests: context-builder, context-route (+9 in wave 2), context-catalogue-screen. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>buildContextPackage: allowlist serialiser, our own text for every fact and reason, catalogue screen. Real inputs wired: longitudinal results and the evaluateSafety state (ad98ac5); the builder hides exactly the answers SafetyState.extraCautionRaisedBy names (7fe39da); recommendation section empty by design (rules off in production). Tests: context-builder, context-route (+9 in wave 2), context-catalogue-screen. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Renderer ctx-prompt-1; generateContextAnswer with structured output, per-request fact-id enum, explicit safety settings, no tools. Proven with a fake at the @google/genai boundary (no dev key locally). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>Renderer ctx-prompt-1; generateContextAnswer with structured output, per-request fact-id enum, explicit safety settings, no tools. Proven with a fake at the @google/genai boundary (no dev key locally). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Self-reported statements are a separate section (source self_reported), citable only by self_reported_echo; a self fact under any other claim type fails self_report_as_measurement. Final run at 2bb45e1: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1189 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>Self-reported statements are a separate section (source self_reported), citable only by self_reported_echo; a self fact under any other claim type fails self_report_as_measurement. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>typecheck, lint, next build, npm run test:local after each merge and at the end (2bb45e1: unit 1189 passed / 47 skipped; stack 47/47)</t>
+          <t>typecheck, lint, next build, npm run test:local after each merge and at the end (3fa1229: unit 1199 passed / 47 skipped; stack 47/47)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Merges: no conflicts. Verifier on shapes: PASS. Final verifier: PASS on all three designs, 4 tracker-text fixes + 2 stale texts (fixed in 1474c34 and this row). Security reviewer: 6 findings (pre-filter misses incl. disguises/Hinglish/splits; today's Echo had no pre-filter or safety settings; validator free text in descriptions; uncited claims and joined reply; caution answer inference; catalogue screen lookalikes) - 5 fixed with tests (e508028, 2bb45e1), 1 owner row H19</t>
+          <t>Merges: no conflicts. Verifier on shapes: PASS. Final verifier: PASS on all three designs, 4 tracker-text fixes + 2 stale texts (fixed in 1474c34 and this row). Security reviewer: 6 findings (pre-filter misses incl. disguises/Hinglish/splits; today's Echo had no pre-filter or safety settings; validator free text in descriptions; uncited claims and joined reply; caution answer inference; catalogue screen lookalikes) - 5 fixed with tests (e508028, 2bb45e1; over-blocking from the widening narrowed in 3fa1229), 1 owner row H19. The fixes were not re-reviewed by a second security pass</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6a36a91, 53d0894, 7da1a54, dda2a91, eee588c, 077330a, 64b4b8c, 7fe39da, ad98ac5, 3f61b3e, 4ae015e, 73380c8, bd6bb86, 49c01bd, 1474c34, e508028, 2bb45e1</t>
+          <t>6a36a91, 53d0894, 7da1a54, dda2a91, eee588c, 077330a, 64b4b8c, 7fe39da, ad98ac5, 3f61b3e, 4ae015e, 73380c8, bd6bb86, 49c01bd, 1474c34, e508028, 2bb45e1, 267f84f, 3fa1229</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 34, IN PROGRESS 1, NOT STARTED 21, BLOCKED 15, OWNER ACTION 20, LATER 8 (total 99)</t>
+          <t>DONE 34, IN PROGRESS 1, NOT STARTED 25, BLOCKED 15, OWNER ACTION 16, LATER 8 (total 99)</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>TD-16</t>
+          <t>TD-16 / TD-17</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -7040,7 +7040,7 @@
       <c r="R61" s="2" t="inlineStr"/>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>Owner decides: a chat display name without digits or change words per product, or accept that the product is left out of chat. The screen is not loosened.</t>
+          <t>Build per TD-17.</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8021,10 +8021,14 @@
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>TD-17</t>
+        </is>
+      </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -8048,7 +8052,7 @@
       <c r="R71" s="2" t="inlineStr"/>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>Owner decides.</t>
+          <t>Build per TD-17.</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
@@ -8095,7 +8099,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8115,12 +8119,12 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>TD-13 / TD-16</t>
+          <t>TD-13 / TD-16 / TD-17</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -8144,7 +8148,7 @@
       <c r="R72" s="2" t="inlineStr"/>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Owner approves the one-line contract edit, or keeps it until F05 is decided.</t>
+          <t>Build per TD-17.</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
@@ -10187,7 +10191,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10207,12 +10211,12 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>TD-08 decision 8</t>
+          <t>TD-08 decision 8 / TD-17</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -10241,14 +10245,10 @@
           <t>Not changed.</t>
         </is>
       </c>
-      <c r="R93" s="2" t="inlineStr">
-        <is>
-          <t>Owner decision: extends the open pregnancy-inference question in E05.</t>
-        </is>
-      </c>
+      <c r="R93" s="2" t="inlineStr"/>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>Owner decides: drop the whole current_products and male_skin_context fields while caution is on, drop the flag from the prompt, or accept the inference.</t>
+          <t>Build per TD-17.</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
@@ -12858,7 +12858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>DECIDED (owner) except 5 and 6.</t>
+          <t>DECIDED (owner) except 5 and 6. 8a extraCaution-to-Gemini part replaced by TD-17 (1) on 2026-10-04.</t>
         </is>
       </c>
     </row>
@@ -14228,52 +14228,52 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>TD-17</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Native L*/a* are provisional research candidates only</t>
+          <t>Wave-2 follow-up owner decisions</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 screening</t>
+          <t>Security review (wave 2) finding 5 (H19); E08, F09, F10 owner rows; e508028 changed today's Echo</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Keep b*, ITA, lbpEntropy</t>
+          <t>H19: drop the whole current_products/male_skin_context fields, or accept the inference; E08: per-product chat display name; F10: keep the type until F05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Primary endpoints for the human study only; not validated measurements</t>
+          <t>(1) H19: every user gets the same instruction to Gemini: do not suggest active ingredients or new products, and advise asking a doctor before starting anything new. The extra-caution flag is no longer sent to Gemini (today's Echo and the context path). Extra caution still applies inside our own code and rules. Replaces the extraCaution part of TD-08 decision 8a. (2) E08: owner-approved product names pass the context screen by exact match only. (3) F10: remove the unused routine_as_directed claim type from the shared shape. (4) F09: the context path's contractVersion label names the contract the data was really read under. (5) The change to today's Echo (fixed referral message for red-flag and self-harm messages, e508028) is accepted</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Only survivors of screening</t>
+          <t>Owner instruction 2026-10-04 (follow-up task)</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>C03-C07</t>
+          <t>H19, E08, F09, F10, H03, F01, F03, E05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Owner may reverse before Phase 1 pre-registration</t>
+          <t>Clinical reviewer (E05) says otherwise</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -14283,76 +14283,76 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>ACCEPTED for study design</t>
+          <t>DECIDED (owner, 2026-10-04). Tracker-local until A14.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>D-13 / D-24</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal comparisons require comparability + noise/evidence</t>
+          <t>Native L*/a* are provisional research candidates only</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Naive % change misleads</t>
+          <t>Phase 0 screening</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Research-doc point ladder</t>
+          <t>Keep b*, ITA, lbpEntropy</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
+          <t>Primary endpoints for the human study only; not validated measurements</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Measurement noise unknown</t>
+          <t>Only survivors of screening</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-13; D-24 uncommitted</t>
+          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>C02, D02, G01</t>
+          <t>C03-C07</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Owner may reverse before Phase 1 pre-registration</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (D-24 uncommitted)</t>
+          <t>ACCEPTED for study design</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-13 / D-24</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -14362,59 +14362,59 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Recommender deterministic and versioned</t>
+          <t>Longitudinal comparisons require comparability + noise/evidence</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4 SKUs, ~6 rules</t>
+          <t>Naive % change misleads</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>DMN/rules engine; ML ranking</t>
+          <t>Research-doc point ladder</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Plain TS pure function + version constants</t>
+          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Auditable</t>
+          <t>Measurement noise unknown</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-08</t>
+          <t>DECISION_LOG D-13; D-24 uncommitted</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>E02, J02</t>
+          <t>C02, D02, G01</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>&gt;20 SKUs or non-engineer rule authors</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>PROPOSED (D-24 uncommitted)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -14424,42 +14424,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Gemini is explanation layer, not authority</t>
+          <t>Recommender deterministic and versioned</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Gemini hallucination/claims risk</t>
+          <t>4 SKUs, ~6 rules</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Gemini owns context</t>
+          <t>DMN/rules engine; ML ranking</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+          <t>Plain TS pure function + version constants</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Auditable</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-14; GATE_02</t>
+          <t>DECISION_LOG D-08</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>B04, F01-F04</t>
+          <t>E02, J02</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&gt;20 SKUs or non-engineer rule authors</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -14469,14 +14469,14 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (paid tier is release gate)</t>
+          <t>PROPOSED</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -14486,104 +14486,104 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>No attribution/efficacy/forecasting</t>
+          <t>Gemini is explanation layer, not authority</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Gemini hallucination/claims risk</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Gemini owns context</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Evidence tiers 3-4</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Prohibited in UI, Gemini, analytics</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>CLAUDE.md</t>
-        </is>
-      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-12</t>
+          <t>DECISION_LOG D-14; GATE_02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>G02, J04, R08</t>
+          <t>B04, F01-F04</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Explicit owner approval</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>PROPOSED (paid tier is release gate)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Client input never authoritative for measured state</t>
+          <t>No attribution/efficacy/forecasting</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Gate 02</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Rules tightening; server chat storage</t>
+          <t>Evidence tiers 3-4</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Path-structural trust; authenticated Echo</t>
+          <t>Prohibited in UI, Gemini, analytics</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Forgeable browser state</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>DECISION_LOG D-12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>A09, B02-B04, C02</t>
+          <t>G02, J04, R08</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Open: client-asserted captureMethod/persistAttempt</t>
+          <t>Explicit owner approval</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -14593,67 +14593,129 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED (branch); owner decision open</t>
+          <t>LOCKED</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>D-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Client input never authoritative for measured state</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Rules tightening; server chat storage</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Path-structural trust; authenticated Echo</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Forgeable browser state</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>A09, B02-B04, C02</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Open: client-asserted captureMethod/persistAttempt</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (branch); owner decision open</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>D-21</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Gate 01 stores raw analysis in scanAnalyses</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Raw preservation</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>skinStates collection</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>users/{uid}/scanAnalyses/{scanId}_{sha16}</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Immutable raw substrate</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>6e9081d</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Systems Architect</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>IMPLEMENTED (not deployed); ID duplicated in HEAD</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>37% = DONE 34 / (total 99 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>42% = DONE 39 / (total 100 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 34, IN PROGRESS 1, NOT STARTED 25, BLOCKED 15, OWNER ACTION 16, LATER 8 (total 99)</t>
+          <t>DONE 39, IN PROGRESS 2, NOT STARTED 20, BLOCKED 15, OWNER ACTION 16, LATER 8 (total 100)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 33, NOT NEEDED 11, NOT CHECKED 54</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 37, NOT NEEDED 11, NOT CHECKED 51</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -6206,13 +6206,21 @@
           <t>Commit + tests</t>
         </is>
       </c>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>f0a45a6</t>
+        </is>
+      </c>
       <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr"/>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>Build in the next longitudinal task; the guard tests stay.</t>
+          <t>test:local and push pending (session stopped at usage limit).</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
@@ -6983,7 +6991,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7028,19 +7036,19 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>bd6bb86</t>
+          <t>8ce5052</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="2" t="inlineStr"/>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>Build per TD-17.</t>
+          <t>test:local and push pending (session stopped at usage limit).</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
@@ -8007,12 +8015,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8046,13 +8054,21 @@
           <t>Decision + commit</t>
         </is>
       </c>
-      <c r="O71" s="2" t="inlineStr"/>
-      <c r="P71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>ad2085b</t>
+        </is>
+      </c>
       <c r="Q71" s="2" t="inlineStr"/>
       <c r="R71" s="2" t="inlineStr"/>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>Build per TD-17.</t>
+          <t>test:local and push pending (session stopped at usage limit).</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
@@ -8099,12 +8115,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8142,13 +8158,21 @@
           <t>Owner approval of the contract edit + commit + test</t>
         </is>
       </c>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>19b2317</t>
+        </is>
+      </c>
       <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr"/>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Build per TD-17.</t>
+          <t>test:local and push pending (session stopped at usage limit).</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
@@ -10191,12 +10215,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -10236,10 +10260,14 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Security review (wave 2) finding 5. The current behaviour (other current products still sent) is pinned by tests/privacy-gemini-inventory.test.ts per owner decision 8, so it was not changed (frozen decision).</t>
-        </is>
-      </c>
-      <c r="P93" s="2" t="inlineStr"/>
+          <t>Security review (wave 2) finding 5. The current behaviour (other current products still sent) is pinned by tests/privacy-gemini-inventory.test.ts per owner decision 8, so it was not changed (frozen decision). Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>fc0285e</t>
+        </is>
+      </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
           <t>Not changed.</t>
@@ -10248,7 +10276,7 @@
       <c r="R93" s="2" t="inlineStr"/>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>Build per TD-17.</t>
+          <t>test:local and push pending (session stopped at usage limit).</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
@@ -10266,32 +10294,32 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H20</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Second security review (2026-10-04) findings</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>Fresh review of e508028, 2bb45e1, 3fa1229, fc0285e and S3 keys. Reproduced: HIGH self-harm phrasings pass the pre-filter (ending my life, end it, hang myself, do not want to live, be dead, jeene ka mann nahi, goliyan); HIGH Devanagari patterns never match folded text (मरना, ZWJ, nukta); MED route checks (Gemini key, history, ledger, 18+, quota) run before the pre-filter so a self-harm message can get 429/503; MED validator: uncertainty/comparability carry free text, clarify/out_of_scope can assert skin state; MED medical misses (hurting, red eyes order, 8-year-old, newborn, temperature, hydroquinone) and false referrals (khatam kar, aankhon, reduce, minor, end my, 2 yrs, 5 kms, melasma, badhiya, I'm a + diet, Greek letter); LOW Latin small caps, Hangul filler; LOW joined window shorter than Gemini window; found during fix: today's Echo replays referred user turns to Gemini in later history. S3: keys clean (uid from token, scanId regex, server-built key); LOW no ContentLength cap on presigned PUT; LOW erase race with 300 s presigned URL. H19 verdict clean; latent: rec section would differ by caution once recommend() is wired; fallback path call vs no call.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10306,10 +10334,14 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr"/>
+          <t>E05, F03</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>GEMINI_BOUNDARY §6</t>
+        </is>
+      </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -10317,48 +10349,56 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>lib/context/prefilter.ts, lib/context/validator.ts, app/api/skin-check/chat/route.ts, lib/s3.ts</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
-        </is>
-      </c>
-      <c r="O94" s="2" t="inlineStr"/>
+          <t>Fix + tests + control cases</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Findings reproduced by test script (all 19 misses and listed false referrals confirmed). No fixes committed yet.</t>
+        </is>
+      </c>
       <c r="P94" s="2" t="inlineStr"/>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R94" s="2" t="inlineStr">
-        <is>
-          <t>Nothing longitudinal is deployed yet.</t>
-        </is>
-      </c>
+          <t>Not fixed</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Fix in commits: (1) pre-filter recall/precision with controls, Devanagari copy (NFC, strip Cf and nukta), no blanket other-script referral (India-first); (2) message-only pre-filter right after body parse, never sign unverified history, joined window = Gemini window, drop referred exchanges from today's Echo history; (3) validator extra-word check on uncertainty/comparability, narrow skin-state list for clarify/out_of_scope. New rows needed: S3 size cap, erase race, other Indic scripts, rec-section caution diff. Then typecheck, lint, build, test:local, push.</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V94" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>Owner instruction 2026-10-04 (follow-up task).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -10373,12 +10413,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -10398,7 +10438,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
+          <t>A12, A13, B01, H01, H03</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -10409,13 +10449,13 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
+          <t>Recorded E2E run against prod</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
@@ -10427,17 +10467,17 @@
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
+          <t>Nothing longitudinal is deployed yet.</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>RELEASE</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -10450,32 +10490,32 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -10485,31 +10525,51 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr"/>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -10522,7 +10582,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -10537,7 +10597,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -10594,7 +10654,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -10609,7 +10669,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>ML recommendation ranking</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -10666,7 +10726,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -10681,7 +10741,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Indian cross-user benchmark</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -10733,16 +10793,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -10757,7 +10813,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Forecasting</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -10809,7 +10865,83 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3fa1229, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47).</t>
+          <t>a5c28b5, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>42% = DONE 39 / (total 100 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>42% = DONE 40 / (total 104 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 39, IN PROGRESS 2, NOT STARTED 20, BLOCKED 15, OWNER ACTION 16, LATER 8 (total 100)</t>
+          <t>DONE 40, IN PROGRESS 1, NOT STARTED 23, BLOCKED 15, OWNER ACTION 17, LATER 8 (total 104)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 37, NOT NEEDED 11, NOT CHECKED 51</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 38, NOT NEEDED 11, NOT CHECKED 54</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V101"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
+          <t>Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6216,11 +6216,15 @@
           <t>f0a45a6</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>Local only.</t>
+        </is>
+      </c>
       <c r="R53" s="2" t="inlineStr"/>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>test:local and push pending (session stopped at usage limit).</t>
+          <t>Owner: confirm the day boundary (UTC now; IST?).</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
@@ -6732,7 +6736,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3.</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7036,7 +7040,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
+          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7044,11 +7048,15 @@
           <t>8ce5052</t>
         </is>
       </c>
-      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>Local only.</t>
+        </is>
+      </c>
       <c r="R61" s="2" t="inlineStr"/>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>test:local and push pending (session stopped at usage limit).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
@@ -7170,37 +7178,37 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Recommendation section must not differ by a hidden caution answer</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>Once recommend() feeds the context package, extra caution withholds the active product, so the rec.* facts Gemini sees differ between users who differ only in a hidden caution answer, and the universal 'no new products' instruction (TD-17 (1)) conflicts with any rec section.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -7210,12 +7218,12 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>A08, D02, E03, E04, E05</t>
+          <t>E02, H19</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>TD-17</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -7225,43 +7233,31 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>lib/context/builder.ts, lib/context/chat.ts</t>
+          <t>lib/context/builder.ts, lib/rules/recommend.ts</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Pure builder + tests</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>buildContextPackage: allowlist serialiser, our own text for every fact and reason, catalogue screen. Real inputs wired: longitudinal results and the evaluateSafety state (ad98ac5); the builder hides exactly the answers SafetyState.extraCautionRaisedBy names (7fe39da); recommendation section empty by design (rules off in production). Tests: context-builder, context-route (+9 in wave 2), context-catalogue-screen. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; ad98ac5, 7fe39da, 3f61b3e, bd6bb86</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>Local only, behind the local-only switch (off in production builds). Context path in production is F08.</t>
-        </is>
-      </c>
+          <t>Design + commit + the H19 equality test extended to rec</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr"/>
       <c r="R63" s="2" t="inlineStr"/>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>F08 (production switch) after its blockers.</t>
+          <t>Decide before wiring recommend() into chat: send no rec section to Gemini, or a caution-independent one.</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7271,14 +7267,14 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Owner decisions TD-16. Formal owner approval of the context brief (lanes README rule 3) was recorded via TD-16.</t>
+          <t>Second security review D(a).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7293,12 +7289,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -7318,7 +7314,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>A08, D02, E03, E04, E05</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7338,33 +7334,33 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>lib/context/renderer.ts, lib/gemini.ts</t>
+          <t>lib/context/builder.ts, lib/context/chat.ts</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
+          <t>Pure builder + tests</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Renderer ctx-prompt-1; generateContextAnswer with structured output, per-request fact-id enum, explicit safety settings, no tools. Proven with a fake at the @google/genai boundary (no dev key locally). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>buildContextPackage: allowlist serialiser, our own text for every fact and reason, catalogue screen. Real inputs wired: longitudinal results and the evaluateSafety state (ad98ac5); the builder hides exactly the answers SafetyState.extraCautionRaisedBy names (7fe39da); recommendation section empty by design (rules off in production). Tests: context-builder, context-route (+9 in wave 2), context-catalogue-screen. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; ad98ac5, 7fe39da, 3f61b3e, bd6bb86</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Local only (fake Gemini). Production needs G1 and H06 (F08).</t>
+          <t>Local only, behind the local-only switch (off in production builds). Context path in production is F08.</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr"/>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>F08.</t>
+          <t>F08 (production switch) after its blockers.</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
@@ -7379,14 +7375,14 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Seed status PARTIALLY READY.</t>
+          <t>Owner decisions TD-16. Formal owner approval of the context brief (lanes README rule 3) was recorded via TD-16.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -7401,12 +7397,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -7426,12 +7422,12 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>D-14 / D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -7446,33 +7442,33 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>lib/context/validator.ts, lib/context/answer.ts</t>
+          <t>lib/context/renderer.ts, lib/gemini.ts</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
+          <t>Schema + renderer + tests</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>Renderer ctx-prompt-1; generateContextAnswer with structured output, per-request fact-id enum, explicit safety settings, no tools. Proven with a fake at the @google/genai boundary (no dev key locally). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; e508028, 2bb45e1</t>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Local only. The second security-fix round (6daa5c7) was re-checked in the wave-2 final review; its findings are fixed. Security review (wave 2) fixes: pre-filter disguises, splits and Hinglish on both chat paths (e508028); validator descriptions, echoes, uncited claims, joined reply (2bb45e1).</t>
+          <t>Local only (fake Gemini). Production needs G1 and H06 (F08).</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr"/>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>F07 offline false-positive check.</t>
+          <t>F08.</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
@@ -7485,12 +7481,16 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>Seed status PARTIALLY READY.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -7525,13 +7525,17 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>D-14 (store rejected for now)</t>
+          <t>D-14 / D-12</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -7546,33 +7550,33 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>lib/context/builder.ts, lib/context/validator.ts</t>
+          <t>lib/context/validator.ts, lib/context/answer.ts</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
+          <t>Validator + adversarial tests</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Self-reported statements are a separate section (source self_reported), citable only by self_reported_echo; a self fact under any other claim type fails self_report_as_measurement. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3.</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; e508028, 2bb45e1</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Local only. SelfReportedStatement.fresh is always true until E07 records confirmations.</t>
+          <t>Local only. The second security-fix round (6daa5c7) was re-checked in the wave-2 final review; its findings are fixed. Security review (wave 2) fixes: pre-filter disguises, splits and Hinglish on both chat paths (e508028); validator descriptions, echoes, uncited claims, joined reply (2bb45e1).</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr"/>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>E07.</t>
+          <t>F07 offline false-positive check.</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
@@ -7590,7 +7594,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -7605,22 +7609,22 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Routine and adherence in the context package</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>The owner asked for a routine and adherence summary in the context package. R-1 A (TD-07) says routine data is not sent to Gemini, and users are told so (ROUTINE_PURPOSE_COPY). The shape allows only { status: "not_shared" }. Routine data next to a "beyond noise" result also invites an attribution claim (D-12).</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -7628,19 +7632,15 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>TD-07 (R-1 A) / D-12</t>
+          <t>D-14 (store rejected for now)</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -7650,29 +7650,33 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>lib/contracts/context-package.ts, lib/consent.ts</t>
+          <t>lib/context/builder.ts, lib/context/validator.ts</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Owner decision; if reopened: new purpose copy, new package version, attribution guard</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr"/>
-      <c r="P67" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>Self-reported statements are a separate section (source self_reported), citable only by self_reported_echo; a self fact under any other claim type fails self_report_as_measurement. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
+        </is>
+      </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Concern recorded 2026-10-04; the frozen decision is not changed.</t>
-        </is>
-      </c>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>Owner decision: keep R-1 A (drop the routine item) or reopen it and change the purpose copy.</t>
-        </is>
-      </c>
+          <t>Local only. SelfReportedStatement.fresh is always true until E07 records confirmations.</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>Owner decides.</t>
+          <t>E07.</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
@@ -7685,16 +7689,12 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
-        <is>
-          <t>Found while writing the shared shapes.</t>
-        </is>
-      </c>
+      <c r="V67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Verified helpline number in the referral copy</t>
+          <t>Routine and adherence in the context package</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>The red-flag and self-harm referral message ships with no phone number (TD-16). A number may be added only after the owner supplies one and verifies it and its hours.</t>
+          <t>The owner asked for a routine and adherence summary in the context package. R-1 A (TD-07) says routine data is not sent to Gemini, and users are told so (ROUTINE_PURPOSE_COPY). The shape allows only { status: "not_shared" }. Routine data next to a "beyond noise" result also invites an attribution claim (D-12).</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -7729,13 +7729,17 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>TD-16 / GEMINI_BOUNDARY §6</t>
+          <t>TD-07 (R-1 A) / D-12</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -7750,29 +7754,29 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>lib/context/prefilter.ts (REFERRAL_COPY)</t>
+          <t>lib/contracts/context-package.ts, lib/consent.ts</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Owner-verified number and hours + commit + test</t>
+          <t>Owner decision; if reopened: new purpose copy, new package version, attribution guard</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>No number in the copy.</t>
+          <t>Concern recorded 2026-10-04; the frozen decision is not changed.</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>Owner has not supplied a verified India helpline.</t>
+          <t>Owner decision: keep R-1 A (drop the routine item) or reopen it and change the purpose copy.</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>Owner supplies and verifies the number; engineer adds it with a test. DEPLOY BLOCKER for switching the context path on in production.</t>
+          <t>Owner decides.</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
@@ -7787,14 +7791,14 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Owner decision 2026-10-04.</t>
+          <t>Found while writing the shared shapes.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -7809,17 +7813,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Offline check of pre-filter and validator misfires</t>
+          <t>Verified helpline number in the referral copy</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>EVALUATION_PLAN §4: measure how often the strict comparison pre-filter (kept by TD-16) and the validator misfire on ordinary questions (e.g. 'should I apply this before bed?').</t>
+          <t>The red-flag and self-harm referral message ships with no phone number (TD-16). A number may be added only after the owner supplies one and verifies it and its hours.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -7829,46 +7833,50 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>F03</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>TD-16</t>
+          <t>TD-16 / GEMINI_BOUNDARY §6</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>lib/context/prefilter.ts, lib/context/validator.ts</t>
+          <t>lib/context/prefilter.ts (REFERRAL_COPY)</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Labelled question set + report</t>
+          <t>Owner-verified number and hours + commit + test</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr"/>
       <c r="P69" s="2" t="inlineStr"/>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>No number in the copy.</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Owner has not supplied a verified India helpline.</t>
+        </is>
+      </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>Build a labelled EN and Hinglish question set; report rates; owner revisits TD-16 (2).</t>
+          <t>Owner supplies and verifies the number; engineer adds it with a test. DEPLOY BLOCKER for switching the context path on in production.</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
@@ -7883,14 +7891,14 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Context report §5.3; Owner instruction 2026-10-04 (wave-2 merge task).</t>
+          <t>Owner decision 2026-10-04.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -7905,17 +7913,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Switch the context path on in production</t>
+          <t>Offline check of pre-filter and validator misfires</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>The context-package chat path is on for local development only (switch ignores production builds).</t>
+          <t>EVALUATION_PLAN §4: measure how often the strict comparison pre-filter (kept by TD-16) and the validator misfire on ordinary questions (e.g. 'should I apply this before bed?').</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -7925,50 +7933,46 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>F06, H06, E05, H17, B10</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>G1 / D-14 / O-4</t>
+          <t>TD-16</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>lib/context/switch.ts</t>
+          <t>lib/context/prefilter.ts, lib/context/validator.ts</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Owner decision + production test</t>
+          <t>Labelled question set + report</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr"/>
       <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>G1 (Gemini data handling), H06 consent copy, F06 helpline, H17 TTL. Also: evaluateSafety throws in production builds until E05/E09, so every context answer would be the fixed fallback.</t>
-        </is>
-      </c>
+      <c r="R70" s="2" t="inlineStr"/>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>Owner decides after the blockers.</t>
+          <t>Build a labelled EN and Hinglish question set; report rates; owner revisits TD-16 (2).</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
@@ -7983,14 +7987,14 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Context report §7.</t>
+          <t>Context report §5.3; Owner instruction 2026-10-04 (wave-2 merge task). H20 (2026-10-04): the validator now rejects free text in uncertainty/comparability and skin-state words in clarify/out_of_scope, so the fallback rate may rise; and a self-harm message split with filler turns ('i want to' / 'ok' / 'die') still passes the joined check. Measure both.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -8005,70 +8009,70 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>ContextSkinState.contractVersion label</t>
+          <t>Switch the context path on in production</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Bands come from scanAnalyses, so the context lane writes scan-analysis-1. Decide the label now that skinstate-2 exists.</t>
+          <t>The context-package chat path is on for local development only (switch ignores production builds).</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>F06, H06, E05, H17, B10</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>TD-17</t>
+          <t>G1 / D-14 / O-4</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>lib/context/builder.ts</t>
+          <t>lib/context/switch.ts</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Decision + commit</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>ad2085b</t>
-        </is>
-      </c>
+          <t>Owner decision + production test</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
       <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>G1 (Gemini data handling), H06 consent copy, F06 helpline, H17 TTL. Also: evaluateSafety throws in production builds until E05/E09, so every context answer would be the fixed fallback.</t>
+        </is>
+      </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>test:local and push pending (session stopped at usage limit).</t>
+          <t>Owner decides after the blockers.</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
@@ -8083,14 +8087,14 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Context report §6.</t>
+          <t>Context report §7.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -8105,12 +8109,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Remove routine_as_directed from the AllowedClaim type</t>
+          <t>ContextSkinState.contractVersion label</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>TD-16 (3) removes the claim type. It was never in allowedClaims at runtime; the type in lib/contracts/context-package.ts still lists it, and that edit was not among the approved contract edits.</t>
+          <t>Bands come from scanAnalyses, so the context lane writes scan-analysis-1. Decide the label now that skinstate-2 exists.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8125,17 +8129,13 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>F05</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>TD-13 / TD-16 / TD-17</t>
+          <t>TD-17</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -8150,29 +8150,33 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>lib/contracts/context-package.ts</t>
+          <t>lib/context/builder.ts</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Owner approval of the contract edit + commit + test</t>
+          <t>Decision + commit</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
+          <t>Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>19b2317</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr"/>
+          <t>ad2085b</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>Local only.</t>
+        </is>
+      </c>
       <c r="R72" s="2" t="inlineStr"/>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>test:local and push pending (session stopped at usage limit).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
@@ -8185,55 +8189,63 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>Context report §6.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>Remove routine_as_directed from the AllowedClaim type</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>TD-16 (3) removes the claim type. It was never in allowedClaims at runtime; the type in lib/contracts/context-package.ts still lists it, and that edit was not among the approved contract edits.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr"/>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>TD-13 / TD-16 / TD-17</t>
+        </is>
+      </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8241,40 +8253,48 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>Systems Architect</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>lib/contracts/context-package.ts</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="2" t="inlineStr"/>
+          <t>Owner approval of the contract edit + commit + test</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>19b2317</t>
+        </is>
+      </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R73" s="2" t="inlineStr">
-        <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
-        </is>
-      </c>
+          <t>Local only.</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr"/>
@@ -8282,32 +8302,32 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Fallback path: a Gemini call or none can differ by a hidden answer</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>When evaluateSafety throws (rules off, or no rule field answered), the context path gives the fixed fallback with no Gemini call. {skin_type, current_products:[prescription]} gets a call while {skin_type} does not. Gemini input is the same; whether a call happens differs. In production builds rules are off, so every user gets the fallback.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8317,17 +8337,17 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>E03, G01</t>
+          <t>F08, E09</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>D-12 (LOCKED)</t>
+          <t>TD-17</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -8337,206 +8357,190 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>Gemini/Context Engineer</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>lib/context/chat.ts, lib/rules/input.ts</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
+          <t>Decision + test</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R74" s="2" t="inlineStr">
-        <is>
-          <t>Needs E03 and G01.</t>
-        </is>
-      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Decide with F08 (production switch).</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V74" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>Second security review D(b).</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>D-16 / D-17 (TD-08, TD-10)</t>
-        </is>
-      </c>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
-        </is>
-      </c>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
-        </is>
-      </c>
+          <t>Approved design + tests + E2E</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
+          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
+          <t>Latest-state/history view can be designed after A13.</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V75" s="2" t="inlineStr">
-        <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>E03, G01</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>D-19 (TD-08, TD-11, TD-12)</t>
+          <t>D-12 (LOCKED)</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -8544,57 +8548,45 @@
           <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
-        </is>
-      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
-        </is>
-      </c>
+          <t>Design reviewed against D-12</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
-        </is>
-      </c>
-      <c r="R76" s="2" t="inlineStr"/>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>Needs E03 and G01.</t>
+        </is>
+      </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V76" s="2" t="inlineStr">
-        <is>
-          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -8609,12 +8601,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -8632,10 +8624,14 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
+          <t>D-16 / D-17 (TD-08, TD-10)</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -8650,37 +8646,37 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
+          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
+          <t>Ledger + erasure route + tests + live verification</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
+          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
+          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
+          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
@@ -8695,14 +8691,14 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -8717,22 +8713,22 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Block writes after an account is erased</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -8740,51 +8736,51 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-19 (TD-08, TD-11, TD-12)</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
+          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="inlineStr"/>
+          <t>Gate + tests</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
+        </is>
+      </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>Needs a rules change outside the privacy lane.</t>
-        </is>
-      </c>
+          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
+          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
@@ -8799,14 +8795,14 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T3; widened to the routine route.</t>
+          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -8821,22 +8817,22 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Support tool to clear a mistaken under-18 record</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -8844,51 +8840,55 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
+      <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>D-19 (decision 4)</t>
+          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
+          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests + audit trail</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="2" t="inlineStr"/>
+          <t>Field inventory + key ownership/tier + consent copy</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+        </is>
+      </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
+          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>Must exist before the final deploy (A13 depends on it).</t>
+          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
+          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
@@ -8903,14 +8903,14 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T17. Deploy blocker.</t>
+          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Final consent copy (AI share and processing)</t>
+          <t>Block writes after an account is erased</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
+          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -8945,22 +8945,22 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>D-16 / decision 6, 7a</t>
+          <t>D-17</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -8970,29 +8970,29 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>lib/consent.ts</t>
+          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Owner/legal copy + version bump + tests updated on purpose</t>
+          <t>Design + commit + tests</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr"/>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
+          <t>Not started (owner: do not do now).</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>Owner or legal supplies both sentences; G1 answered.</t>
+          <t>Needs a rules change outside the privacy lane.</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
+          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
@@ -9007,14 +9007,14 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
+          <t>Proposed by privacy report T3; widened to the routine route.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -9029,12 +9029,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Cross-route under-18 test</t>
+          <t>Support tool to clear a mistaken under-18 record</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
+          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -9057,7 +9057,11 @@
           <t>H02</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>D-19 (decision 4)</t>
+        </is>
+      </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -9065,30 +9069,34 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>tests/</t>
+          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Commit + test result</t>
+          <t>Design + commit + tests + audit trail</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr"/>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R81" s="2" t="inlineStr"/>
+          <t>Not started (owner: do not do now).</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>Must exist before the final deploy (A13 depends on it).</t>
+        </is>
+      </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>Write the test against the merged routes.</t>
+          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
@@ -9103,14 +9111,14 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T6.</t>
+          <t>Proposed by privacy report T17. Deploy blocker.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -9125,12 +9133,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Gemini field scope: self-reported dryness and gender inference</t>
+          <t>Final consent copy (AI share and processing)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
+          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -9145,7 +9153,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -9155,7 +9163,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Decision 8</t>
+          <t>D-16 / decision 6, 7a</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -9170,12 +9178,12 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts</t>
+          <t>lib/consent.ts</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Owner decision (+ commit if changed)</t>
+          <t>Owner/legal copy + version bump + tests updated on purpose</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
@@ -9187,12 +9195,12 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>Owner decision.</t>
+          <t>Owner or legal supplies both sentences; G1 answered.</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
+          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
@@ -9207,14 +9215,14 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T8, T9.</t>
+          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -9229,12 +9237,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Required Gemini allowlist parameter</t>
+          <t>Cross-route under-18 test</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
+          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -9249,12 +9257,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -9265,17 +9273,17 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
+          <t>tests/</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Commit + test result</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr"/>
@@ -9288,12 +9296,12 @@
       <c r="R83" s="2" t="inlineStr"/>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Make the parameter required.</t>
+          <t>Write the test against the merged routes.</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9303,14 +9311,14 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T10.</t>
+          <t>Proposed by privacy report T6.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>H10</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -9325,17 +9333,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Require age attestation on upload and scan</t>
+          <t>Gemini field scope: self-reported dryness and gender inference</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
+          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9345,50 +9353,54 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Decision 3a</t>
+          <t>Decision 8</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
+          <t>lib/skin-check-format.ts</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Owner decision (+ commit if changed)</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr"/>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Later.</t>
-        </is>
-      </c>
-      <c r="R84" s="2" t="inlineStr"/>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision.</t>
+        </is>
+      </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>After old bundles are gone.</t>
+          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
@@ -9403,14 +9415,14 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T13.</t>
+          <t>Proposed by privacy report T8, T9.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -9425,12 +9437,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Engine stores no image</t>
+          <t>Required Gemini allowlist parameter</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
+          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -9445,10 +9457,14 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -9457,17 +9473,17 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>CV/ML Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>skin-scan engine</t>
+          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Code read + runtime check</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr"/>
@@ -9480,12 +9496,12 @@
       <c r="R85" s="2" t="inlineStr"/>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>Read-only check of the engine source and the container.</t>
+          <t>Make the parameter required.</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9495,14 +9511,14 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T15.</t>
+          <t>Proposed by privacy report T10.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>H10</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -9517,17 +9533,17 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>DOM test renderer</t>
+          <t>Require age attestation on upload and scan</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
+          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -9540,47 +9556,47 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>README rule 6</t>
+          <t>Decision 3a</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>package.json, tests/</t>
+          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Owner approval + commit</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr"/>
       <c r="P86" s="2" t="inlineStr"/>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
-        </is>
-      </c>
-      <c r="R86" s="2" t="inlineStr">
-        <is>
-          <t>New dependency needs approval.</t>
-        </is>
-      </c>
+          <t>Later.</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>Owner approves or declines.</t>
+          <t>After old bundles are gone.</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
@@ -9595,14 +9611,14 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T16.</t>
+          <t>Proposed by privacy report T13.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>H13</t>
+          <t>H11</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -9617,12 +9633,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Processing consent after a draft restore</t>
+          <t>Engine stores no image</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
+          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -9637,37 +9653,29 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>D-16 / D-03a</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>CV/ML Engineer</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
+          <t>skin-scan engine</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Decision + commit + tests</t>
+          <t>Code read + runtime check</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
@@ -9677,14 +9685,10 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R87" s="2" t="inlineStr">
-        <is>
-          <t>Owner decides whether restored drafts may carry the consent version.</t>
-        </is>
-      </c>
+      <c r="R87" s="2" t="inlineStr"/>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
+          <t>Read-only check of the engine source and the container.</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
@@ -9699,14 +9703,14 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
+          <t>Proposed by privacy report T15.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>H14</t>
+          <t>H12</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -9721,17 +9725,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Withdraw AI-share consent in the UI</t>
+          <t>DOM test renderer</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
+          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -9741,50 +9745,50 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>README rule 6</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
+          <t>package.json, tests/</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Design check + commit + tests</t>
+          <t>Owner approval + commit</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr"/>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R88" s="2" t="inlineStr"/>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>New dependency needs approval.</t>
+        </is>
+      </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>Check the design, then add a withdraw control.</t>
+          <t>Owner approves or declines.</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
@@ -9799,14 +9803,14 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04.</t>
+          <t>Proposed by privacy report T16.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>H15</t>
+          <t>H13</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -9821,12 +9825,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Low-severity hardening from the security review</t>
+          <t>Processing consent after a draft restore</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
+          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -9844,26 +9848,34 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / D-03a</t>
+        </is>
+      </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
+          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Decision + commit + tests</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
@@ -9873,10 +9885,14 @@
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>Owner decides whether restored drafts may carry the consent version.</t>
+        </is>
+      </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>Add isPlainUid to the upload key path; log name and code only.</t>
+          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
@@ -9891,14 +9907,14 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04 (pre-existing logging).</t>
+          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>H16</t>
+          <t>H14</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -9913,12 +9929,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Consent ledger write slows the scan response</t>
+          <t>Withdraw AI-share consent in the UI</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
+          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -9933,17 +9949,17 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -9953,17 +9969,17 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/route.ts</t>
+          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Commit + test + timing</t>
+          <t>Design check + commit + tests</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr"/>
@@ -9976,7 +9992,7 @@
       <c r="R90" s="2" t="inlineStr"/>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
+          <t>Check the design, then add a withdraw control.</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
@@ -9991,14 +10007,14 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>Verifier observation 2026-10-04 (a52f36d).</t>
+          <t>Security review 2026-10-04.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>H17</t>
+          <t>H15</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -10013,17 +10029,17 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Firestore expiry (TTL) policy for chat turns</t>
+          <t>Low-severity hardening from the security review</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>users/*/chatTurns carry expireAt (90 days, D-15) but no TTL policy exists. Turns include red-flag and self-harm message text.</t>
+          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10033,46 +10049,42 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>D-15</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Firestore (infrastructure)</t>
+          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Policy configured on the India-region database + check</t>
+          <t>Commit + tests</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr"/>
       <c r="P91" s="2" t="inlineStr"/>
-      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
       <c r="R91" s="2" t="inlineStr"/>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>Owner creates the TTL policy on chatTurns.expireAt when the Firestore reset (A04) lands. Deploy blocker for F08.</t>
+          <t>Add isPlainUid to the upload key path; log name and code only.</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
@@ -10087,14 +10099,14 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>Context report §6; Owner instruction 2026-10-04 (wave-2 merge task).</t>
+          <t>Security review 2026-10-04 (pre-existing logging).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>H18</t>
+          <t>H16</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -10109,12 +10121,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Document the context path's sent data</t>
+          <t>Consent ledger write slows the scan response</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>privacy-report.md §5 should list what the new path sends: version labels, lowConfidence, uncertainty and missing facts, not-enough-evidence longitudinal facts, rec.* facts. Pin tests already cover it (add-only).</t>
+          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -10124,22 +10136,22 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -10149,26 +10161,30 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>docs/lanes/privacy-report.md</t>
+          <t>app/api/skin-scan/route.ts</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Committed doc</t>
+          <t>Commit + test + timing</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr"/>
-      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
       <c r="R92" s="2" t="inlineStr"/>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>Write the section.</t>
+          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
@@ -10183,14 +10199,14 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Context report §6.</t>
+          <t>Verifier observation 2026-10-04 (a52f36d).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>H19</t>
+          <t>H17</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -10205,78 +10221,66 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Hidden caution answer can be inferred from what is still sent</t>
+          <t>Firestore expiry (TTL) policy for chat turns</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>With extra caution on, withoutCautionAnswers hides only the matching value. 'Current products: Nothing right now' plus caution can only mean pregnant or breastfeeding; any male_skin_context answer plus caution means a prescription. Affects today's Echo and the context path.</t>
+          <t>users/*/chatTurns carry expireAt (90 days, D-15) but no TTL policy exists. Turns include red-flag and self-harm message text.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>E05, H08</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>TD-08 decision 8 / TD-17</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>lib/gemini.ts (withoutCautionAnswers), lib/context/builder.ts</t>
+          <t>Firestore (infrastructure)</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Owner decision + commit + test</t>
-        </is>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>Security review (wave 2) finding 5. The current behaviour (other current products still sent) is pinned by tests/privacy-gemini-inventory.test.ts per owner decision 8, so it was not changed (frozen decision). Unit run at f0a45a6: vitest 1233 passed / 47 skipped; typecheck 0; next lint clean; next build exit 0. npm run test:local NOT yet run.</t>
-        </is>
-      </c>
-      <c r="P93" s="2" t="inlineStr">
-        <is>
-          <t>fc0285e</t>
-        </is>
-      </c>
-      <c r="Q93" s="2" t="inlineStr">
-        <is>
-          <t>Not changed.</t>
-        </is>
-      </c>
+          <t>Policy configured on the India-region database + check</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr"/>
       <c r="R93" s="2" t="inlineStr"/>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>test:local and push pending (session stopped at usage limit).</t>
+          <t>Owner creates the TTL policy on chatTurns.expireAt when the Firestore reset (A04) lands. Deploy blocker for F08.</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
@@ -10289,12 +10293,16 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>Context report §6; Owner instruction 2026-10-04 (wave-2 merge task).</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>H20</t>
+          <t>H18</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -10309,37 +10317,37 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Second security review (2026-10-04) findings</t>
+          <t>Document the context path's sent data</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Fresh review of e508028, 2bb45e1, 3fa1229, fc0285e and S3 keys. Reproduced: HIGH self-harm phrasings pass the pre-filter (ending my life, end it, hang myself, do not want to live, be dead, jeene ka mann nahi, goliyan); HIGH Devanagari patterns never match folded text (मरना, ZWJ, nukta); MED route checks (Gemini key, history, ledger, 18+, quota) run before the pre-filter so a self-harm message can get 429/503; MED validator: uncertainty/comparability carry free text, clarify/out_of_scope can assert skin state; MED medical misses (hurting, red eyes order, 8-year-old, newborn, temperature, hydroquinone) and false referrals (khatam kar, aankhon, reduce, minor, end my, 2 yrs, 5 kms, melasma, badhiya, I'm a + diet, Greek letter); LOW Latin small caps, Hangul filler; LOW joined window shorter than Gemini window; found during fix: today's Echo replays referred user turns to Gemini in later history. S3: keys clean (uid from token, scanId regex, server-built key); LOW no ContentLength cap on presigned PUT; LOW erase race with 300 s presigned URL. H19 verdict clean; latent: rec section would differ by caution once recommend() is wired; fallback path call vs no call.</t>
+          <t>privacy-report.md §5 should list what the new path sends: version labels, lowConfidence, uncertainty and missing facts, not-enough-evidence longitudinal facts, rec.* facts. Pin tests already cover it (add-only).</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>E05, F03</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>GEMINI_BOUNDARY §6</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -10354,29 +10362,21 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>lib/context/prefilter.ts, lib/context/validator.ts, app/api/skin-check/chat/route.ts, lib/s3.ts</t>
+          <t>docs/lanes/privacy-report.md</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Fix + tests + control cases</t>
-        </is>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>Findings reproduced by test script (all 19 misses and listed false referrals confirmed). No fixes committed yet.</t>
-        </is>
-      </c>
+          <t>Committed doc</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr"/>
-      <c r="Q94" s="2" t="inlineStr">
-        <is>
-          <t>Not fixed</t>
-        </is>
-      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
       <c r="R94" s="2" t="inlineStr"/>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>Fix in commits: (1) pre-filter recall/precision with controls, Devanagari copy (NFC, strip Cf and nukta), no blanket other-script referral (India-first); (2) message-only pre-filter right after body parse, never sign unverified history, joined window = Gemini window, drop referred exchanges from today's Echo history; (3) validator extra-word check on uncertainty/comparability, narrow skin-state list for clarify/out_of_scope. New rows needed: S3 size cap, erase race, other Indic scripts, rec-section caution diff. Then typecheck, lint, build, test:local, push.</t>
+          <t>Write the section.</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
@@ -10391,57 +10391,61 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>Owner instruction 2026-10-04 (follow-up task).</t>
+          <t>Context report §6.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H19</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Hidden caution answer can be inferred from what is still sent</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>With extra caution on, withoutCautionAnswers hides only the matching value. 'Current products: Nothing right now' plus caution can only mean pregnant or breastfeeding; any male_skin_context answer plus caution means a prescription. Affects today's Echo and the context path.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr"/>
+          <t>E05, H08</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>TD-08 decision 8 / TD-17</t>
+        </is>
+      </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -10449,40 +10453,48 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts (withoutCautionAnswers), lib/context/builder.ts</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
-        </is>
-      </c>
-      <c r="O95" s="2" t="inlineStr"/>
-      <c r="P95" s="2" t="inlineStr"/>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Security review (wave 2) finding 5. The current behaviour (other current products still sent) is pinned by tests/privacy-gemini-inventory.test.ts per owner decision 8, so it was not changed (frozen decision). Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47). Pin: tests/privacy-gemini-inventory.test.ts (5 hidden-answer pairs, both paths, retry included). Second security review: no remaining difference with current wiring.</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>fc0285e</t>
+        </is>
+      </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R95" s="2" t="inlineStr">
-        <is>
-          <t>Nothing longitudinal is deployed yet.</t>
-        </is>
-      </c>
+          <t>Local only.</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V95" s="2" t="inlineStr"/>
@@ -10490,37 +10502,37 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>H20</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>Second security review (2026-10-04) findings</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>Fresh review of e508028, 2bb45e1, 3fa1229, fc0285e and S3 keys. Reproduced: HIGH self-harm phrasings pass the pre-filter (ending my life, end it, hang myself, do not want to live, be dead, jeene ka mann nahi, goliyan); HIGH Devanagari patterns never match folded text (मरना, ZWJ, nukta); MED route checks (Gemini key, history, ledger, 18+, quota) run before the pre-filter so a self-harm message can get 429/503; MED validator: uncertainty/comparability carry free text, clarify/out_of_scope can assert skin state; MED medical misses (hurting, red eyes order, 8-year-old, newborn, temperature, hydroquinone) and false referrals (khatam kar, aankhon, reduce, minor, end my, 2 yrs, 5 kms, melasma, badhiya, I'm a + diet, Greek letter); LOW Latin small caps, Hangul filler; LOW joined window shorter than Gemini window; found during fix: today's Echo replays referred user turns to Gemini in later history. S3: keys clean (uid from token, scanId regex, server-built key); LOW no ContentLength cap on presigned PUT; LOW erase race with 300 s presigned URL. H19 verdict clean; latent: rec section would differ by caution once recommend() is wired; fallback path call vs no call.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -10530,10 +10542,14 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr"/>
+          <t>E05, F03</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>GEMINI_BOUNDARY §6 (updated)</t>
+        </is>
+      </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -10541,73 +10557,85 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>lib/context/prefilter.ts, lib/context/validator.ts, app/api/skin-check/chat/route.ts, lib/s3.ts</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
-        </is>
-      </c>
-      <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" s="2" t="inlineStr"/>
+          <t>Fix + tests + control cases</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>All findings reproduced first, then fixed with tests and normal-question controls. Pre-filter (c0a0f87): self-harm EN/Hinglish additions, Devanagari copy (NFC, no Cf, no nukta), medical misses, false referrals narrowed, Latin small caps and Hangul fillers, Greek prefix carve-out; spaced phrases now need word boundaries. Route (7f53d70): message-only referral before key/history/ledger/18+/quota, forged history never signed, joined check = Gemini window, today's Echo no longer replays referred turns. Validator (5d607e3): uncertainty/comparability limited to cited facts' words and their fact kinds; clarify/out_of_scope cannot state skin condition; 'once' a number. S3 (a5c28b5): presign signs content-length (cap 25 MB, provisional) and content-type. Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>c0a0f87, 7f53d70, 5d607e3, a5c28b5</t>
+        </is>
+      </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R96" s="2" t="inlineStr">
-        <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
-        </is>
-      </c>
+          <t>Local only.</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>Follow-ups are rows H21, H22, E10, F11; F07 measures misfire and fallback rates.</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V96" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>Owner instruction 2026-10-04 (follow-up task).</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>H21</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Account erase vs a live presigned upload URL</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>A presigned PUT issued up to 300 s before an erase can still land after the S3 step, leaving a photo after the account is deleted (second security review, LOW). Re-listing at the end does not close it.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -10617,69 +10645,93 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>D-17</t>
+        </is>
+      </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>app/api/account/erase/route.ts, lib/s3.ts</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Design + commit + test</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr"/>
       <c r="P97" s="2" t="inlineStr"/>
       <c r="Q97" s="2" t="inlineStr"/>
       <c r="R97" s="2" t="inlineStr"/>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Options: a second S3 sweep after UPLOAD_URL_TTL_SECONDS (deferred job), or a bucket rule; owner picks.</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V97" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>Second security review (H20).</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>H22</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Self-harm in other Indian scripts is not caught</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>The chat pre-filter covers English, Hinglish and Devanagari. Tamil, Bengali, Telugu and other scripts pass unreferred; referring every such message would block those users (India-first).</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -10689,69 +10741,93 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>GEMINI_BOUNDARY §6</t>
+        </is>
+      </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Product/Routine Rules Engineer</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>lib/context/prefilter.ts</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision + reviewed word lists + tests</t>
+        </is>
+      </c>
       <c r="O98" s="2" t="inlineStr"/>
       <c r="P98" s="2" t="inlineStr"/>
       <c r="Q98" s="2" t="inlineStr"/>
       <c r="R98" s="2" t="inlineStr"/>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Owner decides which languages are served and sources reviewed lists (with the E05 clinical reviewer).</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V98" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>Advisor + second security review (H20).</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>End-to-end production evaluation</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -10761,26 +10837,46 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>A12, A13, B01, H01, H03</t>
+        </is>
+      </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>QA/Test Engineer</t>
+        </is>
+      </c>
       <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Recorded E2E run against prod</t>
+        </is>
+      </c>
       <c r="O99" s="2" t="inlineStr"/>
       <c r="P99" s="2" t="inlineStr"/>
-      <c r="Q99" s="2" t="inlineStr"/>
-      <c r="R99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>Nothing longitudinal is deployed yet.</t>
+        </is>
+      </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Write E2E script while A13 is pending.</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
@@ -10798,32 +10894,32 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Release Validation</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Full red-team sweep</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -10833,31 +10929,51 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
       <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
       <c r="O100" s="2" t="inlineStr"/>
       <c r="P100" s="2" t="inlineStr"/>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>Needs I01 and the Gemini/safety layers.</t>
+        </is>
+      </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>RED TEAM</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -10865,16 +10981,12 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V100" s="2" t="inlineStr">
-        <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
-        </is>
-      </c>
+      <c r="V100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -10889,7 +11001,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>Population priors / mixed effects</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -10942,6 +11054,298 @@
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>ML recommendation ranking</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>J03</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Indian cross-user benchmark</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11904,7 +12308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12730,80 +13134,162 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>followup-session-2026-10-04</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Program Lead</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>TD-17 decisions; H19, E08, F10, F09, D06; second security review and fixes (H20)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>H19, E08, F09, F10, D06, H20</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>main (skin-check)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>longitudinal-platform</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts, lib/context/{builder,renderer,validator,prefilter,chat,lexicon}.ts, lib/contracts/context-package.ts, lib/echo-trusted-context.ts, lib/longitudinal/{settings,baseline}.ts, lib/s3.ts, lib/api.ts, app/api/skin-check/chat/route.ts, app/api/skin-scan/upload/route.ts, docs/architecture/GEMINI_BOUNDARY.md, tests, tracker</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>typecheck, lint, next build, npm run test:local at a5c28b5 (unit 1326 / 47 skipped; stack 47/47)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Security reviewer (fresh): 2 high (self-harm phrasings; Devanagari never matched), 4 medium (referral after refusals; validator free text; uncited skin claims; medical misses and false referrals), lows (lookalikes, window, S3 size, erase race); all reproduced, fixed with tests except erase race (H21) and other scripts (H22). Found during fix: today's Echo replayed referred turns to Gemini (fixed).</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>TD-17 recorded</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>fbdaa03, fc0285e, 8ce5052, 19b2317, ad2085b, f0a45a6, 114c73e, c0a0f87, 7f53d70, 5d607e3, a5c28b5</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Security fixes not re-reviewed by a third pass</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>earlier sessions (gates 01-04, Phase 0)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>A01-A12, B02-B04</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>longitudinal-platform</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>see commits</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>see DECISION_LOG</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>61c149a..91d20bc</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>unknown - not reconstructable from repo</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>a5c28b5, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+          <t>94887f3, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+          <t>Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+          <t>Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+          <t>Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Security review (wave 2) finding 5. The current behaviour (other current products still sent) is pinned by tests/privacy-gemini-inventory.test.ts per owner decision 8, so it was not changed (frozen decision). Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47). Pin: tests/privacy-gemini-inventory.test.ts (5 hidden-answer pairs, both paths, retry included). Second security review: no remaining difference with current wiring.</t>
+          <t>Security review (wave 2) finding 5. The current behaviour (other current products still sent) is pinned by tests/privacy-gemini-inventory.test.ts per owner decision 8, so it was not changed (frozen decision). Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47). Pin: tests/privacy-gemini-inventory.test.ts (5 hidden-answer pairs, both paths, retry included). Second security review: no remaining difference with current wiring.</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>All findings reproduced first, then fixed with tests and normal-question controls. Pre-filter (c0a0f87): self-harm EN/Hinglish additions, Devanagari copy (NFC, no Cf, no nukta), medical misses, false referrals narrowed, Latin small caps and Hangul fillers, Greek prefix carve-out; spaced phrases now need word boundaries. Route (7f53d70): message-only referral before key/history/ledger/18+/quota, forged history never signed, joined check = Gemini window, today's Echo no longer replays referred turns. Validator (5d607e3): uncertainty/comparability limited to cited facts' words and their fact kinds; clarify/out_of_scope cannot state skin condition; 'once' a number. S3 (a5c28b5): presign signs content-length (cap 25 MB, provisional) and content-type. Final run at a5c28b5: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1326 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+          <t>All findings reproduced first, then fixed with tests and normal-question controls. Pre-filter (c0a0f87): self-harm EN/Hinglish additions, Devanagari copy (NFC, no Cf, no nukta), medical misses, false referrals narrowed, Latin small caps and Hangul fillers, Greek prefix carve-out; spaced phrases now need word boundaries. Route (7f53d70): message-only referral before key/history/ledger/18+/quota, forged history never signed, joined check = Gemini window, today's Echo no longer replays referred turns. Validator (5d607e3): uncertainty/comparability limited to cited facts' words and their fact kinds; clarify/out_of_scope cannot state skin condition; 'once' a number. S3 (a5c28b5): presign signs content-length (cap 25 MB, provisional) and content-type. Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47). Follow-up (94887f3): old hits lost by the narrowing restored and pinned; the early referral is recorded only for an admitted user. Deploy check: one real-S3 upload (S3Mock does not verify signatures).</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>c0a0f87, 7f53d70, 5d607e3, a5c28b5</t>
+          <t>c0a0f87, 7f53d70, 5d607e3, a5c28b5, 94887f3</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>typecheck, lint, next build, npm run test:local at a5c28b5 (unit 1326 / 47 skipped; stack 47/47)</t>
+          <t>typecheck, lint, next build, npm run test:local at 94887f3 (unit 1350 / 47 skipped; stack 47/47)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>fbdaa03, fc0285e, 8ce5052, 19b2317, ad2085b, f0a45a6, 114c73e, c0a0f87, 7f53d70, 5d607e3, a5c28b5</t>
+          <t>fbdaa03, fc0285e, 8ce5052, 19b2317, ad2085b, f0a45a6, 114c73e, c0a0f87, 7f53d70, 5d607e3, a5c28b5, 2a2fadb, 94887f3</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 40, IN PROGRESS 1, NOT STARTED 23, BLOCKED 15, OWNER ACTION 17, LATER 8 (total 104)</t>
+          <t>DONE 40, IN PROGRESS 1, NOT STARTED 24, BLOCKED 15, OWNER ACTION 16, LATER 8 (total 104)</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal report 4.3, 4.4. Not built in the merge task (owner: add rows, do not build).</t>
+          <t>Longitudinal report 4.3, 4.4. Not built in the merge task (owner: add rows, do not build). TD-18 (2): day boundary is India time.</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>GEMINI_BOUNDARY §6</t>
+          <t>GEMINI_BOUNDARY §6 / TD-18</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -10780,7 +10780,7 @@
       <c r="R98" s="2" t="inlineStr"/>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>Owner decides which languages are served and sources reviewed lists (with the E05 clinical reviewer).</t>
+          <t>Build per TD-18 (1).</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
@@ -13476,7 +13476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14908,52 +14908,52 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>TD-18</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Native L*/a* are provisional research candidates only</t>
+          <t>Release-prep owner decisions</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 screening</t>
+          <t>H22; D06 day boundary; upload cap; dashboard lane report §4 (O-D1 to O-D6)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Keep b*, ITA, lbpEntropy</t>
+          <t>H22: refer every other-script message, or accept the gap; D06: UTC; O-D1: hide while rules off; O-D3: URL only; O-D4: show past readings; O-D6: keep 'yet'</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Primary endpoints for the human study only; not validated measurements</t>
+          <t>(1) H22: a message in a script Echo does not support never goes to Gemini; it gets a fixed reply saying Echo understands English and Hindi only, plus the referral line. (2) The one-scan-per-day baseline rule uses India time (Asia/Kolkata). (3) The upload cap stays 25 MB, with a clear message to the user. (4) O-D1: no recommendations on the dashboard in any build. (5) O-D2: the trend display is decided later. (6) O-D3: the dashboard is reached from the results screen, the account page and the signed-in start page. (7) O-D4: past checks show no readings. (8) O-D5: the dashboard reads skin states in the browser for display only. (9) O-D6: the trend text does not say 'yet'</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Only survivors of screening</t>
+          <t>Owner instruction 2026-10-04 (release-prep task)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>C03-C07</t>
+          <t>H22, D06, H20, G01, H14, F07</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Owner may reverse before Phase 1 pre-registration</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -14963,76 +14963,76 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>ACCEPTED for study design</t>
+          <t>DECIDED (owner, 2026-10-04). O-D2 open (decided later). Tracker-local until A14.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>D-13 / D-24</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal comparisons require comparability + noise/evidence</t>
+          <t>Native L*/a* are provisional research candidates only</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Naive % change misleads</t>
+          <t>Phase 0 screening</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Research-doc point ladder</t>
+          <t>Keep b*, ITA, lbpEntropy</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
+          <t>Primary endpoints for the human study only; not validated measurements</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Measurement noise unknown</t>
+          <t>Only survivors of screening</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-13; D-24 uncommitted</t>
+          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>C02, D02, G01</t>
+          <t>C03-C07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Owner may reverse before Phase 1 pre-registration</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (D-24 uncommitted)</t>
+          <t>ACCEPTED for study design</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-13 / D-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -15042,59 +15042,59 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Recommender deterministic and versioned</t>
+          <t>Longitudinal comparisons require comparability + noise/evidence</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4 SKUs, ~6 rules</t>
+          <t>Naive % change misleads</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DMN/rules engine; ML ranking</t>
+          <t>Research-doc point ladder</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Plain TS pure function + version constants</t>
+          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Auditable</t>
+          <t>Measurement noise unknown</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-08</t>
+          <t>DECISION_LOG D-13; D-24 uncommitted</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>E02, J02</t>
+          <t>C02, D02, G01</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>&gt;20 SKUs or non-engineer rule authors</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>PROPOSED (D-24 uncommitted)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -15104,42 +15104,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Gemini is explanation layer, not authority</t>
+          <t>Recommender deterministic and versioned</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Gemini hallucination/claims risk</t>
+          <t>4 SKUs, ~6 rules</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Gemini owns context</t>
+          <t>DMN/rules engine; ML ranking</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+          <t>Plain TS pure function + version constants</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Auditable</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-14; GATE_02</t>
+          <t>DECISION_LOG D-08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>B04, F01-F04</t>
+          <t>E02, J02</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&gt;20 SKUs or non-engineer rule authors</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -15149,14 +15149,14 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (paid tier is release gate)</t>
+          <t>PROPOSED</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -15166,104 +15166,104 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>No attribution/efficacy/forecasting</t>
+          <t>Gemini is explanation layer, not authority</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Gemini hallucination/claims risk</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Gemini owns context</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Evidence tiers 3-4</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Prohibited in UI, Gemini, analytics</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>CLAUDE.md</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-12</t>
+          <t>DECISION_LOG D-14; GATE_02</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>G02, J04, R08</t>
+          <t>B04, F01-F04</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Explicit owner approval</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>PROPOSED (paid tier is release gate)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Client input never authoritative for measured state</t>
+          <t>No attribution/efficacy/forecasting</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Gate 02</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Rules tightening; server chat storage</t>
+          <t>Evidence tiers 3-4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Path-structural trust; authenticated Echo</t>
+          <t>Prohibited in UI, Gemini, analytics</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Forgeable browser state</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>DECISION_LOG D-12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>A09, B02-B04, C02</t>
+          <t>G02, J04, R08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Open: client-asserted captureMethod/persistAttempt</t>
+          <t>Explicit owner approval</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -15273,67 +15273,129 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED (branch); owner decision open</t>
+          <t>LOCKED</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>D-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Client input never authoritative for measured state</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Rules tightening; server chat storage</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Path-structural trust; authenticated Echo</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Forgeable browser state</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>A09, B02-B04, C02</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Open: client-asserted captureMethod/persistAttempt</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (branch); owner decision open</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>D-21</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Gate 01 stores raw analysis in scanAnalyses</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Raw preservation</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>skinStates collection</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>users/{uid}/scanAnalyses/{scanId}_{sha16}</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Immutable raw substrate</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>6e9081d</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Systems Architect</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>IMPLEMENTED (not deployed); ID duplicated in HEAD</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>94887f3, 2026-10-04: typecheck 0 errors, lint clean, next build pass, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+          <t>fe85d09, 2026-10-04: typecheck 0, lint clean, npm run test:local exit 0 (unit 1437 passed / 52 skipped; stack 12 files 52/52); npm run test:browser 29/29 at e8916bb. next build not yet rerun after the merge.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>42% = DONE 40 / (total 104 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>47% = DONE 45 / (total 104 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 40, IN PROGRESS 1, NOT STARTED 24, BLOCKED 15, OWNER ACTION 16, LATER 8 (total 104)</t>
+          <t>DONE 45, IN PROGRESS 1, NOT STARTED 20, BLOCKED 14, OWNER ACTION 16, LATER 8 (total 104)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 38, NOT NEEDED 11, NOT CHECKED 54</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 43, NOT NEEDED 11, NOT CHECKED 49</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+          <t>Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47). India time (Asia/Kolkata) in 4eee9dd.</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -8458,21 +8458,25 @@
           <t>Approved design + tests + E2E</t>
         </is>
       </c>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>lane/dashboard merged; O-D1/O-D3/O-D6, K-1, G-1, R-5 fixed. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>merge c3cf0d6; a027ce5, ff29605, 457c1e8, 3890924</t>
+        </is>
+      </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="R75" s="2" t="inlineStr">
-        <is>
-          <t>Comparable-change views need C02/D02; server-read history needs gate 01 in prod (A13).</t>
-        </is>
-      </c>
+      <c r="R75" s="2" t="inlineStr"/>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Latest-state/history view can be designed after A13.</t>
+          <t>O-D2 (trend display) decided later.</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
@@ -8935,12 +8939,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8978,21 +8982,25 @@
           <t>Design + commit + tests</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>erasedAccounts marker checked by rules + second sweep after 70 min; e2e proves late upload, late server write and old-token client write leave nothing. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>673c66d</t>
+        </is>
+      </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
           <t>Not started (owner: do not do now).</t>
         </is>
       </c>
-      <c r="R80" s="2" t="inlineStr">
-        <is>
-          <t>Needs a rules change outside the privacy lane.</t>
-        </is>
-      </c>
+      <c r="R80" s="2" t="inlineStr"/>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>Choose a second S3 and Firestore sweep after max(upload URL lifetime, ID-token lifetime), or a short-lived uid tombstone checked by rules and the server routes.</t>
+          <t>DEPLOY BLOCKER: a cron must call GET /api/account/erase/sweep with Authorization: Bearer $CRON_SECRET (e.g. every 15 min); set CRON_SECRET in production.</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
@@ -9939,12 +9947,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -9982,8 +9990,16 @@
           <t>Design check + commit + tests</t>
         </is>
       </c>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>ConsentSection on /dashboard and /account; withdraw browser test. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>merge c3cf0d6</t>
+        </is>
+      </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
@@ -9992,7 +10008,7 @@
       <c r="R90" s="2" t="inlineStr"/>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>Check the design, then add a withdraw control.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
@@ -10635,12 +10651,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -10678,13 +10694,21 @@
           <t>Design + commit + test</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr"/>
-      <c r="P97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Same fix as H04; e2e uploads with a link issued before the delete. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>673c66d</t>
+        </is>
+      </c>
       <c r="Q97" s="2" t="inlineStr"/>
       <c r="R97" s="2" t="inlineStr"/>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>Options: a second S3 sweep after UPLOAD_URL_TTL_SECONDS (deferred job), or a bucket rule; owner picks.</t>
+          <t>DEPLOY BLOCKER: a cron must call GET /api/account/erase/sweep with Authorization: Bearer $CRON_SECRET (e.g. every 15 min); set CRON_SECRET in production.</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
@@ -10731,12 +10755,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -10774,13 +10798,21 @@
           <t>Owner decision + reviewed word lists + tests</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Fixed reply for any other script, before gates, never to Gemini, left out of later history. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>4eee9dd</t>
+        </is>
+      </c>
       <c r="Q98" s="2" t="inlineStr"/>
       <c r="R98" s="2" t="inlineStr"/>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>Build per TD-18 (1).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
@@ -10968,7 +11000,7 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>IN PROGRESS 2026-10-04: red team A-E launched on the local stack; B, C, D stopped at the account session limit (resets 20:30 IST) and must be rerun; then fixes and a fresh review.</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>47% = DONE 45 / (total 104 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>42% = DONE 45 / (total 114 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 45, IN PROGRESS 1, NOT STARTED 20, BLOCKED 14, OWNER ACTION 16, LATER 8 (total 104)</t>
+          <t>DONE 45, IN PROGRESS 2, NOT STARTED 21, BLOCKED 13, OWNER ACTION 25, LATER 8 (total 114)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 43, NOT NEEDED 11, NOT CHECKED 49</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 43, NOT NEEDED 11, NOT CHECKED 59</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V105"/>
+  <dimension ref="A1:V115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,27 +6246,27 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Product catalog normalization</t>
+          <t>Dashboard counts starting checks that are unusable on their own</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
+          <t>Red team E F3: the page counts a check with a missing region or a low-pixel region as a starting check (the engine skips it per quantity). The engine-boundary case is fixed (6f4fb8c).</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6276,18 +6276,22 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>D01, G01</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>D-08 / D-09 / D-12 (TD-07)</t>
+          <t>TD-14</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -6297,47 +6301,35 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>lib/catalog/</t>
+          <t>components/dashboard/state.ts, lib/longitudinal/baseline.ts</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Owner-supplied master data + versioned schema</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane routine, merged daa0b4a): versioned catalogue schema, synthetic sample, owner template lib/catalog/catalogue-template.csv with a drift check, D-12 word check with the exact-name exception (PRODUCT_NAME_EXCEPTIONS). Tests: catalog-schema (20). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>e45da38; merge daa0b4a</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>Schema only; data is synthetic (R-3 A).</t>
-        </is>
-      </c>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Owner catalogue data. Deploy blocker (routine T1): the deploy is blocked while any product has dataSource "synthetic".</t>
+          <t>Owner decision</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>Owner fills lib/catalog/catalogue-template.csv (fields: routine-report.md section 6), including "Clear Seal" as an owner row; then replace the synthetic CATALOGUE. OPEN-R1 answered by R-2 B (no product cards for now).</t>
+          <t>Options: (a) the page counts only checks usable on their own account for every region (SELF_UNUSABLE); (b) keep one count for the photo, per-quantity detail in the engine. Recommendation: (a).</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6347,109 +6339,97 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Proposed D-12 clarification (registered own-brand name is not by itself a claim) recorded in TD-07.</t>
+          <t>Red team I02.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Products / Routine</t>
+          <t>Longitudinal Intelligence</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Product eligibility / safety rules</t>
+          <t>A newer malformed record hides a valid reading of the same check</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Deterministic, versioned eligibility + safety constraints.</t>
+          <t>Red team A F4: Echo and the dashboard both take the newest primary record and validate only that one, so one bad server write makes a good reading disappear (consistent, but lossy).</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>E01, E05</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-21</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>lib/rules/</t>
+          <t>lib/echo-trusted-context.ts, components/dashboard/state.ts, lib/longitudinal/baseline.ts</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Pure function + version constant + tests</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>Library built: recommend(input, catalogue) with RULESET_VERSION rules-0-provisional, inputSha256 (scope per TD-15), base/active by ingredient class. Off in production builds (on only for NODE_ENV test/development; fails closed), tested for production, unset, empty and staging. Not called anywhere: the context package's recommendation section stays empty. Tests: 143 rules tests in 5 files (+2 in wave-2 wiring). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>lane/rules 8cd98f9, 619dd7c, d0a7409, 45b6231, 1b0741f; merge 7da1a54</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>Local only. Owner decisions TD-15 applied (extra caution withholds the active; prescriber line hidden under a red flag).</t>
-        </is>
-      </c>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr"/>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Real catalogue (E01; the synthetic one has no niacinamide serum, so the active never has an item) and clinical sign-off (E05).</t>
+          <t>Owner decision</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>E01 data, then E05 sign-off (E09), then a caller that treats any throw as 'show nothing' (rules report 6.4).</t>
+          <t>Options: (a) pick the newest VALID record in all three places; (b) keep. Recommendation: (a).</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>LONGITUDINAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6457,12 +6437,16 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Red team I02. Server-only records: needs a server bug to reach.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6477,17 +6461,17 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Routine model + event history</t>
+          <t>Product catalog normalization</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
+          <t>Versioned own-brand catalog: ingredients, classes, claims, constraints, cost, availability.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6497,58 +6481,58 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>R-1..R-6 (TD-07)</t>
+          <t>D-08 / D-09 / D-12 (TD-07)</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>lib/routine/, app/api/routine/events, components/routine, app/(marketing)/routine, firestore.rules lane:routine</t>
+          <t>lib/catalog/</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Data model doc + approved gate + tests</t>
+          <t>Owner-supplied master data + versioned schema</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Built (lane routine, merged daa0b4a): event schemas and currentRoutine(); GET/POST /api/routine/events (uid from the verified token only, strict schemas, idempotent eventIds, 4 KB body cap, 200 writes/uid/day); server-written events, owner read-only rules, collection-group denied; /routine page (own record only, no skin data, no claims). Follow-ups: purpose text moved to lib/consent.ts (7662ed7); root site description neutral (90c30a1, routine T6); erasure covers routineEvents (2f00819). Tests: routine-events, routine-copy, routine-route, firestore-rules-routine, routine.e2e, layout-description. Security review: no cross-user path. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier: routine PASS.</t>
+          <t>Built (lane routine, merged daa0b4a): versioned catalogue schema, synthetic sample, owner template lib/catalog/catalogue-template.csv with a drift check, D-12 word check with the exact-name exception (PRODUCT_NAME_EXCEPTIONS). Tests: catalog-schema (20). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>e9331f3, 6f8c22c, 0f56ea6, ac275fa, 0e37830, e08aa89, 779e967; merge daa0b4a; 7662ed7, 90c30a1, 2f00819</t>
+          <t>e45da38; merge daa0b4a</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Local only; not deployed (A04, A13). Signed-in /routine page not clicked through in a browser.</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr"/>
+          <t>Schema only; data is synthetic (R-3 A).</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Owner catalogue data. Deploy blocker (routine T1): the deploy is blocked while any product has dataSource "synthetic".</t>
+        </is>
+      </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>Browser click-through (E06). Doc alignment (A21). Rate-limit store (B09). Deploy with A13 after A04.</t>
+          <t>Owner fills lib/catalog/catalogue-template.csv (fields: routine-report.md section 6), including "Clear Seal" as an owner row; then replace the synthetic CATALOGUE. OPEN-R1 answered by R-2 B (no product cards for now).</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -6563,14 +6547,14 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>A04 dependency applies to deployment only.</t>
+          <t>Proposed D-12 clarification (registered own-brand name is not by itself a claim) recorded in TD-07.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6585,17 +6569,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Adherence summary</t>
+          <t>Product eligibility / safety rules</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
+          <t>Deterministic, versioned eligibility + safety constraints.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6605,15 +6589,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr"/>
+          <t>E01, E05</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -6626,33 +6614,37 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>lib/routine/adherence.ts</t>
+          <t>lib/rules/</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Function + tests</t>
+          <t>Pure function + version constant + tests</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>adherence(): used / skipped / unknown, counts only; a day with no log is unknown, never skipped. GET /api/routine/events?tz= returns the 7-day summary. Tests: routine-adherence (13), routine.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+          <t>Library built: recommend(input, catalogue) with RULESET_VERSION rules-0-provisional, inputSha256 (scope per TD-15), base/active by ingredient class. Off in production builds (on only for NODE_ENV test/development; fails closed), tested for production, unset, empty and staging. Not called anywhere: the context package's recommendation section stays empty. Tests: 143 rules tests in 5 files (+2 in wave-2 wiring). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0e4bf16; merge daa0b4a</t>
+          <t>lane/rules 8cd98f9, 619dd7c, d0a7409, 45b6231, 1b0741f; merge 7da1a54</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>Local only.</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr"/>
+          <t>Local only. Owner decisions TD-15 applied (extra caution withholds the active; prescriber line hidden under a red flag).</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Real catalogue (E01; the synthetic one has no niacinamide serum, so the active never has an item) and clinical sign-off (E05).</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>None for the function. Deploy with E03.</t>
+          <t>E01 data, then E05 sign-off (E09), then a caller that treats any throw as 'show nothing' (rules report 6.4).</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
@@ -6670,7 +6662,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6685,17 +6677,17 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Red-flag triage interlock</t>
+          <t>Routine model + event history</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Safety layer overrides cosmetic recommendations.</t>
+          <t>Products, routines, starts, stops, substitutions, schedule history (append-only).</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6705,63 +6697,63 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>R-1..R-6 (TD-07)</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>lib/rules/safety.ts, lib/rules/settings.ts, lib/context/prefilter.ts</t>
+          <t>lib/routine/, app/api/routine/events, components/routine, app/(marketing)/routine, firestore.rules lane:routine</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+          <t>Data model doc + approved gate + tests</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3.</t>
+          <t>Built (lane routine, merged daa0b4a): event schemas and currentRoutine(); GET/POST /api/routine/events (uid from the verified token only, strict schemas, idempotent eventIds, 4 KB body cap, 200 writes/uid/day); server-written events, owner read-only rules, collection-group denied; /routine page (own record only, no skin data, no claims). Follow-ups: purpose text moved to lib/consent.ts (7662ed7); root site description neutral (90c30a1, routine T6); erasure covers routineEvents (2f00819). Tests: routine-events, routine-copy, routine-route, firestore-rules-routine, routine.e2e, layout-description. Security review: no cross-user path. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Verifier: routine PASS.</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>lane/rules 8cd98f9, 619dd7c, d0a7409, 45b6231, 1b0741f; merge 7da1a54; eee588c, 7fe39da, 3f61b3e, e508028, 2bb45e1</t>
+          <t>e9331f3, 6f8c22c, 0f56ea6, ac275fa, 0e37830, e08aa89, 779e967; merge daa0b4a; 7662ed7, 90c30a1, 2f00819</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Local only. Security review (wave 2) fixes: pre-filter disguises, splits and Hinglish on both chat paths (e508028); validator descriptions, echoes, uncited claims, joined reply (2bb45e1). Lists PROVISIONAL (REVIEW_STATUS provisional).</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>Red-flag and caution lists need qualified clinical sign-off sourced by the owner.</t>
-        </is>
-      </c>
+          <t>Local only; not deployed (A04, A13). Signed-in /routine page not clicked through in a browser.</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>Owner nominates the clinical reviewer, who signs rules report §4, the caution sentence and the pregnancy-inference question; then E09.</t>
+          <t>Browser click-through (E06). Doc alignment (A21). Rate-limit store (B09). Deploy with A13 after A04.</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6771,14 +6763,14 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04 (privacy T12): also review EXTRA_CAUTION_TRIGGERS and the caution sentence; decide whether the residual pregnancy inference is acceptable or drop the flag or trigger.</t>
+          <t>A04 dependency applies to deployment only.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -6793,22 +6785,22 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Routine page browser click-through</t>
+          <t>Adherence summary</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Signed-in click-through of /routine on the local stack (read, add, stop, swap, log).</t>
+          <t>used / skipped / unknown; missing log is never 'skipped'.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6829,30 +6821,38 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>components/routine, app/(marketing)/routine</t>
+          <t>lib/routine/adherence.ts</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Recorded local click-through</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr"/>
-      <c r="P59" s="2" t="inlineStr"/>
+          <t>Function + tests</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>adherence(): used / skipped / unknown, counts only; a day with no log is unknown, never skipped. GET /api/routine/events?tz= returns the 7-day summary. Tests: routine-adherence (13), routine.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>0e4bf16; merge daa0b4a</t>
+        </is>
+      </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>Not started. The API flow is covered by routine.e2e.</t>
+          <t>Local only.</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr"/>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>Run npm run dev:local and click through as a seeded user.</t>
+          <t>None for the function. Deploy with E03.</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
@@ -6865,16 +6865,12 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by routine report T7.</t>
-        </is>
-      </c>
+      <c r="V59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6889,71 +6885,83 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Record which answers were confirmed on this check, server-side</t>
+          <t>Red-flag triage interlock</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>TD-15 (3a). Rules and the context package need the step ids answered or re-confirmed on this check (confirmedThisScan; SelfReportedStatement.fresh). Today every answer counts as reused.</t>
+          <t>Safety layer overrides cosmetic recommendations.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>TD-15 / D-19 / D-26</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>lib/firebase/skin-checks.ts, firestore.rules, a new server save route</t>
+          <t>lib/rules/safety.ts, lib/rules/settings.ts, lib/context/prefilter.ts</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Route + rules + tests</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr"/>
+          <t>Approved red-flag criteria + tests (EN + Hinglish)</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3.</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>lane/rules 8cd98f9, 619dd7c, d0a7409, 45b6231, 1b0741f; merge 7da1a54; eee588c, 7fe39da, 3f61b3e, e508028, 2bb45e1</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>Local only. Security review (wave 2) fixes: pre-filter disguises, splits and Hinglish on both chat paths (e508028); validator descriptions, echoes, uncited claims, joined reply (2bb45e1). Lists PROVISIONAL (REVIEW_STATUS provisional).</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Red-flag and caution lists need qualified clinical sign-off sourced by the owner.</t>
+        </is>
+      </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Design with the D-10 record task.</t>
+          <t>Owner nominates the clinical reviewer, who signs rules report §4, the caution sentence and the pregnancy-inference question; then E09.</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>ROUTINE/PRODUCT SYSTEM</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -6963,14 +6971,14 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Not a small change: skinChecks are written by the browser (setDoc under firestore.rules); there is no server save route to hook into. Wiring item 9 of the wave-2 merge task.</t>
+          <t>2026-10-04 (privacy T12): also review EXTRA_CAUTION_TRIGGERS and the caution sentence; decide whether the residual pregnancy inference is acceptable or drop the flag or trigger.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -6985,22 +6993,22 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Catalogue texts that fail the context screen</t>
+          <t>Routine page browser click-through</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>tests/context-catalogue-screen.test.ts pins two texts the context builder would drop from chat: the synthetic name 'Sample Sunscreen SPF 50' (digits) and the owner-approved name exception 'Clear Seal' ('clear' is a change word).</t>
+          <t>Signed-in click-through of /routine on the local stack (read, add, stop, swap, log).</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -7010,14 +7018,10 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>TD-16 / TD-17</t>
-        </is>
-      </c>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -7025,38 +7029,30 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>lib/catalog/catalogue.ts, lib/context/builder.ts</t>
+          <t>components/routine, app/(marketing)/routine</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Owner decision + commit + test</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>8ce5052</t>
-        </is>
-      </c>
+          <t>Recorded local click-through</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>Local only.</t>
+          <t>Not started. The API flow is covered by routine.e2e.</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr"/>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Run npm run dev:local and click through as a seeded user.</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
@@ -7071,14 +7067,14 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Wiring item 8.</t>
+          <t>Proposed by routine report T7.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7093,17 +7089,17 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Clinical sign-off commit for the rules</t>
+          <t>Record which answers were confirmed on this check, server-side</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>After sign-off, flip REVIEW_STATUS to clinically_reviewed in a reviewed commit with a RULESET_VERSION bump; there is no environment override.</t>
+          <t>TD-15 (3a). Rules and the context package need the step ids answered or re-confirmed on this check (confirmedThisScan; SelfReportedStatement.fresh). Today every answer counts as reused.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7113,17 +7109,17 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>TD-15 / D-19 / D-26</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -7133,30 +7129,26 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>lib/rules/settings.ts, tests/rules-settings.test.ts</t>
+          <t>lib/firebase/skin-checks.ts, firestore.rules, a new server save route</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Reviewer record + commit + tests</t>
+          <t>Route + rules + tests</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr"/>
       <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>Clinical reviewer sign-off (E05).</t>
-        </is>
-      </c>
+      <c r="R62" s="2" t="inlineStr"/>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>Wait on E05.</t>
+          <t>Design with the D-10 record task.</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
@@ -7171,14 +7163,14 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Rules report §7.</t>
+          <t>Not a small change: skinChecks are written by the browser (setDoc under firestore.rules); there is no server save route to hook into. Wiring item 9 of the wave-2 merge task.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -7193,37 +7185,37 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Recommendation section must not differ by a hidden caution answer</t>
+          <t>Catalogue texts that fail the context screen</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Once recommend() feeds the context package, extra caution withholds the active product, so the rec.* facts Gemini sees differ between users who differ only in a hidden caution answer, and the universal 'no new products' instruction (TD-17 (1)) conflicts with any rec section.</t>
+          <t>tests/context-catalogue-screen.test.ts pins two texts the context builder would drop from chat: the synthetic name 'Sample Sunscreen SPF 50' (digits) and the owner-approved name exception 'Clear Seal' ('clear' is a change word).</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>E02, H19</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>TD-17</t>
+          <t>TD-16 / TD-17</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -7238,21 +7230,33 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>lib/context/builder.ts, lib/rules/recommend.ts</t>
+          <t>lib/catalog/catalogue.ts, lib/context/builder.ts</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + the H19 equality test extended to rec</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="inlineStr"/>
-      <c r="Q63" s="2" t="inlineStr"/>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>tests/context-catalogue-screen.test.ts pins both failures (bd6bb86). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>8ce5052</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>Local only.</t>
+        </is>
+      </c>
       <c r="R63" s="2" t="inlineStr"/>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>Decide before wiring recommend() into chat: send no rec section to Gemini, or a caution-independent one.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
@@ -7267,44 +7271,44 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Second security review D(a).</t>
+          <t>Wiring item 8.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Deterministic ContextPackage</t>
+          <t>Clinical sign-off commit for the rules</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
+          <t>After sign-off, flip REVIEW_STATUS to clinically_reviewed in a reviewed commit with a RULESET_VERSION bump; there is no environment override.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -7314,12 +7318,12 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>A08, D02, E03, E04, E05</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -7329,43 +7333,35 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>lib/context/builder.ts, lib/context/chat.ts</t>
+          <t>lib/rules/settings.ts, tests/rules-settings.test.ts</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Pure builder + tests</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>buildContextPackage: allowlist serialiser, our own text for every fact and reason, catalogue screen. Real inputs wired: longitudinal results and the evaluateSafety state (ad98ac5); the builder hides exactly the answers SafetyState.extraCautionRaisedBy names (7fe39da); recommendation section empty by design (rules off in production). Tests: context-builder, context-route (+9 in wave 2), context-catalogue-screen. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; ad98ac5, 7fe39da, 3f61b3e, bd6bb86</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>Local only, behind the local-only switch (off in production builds). Context path in production is F08.</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="inlineStr"/>
+          <t>Reviewer record + commit + tests</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Clinical reviewer sign-off (E05).</t>
+        </is>
+      </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>F08 (production switch) after its blockers.</t>
+          <t>Wait on E05.</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7375,44 +7371,44 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Owner decisions TD-16. Formal owner approval of the context brief (lanes README rule 3) was recorded via TD-16.</t>
+          <t>Rules report §7.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Gemini schema renderer</t>
+          <t>Recommendation section must not differ by a hidden caution answer</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
+          <t>Once recommend() feeds the context package, extra caution withholds the active product, so the rec.* facts Gemini sees differ between users who differ only in a hidden caution answer, and the universal 'no new products' instruction (TD-17 (1)) conflicts with any rec section.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -7422,12 +7418,12 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E02, H19</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>TD-17</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -7437,43 +7433,31 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>lib/context/renderer.ts, lib/gemini.ts</t>
+          <t>lib/context/builder.ts, lib/rules/recommend.ts</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Schema + renderer + tests</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>Renderer ctx-prompt-1; generateContextAnswer with structured output, per-request fact-id enum, explicit safety settings, no tools. Proven with a fake at the @google/genai boundary (no dev key locally). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
-          <t>Local only (fake Gemini). Production needs G1 and H06 (F08).</t>
-        </is>
-      </c>
+          <t>Design + commit + the H19 equality test extended to rec</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
       <c r="R65" s="2" t="inlineStr"/>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>F08.</t>
+          <t>Decide before wiring recommend() into chat: send no rec section to Gemini, or a caution-independent one.</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7483,59 +7467,59 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Seed status PARTIALLY READY.</t>
+          <t>Second security review D(a).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Context / Gemini</t>
+          <t>Products / Routine</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Grounding / number / reference validator</t>
+          <t>Routine event dates are client-controlled</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
+          <t>Red team A F9: effectiveDate 1900-01-01 is accepted; the future-date check follows the client's time zone, so it is one day loose (Pacific/Kiritimati).</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>D-14 / D-12</t>
+          <t>TD-07</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -7545,43 +7529,31 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Product/Routine Rules Engineer</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>lib/context/validator.ts, lib/context/answer.ts</t>
+          <t>app/api/routine/events</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Validator + adversarial tests</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3.</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; e508028, 2bb45e1</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>Local only. The second security-fix round (6daa5c7) was re-checked in the wave-2 final review; its findings are fixed. Security review (wave 2) fixes: pre-filter disguises, splits and Hinglish on both chat paths (e508028); validator descriptions, echoes, uncited claims, joined reply (2bb45e1).</t>
-        </is>
-      </c>
+          <t>Commit + test</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
       <c r="R66" s="2" t="inlineStr"/>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>F07 offline false-positive check.</t>
+          <t>Add a floor date (account creation or a fixed product start) and check the future against UTC+14 only.</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>ROUTINE/PRODUCT SYSTEM</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7589,12 +7561,16 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>Red team I02. Self-reported data only.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -7609,12 +7585,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>UserAssertion quarantine</t>
+          <t>Deterministic ContextPackage</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>User claims never silently become measured state.</t>
+          <t>Trusted context: SkinState, history, routines, adherence, uncertainty, evidence tier, safety.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -7629,13 +7605,17 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>A08, D02, E03, E04, E05</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>D-14 (store rejected for now)</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -7650,33 +7630,33 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>lib/context/builder.ts, lib/context/validator.ts</t>
+          <t>lib/context/builder.ts, lib/context/chat.ts</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Design + tests</t>
+          <t>Pure builder + tests</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Self-reported statements are a separate section (source self_reported), citable only by self_reported_echo; a self fact under any other claim type fails self_report_as_measurement. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+          <t>buildContextPackage: allowlist serialiser, our own text for every fact and reason, catalogue screen. Real inputs wired: longitudinal results and the evaluateSafety state (ad98ac5); the builder hides exactly the answers SafetyState.extraCautionRaisedBy names (7fe39da); recommendation section empty by design (rules off in production). Tests: context-builder, context-route (+9 in wave 2), context-catalogue-screen. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; ad98ac5, 7fe39da, 3f61b3e, bd6bb86</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Local only. SelfReportedStatement.fresh is always true until E07 records confirmations.</t>
+          <t>Local only, behind the local-only switch (off in production builds). Context path in production is F08.</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr"/>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>E07.</t>
+          <t>F08 (production switch) after its blockers.</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
@@ -7689,12 +7669,16 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>Owner decisions TD-16. Formal owner approval of the context brief (lanes README rule 3) was recorded via TD-16.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -7709,27 +7693,27 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Routine and adherence in the context package</t>
+          <t>Gemini schema renderer</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>The owner asked for a routine and adherence summary in the context package. R-1 A (TD-07) says routine data is not sent to Gemini, and users are told so (ROUTINE_PURPOSE_COPY). The shape allows only { status: "not_shared" }. Routine data next to a "beyond noise" result also invites an attribution claim (D-12).</t>
+          <t>Gemini as explanation layer over a JSON schema with fact-id enum.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -7739,12 +7723,12 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>TD-07 (R-1 A) / D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -7754,29 +7738,33 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>lib/contracts/context-package.ts, lib/consent.ts</t>
+          <t>lib/context/renderer.ts, lib/gemini.ts</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Owner decision; if reopened: new purpose copy, new package version, attribution guard</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="inlineStr"/>
+          <t>Schema + renderer + tests</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Renderer ctx-prompt-1; generateContextAnswer with structured output, per-request fact-id enum, explicit safety settings, no tools. Proven with a fake at the @google/genai boundary (no dev key locally). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
+        </is>
+      </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Concern recorded 2026-10-04; the frozen decision is not changed.</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>Owner decision: keep R-1 A (drop the routine item) or reopen it and change the purpose copy.</t>
-        </is>
-      </c>
+          <t>Local only (fake Gemini). Production needs G1 and H06 (F08).</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>Owner decides.</t>
+          <t>F08.</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
@@ -7791,14 +7779,14 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Found while writing the shared shapes.</t>
+          <t>Seed status PARTIALLY READY.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -7813,38 +7801,42 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Verified helpline number in the referral copy</t>
+          <t>Grounding / number / reference validator</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>The red-flag and self-harm referral message ships with no phone number (TD-16). A number may be added only after the owner supplies one and verifies it and its hours.</t>
+          <t>Post-generation validator (digits, comparative/efficacy lexicon, fallback).</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>TD-16 / GEMINI_BOUNDARY §6</t>
+          <t>D-14 / D-12</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -7854,29 +7846,33 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>lib/context/prefilter.ts (REFERRAL_COPY)</t>
+          <t>lib/context/validator.ts, lib/context/answer.ts</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Owner-verified number and hours + commit + test</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr"/>
-      <c r="P69" s="2" t="inlineStr"/>
+          <t>Validator + adversarial tests</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3.</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91; e508028, 2bb45e1</t>
+        </is>
+      </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>No number in the copy.</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>Owner has not supplied a verified India helpline.</t>
-        </is>
-      </c>
+          <t>Local only. The second security-fix round (6daa5c7) was re-checked in the wave-2 final review; its findings are fixed. Security review (wave 2) fixes: pre-filter disguises, splits and Hinglish on both chat paths (e508028); validator descriptions, echoes, uncited claims, joined reply (2bb45e1).</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>Owner supplies and verifies the number; engineer adds it with a test. DEPLOY BLOCKER for switching the context path on in production.</t>
+          <t>F07 offline false-positive check.</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
@@ -7889,16 +7885,12 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V69" s="2" t="inlineStr">
-        <is>
-          <t>Owner decision 2026-10-04.</t>
-        </is>
-      </c>
+      <c r="V69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -7913,22 +7905,22 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Offline check of pre-filter and validator misfires</t>
+          <t>UserAssertion quarantine</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>EVALUATION_PLAN §4: measure how often the strict comparison pre-filter (kept by TD-16) and the validator misfire on ordinary questions (e.g. 'should I apply this before bed?').</t>
+          <t>User claims never silently become measured state.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -7936,14 +7928,10 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>F03</t>
-        </is>
-      </c>
+      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>TD-16</t>
+          <t>D-14 (store rejected for now)</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -7953,26 +7941,38 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>lib/context/prefilter.ts, lib/context/validator.ts</t>
+          <t>lib/context/builder.ts, lib/context/validator.ts</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Labelled question set + report</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
+          <t>Design + tests</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Self-reported statements are a separate section (source self_reported), citable only by self_reported_echo; a self fact under any other claim type fails self_report_as_measurement. Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47)</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>lane/context bbb9cd9, 2b6499d, 5031362, fa1694d, 9c711af, f1fce4e, 0370e63, f6f2c6a, 6daa5c7; merge dda2a91</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>Local only. SelfReportedStatement.fresh is always true until E07 records confirmations.</t>
+        </is>
+      </c>
       <c r="R70" s="2" t="inlineStr"/>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>Build a labelled EN and Hinglish question set; report rates; owner revisits TD-16 (2).</t>
+          <t>E07.</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
@@ -7985,16 +7985,12 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V70" s="2" t="inlineStr">
-        <is>
-          <t>Context report §5.3; Owner instruction 2026-10-04 (wave-2 merge task). H20 (2026-10-04): the validator now rejects free text in uncertainty/comparability and skin-state words in clarify/out_of_scope, so the fallback rate may rise; and a self-harm message split with filler turns ('i want to' / 'ok' / 'die') still passes the joined check. Measure both.</t>
-        </is>
-      </c>
+      <c r="V70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -8009,17 +8005,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Switch the context path on in production</t>
+          <t>Routine and adherence in the context package</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>The context-package chat path is on for local development only (switch ignores production builds).</t>
+          <t>The owner asked for a routine and adherence summary in the context package. R-1 A (TD-07) says routine data is not sent to Gemini, and users are told so (ROUTINE_PURPOSE_COPY). The shape allows only { status: "not_shared" }. Routine data next to a "beyond noise" result also invites an attribution claim (D-12).</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8029,17 +8025,17 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>F06, H06, E05, H17, B10</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>G1 / D-14 / O-4</t>
+          <t>TD-07 (R-1 A) / D-12</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -8054,25 +8050,29 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>lib/context/switch.ts</t>
+          <t>lib/contracts/context-package.ts, lib/consent.ts</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Owner decision + production test</t>
+          <t>Owner decision; if reopened: new purpose copy, new package version, attribution guard</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr"/>
       <c r="P71" s="2" t="inlineStr"/>
-      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>Concern recorded 2026-10-04; the frozen decision is not changed.</t>
+        </is>
+      </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>G1 (Gemini data handling), H06 consent copy, F06 helpline, H17 TTL. Also: evaluateSafety throws in production builds until E05/E09, so every context answer would be the fixed fallback.</t>
+          <t>Owner decision: keep R-1 A (drop the routine item) or reopen it and change the purpose copy.</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>Owner decides after the blockers.</t>
+          <t>Owner decides.</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
@@ -8087,14 +8087,14 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Context report §7.</t>
+          <t>Found while writing the shared shapes.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -8109,74 +8109,70 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>ContextSkinState.contractVersion label</t>
+          <t>Verified helpline number in the referral copy</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Bands come from scanAnalyses, so the context lane writes scan-analysis-1. Decide the label now that skinstate-2 exists.</t>
+          <t>The red-flag and self-harm referral message ships with no phone number (TD-16). A number may be added only after the owner supplies one and verifies it and its hours.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>TD-17</t>
+          <t>TD-16 / GEMINI_BOUNDARY §6</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>lib/context/builder.ts</t>
+          <t>lib/context/prefilter.ts (REFERRAL_COPY)</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Decision + commit</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>ad2085b</t>
-        </is>
-      </c>
+          <t>Owner-verified number and hours + commit + test</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Local only.</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr"/>
+          <t>No number in the copy.</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>Owner has not supplied a verified India helpline.</t>
+        </is>
+      </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Owner supplies and verifies the number; engineer adds it with a test. DEPLOY BLOCKER for switching the context path on in production.</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
@@ -8191,14 +8187,14 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Context report §6.</t>
+          <t>Owner decision 2026-10-04.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -8213,37 +8209,37 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Remove routine_as_directed from the AllowedClaim type</t>
+          <t>Offline check of pre-filter and validator misfires</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>TD-16 (3) removes the claim type. It was never in allowedClaims at runtime; the type in lib/contracts/context-package.ts still lists it, and that edit was not among the approved contract edits.</t>
+          <t>EVALUATION_PLAN §4: measure how often the strict comparison pre-filter (kept by TD-16) and the validator misfire on ordinary questions (e.g. 'should I apply this before bed?').</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>TD-13 / TD-16 / TD-17</t>
+          <t>TD-16</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -8253,38 +8249,26 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>QA/Test Engineer</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>lib/contracts/context-package.ts</t>
+          <t>lib/context/prefilter.ts, lib/context/validator.ts</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Owner approval of the contract edit + commit + test</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>19b2317</t>
-        </is>
-      </c>
-      <c r="Q73" s="2" t="inlineStr">
-        <is>
-          <t>Local only.</t>
-        </is>
-      </c>
+          <t>Labelled question set + report</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr"/>
       <c r="R73" s="2" t="inlineStr"/>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Build a labelled EN and Hinglish question set; report rates; owner revisits TD-16 (2).</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
@@ -8297,12 +8281,16 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>Context report §5.3; Owner instruction 2026-10-04 (wave-2 merge task). H20 (2026-10-04): the validator now rejects free text in uncertainty/comparability and skin-state words in clarify/out_of_scope, so the fallback rate may rise; and a self-harm message split with filler turns ('i want to' / 'ok' / 'die') still passes the joined check. Measure both. Red team I02: still not caught by the pre-filter: reversed text ('edicius'), base64, and a self-harm split padded with filler turns. Today's Echo reply screen (f91c471) is provisional; measure its fallback rate too.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -8317,17 +8305,17 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Fallback path: a Gemini call or none can differ by a hidden answer</t>
+          <t>Switch the context path on in production</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>When evaluateSafety throws (rules off, or no rule field answered), the context path gives the fixed fallback with no Gemini call. {skin_type, current_products:[prescription]} gets a call while {skin_type} does not. Gemini input is the same; whether a call happens differs. In production builds rules are off, so every user gets the fallback.</t>
+          <t>The context-package chat path is on for local development only (switch ignores production builds).</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8337,22 +8325,22 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>F08, E09</t>
+          <t>F06, H06, E05, H17, B10</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>TD-17</t>
+          <t>G1 / D-14 / O-4</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -8362,21 +8350,25 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>lib/context/chat.ts, lib/rules/input.ts</t>
+          <t>lib/context/switch.ts</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Decision + test</t>
+          <t>Owner decision + production test</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr"/>
       <c r="Q74" s="2" t="inlineStr"/>
-      <c r="R74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>G1 (Gemini data handling), H06 consent copy, F06 helpline, H17 TTL. Also: evaluateSafety throws in production builds until E05/E09, so every context answer would be the fixed fallback.</t>
+        </is>
+      </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Decide with F08 (production switch).</t>
+          <t>Owner decides after the blockers.</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
@@ -8391,34 +8383,34 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Second security review D(b).</t>
+          <t>Context report §7.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal dashboard</t>
+          <t>ContextSkinState.contractVersion label</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
+          <t>Bands come from scanAnalyses, so the context lane writes scan-analysis-1. Decide the label now that skinstate-2 exists.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -8433,15 +8425,15 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>A13, C02, D02</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr"/>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>TD-17</t>
+        </is>
+      </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8449,97 +8441,105 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>Systems Architect</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>lib/context/builder.ts</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Approved design + tests + E2E</t>
+          <t>Decision + commit</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>lane/dashboard merged; O-D1/O-D3/O-D6, K-1, G-1, R-5 fixed. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+          <t>Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>merge c3cf0d6; a027ce5, ff29605, 457c1e8, 3890924</t>
+          <t>ad2085b</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Local only.</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr"/>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>O-D2 (trend display) decided later.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V75" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>Context report §6.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Product-response timeline UX</t>
+          <t>Remove routine_as_directed from the AllowedClaim type</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Routine events next to observations, no causal claims.</t>
+          <t>TD-16 (3) removes the claim type. It was never in allowedClaims at runtime; the type in lib/contracts/context-package.ts still lists it, and that edit was not among the approved contract edits.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>E03, G01</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>D-12 (LOCKED)</t>
+          <t>TD-13 / TD-16 / TD-17</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -8549,40 +8549,48 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>Systems Architect</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>lib/contracts/context-package.ts</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Design reviewed against D-12</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="inlineStr"/>
+          <t>Owner approval of the contract edit + commit + test</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47).</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>19b2317</t>
+        </is>
+      </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R76" s="2" t="inlineStr">
-        <is>
-          <t>Needs E03 and G01.</t>
-        </is>
-      </c>
+          <t>Local only.</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Wait.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr"/>
@@ -8590,27 +8598,27 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>F12</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Consent / retention / deletion fan-out</t>
+          <t>Which Echo path ships to production</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
+          <t>Red team B F-B1/E F1: today's Echo (production path) had no output check; now it has a provisional word screen (f91c471). The context path has the full structured validator but is local-only (F08).</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -8620,7 +8628,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -8630,12 +8638,12 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-17 (TD-08, TD-10)</t>
+          <t>G1.6 / D-14</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -8645,47 +8653,35 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
+          <t>lib/context/switch.ts, lib/echo-reply-screen.ts</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Ledger + erasure route + tests + live verification</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
-          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
-        </is>
-      </c>
+          <t>Owner decision</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr"/>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
+          <t>Owner decision</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
+          <t>Options: (a) ship today's Echo with the reply screen; (b) make the context path the production path once F08 blockers clear; (c) ship no chat until (b). Recommendation: (b), with (a) as the interim if chat must ship first.</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -8695,44 +8691,44 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
+          <t>Red team I02.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>18+ gate / safety UX</t>
+          <t>Echo answers about any past check</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
+          <t>Red team E F2: any client naming an older scanId gets Echo about that check (one band set per thread), so two threads side by side compare checks across engine builds, which the dashboard deliberately prevents.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -8740,10 +8736,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>G01</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>D-19 (TD-08, TD-11, TD-12)</t>
+          <t>LONGITUDINAL_METHOD §1</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -8753,43 +8753,35 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
+          <t>app/api/skin-check/chat/route.ts</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Gate + tests</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="inlineStr"/>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision</t>
+        </is>
+      </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
+          <t>Options: (a) only the newest measured check (the dashboard's echoScanId) and the check just made; (b) keep any check. Recommendation: (a).</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -8799,105 +8791,93 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
+          <t>Red team I02.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Context / Gemini</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>In-region prompt/data audit</t>
+          <t>Fallback path: a Gemini call or none can differ by a hidden answer</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
+          <t>When evaluateSafety throws (rules off, or no rule field answered), the context path gives the fixed fallback with no Gemini call. {skin_type, current_products:[prescription]} gets a call while {skin_type} does not. Gemini input is the same; whether a call happens differs. In production builds rules are off, so every user gets the fallback.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>F08, E09</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
+          <t>TD-17</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
+          <t>lib/context/chat.ts, lib/rules/input.ts</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Field inventory + key ownership/tier + consent copy</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
-        </is>
-      </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
-        </is>
-      </c>
-      <c r="R79" s="2" t="inlineStr">
-        <is>
-          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
-        </is>
-      </c>
+          <t>Decision + test</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
+          <t>Decide with F08 (production switch).</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -8907,34 +8887,34 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
+          <t>Second security review D(b).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Block writes after an account is erased</t>
+          <t>Longitudinal dashboard</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
+          <t>Latest state, history, comparable change only, confidence, routine, adherence, evidence, privacy controls.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -8954,14 +8934,10 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>D-17</t>
-        </is>
-      </c>
+          <t>A13, C02, D02</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -8969,85 +8945,77 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
-        </is>
-      </c>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests</t>
+          <t>Approved design + tests + E2E</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>erasedAccounts marker checked by rules + second sweep after 70 min; e2e proves late upload, late server write and old-token client write leave nothing. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+          <t>lane/dashboard merged; O-D1/O-D3/O-D6, K-1, G-1, R-5 fixed. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>673c66d</t>
+          <t>merge c3cf0d6; a027ce5, ff29605, 457c1e8, 3890924</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>DEPLOY BLOCKER: a cron must call GET /api/account/erase/sweep with Authorization: Bearer $CRON_SECRET (e.g. every 15 min); set CRON_SECRET in production.</t>
+          <t>O-D2 (trend display) decided later.</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V80" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by privacy report T3; widened to the routine route.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Privacy / Safety</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Support tool to clear a mistaken under-18 record</t>
+          <t>Product-response timeline UX</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
+          <t>Routine events next to observations, no causal claims.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9057,17 +9025,17 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>E03, G01</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>D-19 (decision 4)</t>
+          <t>D-12 (LOCKED)</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -9077,56 +9045,48 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
-        </is>
-      </c>
+          <t>Frontend/Dashboard Engineer</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + tests + audit trail</t>
+          <t>Design reviewed against D-12</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr"/>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>Not started (owner: do not do now).</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>Must exist before the final deploy (A13 depends on it).</t>
+          <t>Needs E03 and G01.</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
+          <t>Wait.</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="V81" s="2" t="inlineStr">
-        <is>
-          <t>Proposed by privacy report T17. Deploy blocker.</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -9141,12 +9101,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Final consent copy (AI share and processing)</t>
+          <t>Consent / retention / deletion fan-out</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
+          <t>Server-written consent ledger; erasure S3 -&gt; Firestore -&gt; Auth.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -9156,7 +9116,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -9166,12 +9126,12 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>D-16 / decision 6, 7a</t>
+          <t>D-16 / D-17 (TD-08, TD-10)</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -9186,29 +9146,37 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>lib/consent.ts</t>
+          <t>app/api/account/, lib/s3.ts, lib/s3-key.ts, lib/consent.ts, firestore.rules lane:privacy, DeleteAccount.tsx</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Owner/legal copy + version bump + tests updated on purpose</t>
-        </is>
-      </c>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="inlineStr"/>
+          <t>Ledger + erasure route + tests + live verification</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy, merged 1dd4acf): server-written consentLedger (owner read-only rules); presign records image_retention; erase route (fresh sign-in, preflight, revoke -&gt; S3 prefix with a separate erase credential pair -&gt; Firestore recursiveDelete -&gt; Auth; receipt with no uid); delete section on /account. After merge: R5 dev guard refuses real AWS erase keys (9b534e7); erasure proven to remove routineEvents (2f00819) and the under-18 record, and the tab marker is cleared (bc45a01, owner TD-10); processing consent recorded per scan (a52f36d, step 14, R3/R4; recovery re-send fix 2d0d1a1 from security review). Tests: privacy-ledger, privacy-erase, privacy-s3-erase, privacy-delete-account, privacy-processing-consent, firestore-rules-privacy, privacy.e2e. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0.</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>52cbbbc, 9808fd5, bbaa10a, 2155645, f8f2b64, 72b293d; merge 1dd4acf; 9b534e7, 2f00819, bc45a01, a52f36d, 2d0d1a1, bff6e25</t>
+        </is>
+      </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
+          <t>Local only (S3Mock, emulators). No production erase principal exists.</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>Owner or legal supplies both sentences; G1 answered.</t>
+          <t>Owner: erase IAM principal and policy (decision 11a, privacy T4); retention period (decision 5, privacy T5: IMAGE_RETENTION_PERIOD_DAYS is null).</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
+          <t>Owner creates the erase principal (ListBucket on users/*, DeleteObject); re-check versioning and Object Lock before go-live; decide the retention number, then an S3 lifecycle rule (infra). Writes after erase: H04. Final processing copy: H06.</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
@@ -9223,14 +9191,14 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
+          <t>H01_S3_ERASURE_READINESS.md (4631de5): versioning never enabled, no Object Lock, no lifecycle.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -9245,66 +9213,74 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Cross-route under-18 test</t>
+          <t>18+ gate / safety UX</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
+          <t>Server-side 18+ attestation; re-confirm sensitive answers per scan.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>D-19 (TD-08, TD-11, TD-12)</t>
+        </is>
+      </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>tests/</t>
+          <t>app/api/account/attestation, app/api/account/_ledger.ts, app/api/skin-scan/*, app/api/skin-check/chat, lib/useSkinCheckFlow.ts, SkinCheckFlow.tsx, PhoneAuthStep.tsx</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Commit + test result</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr"/>
-      <c r="P83" s="2" t="inlineStr"/>
+          <t>Gate + tests</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy 1dd4acf, held gates bdc462f with owner-approved R-A test blocks): attestation route; sticky under-18 (decision 4) refused 403 UNDER_18 on upload, scan (preamble) and chat; chat also needs an attestation; no record degrades on upload/scan (decision 3a); phone stored as "verified"; current_products and female_skin_context re-confirmed every scan, blank. After merge: confirm step "You chose under 18. Is that right?" before anything is recorded (edc4451, TD-12); "Last time you said: ..." hint (c2834cf, R9). Tests: privacy-attestation, privacy-scan-gate, privacy-chat-gate, privacy-age-memory, privacy-reconfirm, privacy-phone, skin-check-flow-navigation (R6). Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review: no bypass found beyond the documented decision-3a degrade and self-attestation limits.</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>743c24c, 4464282, a9719a2, a22a317, 72b293d, d46d6a5, f15c24a; merges 1dd4acf, bdc462f; edc4451, c2834cf</t>
+        </is>
+      </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Local only. Self-attestation: a new tab defeats the device marker; the server record is sticky. TD-11 decided 2026-10-04.</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr"/>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Write the test against the merged routes.</t>
+          <t>Nothing left in this row. Follow-on rows: H05 support tool (deploy blocker), H07 cross-route test, H10 require attestation later. Deploy with A13.</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
@@ -9319,14 +9295,14 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T6.</t>
+          <t>Erasure resets the sticky state by owner decision (TD-10): a recorded minor can erase and start a new account.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -9341,12 +9317,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Gemini field scope: self-reported dryness and gender inference</t>
+          <t>In-region prompt/data audit</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
+          <t>What reaches Gemini, where processed/logged; consent and minimization.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -9356,22 +9332,18 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Decision 8</t>
+          <t>PREFLIGHT G1 / D-14 (TD-08)</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -9386,29 +9358,37 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts</t>
+          <t>lib/gemini.ts, lib/skin-check-format.ts, lib/echo-history-token.ts, app/api/account/consent, EchoPage.tsx</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Owner decision (+ commit if changed)</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="inlineStr"/>
+          <t>Field inventory + key ownership/tier + consent copy</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>c468f1a, bae775f, 4b47292, 72b293d, f15c24a; merges 1dd4acf, bdc462f; 85c7b47, 7e8071b</t>
+        </is>
+      </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
+          <t>Local only. Step 13 must not reach production before decision 6 and final copy.</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>Owner decision.</t>
+          <t>Owner: G1 key project and tier (decision 6); final AI-share copy (decision 7a) -&gt; H06.</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
+          <t>Owner answers G1 and supplies copy (H06). Owner scope items H08 (Dryness self-report, gender inference). Clinical review of EXTRA_CAUTION_TRIGGERS under E05.</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
@@ -9423,14 +9403,14 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T8, T9.</t>
+          <t>Known inferences: gender from male_skin_context; self-reported dryness from primary_concerns / skin_type.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -9445,35 +9425,39 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Required Gemini allowlist parameter</t>
+          <t>Block writes after an account is erased</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
+          <t>After an erase, these can still write: a presigned PUT (up to 300 s), an in-flight scan, Firestore client writes with an unexpired ID token, and /api/routine/events through the Admin SDK with an unexpired token.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr"/>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>D-17</t>
+        </is>
+      </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -9481,35 +9465,43 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Gemini/Context Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
+          <t>app/api/account/erase, firestore.rules, app/api/skin-scan/*, app/api/routine/events</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr"/>
-      <c r="P85" s="2" t="inlineStr"/>
+          <t>Design + commit + tests</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>erasedAccounts marker checked by rules + second sweep after 70 min; e2e proves late upload, late server write and old-token client write leave nothing. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>673c66d</t>
+        </is>
+      </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Not started (owner: do not do now).</t>
         </is>
       </c>
       <c r="R85" s="2" t="inlineStr"/>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>Make the parameter required.</t>
+          <t>DEPLOY BLOCKER: a cron must call GET /api/account/erase/sweep with Authorization: Bearer $CRON_SECRET (e.g. every 15 min); set CRON_SECRET in production.</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>GEMINI CONTEXT LAYER</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9519,14 +9511,14 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T10.</t>
+          <t>Proposed by privacy report T3; widened to the routine route. Red team I02 (D): proven live, including a scan still running when the account was erased.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>H10</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -9541,17 +9533,17 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Require age attestation on upload and scan</t>
+          <t>Support tool to clear a mistaken under-18 record</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
+          <t>Decision 4 says support clears a wrong under-18 entry; no tool exists. An adult who mis-taps "&lt;18" and confirms it stays blocked.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -9561,7 +9553,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -9571,7 +9563,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Decision 3a</t>
+          <t>D-19 (decision 4)</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -9581,30 +9573,34 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
+          <t>scripts/ or an admin route; app/api/account/_ledger.ts</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Commit + tests</t>
+          <t>Design + commit + tests + audit trail</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr"/>
       <c r="P86" s="2" t="inlineStr"/>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Later.</t>
-        </is>
-      </c>
-      <c r="R86" s="2" t="inlineStr"/>
+          <t>Not started (owner: do not do now).</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>Must exist before the final deploy (A13 depends on it).</t>
+        </is>
+      </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>After old bundles are gone.</t>
+          <t>Design an audited support action that appends a clearing entry (ledger stays append-only).</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
@@ -9619,14 +9615,14 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T13.</t>
+          <t>Proposed by privacy report T17. Deploy blocker.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -9641,17 +9637,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Engine stores no image</t>
+          <t>Final consent copy (AI share and processing)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
+          <t>AI_SHARE_CONSENT_VERSION and PROCESSING_CONSENT_VERSION both contain DRAFT; tests pin it. AI share also waits on decision 6 (G1). Processing copy must cover storing measurements (D-16); today it reuses the existing checkbox wording.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -9661,42 +9657,54 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>D-16 / decision 6, 7a</t>
+        </is>
+      </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>CV/ML Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>skin-scan engine</t>
+          <t>lib/consent.ts</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Code read + runtime check</t>
+          <t>Owner/legal copy + version bump + tests updated on purpose</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr"/>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R87" s="2" t="inlineStr"/>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>Owner or legal supplies both sentences; G1 answered.</t>
+        </is>
+      </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>Read-only check of the engine source and the container.</t>
+          <t>Install the copy, bump both versions, update the DRAFT pin tests.</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
@@ -9711,14 +9719,14 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T15.</t>
+          <t>Proposed by privacy report T2; verifier 2026-10-04 (processing). Deploy blocker.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -9733,17 +9741,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DOM test renderer</t>
+          <t>Cross-route under-18 test</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
+          <t>One test: under-18 then 18-24 stays refused on upload, scan and chat.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -9753,18 +9761,18 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>README rule 6</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -9774,29 +9782,25 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>package.json, tests/</t>
+          <t>tests/</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Owner approval + commit</t>
+          <t>Commit + test result</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr"/>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Owner action.</t>
-        </is>
-      </c>
-      <c r="R88" s="2" t="inlineStr">
-        <is>
-          <t>New dependency needs approval.</t>
-        </is>
-      </c>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>Owner approves or declines.</t>
+          <t>Write the test against the merged routes.</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
@@ -9811,14 +9815,14 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>Proposed by privacy report T16.</t>
+          <t>Proposed by privacy report T6.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>H13</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -9833,17 +9837,17 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Processing consent after a draft restore</t>
+          <t>Gemini field scope: self-reported dryness and gender inference</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
+          <t>Confirm self-reported "Dryness" answers (primary_concerns, skin_type) may still go to Gemini (decision 8 removed only the measured band); gender can be inferred from male_skin_context: accept, or drop that step from Gemini.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -9853,17 +9857,17 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>D-16 / D-03a</t>
+          <t>Decision 8</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -9873,34 +9877,34 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Security/Privacy Reviewer</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
+          <t>lib/skin-check-format.ts</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Decision + commit + tests</t>
+          <t>Owner decision (+ commit if changed)</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr"/>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Owner action.</t>
         </is>
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>Owner decides whether restored drafts may carry the consent version.</t>
+          <t>Owner decision.</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
+          <t>Owner decides; pin test changes on purpose if a field is dropped.</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
@@ -9915,14 +9919,14 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
+          <t>Proposed by privacy report T8, T9. Red team I02 (B): gender is still inferable from male_skin_context answers; unchanged, owner item.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>H14</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -9937,27 +9941,27 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Withdraw AI-share consent in the UI</t>
+          <t>Required Gemini allowlist parameter</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
+          <t>summarizeSkinCheckAnswers defaults to sending everything configured as sent; make its allowlist required and update echo-prompt-answers.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -9965,11 +9969,7 @@
           <t>H03</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>D-16</t>
-        </is>
-      </c>
+      <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -9977,29 +9977,21 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Frontend/Dashboard Engineer</t>
+          <t>Gemini/Context Engineer</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
+          <t>lib/skin-check-format.ts, tests/echo-prompt-answers.test.ts</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Design check + commit + tests</t>
-        </is>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>ConsentSection on /dashboard and /account; withdraw browser test. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
-        </is>
-      </c>
-      <c r="P90" s="2" t="inlineStr">
-        <is>
-          <t>merge c3cf0d6</t>
-        </is>
-      </c>
+          <t>Commit + tests</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
       <c r="Q90" s="2" t="inlineStr">
         <is>
           <t>Not started.</t>
@@ -10008,12 +10000,12 @@
       <c r="R90" s="2" t="inlineStr"/>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Make the parameter required.</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>PRIVACY/SAFETY</t>
+          <t>GEMINI CONTEXT LAYER</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10023,14 +10015,14 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04.</t>
+          <t>Proposed by privacy report T10.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>H15</t>
+          <t>H10</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -10045,17 +10037,17 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Low-severity hardening from the security review</t>
+          <t>Require age attestation on upload and scan</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
+          <t>Flip REQUIRE_AGE_ATTESTATION to true once old bundles are gone (decision 3a), with R8 (PhotoCapture must not retry endlessly on UNDER_18 / ATTESTATION_REQUIRED).</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10068,8 +10060,16 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Decision 3a</t>
+        </is>
+      </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
+          <t>app/api/account/_ledger.ts, PhotoCapture.tsx</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10094,13 +10094,13 @@
       <c r="P91" s="2" t="inlineStr"/>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Later.</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr"/>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>Add isPlainUid to the upload key path; log name and code only.</t>
+          <t>After old bundles are gone.</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
@@ -10115,14 +10115,14 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>Security review 2026-10-04 (pre-existing logging).</t>
+          <t>Proposed by privacy report T13.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>H16</t>
+          <t>H11</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Consent ledger write slows the scan response</t>
+          <t>Engine stores no image</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
+          <t>Confirm the engine writes no image to disk or S3 (privacy design section 5.1 row 17).</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -10157,19 +10157,11 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -10177,17 +10169,17 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>CV/ML Engineer</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>app/api/skin-scan/route.ts</t>
+          <t>skin-scan engine</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Commit + test + timing</t>
+          <t>Code read + runtime check</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr"/>
@@ -10200,7 +10192,7 @@
       <c r="R92" s="2" t="inlineStr"/>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
+          <t>Read-only check of the engine source and the container.</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
@@ -10215,14 +10207,14 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Verifier observation 2026-10-04 (a52f36d).</t>
+          <t>Proposed by privacy report T15.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>H17</t>
+          <t>H12</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -10237,12 +10229,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Firestore expiry (TTL) policy for chat turns</t>
+          <t>DOM test renderer</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>users/*/chatTurns carry expireAt (90 days, D-15) but no TTL policy exists. Turns include red-flag and self-harm message text.</t>
+          <t>UI flows are tested by source pins only; a DOM renderer is a new dev dependency.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -10257,17 +10249,13 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>README rule 6</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -10277,26 +10265,34 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Backend/Data Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Firestore (infrastructure)</t>
+          <t>package.json, tests/</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Policy configured on the India-region database + check</t>
+          <t>Owner approval + commit</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr"/>
-      <c r="Q93" s="2" t="inlineStr"/>
-      <c r="R93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>Owner action.</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>New dependency needs approval.</t>
+        </is>
+      </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>Owner creates the TTL policy on chatTurns.expireAt when the Firestore reset (A04) lands. Deploy blocker for F08.</t>
+          <t>Owner approves or declines.</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
@@ -10311,14 +10307,14 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>Context report §6; Owner instruction 2026-10-04 (wave-2 merge task).</t>
+          <t>Proposed by privacy report T16.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>H18</t>
+          <t>H13</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -10333,12 +10329,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Document the context path's sent data</t>
+          <t>Processing consent after a draft restore</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>privacy-report.md §5 should list what the new path sends: version labels, lowConfidence, uncertainty and missing facts, not-enough-evidence longitudinal facts, rec.* facts. Pin tests already cover it (add-only).</t>
+          <t>processingConsentVersion is not saved in the draft, so a restored scan retried from the dashboard writes no analysis record and no ledger entry (fails closed; Echo then has no record for that scan).</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -10348,51 +10344,59 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>NOT NEEDED</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>D-16 / D-03a</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>docs/lanes/privacy-report.md</t>
+          <t>lib/skin-check-draft.ts, lib/useSkinCheckFlow.ts</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Committed doc</t>
+          <t>Decision + commit + tests</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr"/>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>Owner decides whether restored drafts may carry the consent version.</t>
+        </is>
+      </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>Write the section.</t>
+          <t>Decide, then mirror the retention-version handling or keep fail-closed.</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
@@ -10407,14 +10411,14 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>Context report §6.</t>
+          <t>Found 2026-10-04 while building step 14 (a52f36d); verifier observation.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>H19</t>
+          <t>H14</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -10429,12 +10433,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Hidden caution answer can be inferred from what is still sent</t>
+          <t>Withdraw AI-share consent in the UI</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>With extra caution on, withoutCautionAnswers hides only the matching value. 'Current products: Nothing right now' plus caution can only mean pregnant or breastfeeding; any male_skin_context answer plus caution means a prescription. Affects today's Echo and the context path.</t>
+          <t>The consent route accepts granted:false, but Echo has no control to withdraw.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -10449,17 +10453,17 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>E05, H08</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>TD-08 decision 8 / TD-17</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -10469,32 +10473,32 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Security/Privacy Reviewer</t>
+          <t>Frontend/Dashboard Engineer</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>lib/gemini.ts (withoutCautionAnswers), lib/context/builder.ts</t>
+          <t>components/skin-check/EchoPage.tsx, app/(marketing)/account</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Owner decision + commit + test</t>
+          <t>Design check + commit + tests</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Security review (wave 2) finding 5. The current behaviour (other current products still sent) is pinned by tests/privacy-gemini-inventory.test.ts per owner decision 8, so it was not changed (frozen decision). Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47). Pin: tests/privacy-gemini-inventory.test.ts (5 hidden-answer pairs, both paths, retry included). Second security review: no remaining difference with current wiring.</t>
+          <t>ConsentSection on /dashboard and /account; withdraw browser test. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>fc0285e</t>
+          <t>merge c3cf0d6</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>Local only.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr"/>
@@ -10513,12 +10517,16 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>Security review 2026-10-04.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>H20</t>
+          <t>H15</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -10533,39 +10541,31 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Second security review (2026-10-04) findings</t>
+          <t>Low-severity hardening from the security review</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Fresh review of e508028, 2bb45e1, 3fa1229, fc0285e and S3 keys. Reproduced: HIGH self-harm phrasings pass the pre-filter (ending my life, end it, hang myself, do not want to live, be dead, jeene ka mann nahi, goliyan); HIGH Devanagari patterns never match folded text (मरना, ZWJ, nukta); MED route checks (Gemini key, history, ledger, 18+, quota) run before the pre-filter so a self-harm message can get 429/503; MED validator: uncertainty/comparability carry free text, clarify/out_of_scope can assert skin state; MED medical misses (hurting, red eyes order, 8-year-old, newborn, temperature, hydroquinone) and false referrals (khatam kar, aankhon, reduce, minor, end my, 2 yrs, 5 kms, melasma, badhiya, I'm a + diet, Greek letter); LOW Latin small caps, Hangul filler; LOW joined window shorter than Gemini window; found during fix: today's Echo replays referred user turns to Gemini in later history. S3: keys clean (uid from token, scanId regex, server-built key); LOW no ContentLength cap on presigned PUT; LOW erase race with 300 s presigned URL. H19 verdict clean; latent: rec section would differ by caution once recommend() is wired; fallback path call vs no call.</t>
+          <t>Upload route builds the S3 key from the verified uid without isPlainUid (safe for phone-auth uids). app/api/skin-scan/route.ts logs the whole fetch error (:196) and the full zod error (:364), which can carry engine response values (no uid).</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>E05, F03</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>GEMINI_BOUNDARY §6 (updated)</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -10578,33 +10578,25 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>lib/context/prefilter.ts, lib/context/validator.ts, app/api/skin-check/chat/route.ts, lib/s3.ts</t>
+          <t>app/api/skin-scan/upload/route.ts, app/api/skin-scan/route.ts</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Fix + tests + control cases</t>
-        </is>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>All findings reproduced first, then fixed with tests and normal-question controls. Pre-filter (c0a0f87): self-harm EN/Hinglish additions, Devanagari copy (NFC, no Cf, no nukta), medical misses, false referrals narrowed, Latin small caps and Hangul fillers, Greek prefix carve-out; spaced phrases now need word boundaries. Route (7f53d70): message-only referral before key/history/ledger/18+/quota, forged history never signed, joined check = Gemini window, today's Echo no longer replays referred turns. Validator (5d607e3): uncertainty/comparability limited to cited facts' words and their fact kinds; clarify/out_of_scope cannot state skin condition; 'once' a number. S3 (a5c28b5): presign signs content-length (cap 25 MB, provisional) and content-type. Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47). Follow-up (94887f3): old hits lost by the narrowing restored and pinned; the early referral is recorded only for an admitted user. Deploy check: one real-S3 upload (S3Mock does not verify signatures).</t>
-        </is>
-      </c>
-      <c r="P96" s="2" t="inlineStr">
-        <is>
-          <t>c0a0f87, 7f53d70, 5d607e3, a5c28b5, 94887f3</t>
-        </is>
-      </c>
+          <t>Commit + tests</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Local only.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr"/>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>Follow-ups are rows H21, H22, E10, F11; F07 measures misfire and fallback rates.</t>
+          <t>Add isPlainUid to the upload key path; log name and code only.</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
@@ -10619,14 +10611,14 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>Owner instruction 2026-10-04 (follow-up task).</t>
+          <t>Security review 2026-10-04 (pre-existing logging).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>H21</t>
+          <t>H16</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -10641,27 +10633,27 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Account erase vs a live presigned upload URL</t>
+          <t>Consent ledger write slows the scan response</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>A presigned PUT issued up to 300 s before an erase can still land after the S3 step, leaving a photo after the account is deleted (second security review, LOW). Re-listing at the end does not close it.</t>
+          <t>The processing-consent ledger write (app/api/skin-scan/route.ts, recordProcessingConsent) is awaited before the response and can add about 2 s (LEDGER_TIMEOUT_MS) on a slow or failing ledger, before the 3 s persist timeout.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -10671,7 +10663,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -10686,29 +10678,25 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>app/api/account/erase/route.ts, lib/s3.ts</t>
+          <t>app/api/skin-scan/route.ts</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Design + commit + test</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>Same fix as H04; e2e uploads with a link issued before the delete. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
-        </is>
-      </c>
-      <c r="P97" s="2" t="inlineStr">
-        <is>
-          <t>673c66d</t>
-        </is>
-      </c>
-      <c r="Q97" s="2" t="inlineStr"/>
+          <t>Commit + test + timing</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
       <c r="R97" s="2" t="inlineStr"/>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>DEPLOY BLOCKER: a cron must call GET /api/account/erase/sweep with Authorization: Bearer $CRON_SECRET (e.g. every 15 min); set CRON_SECRET in production.</t>
+          <t>Run the ledger write in parallel with the persist, or lower its timeout; keep it best-effort.</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
@@ -10723,14 +10711,14 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>Second security review (H20).</t>
+          <t>Verifier observation 2026-10-04 (a52f36d).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>H22</t>
+          <t>H17</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -10745,74 +10733,66 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Self-harm in other Indian scripts is not caught</t>
+          <t>Firestore expiry (TTL) policy for chat turns</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>The chat pre-filter covers English, Hinglish and Devanagari. Tamil, Bengali, Telugu and other scripts pass unreferred; referring every such message would block those users (India-first).</t>
+          <t>users/*/chatTurns carry expireAt (90 days, D-15) but no TTL policy exists. Turns include red-flag and self-harm message text.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>CHECKED LOCAL</t>
+          <t>NOT CHECKED</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>GEMINI_BOUNDARY §6 / TD-18</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Product/Routine Rules Engineer</t>
+          <t>Backend/Data Engineer</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>lib/context/prefilter.ts</t>
+          <t>Firestore (infrastructure)</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Owner decision + reviewed word lists + tests</t>
-        </is>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>Fixed reply for any other script, before gates, never to Gemini, left out of later history. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
-        </is>
-      </c>
-      <c r="P98" s="2" t="inlineStr">
-        <is>
-          <t>4eee9dd</t>
-        </is>
-      </c>
+          <t>Policy configured on the India-region database + check</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
       <c r="Q98" s="2" t="inlineStr"/>
       <c r="R98" s="2" t="inlineStr"/>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Owner creates the TTL policy on chatTurns.expireAt when the Firestore reset (A04) lands. Deploy blocker for F08.</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
@@ -10827,57 +10807,61 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>Advisor + second security review (H20).</t>
+          <t>Context report §6; Owner instruction 2026-10-04 (wave-2 merge task).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>H18</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>End-to-end production evaluation</t>
+          <t>Document the context path's sent data</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+          <t>privacy-report.md §5 should list what the new path sends: version labels, lowConfidence, uncertainty and missing facts, not-enough-evidence longitudinal facts, rec.* facts. Pin tests already cover it (add-only).</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>NOT NEEDED</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>A12, A13, B01, H01, H03</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr"/>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -10885,91 +10869,95 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>QA/Test Engineer</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>docs/lanes/privacy-report.md</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Recorded E2E run against prod</t>
+          <t>Committed doc</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr"/>
       <c r="P99" s="2" t="inlineStr"/>
-      <c r="Q99" s="2" t="inlineStr">
-        <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R99" s="2" t="inlineStr">
-        <is>
-          <t>Nothing longitudinal is deployed yet.</t>
-        </is>
-      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>Write the section.</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V99" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>Context report §6.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>H19</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Release Validation</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Full red-team sweep</t>
+          <t>Hidden caution answer can be inferred from what is still sent</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+          <t>With extra caution on, withoutCautionAnswers hides only the matching value. 'Current products: Nothing right now' plus caution can only mean pregnant or breastfeeding; any male_skin_context answer plus caution means a prescription. Affects today's Echo and the context path.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>I01, F03, E05</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr"/>
+          <t>E05, H08</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>TD-08 decision 8 / TD-17</t>
+        </is>
+      </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
@@ -10977,40 +10965,48 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Red-Team Reviewer</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>lib/gemini.ts (withoutCautionAnswers), lib/context/builder.ts</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Red-team report</t>
-        </is>
-      </c>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" s="2" t="inlineStr"/>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Security review (wave 2) finding 5. The current behaviour (other current products still sent) is pinned by tests/privacy-gemini-inventory.test.ts per owner decision 8, so it was not changed (frozen decision). Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47). Pin: tests/privacy-gemini-inventory.test.ts (5 hidden-answer pairs, both paths, retry included). Second security review: no remaining difference with current wiring.</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>fc0285e</t>
+        </is>
+      </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R100" s="2" t="inlineStr">
-        <is>
-          <t>Needs I01 and the Gemini/safety layers.</t>
-        </is>
-      </c>
+          <t>Local only.</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS 2026-10-04: red team A-E launched on the local stack; B, C, D stopped at the account session limit (resets 20:30 IST) and must be rerun; then fixes and a fresh review.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>RED TEAM</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr"/>
@@ -11018,248 +11014,348 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>H20</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Population priors / mixed effects</t>
+          <t>Second security review (2026-10-04) findings</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Fresh review of e508028, 2bb45e1, 3fa1229, fc0285e and S3 keys. Reproduced: HIGH self-harm phrasings pass the pre-filter (ending my life, end it, hang myself, do not want to live, be dead, jeene ka mann nahi, goliyan); HIGH Devanagari patterns never match folded text (मरना, ZWJ, nukta); MED route checks (Gemini key, history, ledger, 18+, quota) run before the pre-filter so a self-harm message can get 429/503; MED validator: uncertainty/comparability carry free text, clarify/out_of_scope can assert skin state; MED medical misses (hurting, red eyes order, 8-year-old, newborn, temperature, hydroquinone) and false referrals (khatam kar, aankhon, reduce, minor, end my, 2 yrs, 5 kms, melasma, badhiya, I'm a + diet, Greek letter); LOW Latin small caps, Hangul filler; LOW joined window shorter than Gemini window; found during fix: today's Echo replays referred user turns to Gemini in later history. S3: keys clean (uid from token, scanId regex, server-built key); LOW no ContentLength cap on presigned PUT; LOW erase race with 300 s presigned URL. H19 verdict clean; latent: rec section would differ by caution once recommend() is wired; fallback path call vs no call.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>E05, F03</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>GEMINI_BOUNDARY §6 (updated)</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
-      <c r="P101" s="2" t="inlineStr"/>
-      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>lib/context/prefilter.ts, lib/context/validator.ts, app/api/skin-check/chat/route.ts, lib/s3.ts</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Fix + tests + control cases</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>All findings reproduced first, then fixed with tests and normal-question controls. Pre-filter (c0a0f87): self-harm EN/Hinglish additions, Devanagari copy (NFC, no Cf, no nukta), medical misses, false referrals narrowed, Latin small caps and Hangul fillers, Greek prefix carve-out; spaced phrases now need word boundaries. Route (7f53d70): message-only referral before key/history/ledger/18+/quota, forged history never signed, joined check = Gemini window, today's Echo no longer replays referred turns. Validator (5d607e3): uncertainty/comparability limited to cited facts' words and their fact kinds; clarify/out_of_scope cannot state skin condition; 'once' a number. S3 (a5c28b5): presign signs content-length (cap 25 MB, provisional) and content-type. Final run at 94887f3: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1350 passed / 47 skipped in 76 files; stack 10 files 47/47). Follow-up (94887f3): old hits lost by the narrowing restored and pinned; the early referral is recorded only for an admitted user. Deploy check: one real-S3 upload (S3Mock does not verify signatures).</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>c0a0f87, 7f53d70, 5d607e3, a5c28b5, 94887f3</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>Local only.</t>
+        </is>
+      </c>
       <c r="R101" s="2" t="inlineStr"/>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Follow-ups are rows H21, H22, E10, F11; F07 measures misfire and fallback rates.</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V101" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>Owner instruction 2026-10-04 (follow-up task).</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>H21</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>ML recommendation ranking</t>
+          <t>Account erase vs a live presigned upload URL</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>A presigned PUT issued up to 300 s before an erase can still land after the S3 step, leaving a photo after the account is deleted (second security review, LOW). Re-listing at the end does not close it.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>D-17</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>app/api/account/erase/route.ts, lib/s3.ts</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Design + commit + test</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Same fix as H04; e2e uploads with a link issued before the delete. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>673c66d</t>
+        </is>
+      </c>
       <c r="Q102" s="2" t="inlineStr"/>
       <c r="R102" s="2" t="inlineStr"/>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>DEPLOY BLOCKER: a cron must call GET /api/account/erase/sweep with Authorization: Bearer $CRON_SECRET (e.g. every 15 min); set CRON_SECRET in production.</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V102" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>Second security review (H20). Red team I02 (D): proven live, including a scan still running when the account was erased.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>H22</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Indian cross-user benchmark</t>
+          <t>Self-harm in other Indian scripts is not caught</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>The chat pre-filter covers English, Hinglish and Devanagari. Tamil, Bengali, Telugu and other scripts pass unreferred; referring every such message would block those users (India-first).</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>GEMINI_BOUNDARY §6 / TD-18</t>
+        </is>
+      </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Product/Routine Rules Engineer</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>lib/context/prefilter.ts</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision + reviewed word lists + tests</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Fixed reply for any other script, before gates, never to Gemini, left out of later history. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>4eee9dd</t>
+        </is>
+      </c>
       <c r="Q103" s="2" t="inlineStr"/>
       <c r="R103" s="2" t="inlineStr"/>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="V103" s="2" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>Advisor + second security review (H20).</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>H23</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>Revoked ID token still reads and writes Firestore for up to an hour</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Red team A F1: Firestore rules do not check revocation. Erasure is covered (erasedAccounts, H04); any other revocation (forced sign-out, disabled number) is not.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -11269,73 +11365,97 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>H04</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>D-26</t>
+        </is>
+      </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>firestore.rules</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision</t>
+        </is>
+      </c>
       <c r="O104" s="2" t="inlineStr"/>
       <c r="P104" s="2" t="inlineStr"/>
       <c r="Q104" s="2" t="inlineStr"/>
-      <c r="R104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision</t>
+        </is>
+      </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>Do not start without evidence and explicit approval.</t>
+          <t>Options: (a) a revokedAfter/{uid} marker compared with request.auth.token.auth_time in rules; (b) accept and document the one-hour window. Recommendation: (b) now (no forced sign-out flow exists); (a) when one is built.</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>RELEASE</t>
+          <t>PRIVACY/SAFETY</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+          <t>Red team I02.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>H24</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Later / Research-dependent</t>
+          <t>Privacy / Safety</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>True digital twin</t>
+          <t>A recorded under-18 account can still write skinChecks from a tampered client</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Not in core release.</t>
+          <t>Red team C F5: the server refuses chat, scan and upload (UNDER_18), but rules have no age check, so a modified client can store a minor's quiz answers and a stored-image claim.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>OWNER ACTION</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -11345,39 +11465,911 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>D-19</t>
+        </is>
+      </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>firestore.rules, app/api/account/attestation</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision + commit + rules test</t>
+        </is>
+      </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr"/>
       <c r="Q105" s="2" t="inlineStr"/>
-      <c r="R105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision</t>
+        </is>
+      </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
+          <t>Options: (a) the attestation route writes an under18Accounts/{uid} marker the rules check (as erasedAccounts); (b) accept. Recommendation: (a).</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>Red team I02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>H25</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>The 18+ attestation version is not checked</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Red team C F7c: ageStatus accepts an age_18_plus grant at any version; AI-share requires the current version.</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>OWNER ACTION</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>D-19</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>app/api/account/_ledger.ts</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>Options: (a) require the current AGE_ATTESTATION_VERSION (users are asked again when the copy changes); (b) any version counts. Recommendation: (a).</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>Red team I02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>H26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Delete copy promises more than the system can do</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Red team D F1: 'permanently deletes your photos, your scans, your answers' — but text already sent to Gemini stays with Google under its terms, and data from a request still running is removed by the sweep up to about 70 minutes plus the cron interval later.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>OWNER ACTION</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>H04, H06</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>D-17</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>app/(marketing)/account/DeleteAccount.tsx</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Owner copy + commit</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>Owner copy</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>Recommended wording: 'Deleted now. Anything still arriving is removed within about 2 hours. Messages you already sent to the AI assistant are held by Google under its terms.' Decide with H06 (final consent copy) and G1 (Gemini tier/region).</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>Red team I02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Privacy / Safety</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>'Photo kept' line trusts the client record</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Red team A F6: a skinCheck can claim image.stored with consent for a photo never uploaded; the dashboard then says 'Photo ... kept'.</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>OWNER ACTION</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>G01, H01</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Security/Privacy Reviewer</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>components/dashboard/state.ts</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision + commit + test</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>Owner decision</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>Options: (a) derive 'kept' from the server (the presign ledger entry or an S3 HEAD); (b) keep the client claim. Recommendation: (a), from the ledger entry.</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>PRIVACY/SAFETY</t>
+        </is>
+      </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>Red team I02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Release Validation</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end production evaluation</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Verify trusted flow, persistence, Echo isolation in production.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>A12, A13, B01, H01, H03</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>QA/Test Engineer</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Recorded E2E run against prod</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>Nothing longitudinal is deployed yet.</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>Write E2E script while A13 is pending.</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Release Validation</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Full red-team sweep</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial review across trust, Gemini, privacy, safety.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>I01, F03, E05</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Red-Team Reviewer</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Red-team report</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>IN PROGRESS 2026-10-04: red team A-E launched on the local stack; B, C, D stopped at the account session limit (resets 20:30 IST) and must be rerun; then fixes and a fresh review.</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>RED TEAM</t>
+        </is>
+      </c>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>J01</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Population priors / mixed effects</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr"/>
+      <c r="R111" s="2" t="inlineStr"/>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
           <t>Do not start without evidence and explicit approval.</t>
         </is>
       </c>
-      <c r="T105" s="2" t="inlineStr">
+      <c r="T111" s="2" t="inlineStr">
         <is>
           <t>RELEASE</t>
         </is>
       </c>
-      <c r="U105" s="2" t="inlineStr">
+      <c r="U111" s="2" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="V105" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>ML recommendation ranking</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="R112" s="2" t="inlineStr"/>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>J03</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Indian cross-user benchmark</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr"/>
+      <c r="R113" s="2" t="inlineStr"/>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting needs explicit approval (CLAUDE.md, D-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Later / Research-dependent</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>True digital twin</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Not in core release.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr"/>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>Do not start without evidence and explicit approval.</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr">
+        <is>
+          <t>RELEASE</t>
+        </is>
+      </c>
+      <c r="U115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="V115" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>fe85d09, 2026-10-04: typecheck 0, lint clean, npm run test:local exit 0 (unit 1437 passed / 52 skipped; stack 12 files 52/52); npm run test:browser 29/29 at e8916bb. next build not yet rerun after the merge.</t>
+          <t>57b63c8, 2026-10-05: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1645 passed / 56 skipped; stack 13 files 56/56), npm run test:browser 29/29.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>42% = DONE 45 / (total 114 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
+          <t>44% = DONE 47 / (total 114 - LATER 8). Execution tracking only; NOT scientific accuracy or product readiness. DONE includes branch-only work not deployed.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 45, IN PROGRESS 2, NOT STARTED 21, BLOCKED 13, OWNER ACTION 25, LATER 8 (total 114)</t>
+          <t>DONE 47, IN PROGRESS 1, NOT STARTED 21, BLOCKED 12, OWNER ACTION 25, LATER 8 (total 114)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHECKED PROD 1, CHECKED LOCAL 43, NOT NEEDED 11, NOT CHECKED 59</t>
+          <t>CHECKED PROD 1, CHECKED LOCAL 45, NOT NEEDED 11, NOT CHECKED 57</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3.</t>
+          <t>Quiz interlock evaluateSafety (provisional list, rules report §4), with internal extraCautionRaisedBy (eee588c). One extra-caution list: lib/gemini.ts copy removed, Echo uses the same matcher (7fe39da). In the chat path any safety error gives the fixed fallback, never 'no red flag' (3f61b3e). Chat red-flag pre-filter with EN and Hinglish tests built in the context lane (bbb9cd9, f6f2c6a, 6daa5c7). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3. Red team I02 fixes: 2ccd8fa, f91c471, 36476f7, 6f4fb8c, b037c2c, 36ab480, d5f9017, d379afa, 293c3dd, 3fc0dda, 2301e19, 57b63c8.</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3.</t>
+          <t>validateAnswer: one check per ForbiddenClaim plus malformed_output; reject, one retry (none after a red flag or user premise), fixed fallback. Tests: context-validator (31), context-answer (11), context-attacks (91). Final run at 3fa1229: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1199 passed / 47 skipped in 74 files; stack 10 files 47/47) Second security review (H20) fixes: c0a0f87, 7f53d70, 5d607e3. Red team I02 fixes: 2ccd8fa, f91c471, 36476f7, 6f4fb8c, b037c2c, 36ab480, d5f9017, d379afa, 293c3dd, 3fc0dda, 2301e19, 57b63c8.</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Context report §5.3; Owner instruction 2026-10-04 (wave-2 merge task). H20 (2026-10-04): the validator now rejects free text in uncertainty/comparability and skin-state words in clarify/out_of_scope, so the fallback rate may rise; and a self-harm message split with filler turns ('i want to' / 'ok' / 'die') still passes the joined check. Measure both. Red team I02: still not caught by the pre-filter: reversed text ('edicius'), base64, and a self-harm split padded with filler turns. Today's Echo reply screen (f91c471) is provisional; measure its fallback rate too.</t>
+          <t>Context report §5.3; Owner instruction 2026-10-04 (wave-2 merge task). H20 (2026-10-04): the validator now rejects free text in uncertainty/comparability and skin-state words in clarify/out_of_scope, so the fallback rate may rise; and a self-harm message split with filler turns ('i want to' / 'ok' / 'die') still passes the joined check. Measure both. Red team I02: still not caught by the pre-filter: reversed text ('edicius'), base64, and a self-harm split padded with filler turns. Today's Echo reply screen (f91c471) is provisional; measure its fallback rate too. Today's Echo now uses the recall-first comparison list (57b63c8): ordinary questions with before/better/change get the fixed answer; measure with the reply-screen fallback rate.</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Red team I02.</t>
+          <t>Red team I02. Final review: a word-list screen on free text keeps losing to paraphrase (3 rounds). Recommendation stands: the context path in production.</t>
         </is>
       </c>
     </row>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>lane/dashboard merged; O-D1/O-D3/O-D6, K-1, G-1, R-5 fixed. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+          <t>lane/dashboard merged; O-D1/O-D3/O-D6, K-1, G-1, R-5 fixed. Final run at 57b63c8: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1645 passed / 56 skipped in 81 files; stack 13 files 56/56), npm run test:browser 29/29.</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini.</t>
+          <t>Built (lane privacy, merged 1dd4acf; chat gate bdc462f): pin test of every field sent to Gemini (privacy-report section 5); removed name, age, gender, female_skin_context, phone fields, Dryness band, Pores, numeric scores, ids, consent fields, unknown keys; extraCaution flag as one fixed sentence; AI-share consent route and Echo prompt (DRAFT copy, local only), chat refuses 403 AI_CONSENT_REQUIRED. After merge: Echo history token v2 so pre-minimisation threads stop verifying (85c7b47, R-F); GEMINI_BOUNDARY.md names aligned (7e8071b, R-G). Tests: privacy-gemini-inventory, privacy-consent-route, privacy-chat-gate, echo-history-token. Final run 2026-10-04 at bff6e25: npm run test:local exit 0 (unit 597 passed / 41 skipped in 53 files; stack 41/41: rules 24 + routine 8 + privacy 5, e2e routine, privacy, local-stack, capture); typecheck 0; lint clean; next build exit 0. Security review (2026-10-04): no removed field reaches Gemini. Red team I02 fixes: 2ccd8fa, f91c471, 36476f7, 6f4fb8c, b037c2c, 36ab480, d5f9017, d379afa, 293c3dd, 3fc0dda, 2301e19, 57b63c8.</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>erasedAccounts marker checked by rules + second sweep after 70 min; e2e proves late upload, late server write and old-token client write leave nothing. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+          <t>erasedAccounts marker checked by rules + second sweep after 70 min; e2e proves late upload, late server write and old-token client write leave nothing. Final run at 57b63c8: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1645 passed / 56 skipped in 81 files; stack 13 files 56/56), npm run test:browser 29/29.</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -9496,7 +9496,7 @@
       <c r="R85" s="2" t="inlineStr"/>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>DEPLOY BLOCKER: a cron must call GET /api/account/erase/sweep with Authorization: Bearer $CRON_SECRET (e.g. every 15 min); set CRON_SECRET in production.</t>
+          <t>DEPLOY BLOCKER: a cron must call GET /api/account/erase/sweep with Authorization: Bearer $CRON_SECRET (e.g. every 15 min); set CRON_SECRET in production. Also: CRON_SECRET set in production.</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ConsentSection on /dashboard and /account; withdraw browser test. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+          <t>ConsentSection on /dashboard and /account; withdraw browser test. Final run at 57b63c8: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1645 passed / 56 skipped in 81 files; stack 13 files 56/56), npm run test:browser 29/29.</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Same fix as H04; e2e uploads with a link issued before the delete. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+          <t>Same fix as H04; e2e uploads with a link issued before the delete. Final run at 57b63c8: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1645 passed / 56 skipped in 81 files; stack 13 files 56/56), npm run test:browser 29/29.</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Fixed reply for any other script, before gates, never to Gemini, left out of later history. test:local at fe85d09: unit 1437 passed / 52 skipped; stack 12 files 52/52. test:browser at e8916bb: 29/29.</t>
+          <t>Fixed reply for any other script, before gates, never to Gemini, left out of later history. Final run at 57b63c8: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1645 passed / 56 skipped in 81 files; stack 13 files 56/56), npm run test:browser 29/29.</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -11890,21 +11890,25 @@
           <t>Recorded E2E run against prod</t>
         </is>
       </c>
-      <c r="O109" s="2" t="inlineStr"/>
-      <c r="P109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Local end-to-end coverage instead of a production run (the production check happens after deploy): test:local e2e (local-stack, privacy erase + late writes, fake Gemini, longitudinal series, capture) and test:browser 29 flows on a phone screen. Final run at 57b63c8: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1645 passed / 56 skipped in 81 files; stack 13 files 56/56), npm run test:browser 29/29.</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>fe85d09, e8916bb, 673c66d</t>
+        </is>
+      </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
-        </is>
-      </c>
-      <c r="R109" s="2" t="inlineStr">
-        <is>
-          <t>Nothing longitudinal is deployed yet.</t>
-        </is>
-      </c>
+          <t>CHECKED LOCAL only; production run after deploy.</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr"/>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>Write E2E script while A13 is pending.</t>
+          <t>After deploy (owner): run the same flows against production, incl. one real S3 upload and the erase sweep via the cron.</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
@@ -11947,12 +11951,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>CHECKED LOCAL</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -11982,17 +11986,25 @@
           <t>Red-team report</t>
         </is>
       </c>
-      <c r="O110" s="2" t="inlineStr"/>
-      <c r="P110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Five reviewers (A trust boundary, B Gemini x2 passes, C gates, D privacy, E change claims) attacked the running local stack; every finding reproduced by a test, then fixed or made an owner row. Final fresh reviewer over all fixes + two rechecks: its HIGHs (Hindi replies, self-harm variants, comparison over-blocking, change claims) fixed; residual: a word-list screen on today's Echo free text can still miss a paraphrased change claim (F12). Final run at 57b63c8: typecheck 0, lint clean, next build exit 0, npm run test:local exit 0 (unit 1645 passed / 56 skipped in 81 files; stack 13 files 56/56), npm run test:browser 29/29.</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>2ccd8fa, f91c471, 36476f7, 6f4fb8c, b037c2c, 36ab480, d5f9017, d379afa, 293c3dd, 3fc0dda, 2301e19, 57b63c8</t>
+        </is>
+      </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>CHECKED LOCAL only; production red team after deploy.</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr"/>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS 2026-10-04: red team A-E launched on the local stack; B, C, D stopped at the account session limit (resets 20:30 IST) and must be rerun; then fixes and a fresh review.</t>
+          <t>Owner rows F12, F13, H23-H27, D07, D08; F07 measures pre-filter and reply-screen misfires; production red team after deploy.</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
@@ -13332,7 +13344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14240,80 +14252,162 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>release-prep-session-2026-10-04</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Program Lead</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>TD-18; merge lane/dashboard; Part 2 fixes 1-9; red team A-E; fixes; final review</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>G01, H14, H22, D06, H04, H21, I01, I02</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>main (skin-check)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>longitudinal-platform</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>see commits</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>typecheck, lint, next build, test:local, test:browser at 57b63c8</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Red team: 2 HIGH (self-harm and Devanagari recall; today's Echo unchecked replies) + mediums/lows; all reproduced, fixed or owner rows. Final review HIGHs fixed; residual paraphrase limit on today's Echo (F12).</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>TD-18, TD-19</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>a6f2275, c3cf0d6, 4eee9dd, a027ce5, ff29605, 457c1e8, 7bcbe95, 215ea2c, 3890924, 2a9cbc0, 18f2eef, 673c66d, e8916bb, fe85d09, 2ccd8fa, f91c471, 36476f7, 6f4fb8c, b037c2c, 36ab480, d5f9017, d379afa, 293c3dd, 3fc0dda, 2301e19, 57b63c8, 754dfb5</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Final reviewer + 2 rechecks</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>earlier sessions (gates 01-04, Phase 0)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>A01-A12, B02-B04</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>longitudinal-platform</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>see commits</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>see gate reports</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>see DECISION_LOG</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>61c149a..91d20bc</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>unknown - not reconstructable from repo</t>
         </is>
@@ -14500,7 +14594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15994,52 +16088,52 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>TD-19</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Native L*/a* are provisional research candidates only</t>
+          <t>Erasure: a short-lived uid marker plus a second sweep (H04, H21)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 screening</t>
+          <t>After an erase, an old ID token (rules do not check revocation), a request still running and an upload link still valid can each leave data</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Keep b*, ITA, lbpEntropy</t>
+          <t>A second sweep only; a marker only; checking the marker in every server writer</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Primary endpoints for the human study only; not validated measurements</t>
+          <t>erasedAccounts/{uid} (uid, sweepAfter, markedAt; nothing else) written first; firestore.rules refuse client writes while it exists; a cron-called sweep (GET /api/account/erase/sweep, Bearer CRON_SECRET) after ID-token lifetime + longest request + upload-link lifetime (70 min) re-erases S3, the Firestore tree and Auth, then removes the marker. No TTL on the marker (it must outlive the sweep). The marker retains a deleted account's uid until the sweep: owner acknowledgment</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Only survivors of screening</t>
+          <t>Owner brief 2026-10-04 (fix 8); advisor review</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
+          <t>673c66d</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>C03-C07</t>
+          <t>H04, H21, H01, H26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Owner may reverse before Phase 1 pre-registration</t>
+          <t>A sweep that cannot run (no cron) leaves the marker and late data</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -16049,76 +16143,76 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>ACCEPTED for study design</t>
+          <t>DECIDED for build; production needs the cron (deploy blocker). Tracker-local until A14.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>D-13 / D-24</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal comparisons require comparability + noise/evidence</t>
+          <t>Native L*/a* are provisional research candidates only</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Naive % change misleads</t>
+          <t>Phase 0 screening</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Research-doc point ladder</t>
+          <t>Keep b*, ITA, lbpEntropy</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
+          <t>Primary endpoints for the human study only; not validated measurements</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Measurement noise unknown</t>
+          <t>Only survivors of screening</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-13; D-24 uncommitted</t>
+          <t>MEASUREMENT_METRIC_DECISION.md, 59d9923, 91d20bc</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>C02, D02, G01</t>
+          <t>C03-C07</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Owner may reverse before Phase 1 pre-registration</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Measurement Scientist</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (D-24 uncommitted)</t>
+          <t>ACCEPTED for study design</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-13 / D-24</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -16128,59 +16222,59 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Recommender deterministic and versioned</t>
+          <t>Longitudinal comparisons require comparability + noise/evidence</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4 SKUs, ~6 rules</t>
+          <t>Naive % change misleads</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DMN/rules engine; ML ranking</t>
+          <t>Research-doc point ladder</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Plain TS pure function + version constants</t>
+          <t>Pairwise, keyed comparability; change claims gated on validation protocol</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Auditable</t>
+          <t>Measurement noise unknown</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-08</t>
+          <t>DECISION_LOG D-13; D-24 uncommitted</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>E02, J02</t>
+          <t>C02, D02, G01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>&gt;20 SKUs or non-engineer rule authors</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Systems Architect</t>
+          <t>Measurement Scientist</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>PROPOSED (D-24 uncommitted)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -16190,42 +16284,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Gemini is explanation layer, not authority</t>
+          <t>Recommender deterministic and versioned</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Gemini hallucination/claims risk</t>
+          <t>4 SKUs, ~6 rules</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Gemini owns context</t>
+          <t>DMN/rules engine; ML ranking</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+          <t>Plain TS pure function + version constants</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>Auditable</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-14; GATE_02</t>
+          <t>DECISION_LOG D-08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>B04, F01-F04</t>
+          <t>E02, J02</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>&gt;20 SKUs or non-engineer rule authors</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -16235,14 +16329,14 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED (paid tier is release gate)</t>
+          <t>PROPOSED</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -16252,104 +16346,104 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>No attribution/efficacy/forecasting</t>
+          <t>Gemini is explanation layer, not authority</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Gemini hallucination/claims risk</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Gemini owns context</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Server-built ContextPackage, pre-filters, schema, validator</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Evidence tiers 3-4</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Prohibited in UI, Gemini, analytics</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>CLAUDE.md</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>DECISION_LOG D-12</t>
+          <t>DECISION_LOG D-14; GATE_02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>G02, J04, R08</t>
+          <t>B04, F01-F04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Explicit owner approval</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Systems Architect</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>PROPOSED (paid tier is release gate)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Client input never authoritative for measured state</t>
+          <t>No attribution/efficacy/forecasting</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Gate 02</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Rules tightening; server chat storage</t>
+          <t>Evidence tiers 3-4</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Path-structural trust; authenticated Echo</t>
+          <t>Prohibited in UI, Gemini, analytics</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Forgeable browser state</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>155cb69, 955c1cc</t>
+          <t>DECISION_LOG D-12</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>A09, B02-B04, C02</t>
+          <t>G02, J04, R08</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Open: client-asserted captureMethod/persistAttempt</t>
+          <t>Explicit owner approval</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -16359,67 +16453,129 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED (branch); owner decision open</t>
+          <t>LOCKED</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>D-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Client input never authoritative for measured state</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Gate 02</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Rules tightening; server chat storage</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Path-structural trust; authenticated Echo</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Forgeable browser state</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>155cb69, 955c1cc</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>A09, B02-B04, C02</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Open: client-asserted captureMethod/persistAttempt</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (branch); owner decision open</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>D-21</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Gate 01 stores raw analysis in scanAnalyses</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Raw preservation</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>skinStates collection</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>users/{uid}/scanAnalyses/{scanId}_{sha16}</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Immutable raw substrate</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>6e9081d</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Systems Architect</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>IMPLEMENTED (not deployed); ID duplicated in HEAD</t>
         </is>

--- a/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
+++ b/docs/PROJECT_SKIN_EXECUTION_TRACKER.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DONE 47, IN PROGRESS 1, NOT STARTED 21, BLOCKED 12, OWNER ACTION 25, LATER 8 (total 114)</t>
+          <t>DONE 47, IN PROGRESS 2, NOT STARTED 21, BLOCKED 12, OWNER ACTION 24, LATER 8 (total 114)</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Red team I02.</t>
+          <t>Red team I02. Owner 2026-10-05 (TD-20): apply the recommendation only if it makes the app stricter or more honest; otherwise leave open.</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>Red team I02. Server-only records: needs a server bug to reach.</t>
+          <t>Red team I02. Server-only records: needs a server bug to reach. Owner 2026-10-05 (TD-20): apply the recommendation only if it makes the app stricter or more honest; otherwise leave open.</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,11 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Owner 2026-10-05 (TD-20): recommendations stay off in production builds until clinical sign-off.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -6971,7 +6975,7 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04 (privacy T12): also review EXTRA_CAUTION_TRIGGERS and the caution sentence; decide whether the residual pregnancy inference is acceptable or drop the flag or trigger.</t>
+          <t>2026-10-04 (privacy T12): also review EXTRA_CAUTION_TRIGGERS and the caution sentence; decide whether the residual pregnancy inference is acceptable or drop the flag or trigger. Owner 2026-10-05 (TD-20): switch split; the red-flag and extra-caution check runs in production builds, marked provisional (it only adds caution).</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8627,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>OWNER ACTION</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -8676,7 +8680,7 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>Options: (a) ship today's Echo with the reply screen; (b) make the context path the production path once F08 blockers clear; (c) ship no chat until (b). Recommendation: (b), with (a) as the interim if chat must ship first.</t>
+          <t>Owner decided 2026-10-05 (TD-20): option (b), the context path is the chat that ships; today's Echo stays in the code behind the switch. Build: make the context path the default switch value.</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
@@ -8791,7 +8795,7 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Red team I02.</t>
+          <t>Red team I02. Owner 2026-10-05 (TD-20): apply the recommendation only if it makes the app stricter or more honest; otherwise leave open.</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11427,7 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>Red team I02.</t>
+          <t>Red team I02. Owner 2026-10-05 (TD-20): apply the recommendation only if it makes the app stricter or more honest; otherwise leave open.</t>
         </is>
       </c>
     </row>
@@ -11523,7 +11527,7 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>Red team I02.</t>
+          <t>Red team I02. Owner 2026-10-05 (TD-20): apply the recommendation only if it makes the app stricter or more honest; otherwise leave open.</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11627,7 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>Red team I02.</t>
+          <t>Red team I02. Owner 2026-10-05 (TD-20): apply the recommendation only if it makes the app stricter or more honest; otherwise leave open.</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11827,7 @@
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>Red team I02.</t>
+          <t>Red team I02. Owner 2026-10-05 (TD-20): apply the recommendation only if it makes the app stricter or more honest; otherwise leave open.</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16143,59 +16147,59 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>DECIDED for build; production needs the cron (deploy blocker). Tracker-local until A14.</t>
+          <t>DECIDED for build; production needs the cron (deploy blocker). Tracker-local until A14. Owner acknowledged 2026-10-05 (TD-20).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>TD-20</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Native L*/a* are provisional research candidates only</t>
+          <t>Owner decisions after the red team (F12, the switch split, TD-19, owner rows)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Phase 0 screening</t>
+          <t>I02 owner rows F12, F13, H23-H27